--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,24 +683,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
+          <t>Tanisha Bhise death: As in-laws take care of twin girls, husband in ‘a daze’, can’t understand how wife passed away</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
+          <t>https://indianexpress.com/article/cities/pune/tanisha-bhise-pune-hospital-death-in-laws-twin-girls-9925235/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tanisha Bhise death: As in-laws take care of twin girls, husband in ‘a daze’, can’t understand how wife passed away</t>
+          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/tanisha-bhise-pune-hospital-death-in-laws-twin-girls-9925235/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
         </is>
       </c>
     </row>
@@ -731,132 +731,132 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Abitkar attributes delay in loan waiver to Ladki Bahin scheme; no mention in BJP’s poll manifesto, says S</t>
+          <t>Maharashtra to run organ donation drive across state from August 3 to 15: Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Soon, mandatory ‘no denial policy’ for hospitals in state: DCM Pawar</t>
+          <t>Abitkar attributes delay in loan waiver to Ladki Bahin scheme; no mention in BJP’s poll manifesto, says S</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Woman’s death after delivery in Pune: Maharashtra sets up probe committee</t>
+          <t>Soon, mandatory ‘no denial policy’ for hospitals in state: DCM Pawar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/pune-hospital-pregnant-woman-dies-probe-9924556/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
+          <t>Woman’s death after delivery in Pune: Maharashtra sets up probe committee</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
+          <t>https://indianexpress.com/article/cities/pune/pune-hospital-pregnant-woman-dies-probe-9924556/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Maha to relax norms for nursing homes, hospitals with up to 10 beds</t>
+          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
+          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Maharashtra to run organ donation drive across state from August 3 to 15: Health Minister Prakash Abitkar</t>
+          <t>Maha to relax norms for nursing homes, hospitals with up to 10 beds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mumbai's new 300-bed cancer center assures personalized, ai-powered treatment: Here's how</t>
+          <t>Major Health Boost for Nagpur And Vidarbha: Govt plans facilities, incentives for doctors in remote areas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Major Health Boost for Nagpur And Vidarbha: Govt plans facilities, incentives for doctors in remote areas</t>
+          <t>GBS Outbreak Scare: Maharashtra Minister Announces New Law For Clean Water Supply, Fines For Polluters</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
+          <t>https://www.news18.com/india/gbs-outbreak-scare-maharashtra-minister-announces-new-law-for-clean-water-supply-fines-for-polluters-9218986.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GBS Outbreak Scare: Maharashtra Minister Announces New Law For Clean Water Supply, Fines For Polluters</t>
+          <t>Rising obesity in children matter of grave concern, parents must take it seriously: Abitkar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/gbs-outbreak-scare-maharashtra-minister-announces-new-law-for-clean-water-supply-fines-for-polluters-9218986.html</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rising obesity in children matter of grave concern, parents must take it seriously: Abitkar</t>
+          <t>Cashless treatment up to ₹1 lakh for accident victims in Maharashtra</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
+          <t>https://www.thehindu.com/news/national/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-1-lakh/article69463926.ece</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cashless treatment up to ₹1 lakh for accident victims in Maharashtra</t>
+          <t>Mumbai's new 300-bed cancer center assures personalized, ai-powered treatment: Here's how</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-1-lakh/article69463926.ece</t>
+          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
         </is>
       </c>
     </row>
@@ -1019,72 +1019,72 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Contractual NHM staff may get permanent jobs; honorarium hike planned</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister/2710544/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Contractual NHM staff may get permanent jobs; honorarium hike planned</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
+          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister/2710544/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
+          <t>Centre to revise CGHS rates soon, union minister assures</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2105326</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Centre to revise CGHS rates soon, union minister assures</t>
+          <t>Maharashtra cancels Licenses of 258 Private Hospitals for Violations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
+          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Maharashtra cancels Licenses of 258 Private Hospitals for Violations</t>
+          <t>HMPV Outbreak LIVE Updates: No cause for concern, says Maharashtra Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
+          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Maharashtra To Provide Free Cancer Vaccines For Girls Aged 0-14 Amid Rising Cases</t>
+          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/india/maharashtra-to-provide-free-cancer-vaccines-for-girls-aged-0-14-amid-rising-cases-article-118653086</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
         </is>
       </c>
     </row>
@@ -1103,36 +1103,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alert After Covid Cases Rise | Maharashtra Health Minister: “No Need To Panic”</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/alert-after-covid-cases-rise-maharashtra-health-minister-no-need-to-panic-477235-2025-05-21</t>
+          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Accident victims in Maharashtra to receive cashless treatment up to Rs 1 lakh</t>
+          <t>Alert After Covid Cases Rise | Maharashtra Health Minister: “No Need To Panic”</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh/articleshow/120402888.cms</t>
+          <t>https://www.businesstoday.in/bt-tv/video/alert-after-covid-cases-rise-maharashtra-health-minister-no-need-to-panic-477235-2025-05-21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
+          <t>Accident victims in Maharashtra to receive cashless treatment up to Rs 1 lakh</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
+          <t>https://m.economictimes.com/news/india/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh/articleshow/120402888.cms</t>
         </is>
       </c>
     </row>
@@ -1247,132 +1247,132 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maharashtra Govt To Provide Free Cancer Vaccines For Girls Aged 0-14 Amid Rising Cases, Says Health Minister</t>
+          <t>Maharashtra Clears ₹20,000 Crore For Shaktipeeth Expressway Amid Fierce Farmer Opposition</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-to-provide-free-cancer-vaccines-for-girls-aged-0-14-amid-rising-cases-says-health-minister-prakash-abitkar</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-clears-20000-crore-for-shaktipeeth-expressway-amid-fierce-farmer-opposition</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Maharashtra Clears ₹20,000 Crore For Shaktipeeth Expressway Amid Fierce Farmer Opposition</t>
+          <t>Maharashtra Govt Launches Cashless Treatment Scheme For Accident Victims, Covers ₹1 Lakh Per Case</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-clears-20000-crore-for-shaktipeeth-expressway-amid-fierce-farmer-opposition</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-launches-cashless-treatment-scheme-for-accident-victims-covers-1-lakh-per-case</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Launches Cashless Treatment Scheme For Accident Victims, Covers ₹1 Lakh Per Case</t>
+          <t>Over 12,000 Child Deaths Reported In Maharashtra Between April 2024 And February 2025: Minister Prakash Abitka</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-launches-cashless-treatment-scheme-for-accident-victims-covers-1-lakh-per-case</t>
+          <t>https://www.freepressjournal.in/mumbai/over-12000-child-deaths-reported-in-maharashtra-between-april-2024-and-february-2025-minister-prakash-abitka</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Over 12,000 Child Deaths Reported In Maharashtra Between April 2024 And February 2025: Minister Prakash Abitka</t>
+          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/over-12000-child-deaths-reported-in-maharashtra-between-april-2024-and-february-2025-minister-prakash-abitka</t>
+          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
+          <t>महाराष्ट्र में गुइलेन-बैरे सिंड्रोम के 197 मरीज : स्वास्थ्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
+          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>पुणे में कम हो रहे हैं जीबीएस के मरीज : प्रकाश आबिटकर</t>
+          <t>महाराष्ट्र में फिर कोरोना का डर? स्वास्थ्य मंत्री ने दिए अहम निर्देश, बोले- 'घबराएं</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/states/gbs-cases-are-decreasing-in-pune-prakash-abitkar-533378-1</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: मंत्रिमंडल की बैठक में जीबीएस बीमारी पर हुई चर्चा, स्वास्थ्य मंत्री ने कही ये बात</t>
+          <t>Cashless Treatment in Accident: दुर्घटनाग्रस्त के लिए 1 लाख तक फ्री इलाज</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-gbs-disease-was-discussed-in-the-cabinet-meeting-health-minister-said-this-2025-01-28-1108795</t>
+          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में फिर कोरोना का डर? स्वास्थ्य मंत्री ने दिए अहम निर्देश, बोले- 'घबराएं</t>
+          <t>उद्धव ने जिसके लिए लिया था ‘पंजे’ से पंगा, अब उसी ने छोड़ा साथ, महायुति की ताकत बढ़ी</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cashless Treatment in Accident: दुर्घटनाग्रस्त के लिए 1 लाख तक फ्री इलाज</t>
+          <t>Shaktipeeth Expressway: शक्तिपीठ एक्सप्रेसवे के खिलाफ सड़क पर उतरे किसान, फडणवीस ने विधानसभा में गिनाए महामार्ग के फायदे-नुकसान</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>उद्धव ने जिसके लिए लिया था ‘पंजे’ से पंगा, अब उसी ने छोड़ा साथ, महायुति की ताकत बढ़ी</t>
+          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की बेटियों के लिए किया ये ऐलान</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
+          <t>https://hindi.news24online.com/state/mumbai/devendra-fadnavis-government-announces-free-cancer-vaccine-for-girls-under-14-years-of-age-maharashtra-news/1088804/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में गुइलेन-बैरे सिंड्रोम के 197 मरीज : स्वास्थ्य मंत्री प्रकाश आबिटकर</t>
+          <t>Organ Donation: अंगदान को नया आयाम, महाराष्ट्र के अन्य चार शहरों में खुलेंगे ZTCC सेंटर</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
+          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
         </is>
       </c>
     </row>
@@ -1391,24 +1391,24 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Organ Donation: अंगदान को नया आयाम, महाराष्ट्र के अन्य चार शहरों में खुलेंगे ZTCC सेंटर</t>
+          <t>Madhuri Elephant: हथिनी 'माधुरी' को वापस लाने के लिए मुख्यमंत्री देवेंद्र फडणवीस का बड़ा फैसला, राज्य सरकार भी सुप्रीम कोर्ट में दाखिल करेगी पुनर्विचार याचिका</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
+          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Madhuri Elephant: हथिनी 'माधुरी' को वापस लाने के लिए मुख्यमंत्री देवेंद्र फडणवीस का बड़ा फैसला, राज्य सरकार भी सुप्रीम कोर्ट में दाखिल करेगी पुनर्विचार याचिका</t>
+          <t>महाराष्ट्र सरकार का बड़ा फैसला, 0-14 साल की लड़कियों को मिलेगी मुफ्त कैंसर वैक्सीन</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
+          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
         </is>
       </c>
     </row>
@@ -1463,840 +1463,840 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: 'दादा नेहमी आमच्या परीक्षा घेतात अन् आमची अडचण होते', आरोग्यमंत्री प्रकाश</t>
+          <t>Maha Health Minister urges Mandaviya to revise income eligibility limit for ESIS beneficiaries</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
+          <t>https://www.thehawk.in/news/health/maha-health-minister-urges-mandaviya-to-revise-income-eligibility-limit-for-esis-beneficiaries</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या राजकारणात आबिटकरांचे प्रकाशपर्व!</t>
+          <t>Prakash Abitkar: 'दादा नेहमी आमच्या परीक्षा घेतात अन् आमची अडचण होते', आरोग्यमंत्री प्रकाश</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/prakash-abitkar-is-now-the-focus-of-kolhapur-politics-mrj-95-4843588/</t>
+          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>कोल्हापूर शहराची हद्दवाढ, खंडपीठ होणारच; पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
+          <t>आरोग्यमंत्री प्रकाश आबिटकर म्हणाले, काही बिघडणार…</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/kolhapur-city-limits-to-be-expanded-bench-to-be-formed-says-guardian-minister-prakash-abitkar-a-a746/</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-on-inquiry-of-health-department-s-irregularity-pune-print-news-ggy-03-css-98-4923177/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>राज्यातील आरोग्यसंस्थांमध्ये दोन हजार पदनिर्मितीस मान्यता : आरोग्यमंत्री आबिटकर</t>
+          <t>कोल्हापूर शहराची हद्दवाढ, खंडपीठ होणारच; पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-health-department-2070-new-posts-approved</t>
+          <t>https://www.lokmat.com/kolhapur/kolhapur-city-limits-to-be-expanded-bench-to-be-formed-says-guardian-minister-prakash-abitkar-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Prakashrao Abitkar | मंत्री प्रकाश आबिटकर यांचा अजेंडा काय? जाणून घ्या...</t>
+          <t>राज्यातील आरोग्यसंस्थांमध्ये दोन हजार पदनिर्मितीस मान्यता : आरोग्यमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/what-is-minister-prakash-abitkars-agenda-find-out</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-health-department-2070-new-posts-approved</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
+          <t>Prakashrao Abitkar | मंत्री प्रकाश आबिटकर यांचा अजेंडा काय? जाणून घ्या...</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
+          <t>https://www.lokshahi.com/news/what-is-minister-prakash-abitkars-agenda-find-out</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>'जीबीएस' आजारानं रुग्णाचा मृत्यू होतो का? आरोग्यमंत्र्यांनी थेटच सांगितलं...</t>
+          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tanisha Bhise Death Case : पैशांच्या डिपॉझिटसाठी उपचार नाकारणाऱ्या सर्व हॉस्पिटल्सवर कारवाई होणार? आरोग्यमंत्र्यांकडून महत्त्वाची माहिती</t>
+          <t>'जीबीएस' आजारानं रुग्णाचा मृत्यू होतो का? आरोग्यमंत्र्यांनी थेटच सांगितलं...</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : पालकमंत्री कोणावर होणार मेहरबान? भाजपमध्ये मोठी स्पर्धा</t>
+          <t>Tanisha Bhise Death Case : पैशांच्या डिपॉझिटसाठी उपचार नाकारणाऱ्या सर्व हॉस्पिटल्सवर कारवाई होणार? आरोग्यमंत्र्यांकडून महत्त्वाची माहिती</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/kolhapur-guardian-minister-prakash-abitkar-who-will-get-favor-bjp-big-competition-rg90-gs97</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>राज्यात प्रथमच स्वतंत्र आरोग्य धोरण; आरोग्यमंत्री प्रकाश आबिटकर यांची घोषणा</t>
+          <t>Prakash Abitkar : पालकमंत्री कोणावर होणार मेहरबान? भाजपमध्ये मोठी स्पर्धा</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-announces-separate-health-policy-for-the-maharashtra-state-amy-95-4860385/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/kolhapur-guardian-minister-prakash-abitkar-who-will-get-favor-bjp-big-competition-rg90-gs97</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या हद्दवाढीसाठी लवकरच मुख्यमंत्र्यांसोबत बैठक, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
+          <t>कोल्हापूरच्या राजकारणात आबिटकरांचे प्रकाशपर्व!</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/meeting-with-chief-minister-soon-for-extension-of-kolhapur-boundary-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
+          <t>https://www.loksatta.com/kolhapur/prakash-abitkar-is-now-the-focus-of-kolhapur-politics-mrj-95-4843588/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Corona virus in Maharashtra: राज्यातील कोरोना व्हायरसबाबत मोठी अपडेट, आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>कोल्हापूरच्या हद्दवाढीसाठी लवकरच मुख्यमंत्र्यांसोबत बैठक, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
+          <t>https://www.lokmat.com/kolhapur/meeting-with-chief-minister-soon-for-extension-of-kolhapur-boundary-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Covid 19: कोरोनाची लक्षणं सौम्य, प्रकाश आबिटकर यांची माहिती</t>
+          <t>Corona virus in Maharashtra: राज्यातील कोरोना व्हायरसबाबत मोठी अपडेट, आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5122212/corona-symptoms-are-mild-prakash-abitkars-gave-detail-information/</t>
+          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : कोल्हापुरातील दिव्यांगांचा एकही प्रश्न शिल्लक ठेवायचा नाही प्रकाश</t>
+          <t>राज्यात प्रथमच स्वतंत्र आरोग्य धोरण; आरोग्यमंत्री प्रकाश आबिटकर यांची घोषणा</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-prakash-abitkar-instructions-no-issue-of-the-disabled-should-be-left-unsolved-marathi-news-1358401</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-announces-separate-health-policy-for-the-maharashtra-state-amy-95-4860385/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kolhapur News: पालकमंत्री प्रकाश आबिटकर शेताच्या बांधावर; भर पावसात चिखलगुट्टा करत भात रोपांची लागण</t>
+          <t>Prakash Abitkar : कोल्हापुरातील दिव्यांगांचा एकही प्रश्न शिल्लक ठेवायचा नाही प्रकाश</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-prakash-abitkar-instructions-no-issue-of-the-disabled-should-be-left-unsolved-marathi-news-1358401</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>विधानसभेत आरोग्यमंत्र्यांची मोठी घोषणा, बीड जिल्हा रुग्णालयातील बडा डॉक्टर</t>
+          <t>वैद्यकीय प्रयोगशाळांच्या तपासणीसाठी कायदा; आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : पालकमंत्री प्रकाश आबिटकरांकडून कोल्हापुरात ध्वजारोहण; म्हणाले, बहुमान मिळाल्याचा सार्थ अभिमान</t>
+          <t>विधानसभेत आरोग्यमंत्र्यांची मोठी घोषणा, बीड जिल्हा रुग्णालयातील बडा डॉक्टर</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
+          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>वैद्यकीय प्रयोगशाळांच्या तपासणीसाठी कायदा; आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>कोल्हापूर जिल्ह्यापासून लंपी दूर ठेवा – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
+          <t>https://www.loksatta.com/kolhapur/lumpy-disease-under-controls-in-kolhapur-district-due-to-implementation-of-effective-vaccination-says-minister-prakash-abitkar-zws-70-5301296/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्यापासून लंपी दूर ठेवा – प्रकाश आबिटकर</t>
+          <t>Kolhapur News: पालकमंत्री प्रकाश आबिटकर शेताच्या बांधावर; भर पावसात चिखलगुट्टा करत भात रोपांची लागण</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/lumpy-disease-under-controls-in-kolhapur-district-due-to-implementation-of-effective-vaccination-says-minister-prakash-abitkar-zws-70-5301296/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : सामान्य नागरिकांना त्रास देणाऱ्यांना रस्त्यावर फटके द्या; गांजा आणि सावकारीवरून पालकमंत्री प्रकाश आबिटकरांचे निर्देश</t>
+          <t>Prakash Abitkar : पालकमंत्री प्रकाश आबिटकरांकडून कोल्हापुरात ध्वजारोहण; म्हणाले, बहुमान मिळाल्याचा सार्थ अभिमान</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : महाराष्ट्राच्या मंत्रिमंडळातला मोठा गौप्यस्फोट, मंत्र्यानेच सांगितली आतली बातमी</t>
+          <t>Prakash Abitkar : सामान्य नागरिकांना त्रास देणाऱ्यांना रस्त्यावर फटके द्या; गांजा आणि सावकारीवरून पालकमंत्री प्रकाश आबिटकरांचे निर्देश</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
+          <t>Maharashtra Politics : महाराष्ट्राच्या मंत्रिमंडळातला मोठा गौप्यस्फोट, मंत्र्यानेच सांगितली आतली बातमी</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Madhuri Elephant News : ‘माधुरी हत्तीणी’च्या ‘नांदणी’वापसीचा मार्ग मोकळा! पण कायद्याचा अडसर; पालकमंत्री आबिटकरांची माहिती</t>
+          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/madhuri-elephant-cleared-for-return-to-nandani-but-legal-hurdles-remain-says-minister-prakash-abitkar-rg84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kolhapur city Extension : हद्दवाढीसाठी शहरवासियांनी न्यायदाता ठरवला, पालकमंत्री अबिटकरांनाच करणार म्होरक्या</t>
+          <t>Madhuri Elephant News : ‘माधुरी हत्तीणी’च्या ‘नांदणी’वापसीचा मार्ग मोकळा! पण कायद्याचा अडसर; पालकमंत्री आबिटकरांची माहिती</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-haddavadh-kruti-samitis-decision-to-approach-guardian-minister-prakash-abitkar-for-boundary-expansion-as11-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/madhuri-elephant-cleared-for-return-to-nandani-but-legal-hurdles-remain-says-minister-prakash-abitkar-rg84</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Hospital : हॉस्पिटलच्या मनमानीला चाप लागणार पेशंट, नातेवाईकांची तक्रार थेट</t>
+          <t>Prakash Abitkar on Covid 19: कोरोनाची लक्षणं सौम्य, प्रकाश आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5122212/corona-symptoms-are-mild-prakash-abitkars-gave-detail-information/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: कोल्हापुरात महायुतीमध्ये शिवसेना हाच सर्वात मोठा पक्ष आगामी निवडणुकांसाठी</t>
+          <t>Kolhapur city Extension : हद्दवाढीसाठी शहरवासियांनी न्यायदाता ठरवला, पालकमंत्री अबिटकरांनाच करणार म्होरक्या</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-haddavadh-kruti-samitis-decision-to-approach-guardian-minister-prakash-abitkar-for-boundary-expansion-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 108 अॅम्ब्युलन्स खरेदीच्या टेंडर प्रक्रियेत काय झालं? श्रीकांत शिंदेंचे</t>
+          <t>Prakash Abitkar on Hospital : हॉस्पिटलच्या मनमानीला चाप लागणार पेशंट, नातेवाईकांची तक्रार थेट</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
+          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kolhapur Political News | कॅरम खेळण्यात आबिटकर-महाडिक दंग; सोशल मीडियावर व्हिडिओ व्हायरल</t>
+          <t>Prakash Abitkar: कोल्हापुरात महायुतीमध्ये शिवसेना हाच सर्वात मोठा पक्ष आगामी निवडणुकांसाठी</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-leaders-dhanajay-mahadik-and-prakash-abitkar-sharangdhar-deshmukh-carrom-match-political-move-sd22</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>राज्यात बॉम्बे नर्सिंग अँक्टची कठोर अमंलबजावणी होणार; आरोग्य मंत्री प्रकाश आबिटकर यांनी माहिती</t>
+          <t>महाराष्ट्राचे आरोग्यमंत्री अचानक रुग्णालयात धडकले, अधिकाऱ्यांवर भडकले, नेमकं काय घडलं?</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/health-minister-prakash-abitkar-has-informed-that-the-bombay-nursing-act-will-be-strictly-implemented-in-the-state-amy-95-4933697/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक, आरोग्य मंत्री प्रकाश आबिटकर यांची माहिती</t>
+          <t>Prakash Abitkar : 108 अॅम्ब्युलन्स खरेदीच्या टेंडर प्रक्रियेत काय झालं? श्रीकांत शिंदेंचे</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/state-labour-insurance-scheme-hospitals-to-be-state-of-the-art-says-health-minister-prakash-abitkar-851510.html</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kolhapur News: कोल्हापुरात ईएसआय रुग्णालयात आरोग्यमंत्र्यांकडून डॉक्टरांची झाडाझडती</t>
+          <t>Kolhapur Political News | कॅरम खेळण्यात आबिटकर-महाडिक दंग; सोशल मीडियावर व्हिडिओ व्हायरल</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-leaders-dhanajay-mahadik-and-prakash-abitkar-sharangdhar-deshmukh-carrom-match-political-move-sd22</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kolhapur Politics | कोल्हापूरचे पालकमंत्री आबिटकर थेट खासदार शाहू महाराजांच्या भेटीला; चर्चांना उधाण</t>
+          <t>राज्यात बॉम्बे नर्सिंग अँक्टची कठोर अमंलबजावणी होणार; आरोग्य मंत्री प्रकाश आबिटकर यांनी माहिती</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-guardian-minister-prakash-abitkar-meets-congress-mp-shahu-maharaj-as80</t>
+          <t>https://www.loksatta.com/maharashtra/health-minister-prakash-abitkar-has-informed-that-the-bombay-nursing-act-will-be-strictly-implemented-in-the-state-amy-95-4933697/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ई-रक्तकोषद्वारे गरजू रुग्णांना मिळणार रक्त उपलब्धतेची माहिती - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Politics | कोल्हापूरचे पालकमंत्री आबिटकर थेट खासदार शाहू महाराजांच्या भेटीला; चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159642/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-guardian-minister-prakash-abitkar-meets-congress-mp-shahu-maharaj-as80</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>अनुदान न मिळाल्याने रखडले ‘आरबीएसके’ पथकांचे वेतन; आरोग्यमंत्री प्रकाश आबिटकर यांची माहिती</t>
+          <t>Kolhapur News: कोल्हापुरात ईएसआय रुग्णालयात आरोग्यमंत्र्यांकडून डॉक्टरांची झाडाझडती</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/salary-of-rbsk-teams-stalled-due-to-non-receipt-of-grant</t>
+          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>‘अलमट्टी’ विरोधात महाराष्ट्राची; कायदेशीर लढाई – प्रकाश आबिटकर</t>
+          <t>ई-रक्तकोषद्वारे गरजू रुग्णांना मिळणार रक्त उपलब्धतेची माहिती - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/guardian-minister-prakash-abitkar-expressed-his-opinion-regarding-the-height-of-the-almatti-dam-while-talking-to-reporters-phm-00-5066152/</t>
+          <t>https://mahasamvad.in/159642/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Almatti Dam : तर आम्हीही तशीच वकिलांची आणि जलतज्ञांची फौज उभा करू 'अलमट्टी'च्या</t>
+          <t>अनुदान न मिळाल्याने रखडले ‘आरबीएसके’ पथकांचे वेतन; आरोग्यमंत्री प्रकाश आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
+          <t>https://pudhari.news/maharashtra/pune/salary-of-rbsk-teams-stalled-due-to-non-receipt-of-grant</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Women Cancer Symptoms : खळबळजनक! महाराष्ट्रातील ‘या’ जिल्ह्यात तब्बल १४ हजारांहून अधिक महिलांमध्ये आढळली 'कॅन्सर'सारखी लक्षणे</t>
+          <t>‘अलमट्टी’ विरोधात महाराष्ट्राची; कायदेशीर लढाई – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/hingoli-women-cancer-symptoms-health-minister-prakash-abitkar-statement-14000-affected-msr87</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-prakash-abitkar-expressed-his-opinion-regarding-the-height-of-the-almatti-dam-while-talking-to-reporters-phm-00-5066152/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>पत्रकारांच्या आरोग्याच्या प्रश्नावर लवकरच बैठक घेणार – मंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar on Almatti Dam : तर आम्हीही तशीच वकिलांची आणि जलतज्ञांची फौज उभा करू 'अलमट्टी'च्या</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170017/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>कोल्हापूर हद्दवाढीवर लवकरच निर्णय</t>
+          <t>Women Cancer Symptoms : खळबळजनक! महाराष्ट्रातील ‘या’ जिल्ह्यात तब्बल १४ हजारांहून अधिक महिलांमध्ये आढळली 'कॅन्सर'सारखी लक्षणे</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-boundary-expansion-decision-soon-prakash-abitkar-ap84</t>
+          <t>https://www.esakal.com/maharashtra/hingoli-women-cancer-symptoms-health-minister-prakash-abitkar-statement-14000-affected-msr87</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Prakash Abitkar | ग्रामीण भागात सेवा दिल्यानंतरच डॉक्टरांना प्रमाणपत्र मिळणार</t>
+          <t>कोल्हापूर हद्दवाढीवर लवकरच निर्णय</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/doctors-rural-service-bond-certificate-upload-health-minister-prakash-abitkar</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-boundary-expansion-decision-soon-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : विरोधकांच्या 108 रुग्णवाहिका घोटाळ्यावर आरोग्यमंत्र्यांचे स्पष्टीकरण, म्हणाले, "त्याचा शासनाशी सबंध नाही..."</t>
+          <t>Prakash Abitkar | ग्रामीण भागात सेवा दिल्यानंतरच डॉक्टरांना प्रमाणपत्र मिळणार</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-108-ambulance-scam-health-minister-prakash-abitkar-clarification-jap93-rg93</t>
+          <t>https://pudhari.news/maharashtra/mumbai/doctors-rural-service-bond-certificate-upload-health-minister-prakash-abitkar</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: पहिल्यांदाच मंत्री अन् पालकमंत्रिपद मिळालं, आबिटकर यांच्यासमोर आता 'हे' मोठ आव्हान</t>
+          <t>Prakash Abitkar : विरोधकांच्या 108 रुग्णवाहिका घोटाळ्यावर आरोग्यमंत्र्यांचे स्पष्टीकरण, म्हणाले, "त्याचा शासनाशी सबंध नाही..."</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-kolhapur-guardian-minister-prakash-abitkar-mahayuti-challenge-mm76-rg93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-108-ambulance-scam-health-minister-prakash-abitkar-clarification-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांच्या सूचनेनुसारच हद्दवाढीची प्रक्रिया सुरू : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar: पहिल्यांदाच मंत्री अन् पालकमंत्रिपद मिळालं, आबिटकर यांच्यासमोर आता 'हे' मोठ आव्हान</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/boundary-expansion-process-initiated-as-per-cm-directive-says-prakash-abitkar-ap84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-kolhapur-guardian-minister-prakash-abitkar-mahayuti-challenge-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Pune GBS : पुण्यातील 'त्या' विहिरीमुळे पसरला गुईलेन बॅरे सिंड्रोम, आरोग्यमंत्र्यांनी दिली धक्कादायक माहिती</t>
+          <t>मुख्यमंत्र्यांच्या सूचनेनुसारच हद्दवाढीची प्रक्रिया सुरू : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/boundary-expansion-process-initiated-as-per-cm-directive-says-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>दोन कोटी शालेय विद्यार्थ्यांची आरोग्य तपासणी करणार – आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>महिन्यातून किमान दोन वेळा आरोग्य संस्थांना अचानक भेटी द्या - आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155891/</t>
+          <t>https://www.lokmat.com/pune/make-surprise-visits-to-health-institutions-at-least-twice-a-month-health-minister-prakash-abitkar-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>"कर्करोगापासून बचाव करण्यासाठी मुलींना मोफत लस...", नेमकं काय म्हणाले आरोग्य मंत्री?</t>
+          <t>Pune GBS : पुण्यातील 'त्या' विहिरीमुळे पसरला गुईलेन बॅरे सिंड्रोम, आरोग्यमंत्र्यांनी दिली धक्कादायक माहिती</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
+          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kolhapur Guardian Minister : मंत्री प्रकाश आबिटकर कोल्हापूरचे पालकमंत्री</t>
+          <t>दोन कोटी शालेय विद्यार्थ्यांची आरोग्य तपासणी करणार – आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-appointed-as-guardian-minister-of-kolhapur-sdj87</t>
+          <t>https://mahasamvad.in/155891/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>flood control planning | पूर नियंत्रणाचे सूक्ष्म नियोजन करा : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Guardian Minister : मंत्री प्रकाश आबिटकर कोल्हापूरचे पालकमंत्री</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/plan-micro-level-flood-control-says-minister-prakash-abitkar-ap84</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-appointed-as-guardian-minister-of-kolhapur-sdj87</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>अवैध गर्भपाताची माहिती देणाऱ्या महिलांच्या मानधनात वाढ – आबिटकर</t>
+          <t>flood control planning | पूर नियंत्रणाचे सूक्ष्म नियोजन करा : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/increase-in-honorarium-of-women-who-provide-information-about-illegal-abortions-say-prakash-abitkar-mrj-95-4843272/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/plan-micro-level-flood-control-says-minister-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>आरोग्य सेवा बळकट करण्यासाठी आरोग्य मंत्र्यांचा सूचनांचा धडाका; आरोग्य भवनमध्ये सर्व अधिकाऱ्यांची बैठक</t>
+          <t>अवैध गर्भपाताची माहिती देणाऱ्या महिलांच्या मानधनात वाढ – आबिटकर</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-suggestions-to-strengthen-healthcare-services-at-the-high-level-meeting-mumbai-print-news-zws-70-5104660/</t>
+          <t>https://www.loksatta.com/kolhapur/increase-in-honorarium-of-women-who-provide-information-about-illegal-abortions-say-prakash-abitkar-mrj-95-4843272/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>‘महादेवी’परत करण्याबाबत ‘वनतारा’ व्यवस्थापन सकारात्मक; प्रकाश आबिटकर यांचा दावा</t>
+          <t>आरोग्य सेवा बळकट करण्यासाठी आरोग्य मंत्र्यांचा सूचनांचा धडाका; आरोग्य भवनमध्ये सर्व अधिकाऱ्यांची बैठक</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-abitkar-claims-positive-response-from-vantara-over-elephant-rds-00-5274363/</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-suggestions-to-strengthen-healthcare-services-at-the-high-level-meeting-mumbai-print-news-zws-70-5104660/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GBS रुग्णांच्या उपचार करताना औषधांचा गैरवापर, जास्त पैसे पैसे घेतल्यास;आरोग्यमंत्री प्रकाश आबिटकर यांचा इशारा</t>
+          <t>"कर्करोगापासून बचाव करण्यासाठी मुलींना मोफत लस...", नेमकं काय म्हणाले आरोग्य मंत्री?</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/beware-if-you-are-robbed-health-minister-prakash-abitkar-warns-a-a1008/</t>
+          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kolhapur Politics: 'गोकुळ'मध्ये मुश्रीफ, सतेज, आबिटकर, कोरे यांची एकी; डोंगळे एकाकी</t>
+          <t>‘महादेवी’परत करण्याबाबत ‘वनतारा’ व्यवस्थापन सकारात्मक; प्रकाश आबिटकर यांचा दावा</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/hasan-mushrif-satej-patil-prakash-abitkar-vinay-kore-are-united-in-gokul-dudh-sangh-politics-arun-dongle-is-alone-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-abitkar-claims-positive-response-from-vantara-over-elephant-rds-00-5274363/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : आरोग्यमंत्र्यांच्या कोल्हापुरातच 'सलमान'ची चर्चा, प्रशासकीय अधिकारीही 'लाभार्थी'</t>
+          <t>GBS रुग्णांच्या उपचार करताना औषधांचा गैरवापर, जास्त पैसे पैसे घेतल्यास;आरोग्यमंत्री प्रकाश आबिटकर यांचा इशारा</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-advises-citizens-to-consult-professionals-that-time-some-officials-visit-salmans-hair-trainer-to-treatment-hair-problem-as11-rg93</t>
+          <t>https://www.lokmat.com/pune/beware-if-you-are-robbed-health-minister-prakash-abitkar-warns-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tanisha Bhise Death Case : ‘मन सुन्न करणारी घटना, कायदेशीर कारवाई..’; दीनानाथ मंगेशकर रुग्णालयातील घटनेनंतर आरोग्यमंत्र्यांची प्रतिक्रिया</t>
+          <t>Kolhapur Politics: 'गोकुळ'मध्ये मुश्रीफ, सतेज, आबिटकर, कोरे यांची एकी; डोंगळे एकाकी</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/health-minister-prakashrao-abitkar-on-dinanath-mangeshkar-hospital-tanisha-bhise-death-case-gkt-96-4997347/</t>
+          <t>https://www.lokmat.com/kolhapur/hasan-mushrif-satej-patil-prakash-abitkar-vinay-kore-are-united-in-gokul-dudh-sangh-politics-arun-dongle-is-alone-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>खासगी रुग्णालयांची नोंदणी आता ऑनलाईन, आरोग्य मंत्री प्रकाश आबिटकर यांची घोषणा</t>
+          <t>Prakash Abitkar : आरोग्यमंत्र्यांच्या कोल्हापुरातच 'सलमान'ची चर्चा, प्रशासकीय अधिकारीही 'लाभार्थी'</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/registration-of-private-hospitals-now-online-health-minister-prakash-abitkar-announced-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-advises-citizens-to-consult-professionals-that-time-some-officials-visit-salmans-hair-trainer-to-treatment-hair-problem-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>कर्करोग प्रतिबंधासाठी जनजागृती गरजेची – मंत्री प्रकाश आबिटकर</t>
+          <t>खासगी रुग्णालयांची नोंदणी आता ऑनलाईन, आरोग्य मंत्री प्रकाश आबिटकर यांची घोषणा</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154597/</t>
+          <t>https://www.lokmat.com/kolhapur/registration-of-private-hospitals-now-online-health-minister-prakash-abitkar-announced-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>जिल्ह्याच्या सर्वांगिण विकासाचा संकल्प सर्वजण मिळून करू - पालकमंत्री प्रकाश आबिटकर यांचे जिल्हावासियांना आवाहन</t>
+          <t>कर्करोग प्रतिबंधासाठी जनजागृती गरजेची – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175693/</t>
+          <t>https://mahasamvad.in/154597/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>‘ईएसआयसी’ रुग्णालयात रुग्णसेवेच्या गुणवत्तेत वाढ करा – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>जिल्ह्याच्या सर्वांगिण विकासाचा संकल्प सर्वजण मिळून करू - पालकमंत्री प्रकाश आबिटकर यांचे जिल्हावासियांना आवाहन</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/170012/</t>
+          <t>https://mahasamvad.in/175693/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>पालकमंत्री आबिटकर यांच्यासमोर नवे आव्हान!</t>
+          <t>‘ईएसआयसी’ रुग्णालयात रुग्णसेवेच्या गुणवत्तेत वाढ करा – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-faces-new-challenge</t>
+          <t>https://www.mahasamvad.in/170012/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री प्रकाश आबिटकर म्हणाले; शाकाहारी- मांसाहारीपेक्षा देशी प्रेम महत्त्वाचे!</t>
+          <t>पालकमंत्री आबिटकर यांच्यासमोर नवे आव्हान!</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-faces-new-challenge</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Pandharpur News | वारकर्‍यांची सेवा हीच पांडुरंगाची सेवा समजून काम करावे : मंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्य मंत्री प्रकाश आबिटकर म्हणाले; शाकाहारी- मांसाहारीपेक्षा देशी प्रेम महत्त्वाचे!</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/serve-warkaris-as-serving-pandurang-says-minister-prakash-abitkar-pandharpur-sk95</t>
+          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर यांच्याकडून गुरुजनांना विधानसभेची हवाई सैर</t>
+          <t>Pandharpur News | वारकर्‍यांची सेवा हीच पांडुरंगाची सेवा समजून काम करावे : मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-minister-prakash-abitkar-takes-senior-citizens-on-air-trip-unique-guru-purnima-initiative-vsd-99-5224693/</t>
+          <t>https://pudhari.news/maharashtra/solapur/serve-warkaris-as-serving-pandurang-says-minister-prakash-abitkar-pandharpur-sk95</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : राष्‍ट्रीय आरोग्‍य अभियानच्‍या कर्मचारी, अधिकारी यांचा पगार लवकरच</t>
+          <t>प्रकाश आबिटकर यांच्याकडून गुरुजनांना विधानसभेची हवाई सैर</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/salaries-of-national-health-mission-employees-and-officers-to-be-disbursed-soon-prakash-abitkar-pjp78</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-minister-prakash-abitkar-takes-senior-citizens-on-air-trip-unique-guru-purnima-initiative-vsd-99-5224693/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>‘जीबीएस’ वर उपचारांविषयी सर्वंकष उपाययोजना करा – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : राष्‍ट्रीय आरोग्‍य अभियानच्‍या कर्मचारी, अधिकारी यांचा पगार लवकरच</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153447/</t>
+          <t>https://www.esakal.com/pune/salaries-of-national-health-mission-employees-and-officers-to-be-disbursed-soon-prakash-abitkar-pjp78</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 'GBS आजारावर सर्वंकष उपाययोजना करा'; आरोग्यमंत्री आबिटकरांचे संबंधित प्रशासनाला महत्त्वपूर्ण निर्देश</t>
+          <t>‘जीबीएस’ वर उपचारांविषयी सर्वंकष उपाययोजना करा – आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/health-minister-prakash-abitkar-instructions-to-take-measures-regarding-gbs-disease-bam92</t>
+          <t>https://mahasamvad.in/153447/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Kolhapur Shivsena: जिल्ह्यातील ठाकरे गट कोणाचाही दावणीला बांधू देणार नाही जुगार अड्डे</t>
+          <t>अरुण सरनाईक यांचा कलाविष्कार सदैव स्मरणात राहणारा : प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-remembers-arun-sarnaiak-for-his-timeless-art-ocd-94-5177138/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री प्रकाश आबिटकर, राज्यमंत्री मेघना बोर्डीकर यांचा तामिळनाडू अभ्यास दौरा</t>
+          <t>Kolhapur Shivsena: जिल्ह्यातील ठाकरे गट कोणाचाही दावणीला बांधू देणार नाही जुगार अड्डे</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157284/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>अपघातग्रस्तांवर एक लाखांपर्यंत कॅशलेस उपचार करा; आरोग्यमंत्री आबिटकर यांचे निर्देश</t>
+          <t>आरोग्यमंत्री प्रकाश आबिटकर, राज्यमंत्री मेघना बोर्डीकर यांचा तामिळनाडू अभ्यास दौरा</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/cashless-treatment-up-to-one-lakh-for-accident-victims-health-minister-directive</t>
+          <t>https://mahasamvad.in/157284/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>राज्यातील ग्रामीण रुग्णालय, प्राथमिक आरोग्य केंद्र इ.आरोग्य संस्थामध्ये दोन हजार पदनिर्मितीसाठी शासनाची मान्यता -आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>अपघातग्रस्तांवर एक लाखांपर्यंत कॅशलेस उपचार करा; आरोग्यमंत्री आबिटकर यांचे निर्देश</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/156822/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/cashless-treatment-up-to-one-lakh-for-accident-victims-health-minister-directive</t>
         </is>
       </c>
     </row>
@@ -2351,60 +2351,60 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>हत्तीरोग मुक्त महाराष्ट्रासाठी औषधोपचार मोहिमेला सहकार्य करा – मंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरू करणार, मंत्री प्रकाश आबिटकर यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/157564/</t>
+          <t>https://www.lokmat.com/kolhapur/awards-to-be-launched-for-all-departments-in-the-health-sector-health-minister-prakash-abitkar-announced-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी</t>
+          <t>हत्तीरोग मुक्त महाराष्ट्रासाठी औषधोपचार मोहिमेला सहकार्य करा – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
+          <t>https://www.mahasamvad.in/157564/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Coronavirus : सिंगापूरनंतर राज्यात कोरोनाचा धोका वाढला? आरोग्यमंत्री म्हणाले...</t>
+          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/maharashtra-health-minister-on-corona-variants-situation-and-government-measures-nck90</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cashless Treatment : अपघातग्रस्तांना १ लाख रुपयांपर्यंत कॅशलेस उपचार मिळणार, राज्य सरकारचा मोठा निर्णय</t>
+          <t>Coronavirus : सिंगापूरनंतर राज्यात कोरोनाचा धोका वाढला? आरोग्यमंत्री म्हणाले...</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/accident-victims-will-get-cashless-treatment-up-to-rs-1-lakh-big-decision-of-the-state-government-prakash-abitkar-gkt-96-5028935/</t>
+          <t>https://saamtv.esakal.com/video/maharashtra-health-minister-on-corona-variants-situation-and-government-measures-nck90</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>महादेवी हत्ती परत येणार?, वनतारा सीईओंसोबतच्या बैठकीतून मठाचे महास्वामी बाहेर पडले, नेमकं काय घडलं.. वाचा</t>
+          <t>Cashless Treatment : अपघातग्रस्तांना १ लाख रुपयांपर्यंत कॅशलेस उपचार मिळणार, राज्य सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/now-a-legal-battle-for-the-mahadevi-elephant-of-nandani-math-guardian-minister-prakash-abitkar-gave-information-after-a-discussion-between-the-ceo-of-vanatara-and-the-mathadhis-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/accident-victims-will-get-cashless-treatment-up-to-rs-1-lakh-big-decision-of-the-state-government-prakash-abitkar-gkt-96-5028935/</t>
         </is>
       </c>
     </row>
@@ -2423,60 +2423,60 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेचा लाभ तळागाळातील गरजू कामगारांपर्यंत पोहोचवावा -सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>महादेवी हत्ती परत येणार?, वनतारा सीईओंसोबतच्या बैठकीतून मठाचे महास्वामी बाहेर पडले, नेमकं काय घडलं.. वाचा</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173263/</t>
+          <t>https://www.lokmat.com/kolhapur/now-a-legal-battle-for-the-mahadevi-elephant-of-nandani-math-guardian-minister-prakash-abitkar-gave-information-after-a-discussion-between-the-ceo-of-vanatara-and-the-mathadhis-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्र्यांसमोरच दोन वैद्यकीय अधिकाऱ्यांमध्ये वाद: प्रकाश आबिटकरांनी दिली ईएसआयसी रुग्णालयाला अचानक भेट...</t>
+          <t>Prakashrao Abitkar : गर्भलिंग निदान सुरु असल्याची टीप देणाऱ्या खबरींना एका लाखाचं बक्षीस</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/maharashtra-health-minister-prakash-abitkar-inspects-esic-hospital-kolhapur-135283124.html</t>
+          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>‘अवयवदान’ ही मानवतेची व सामाजिक बदलाची चळवळ व्हावी – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>राज्य कामगार विमा योजनेचा लाभ तळागाळातील गरजू कामगारांपर्यंत पोहोचवावा -सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/167252/</t>
+          <t>https://mahasamvad.in/173263/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>कामचुकारपणा आला अंगलट! आरोग्यमंत्र्यांचा दणका, हतरू आरोग्य केंद्रातील डॉक्टरसह चौघे निलंबित</t>
+          <t>‘अवयवदान’ ही मानवतेची व सामाजिक बदलाची चळवळ व्हावी – आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-primary-health-center-doctor-and-four-others-suspended</t>
+          <t>https://www.mahasamvad.in/167252/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mahayuti Controversy: कोल्हापुरात 10 आमदार असलेल्या महायुतीत वादाचा भडका; आबिटकरांनाच विरोध,भाजपनं घातला थेट मुद्द्यालाच हात</t>
+          <t>आरोग्यमंत्र्यांसमोरच दोन वैद्यकीय अधिकाऱ्यांमध्ये वाद: प्रकाश आबिटकरांनी दिली ईएसआयसी रुग्णालयाला अचानक भेट...</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-dispute-over-kolhapur-district-committee-bjp-ncp-vs-prakash-abitkar-dk88-rg93</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/maharashtra-health-minister-prakash-abitkar-inspects-esic-hospital-kolhapur-135283124.html</t>
         </is>
       </c>
     </row>
@@ -2615,5302 +2615,5050 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>राज्याच्या प्रगतीत कोल्हापूर जिल्हा अग्रभागी राहण्यासाठी सर्वजण सज्ज होऊया -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्य शिबिरातून मोफत अत्याधुनिक वैद्यकीय सेवा उपलब्ध करून देणार - पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164322/</t>
+          <t>https://mahasamvad.in/173559/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>आरोग्य शिबिरातून मोफत अत्याधुनिक वैद्यकीय सेवा उपलब्ध करून देणार - पालकमंत्री प्रकाश आबिटकर</t>
+          <t>महादेवी हत्तीणीच्या परतीचा मार्ग मोकळा? जनभावना आणि वनताराच्या भूमिकेमुळे परतीची आशा</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173559/</t>
+          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>रुग्णांना दर्जेदार सेवा द्या – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>तानाजी सावंतांच्या कार्यकाळातील ३२०० कोटींचे टेंडर फडणवीसांकडून स्थगित, आरोग्यमंत्री म्हणाले…</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162788/</t>
+          <t>https://www.lokmat.com/pune/fadnavis-cancels-3200-crore-tender-during-tanaji-sawant-tenure-prakash-abitkar-reacts-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>कोल्हापूर शहराची हद्दवाढ झाली पाहिजे: 25 मे पूर्वी मनपा,जि.प.च्या निवडणुका होतील, महायुतीत नाराजी नाही- धनं...</t>
+          <t>रुग्णालयांनी गरजू रुग्णांना शासकीय योजनांचा तत्परतेने लाभ द्यावा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/dhananjay-mahadik-reaction-on-kolhapur-city-expansion-issues-prakash-abitkar-134382678.html</t>
+          <t>https://mahasamvad.in/173259/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>तानाजी सावंतांच्या कार्यकाळातील ३२०० कोटींचे टेंडर फडणवीसांकडून स्थगित, आरोग्यमंत्री म्हणाले…</t>
+          <t>इंदिरा गांधी रुग्णालयात सुविधा पुरवणार – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/fadnavis-cancels-3200-crore-tender-during-tanaji-sawant-tenure-prakash-abitkar-reacts-a-a1008/</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-assures-new-facilities-at-indira-gandhi-hospital-ocd-94-5247730/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>रुग्णालयांनी गरजू रुग्णांना शासकीय योजनांचा तत्परतेने लाभ द्यावा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>बचत गटांच्या चळवळीतून महिलांना आर्थिक सक्षम आणि साक्षर करूया – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173259/</t>
+          <t>https://mahasamvad.in/166403/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>सार्वजनिक बांधकाम विभागांतर्गतची कामे दर्जेदार करा -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur : सतर्क राहा; अलमट्टी, हिप्परगी विसर्गाबाबत समन्वय ठेवा</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158717/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-meeting-at-district-collector-office-dc95</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>बचत गटांच्या चळवळीतून महिलांना आर्थिक सक्षम आणि साक्षर करूया – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>५० हजार हक्काची घरे देण्यासाठी मिशन मोडवर काम करा -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166403/</t>
+          <t>https://mahasamvad.in/154283/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Kolhapur : सतर्क राहा; अलमट्टी, हिप्परगी विसर्गाबाबत समन्वय ठेवा</t>
+          <t>विस्कळीत झालेली, १०२ रुग्णवाहिका सेवा पूर्ववत ?</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-meeting-at-district-collector-office-dc95</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-says-102-ambulance-service-restored-mumbai-print-news-ocd-94-5228346/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>भुदरगड तालुक्यातील सात धबधबे म्हणजे निसर्गात लपलेला अद्भुत खजिना – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>मावळ तालुक्यातील आरोग्य संस्थांना आवश्यक सुविधा द्या - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172859/</t>
+          <t>https://mahasamvad.in/174701/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : ठरलं! महापालिका निवडणुकीत शिंदेंच्या शिवसेनेची सूत्रे अबिटकरांच्या हाती, तर राष्ट्रवादीची धुरा एकटे मुश्रीफ सांभाळणार</t>
+          <t>Pune News: प्रसुतीवेळी महिलेचा मृत्यू प्रकरणात आरोग्य मंत्र्यांचे कारवाईचे आदेश</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-ichalkaranji-municipal-election-political-strategies-party-alliance-hasan-mushrif-prakash-abitkar-jap93-rg93</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-health-minister-prakashrao-abitkar-orders-action-in-case-of-womans-death-during-childbirth-police-will-conduct-investigation-today-will-examine-cctv-along-with-statements-from-nurses-and-doctors-1352627</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीणीच्या परतीचा मार्ग मोकळा? जनभावना आणि वनताराच्या भूमिकेमुळे परतीची आशा</t>
+          <t>Nandani Mahadevi Elephant : वनतारा सकारात्मक! नांदणी मठाची 'महादेवी' परत येण्याची शक्यता, पालकमंत्र्यांनी सांगितलं बैठकीत काय घडलं</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>५० हजार हक्काची घरे देण्यासाठी मिशन मोडवर काम करा -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : काेल्हापूर शहर हद्दवाढीची प्रक्रिया सुरू: प्रकाश आबिटकर ; मुख्यमंत्री, उपमुख्यमंत्री सकारात्मक</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154283/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-city-expansion-process-begins-cm-and-deputy-cm-supportive-abitkar-sdj87</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>विस्कळीत झालेली, १०२ रुग्णवाहिका सेवा पूर्ववत ?</t>
+          <t>Corona Cases In India : देशात कोरोनाची रुग्ण संख्या 257वर, तर राज्यात 53 कोरोना बाधित</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-says-102-ambulance-service-restored-mumbai-print-news-ocd-94-5228346/</t>
+          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>मावळ तालुक्यातील आरोग्य संस्थांना आवश्यक सुविधा द्या - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>Mahayuti News : 'स्थानिक'च्या निवडणुकीआधी महायुतीत नियुक्त्यांसाठी बिगफाईट; नेत्यांची डोकेदुखी वाढली...</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174701/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-leaders-lobby-for-kolhapur-dpdc-appointments-political-pressure-maharashtra-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>येत्या काळात आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरु करणार - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>राष्ट्रीय आरोग्य अभियानाअंतर्गत कंत्राटी कर्मचाऱ्यांना नियमित करण्यासाठी कार्यवाही करा – ग्रामविकास मंत्री जयकुमार गोरे</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165634/</t>
+          <t>https://mahasamvad.in/174852/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Pune News: प्रसुतीवेळी महिलेचा मृत्यू प्रकरणात आरोग्य मंत्र्यांचे कारवाईचे आदेश</t>
+          <t>आरोग्यमंत्री आबिटकर यांनी घेतले श्री विठ्ठल रुक्मिणी मातेचे दर्शन; VIP ट्रिटमेंट टाळत पायी जाणं केलं पसंत</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-health-minister-prakashrao-abitkar-orders-action-in-case-of-womans-death-during-childbirth-police-will-conduct-investigation-today-will-examine-cctv-along-with-statements-from-nurses-and-doctors-1352627</t>
+          <t>https://www.navarashtra.com/maharashtra/health-minister-prakash-abitkar-took-darshan-of-shri-vitthal-rukmini-mata-temple-899077.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Nandani Mahadevi Elephant : वनतारा सकारात्मक! नांदणी मठाची 'महादेवी' परत येण्याची शक्यता, पालकमंत्र्यांनी सांगितलं बैठकीत काय घडलं</t>
+          <t>Mahadevi Elephant : महादेवी हत्तीबाबत जिल्हाधिकारी कार्यालयात झालेल्या बैठकीवर पालकमंत्री आबिटकरांनी दिली सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-abitkar-shares-key-details-after-kolhapur-collector-office-meeting-on-mahadevi-elephant-issue-following-supreme-courts-controversial-order-srs92</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : काेल्हापूर शहर हद्दवाढीची प्रक्रिया सुरू: प्रकाश आबिटकर ; मुख्यमंत्री, उपमुख्यमंत्री सकारात्मक</t>
+          <t>'महापुराच्या परिस्थितीला योग्य पद्धतीने सामोरं जाणार आहोत', Prakash Abitkar on Kolhapur Rainfall</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-city-expansion-process-begins-cm-and-deputy-cm-supportive-abitkar-sdj87</t>
+          <t>https://sarkarnama.esakal.com/video/prakash-abitkar-kolhapur-rain-update-nrs96</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>अंधेरी येथील कामगार रुग्णालयातील आंतररुग्ण सुविधा नागरिकांसाठी उपलब्ध कराव्यात - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात 'नो शॉर्टेज, नो वेस्टेज' धोरण- मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168735/</t>
+          <t>https://mahasamvad.in/168889/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Mahayuti News : 'स्थानिक'च्या निवडणुकीआधी महायुतीत नियुक्त्यांसाठी बिगफाईट; नेत्यांची डोकेदुखी वाढली...</t>
+          <t>Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंचसाठी लगीनघाई; पुढील तीन दिवसात इमारतीचे हस्तांतरण, पालकमंत्र्यांकडून कामकाजाची पाहणी</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-leaders-lobby-for-kolhapur-dpdc-appointments-political-pressure-maharashtra-rm82-rg93</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Corona Cases In India : देशात कोरोनाची रुग्ण संख्या 257वर, तर राज्यात 53 कोरोना बाधित</t>
+          <t>वारसास्थळ यादीतील पन्हाळ्याचा समावेश अभिमानास्पद – आबिटकर</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
+          <t>https://www.loksatta.com/kolhapur/inclusion-of-panhala-in-the-heritage-site-list-is-a-matter-of-pride-says-prakash-abitkar-ssb-93-5224775/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>राष्ट्रीय आरोग्य अभियानाअंतर्गत कंत्राटी कर्मचाऱ्यांना नियमित करण्यासाठी कार्यवाही करा – ग्रामविकास मंत्री जयकुमार गोरे</t>
+          <t>Rural Housing Scheme : घरकुलांच्या उद्दिष्टपूर्तीत दिरंगाई नको ः प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174852/</t>
+          <t>https://agrowon.esakal.com/agro-special/no-delays-tolerated-in-housing-schemes-strict-action-warns-guardian-minister-mj18</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant : महादेवी हत्तीबाबत जिल्हाधिकारी कार्यालयात झालेल्या बैठकीवर पालकमंत्री आबिटकरांनी दिली सविस्तर माहिती</t>
+          <t>kolhapur |अत्याधुनिक सक्शन कम जेटिंग वाहनाचे पालकमंत्री आबिटकर यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-abitkar-shares-key-details-after-kolhapur-collector-office-meeting-on-mahadevi-elephant-issue-following-supreme-courts-controversial-order-srs92</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-inaugurates-advanced-suction-cum-jetting-vehicle-ap84</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>'महापुराच्या परिस्थितीला योग्य पद्धतीने सामोरं जाणार आहोत', Prakash Abitkar on Kolhapur Rainfall</t>
+          <t>चांगल्या कामाचा लोक सन्मान करतात : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/video/prakash-abitkar-kolhapur-rain-update-nrs96</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/rajarshi-shahu-awards-distributed-by-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात 'नो शॉर्टेज, नो वेस्टेज' धोरण- मंत्री प्रकाश आबिटकर</t>
+          <t>बांधकाम पूर्ण झालेली रुग्णालये कार्यान्वित करून जनतेच्या सेवेत आणावीत- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168889/</t>
+          <t>https://mahasamvad.in/168802/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंचसाठी लगीनघाई; पुढील तीन दिवसात इमारतीचे हस्तांतरण, पालकमंत्र्यांकडून कामकाजाची पाहणी</t>
+          <t>Chandrahar Patil: '...म्हणून चंद्रहार पाटलांनी ठाकरेंची साथ सोडली अन् शिंदेंच्या शिवसेनेत प्रवेश केला!'; 'या' मंत्र्यांचा मोठा दावा</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrahar-patil-switch-to-uddhav-thakceray-party-and-joining-eknath-shinde-shiv-sena-prakash-abitkar-big-claims-dk88</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>वारसास्थळ यादीतील पन्हाळ्याचा समावेश अभिमानास्पद – आबिटकर</t>
+          <t>Mahadevi Elephant: 'माधुरी' लवकरच परतणार? नेमके काय म्हणाले पालकमंत्री प्रकाश आबिटकर? वाचाच...</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/inclusion-of-panhala-in-the-heritage-site-list-is-a-matter-of-pride-says-prakash-abitkar-ssb-93-5224775/</t>
+          <t>https://www.navarashtra.com/maharashtra/minister-prakash-abitkar-said-about-madhuri-mahadevi-elepahnt-nandni-math-vantara-947644.html</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>इंदिरा गांधी रुग्णालयात सुविधा पुरवणार – प्रकाश आबिटकर</t>
+          <t>अनावश्यक गर्भाशय शस्त्रक्रिया करणाऱ्यांची गय करणार नाही, आरोग्य मंत्री प्रकाश आबिटकर यांचा इशारा</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-assures-new-facilities-at-indira-gandhi-hospital-ocd-94-5247730/</t>
+          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Rural Housing Scheme : घरकुलांच्या उद्दिष्टपूर्तीत दिरंगाई नको ः प्रकाश आबिटकर</t>
+          <t>बंधपत्रित वैद्यकीय अधिकाऱ्यांना ग्रामीण भागात सेवा देणे बंधनकारक - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/no-delays-tolerated-in-housing-schemes-strict-action-warns-guardian-minister-mj18</t>
+          <t>https://mahasamvad.in/154909/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>कोरोना आपल्यासोबतच राहणार: लोकांना पॅनिक होऊन देऊ नका, आरोग्यमंत्र्यांच्या प्रशासनाला सूचना; आज 105 नवीन रु...</t>
+          <t>Kolhapur Politics : 'खंडपीठ'साठी माणिक पाटलांचं आंदोलन; समजुतीसाठी भाजप अन् शिवसेनेचा पुढाकार, तर राष्ट्रवादी...</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-covid-cases-5-june-update-prakash-abitkar-instruction-to-health-administration-135173703.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-manik-patil-chuyekar-agitation-for-bench-court-was-stopped-in-the-presence-of-mp-dhananjay-mahadik-and-minister-prakashrao-abitkar-pp82-rg93</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>kolhapur |अत्याधुनिक सक्शन कम जेटिंग वाहनाचे पालकमंत्री आबिटकर यांच्या हस्ते लोकार्पण</t>
+          <t>कोल्हापूर खंडपीठ: १५ दिवसांत मुख्यमंत्र्यांसोबत भेट, पालकमंत्री आबिटकर यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-inaugurates-advanced-suction-cum-jetting-vehicle-ap84</t>
+          <t>https://www.lokmat.com/kolhapur/meeting-with-cm-in-15-days-for-kolhapur-bench-guardian-minister-prakash-abitkar-assurance-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>चांगल्या कामाचा लोक सन्मान करतात : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/rajarshi-shahu-awards-distributed-by-zilla-parishad-ap84</t>
+          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>अवयवदान पंधरवड्यास सुरुवात; आजपासून राज्यात जनजागृतीपर विविध उपक्रम</t>
+          <t>मेगा रक्तदान शिबिराचे आयोजन करू नये; राज्य रक्त संक्रमण परिषदेच्या रक्तपेढ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174294/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-health-department-prakash-abitkar-limits-mega-blood-donation-camps-mumbai-print-news-rds-00-5227011/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>बांधकाम पूर्ण झालेली रुग्णालये कार्यान्वित करून जनतेच्या सेवेत आणावीत- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>कोल्हापूरच्या तीर्थक्षेत्रांना निधी कमी पडू देणार नाही</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168802/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/eknath-shinde-promises-funds-for-kolhapur-pilgrimage-sites</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Chandrahar Patil: '...म्हणून चंद्रहार पाटलांनी ठाकरेंची साथ सोडली अन् शिंदेंच्या शिवसेनेत प्रवेश केला!'; 'या' मंत्र्यांचा मोठा दावा</t>
+          <t>Dr. Ashok Thorat : कोविड काळातील भ्रष्टाचार भोवला! बीड जिल्हा शल्य चिकित्सक अशोक थोरात यांचे निलंबन, प्रकाश आबिटकर यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrahar-patil-switch-to-uddhav-thakceray-party-and-joining-eknath-shinde-shiv-sena-prakash-abitkar-big-claims-dk88</t>
+          <t>https://www.esakal.com/maharashtra/beed-district-surgeon-dr-ashok-thorat-suspended-health-minister-prakash-abitkar-announcement-in-vidhansabha-ymk86</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant: 'माधुरी' लवकरच परतणार? नेमके काय म्हणाले पालकमंत्री प्रकाश आबिटकर? वाचाच...</t>
+          <t>कोल्हापूरसह पाच जिल्ह्यांत १८ रोजी ‘सर्किट बेंच’ प्रारंभाचा आनंदोत्सव</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/minister-prakash-abitkar-said-about-madhuri-mahadevi-elepahnt-nandni-math-vantara-947644.html</t>
+          <t>https://www.loksatta.com/kolhapur/mumbai-high-court-circuit-bench-kolhapur-for-five-districts-prakash-abitkar-informed-css-98-5294507/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात माणसाला बर्ड फ्लूची लागण? आरोग्यमंत्र्यांनी दिलं उत्तर</t>
+          <t>kolhapur Politics | पालकमंत्र्यांच्या तालुक्यातूनच महायुतीत बंडखोरीचे वारे</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/bird-flu-outbreak-in-maharastras-village-health-minister-gives-clarification-over-bird-flu/889578</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/ftii-to-deliver-film-making-courses-in-kolhapur-film-city-ap84-2</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री आबिटकर यांनी घेतले श्री विठ्ठल रुक्मिणी मातेचे दर्शन; VIP ट्रिटमेंट टाळत पायी जाणं केलं पसंत</t>
+          <t>Bandh: कोल्हापूर हद्दवाढीच्या विरोधात २० गावांत आज बंद; कृती समितीचा मंत्री आबिटकर, मुश्रीफांना इशारा</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/health-minister-prakash-abitkar-took-darshan-of-shri-vitthal-rukmini-mata-temple-899077.html</t>
+          <t>https://www.lokmat.com/kolhapur/20-villages-to-observe-bandh-today-against-kolhapur-boundary-extension-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्यातील रुग्णालयांत आता आरोग्य विशेषज्ञ, रुग्णांची सोय होणार</t>
+          <t>Sharangdhar Deshmukh : कोल्हापुरात कॉंग्रेसला खिंडार, माजी नगरसेवक करणार शिंदे सेनेत प्रवेश</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/hospitals-in-kolhapur-district-will-now-have-health-specialists-and-facilities-for-patients-a-a819-c746/</t>
+          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>अनावश्यक गर्भाशय शस्त्रक्रिया करणाऱ्यांची गय करणार नाही, आरोग्य मंत्री प्रकाश आबिटकर यांचा इशारा</t>
+          <t>Mahadevrao Mahadik : आप्पा महाडिकांनी दहीहंडी कार्यक्रमात आबिटकर, नरकेंशी केल्या कानगोष्टी; गोकुळ’ च्या राजकारणाला फुटणार उकळी, सतेज पाटलांचे काय?</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/during-kolhapur-dahi-handi-event-appa-mahadik-was-seen-whispering-with-prakash-abitkar-and-chandradeep-narke-political-temperature-around-gokul-dudh-sangh-may-rise-whats-satej-patils-move-srs92</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>बंधपत्रित वैद्यकीय अधिकाऱ्यांना ग्रामीण भागात सेवा देणे बंधनकारक - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>शाहू महाराजांच्या विचारांनी कोल्हापूरचे नाव उज्ज्वल करूया : पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154909/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/lets-glorify-kolhapur-with-shahu-maharajs-ideals-guardian-minister-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>कोल्हापूर खंडपीठ: १५ दिवसांत मुख्यमंत्र्यांसोबत भेट, पालकमंत्री आबिटकर यांचे आश्वासन</t>
+          <t>Free cancer vaccine: राज्यातील 0-14 वयोगटातील मुलींना कॅन्सरविरोधी फ्री लस; कधी मिळणार लस, पाहा!</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/meeting-with-cm-in-15-days-for-kolhapur-bench-guardian-minister-prakash-abitkar-assurance-a-a746/</t>
+          <t>https://saamtv.esakal.com/lifestyle/free-cancer-vaccine-for-girls-aged-0-14-in-the-state-check-when-it-will-be-available-sjk95</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : 'खंडपीठ'साठी माणिक पाटलांचं आंदोलन; समजुतीसाठी भाजप अन् शिवसेनेचा पुढाकार, तर राष्ट्रवादी...</t>
+          <t>Medical Recruitment 2025: मोठी बातमी! राज्यात डॉक्टरांची मेगाभरती, सरकारी नोकरीची सुवर्णसंधी; १,५०० जागा भरल्या जाणार</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-manik-patil-chuyekar-agitation-for-bench-court-was-stopped-in-the-presence-of-mp-dhananjay-mahadik-and-minister-prakashrao-abitkar-pp82-rg93</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
+          <t>शक्तिपीठ महामार्गावरून कोल्हापुरातील मंत्र्यांमधील मतभेद चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
+          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>कोल्हापूरची ओळख ‘मेडिकल हब’ होईल : पालकमंत्री आबिटकर</t>
+          <t>राज्य कामगार विमा सोसायटीच्या रुग्णालयांमधून दर्जेदार आरोग्य सुविधा द्याव्यात- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-will-become-medical-hub-guardian-minister-abitkar</t>
+          <t>https://mahasamvad.in/151861/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या तीर्थक्षेत्रांना निधी कमी पडू देणार नाही</t>
+          <t>Maharashtra Government: अपघातग्रस्त रुग्णांना मिळणार १ लाख रुपयांपर्यंत कॅशलेस उपचार, फडणवीस सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/eknath-shinde-promises-funds-for-kolhapur-pilgrimage-sites</t>
+          <t>https://saamtv.esakal.com/maharashtra/fadnavis-governments-big-move-maharashtra-govt-approves-rs-1-lakh-cashless-treatment-for-accident-victims-pvm91</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>मेगा रक्तदान शिबिराचे आयोजन करू नये; राज्य रक्त संक्रमण परिषदेच्या रक्तपेढ्यांना निर्देश</t>
+          <t>Kolhapur politics : कारे दुरावा कारे अबोला! मंत्री आबिटकर-मुश्रीफ यांच्यातील नाराजी उघड, बँकेच्या अहवालात पालकमंत्र्यांचा फोटोच नाही</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-health-department-prakash-abitkar-limits-mega-blood-donation-camps-mumbai-print-news-rds-00-5227011/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/tension-between-ministers-abitkar-and-mushrif-continues-guardian-minister-prakashrao-abitkars-photo-missing-from-kdcc-bank-report-book-srs92</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Dr. Ashok Thorat : कोविड काळातील भ्रष्टाचार भोवला! बीड जिल्हा शल्य चिकित्सक अशोक थोरात यांचे निलंबन, प्रकाश आबिटकर यांची विधानसभेत घोषणा</t>
+          <t>Gokul Election : विधानसभा, लोकसभेचे उट्टे 'गोकुळ'मध्ये निघणार; मुश्रीफ-सतेज यांची कोंडी, आबिटकर-मंडलिकांसह नरके ठरणार निर्णायक</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/beed-district-surgeon-dr-ashok-thorat-suspended-health-minister-prakash-abitkar-announcement-in-vidhansabha-ymk86</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/gokul-dudh-sangh-president-election-hasan-mushrif-satej-patil-prakash-abitkar-sanjay-mandlik-role-important-bam92</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>कोल्हापूरसह पाच जिल्ह्यांत १८ रोजी ‘सर्किट बेंच’ प्रारंभाचा आनंदोत्सव</t>
+          <t>Kolhapur : कोल्हापूरच्या हद्दवाढीसाठी शासनाची पुढची स्टेप, पालकमंत्री आबिटकरांनी कायदेशीर त्रुटी दूर करण्यावर दिला भर</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/mumbai-high-court-circuit-bench-kolhapur-for-five-districts-prakash-abitkar-informed-css-98-5294507/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/governments-next-step-for-kolhapur-boundary-expansion-guardian-minister-abitkar-emphasizes-on-removing-legal-loopholes-srs92</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री-खंडपीठ कृती समिती यांच्यात लवकरच मुंबईत बैठक</t>
+          <t>प्रकाश आबिटकर यांची माहिती, दोन हजार पदनिर्मितीसाठी शासनाची मान्यता</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/meeting-between-chief-minister-and-khandepeeth-action-committee-to-be-held-soon-in-mumbai-ap84</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>kolhapur Politics | पालकमंत्र्यांच्या तालुक्यातूनच महायुतीत बंडखोरीचे वारे</t>
+          <t>मंगेशकर रुग्णालय प्रकरणात कारवाई लवकरच; आरोग्यमंत्री आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/ftii-to-deliver-film-making-courses-in-kolhapur-film-city-ap84-2</t>
+          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>१०० जेसीबीमधून उपमुख्यमंत्री एकनाथ शिंदे यांच्यावर होणार फुलांची उधळण !</t>
+          <t>आरोग्य मंत्री प्रकाश आबिटकर यांनी घेतली अवयवादानाची शपथ</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/100-jcbs-to-shower-flowers-on-deputy-cm-eknath-shinde</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Sharangdhar Deshmukh : कोल्हापुरात कॉंग्रेसला खिंडार, माजी नगरसेवक करणार शिंदे सेनेत प्रवेश</t>
+          <t>आदर्श गोठा अभियानाच्या धर्तीवर आता जिल्ह्यात स्वच्छ - सुंदर घर अभियान -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
+          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Mahadevrao Mahadik : आप्पा महाडिकांनी दहीहंडी कार्यक्रमात आबिटकर, नरकेंशी केल्या कानगोष्टी; गोकुळ’ च्या राजकारणाला फुटणार उकळी, सतेज पाटलांचे काय?</t>
+          <t>Maharashtra | रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात ‘नो शॉर्टेज, नो वेस्टेज’ धोरण - आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/during-kolhapur-dahi-handi-event-appa-mahadik-was-seen-whispering-with-prakash-abitkar-and-chandradeep-narke-political-temperature-around-gokul-dudh-sangh-may-rise-whats-satej-patils-move-srs92</t>
+          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्याला प्रथमच 2 पालकमंत्री</t>
+          <t>मोठी बातमी! राज्यात 1500 डॉक्टरांची भरती होणार, 10 एप्रिल रोजी जाहिरात निघणार</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-district-gets-2-guardian-ministers-for-the-first-time</t>
+          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>शाहू महाराजांच्या विचारांनी कोल्हापूरचे नाव उज्ज्वल करूया : पालकमंत्री आबिटकर</t>
+          <t>राज्यातील कोरोना रूग्णांच्या संख्येत वाढ; आरोग्यमंत्री आबिटकरांनी दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/lets-glorify-kolhapur-with-shahu-maharajs-ideals-guardian-minister-abitkar-ap84</t>
+          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Free cancer vaccine: राज्यातील 0-14 वयोगटातील मुलींना कॅन्सरविरोधी फ्री लस; कधी मिळणार लस, पाहा!</t>
+          <t>Prakash Abitkar : 4 कर्करोग रुग्णालयांची निर्मिती करणार; आरोग्यमंत्री प्रकाश आबिटकर यांनी केले जाहीर</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/lifestyle/free-cancer-vaccine-for-girls-aged-0-14-in-the-state-check-when-it-will-be-available-sjk95</t>
+          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Medical Recruitment 2025: मोठी बातमी! राज्यात डॉक्टरांची मेगाभरती, सरकारी नोकरीची सुवर्णसंधी; १,५०० जागा भरल्या जाणार</t>
+          <t>आरोग्य मंत्री Prakash Abitkar यांच्याकडून अवयवादानाची शपथ, राज्यात जनजागृतीपर विविध उपक्रम</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/health-minister-prakash-abitkar-takes-oath-for-organ-donation-various-awareness-activities-in-the-state/128039/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्गावरून कोल्हापुरातील मंत्र्यांमधील मतभेद चव्हाट्यावर</t>
+          <t>Kolhapur City Extension : हद्दवाढ नाही तर निवडणूक नाही, कोल्हापूरची कृती समिती आक्रमक</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-shahar-haddavad-samiti-warns-against-municipal-election-without-boundary-extension-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा सोसायटीच्या रुग्णालयांमधून दर्जेदार आरोग्य सुविधा द्याव्यात- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>मोठी बातमी : सतेज पाटील आणि महाडिक यांच्यात पहिल्यांदाच एकमत, दोघेही एकाच फ्रेममध्ये!</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151861/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Maharashtra Government: अपघातग्रस्त रुग्णांना मिळणार १ लाख रुपयांपर्यंत कॅशलेस उपचार, फडणवीस सरकारचा मोठा निर्णय</t>
+          <t>येरवडा रुग्णालयातून '11 लाखांची अंतर्वस्त्रे गायब,' चौकशी समितीच्या अहवालातून कोणता घोटाळा समोर आलाय?</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/fadnavis-governments-big-move-maharashtra-govt-approves-rs-1-lakh-cashless-treatment-for-accident-victims-pvm91</t>
+          <t>https://www.bbc.com/marathi/articles/c93n25pxqe1o</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Kolhapur politics : कारे दुरावा कारे अबोला! मंत्री आबिटकर-मुश्रीफ यांच्यातील नाराजी उघड, बँकेच्या अहवालात पालकमंत्र्यांचा फोटोच नाही</t>
+          <t>Almatti Dam Height : अलमट्टी उंची बाबत 15 दिवसांनी सर्व पक्षीयांसह पुन्हा बैठक आंदोलक आणि</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/tension-between-ministers-abitkar-and-mushrif-continues-guardian-minister-prakashrao-abitkars-photo-missing-from-kdcc-bank-report-book-srs92</t>
+          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>kolhapur | पालकमंत्र्यांकडे जाणार्‍या फायली सहपालकमंत्र्यांमार्फत</t>
+          <t>लाडक्या बहिणीनंतर मुलींसाठी सरकारची मोठी घोषणा, 14 वर्षांपर्यंत मुलींना मोफत मिळणार ही गोष्ट</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shinde-shiv-sena-vs-bjp-kolhapur-political-clash-ap84</t>
+          <t>https://www.tv9marathi.com/maharashtra/pune/maharashtra-government-to-provide-free-cancer-vaccine-for-girl-1358923.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापूरच्या हद्दवाढीसाठी शासनाची पुढची स्टेप, पालकमंत्री आबिटकरांनी कायदेशीर त्रुटी दूर करण्यावर दिला भर</t>
+          <t>नांदणी मठाची 'माधुरी' परत येणार? वनताराचे CEO म्हणाले, कोल्हापूरकरांना सर्व सहकार्य</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/governments-next-step-for-kolhapur-boundary-expansion-guardian-minister-abitkar-emphasizes-on-removing-legal-loopholes-srs92</t>
+          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर यांची माहिती, दोन हजार पदनिर्मितीसाठी शासनाची मान्यता</t>
+          <t>Pune Deenanath Mangeshkar Hospital Highlights: भाजपा कार्यकर्त्यांकडून डॉ. सुश्रुत घैसास यांच्या भावाच्या घराची तोडफोड</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
+          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>मंगेशकर रुग्णालय प्रकरणात कारवाई लवकरच; आरोग्यमंत्री आबिटकर यांची माहिती</t>
+          <t>Nanded News : धक्कादायक! नांदेडच्या शासकीय ग्रामीण रुग्णालयात उंदरांचं साम्राज्य, चक्क</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>महाराष्ट्र सरकार का बड़ा फैसला, 0-14 साल की लड़कियों को मिलेगी मुफ्त कैंसर वैक्सीन</t>
+          <t>Shaktipeeth Expressway च्या भूसंपादनाला मंजुरी अन् 20 हजार कोटींची तरतूद, कोणत्या जिल्ह्यांमधून जाणार...</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री प्रकाश आबिटकर यांनी घेतली अवयवादानाची शपथ</t>
+          <t>Maharashtra Breaking LIVE: देश-विदेशातील महत्त्वाच्या घडामोडींचा आढावा फक्त एका क्लिकवर...</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>आदर्श गोठा अभियानाच्या धर्तीवर आता जिल्ह्यात स्वच्छ - सुंदर घर अभियान -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>प्रकाश आबिटकर आणि जयकुमार गोरे यांचे आदेश, कंत्राटी कर्मचाऱ्यांना नियमित करा</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
+          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Maharashtra | रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात ‘नो शॉर्टेज, नो वेस्टेज’ धोरण - आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : घाबरून न जाऊ नका, लोकांना पॅनिक करू नका – आरोग्यमंत्री अबिटकर</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
+          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>मोठी बातमी! राज्यात 1500 डॉक्टरांची भरती होणार, 10 एप्रिल रोजी जाहिरात निघणार</t>
+          <t>Prakash Abitkar | Corona ला घाबरून न जाऊ नका, लोकांना पॅनिक करू नका : आरोग्यमंत्री</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>राज्यातील कोरोना रूग्णांच्या संख्येत वाढ; आरोग्यमंत्री आबिटकरांनी दिली महत्त्वाची अपडेट</t>
+          <t>Shaktipeeth Highway : सांगली, हिंगोलीसह 10 जिल्ह्यात शक्तीपीठ महामार्गाला कडवा विरोध; कोल्हापुरबाबत पालकमंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-minister-prakash-abitkar-confirms-cancellation-of-shaktipeeth-highway-as11</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 4 कर्करोग रुग्णालयांची निर्मिती करणार; आरोग्यमंत्री प्रकाश आबिटकर यांनी केले जाहीर</t>
+          <t>शक्तिपीठ महामार्गास 2 मंत्र्यांचा विरोध, मंत्रिमंडळ बैठकीत पडसाद राजू शेट्टी</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
+          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>राज्याच्या इतिहासात पहिल्यांदाच 'आरोग्य विषयक धोरण' : मंत्री प्रकाश आबिटकर -</t>
+          <t>Maharashtra: Beed Surgeon Suspended For 'Embezzling Crores In Medicine Procurement During COVID-19'</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>दीनानाथ मंगेशकर रुग्णालयावर कारवाई कधी? आरोग्य मंत्री प्रकाश आबिटकर यांनी दिले उत्तर</t>
+          <t>Lack of voluntary blood donations help ‘red market’ thrive</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-said-about-the-action-taken-by-dinanath-hospital-1387152.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Kolhapur City Extension : हद्दवाढ नाही तर निवडणूक नाही, कोल्हापूरची कृती समिती आक्रमक</t>
+          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की लड़कियों को फ्री में दी जाएगी कैंसर की वैक्सीन</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-shahar-haddavad-samiti-warns-against-municipal-election-without-boundary-extension-as11-rg93</t>
+          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>मोठी बातमी : सतेज पाटील आणि महाडिक यांच्यात पहिल्यांदाच एकमत, दोघेही एकाच फ्रेममध्ये!</t>
+          <t>फडणवीस सरकार की 20,787 करोड़ रुपये की मंजूरी, तैयार होगा नागपुर-गोवा शक्तिपीठ एक्सप्रेसवे!</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
+          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>येरवडा रुग्णालयातून '11 लाखांची अंतर्वस्त्रे गायब,' चौकशी समितीच्या अहवालातून कोणता घोटाळा समोर आलाय?</t>
+          <t>Central team focuses on source, diagnosis amid GBS cases surge | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/articles/c93n25pxqe1o</t>
+          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Almatti Dam Height : अलमट्टी उंची बाबत 15 दिवसांनी सर्व पक्षीयांसह पुन्हा बैठक आंदोलक आणि</t>
+          <t>GBS Outbreak: First fatality confirmed in Pune as cases surge</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
+          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणीनंतर मुलींसाठी सरकारची मोठी घोषणा, 14 वर्षांपर्यंत मुलींना मोफत मिळणार ही गोष्ट</t>
+          <t>खौफनाक: महाराष्ट्र में एक जिले में 14000 महिलाओं में मिले कैंसर के लक्षण, क्या बोले स्वास्थ्य मंत्री?</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/pune/maharashtra-government-to-provide-free-cancer-vaccine-for-girl-1358923.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>नांदणी मठाची 'माधुरी' परत येणार? वनताराचे CEO म्हणाले, कोल्हापूरकरांना सर्व सहकार्य</t>
+          <t>State to bring all diagnostic labs under health dept’s purview</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Pune Deenanath Mangeshkar Hospital Highlights: भाजपा कार्यकर्त्यांकडून डॉ. सुश्रुत घैसास यांच्या भावाच्या घराची तोडफोड</t>
+          <t>No one has to worry, says Maharashtra Health Minister Abitkar on HMPV</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
+          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Nanded News : धक्कादायक! नांदेडच्या शासकीय ग्रामीण रुग्णालयात उंदरांचं साम्राज्य, चक्क</t>
+          <t>Maharashtra Accident Victims: Cashless Treatment up to Rs 1 Lakh in Emergency Hospitals</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
+          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway च्या भूसंपादनाला मंजुरी अन् 20 हजार कोटींची तरतूद, कोणत्या जिल्ह्यांमधून जाणार...</t>
+          <t>Statewide awareness campaign on organ donation from Aug 3 to 15</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking LIVE: देश-विदेशातील महत्त्वाच्या घडामोडींचा आढावा फक्त एका क्लिकवर...</t>
+          <t>Maharashtra cabinet approves Mahalaxmi &amp; Jotiba temple development plans</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर आणि जयकुमार गोरे यांचे आदेश, कंत्राटी कर्मचाऱ्यांना नियमित करा</t>
+          <t>One Day for Farmer initiative implemented in Kolhapur district</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : घाबरून न जाऊ नका, लोकांना पॅनिक करू नका – आरोग्यमंत्री अबिटकर</t>
+          <t>Maharashtra: Child Health Drive Faces Backlash Over Unpaid RBSK Medical Teams</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
+          <t>https://www.thebridgechronicle.com/news/maharashtra-child-health-drive-faces-backlash-over-unpaid-rbsk-medical-teams</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Prakash Abitkar | Corona ला घाबरून न जाऊ नका, लोकांना पॅनिक करू नका : आरोग्यमंत्री</t>
+          <t>Maha to accredit private hospitals under Health Tourism Policy</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Shaktipeeth Highway : सांगली, हिंगोलीसह 10 जिल्ह्यात शक्तीपीठ महामार्गाला कडवा विरोध; कोल्हापुरबाबत पालकमंत्र्यांनी दिले संकेत</t>
+          <t>Maharashtra To Launch Statewide Organ Donation Drive From August 3 To 15</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-minister-prakash-abitkar-confirms-cancellation-of-shaktipeeth-highway-as11</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-launch-statewide-organ-donation-drive-from-august-3-to-15</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Mangeshkar Hospital: मंगेशकर रुग्णालय प्रकरणी कारवाई कधी होणार? आरोग्यमंत्री अबिटकर यांनी स्पष्ट सांगितलं</t>
+          <t>Pune: Yerawada Mental Hospital Extends OPD Timing Till 5PM</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/mangeshkar-hospital-controversy-health-minister-prakash-abitkar-statement-about-action-aau85</t>
+          <t>https://www.freepressjournal.in/pune/pune-yerawada-mental-hospital-extends-opd-timing-till-5pm</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्गास 2 मंत्र्यांचा विरोध, मंत्रिमंडळ बैठकीत पडसाद राजू शेट्टी</t>
+          <t>Mushrif appeals to Gokul chairman Arun Dongale to resign</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Maharashtra: Beed Surgeon Suspended For 'Embezzling Crores In Medicine Procurement During COVID-19'</t>
+          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>First death linked to Guillain-Barré syndrome in Solapur as Pune cases rise to 110</t>
+          <t>Spell out measures taken to prevent children deaths in Maharashtra: NCP (SP) to govt | Latest News India</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://english.mathrubhumi.com/news/india/first-death-linked-to-guillain-barre-syndrome-in-solapur-6faa62a2</t>
+          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Lack of voluntary blood donations help ‘red market’ thrive</t>
+          <t>Health dept to focus on doorstep services amid Covid cases, monsoon</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>मुंबई में कोरोना के 53 मरीज मिले, दो संक्रमितों की मौत, स्वास्थ्य मंत्री बोले- सरकार अलर्ट मोड पर है</t>
+          <t>With 1.6L units till May, Pune dist ahead in blood donation so far this year</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/new-corona-cases-in-mumbai-two-died-maharashtra-government-on-alert-mode-19611659</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की लड़कियों को फ्री में दी जाएगी कैंसर की वैक्सीन</t>
+          <t>Maharashtra: Thousands Join Silent March In Kolhapur To Demand Return Of Elephant Mahadevi From Vantara</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-thousands-join-silent-march-in-kolhapur-to-demand-return-of-elephant-mahadevi-from-vantara-video</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार की 20,787 करोड़ रुपये की मंजूरी, तैयार होगा नागपुर-गोवा शक्तिपीठ एक्सप्रेसवे!</t>
+          <t>One more decision of Shiv Sena ex-min Tanaji Sawant clouded by controversy</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Central team focuses on source, diagnosis amid GBS cases surge | Latest News India - Hindustan Times</t>
+          <t>How the transfer of an elephant in Kolhapur led to a boycott of Jio</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
+          <t>https://indianexpress.com/article/cities/pune/how-the-transfer-of-an-elephant-in-kolhapur-led-to-a-boycott-of-jio-10164145/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>GBS Outbreak: First fatality confirmed in Pune as cases surge</t>
+          <t>Guillain-Barré Syndrome: An explainer as cases are on the rise in Maharashtra</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
+          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>खौफनाक: महाराष्ट्र में एक जिले में 14000 महिलाओं में मिले कैंसर के लक्षण, क्या बोले स्वास्थ्य मंत्री?</t>
+          <t>Deenanath Mangeshkar Hospital Controversy Deepens</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
+          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>No one has to worry, says Maharashtra Health Minister Abitkar on HMPV</t>
+          <t>Deenanath Mangeshkar Hospital Under Fire: BJP MLC’s PA’s Wife......</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
+          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy-pregnant-woman-death</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Maharashtra Accident Victims: Cashless Treatment up to Rs 1 Lakh in Emergency Hospitals</t>
+          <t>People staying within 100m periphery of Panhala fort fear displacement</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Maharashtra cabinet approves Mahalaxmi &amp; Jotiba temple development plans</t>
+          <t>The Controversy of Mahadevi: A 36-Year-Old Elephant's Journey from Kolhapur to Gujarat</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3526640-the-controversy-of-mahadevi-a-36-year-old-elephants-journey-from-kolhapur-to-gujarat</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>One Day for Farmer initiative implemented in Kolhapur district</t>
+          <t>Guillain Barre: मुंबई में पहला संदिग्ध जीबीएस केस आया सामने, जानें कैसे करें इससे बचाव</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
+          <t>https://ndtv.in/health/1st-suspected-gbs-case-surfaced-in-mumbai-know-how-to-prevent-it-7662749</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Maharashtra: Child Health Drive Faces Backlash Over Unpaid RBSK Medical Teams</t>
+          <t>महाराष्ट्र-कर्नाटक सीमा विवाद अब होगा हल! राज्य सरकार ने विपक्ष संग समिति का किया पुनर्गठन</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/maharashtra-child-health-drive-faces-backlash-over-unpaid-rbsk-medical-teams</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-government-reconstitutes-committee-resolve-border-dispute-karnataka-1260125.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Maha to accredit private hospitals under Health Tourism Policy</t>
+          <t>शिंदे-दादा के क्षेत्र में सर्वाधिक फर्जी लाडली बहनें!</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
+          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Maharashtra To Launch Statewide Organ Donation Drive From August 3 To 15</t>
+          <t>Assembly election losers from MVA first pick in Mahayuti poaching spree</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-launch-statewide-organ-donation-drive-from-august-3-to-15</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Pune: Yerawada Mental Hospital Extends OPD Timing Till 5PM</t>
+          <t>Kolhapur politics : वडील उद्धव ठाकरेंसोबत तर मुलगा मात्र अजित पवारांच्या राष्ट्रवादीच्या स्टेजवर; कोल्हापूरचं हटके राजकारण!</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-yerawada-mental-hospital-extends-opd-timing-till-5pm</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-kp-patil-with-uddhav-thackeray-son-ranjit-patil-on-ajit-pawar-stage-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>JP Nadda Launches National Mass Drug Administration Round for Elimination of Lymphatic Filariasis</t>
+          <t>‘पुढारी’कार डॉ. ग. गो. जाधव यांना अभिवादन</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/jp-nadda-launches-national-mass-drug-administration-round-for-elimination-of-lymphatic-filariasis/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/greetings-to-pudhari-dr-g-g-jadhav-ap84</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Mushrif appeals to Gokul chairman Arun Dongale to resign</t>
+          <t>तुमच्यात काही मतभेद असतील तर सांगा, मी मिटवतो ! शाहू महाराजांची कोपरखळी, शिवसेना नेत्यांनाही हसू आवरेना</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
+          <t>https://maharashtranews1.com/If-there-are-any-disagreements-among-you--tell-me--and-I-will-resolve-them--Shahu-Maharaj-s-jab-even-made-the-Shiv-Sena-leaders-unable-to-contain-their-laughter-</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
+          <t>Maharashtra Government To Provide Free Cancer Vaccine For Girls Aged 0-14</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-7825621</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Spell out measures taken to prevent children deaths in Maharashtra: NCP (SP) to govt | Latest News India</t>
+          <t>Maharashtra Expands Cashless Treatment For Accident Victims Up To ₹1 Lakh</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-expands-cashless-treatment-for-accident-victims-up-to-1-lakh</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Health dept to focus on doorstep services amid Covid cases, monsoon</t>
+          <t>Kolhapur Politics : कोल्हापुरचं राजकारण फिरवणारे बंटी पाटील एकटे कसे पडले? 'घात' कुठे झाला?</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-satej-patil-political-isolation-hasan-mushrif-chandradeep-narke-defection-congress-maharashtra-hn97</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>With 1.6L units till May, Pune dist ahead in blood donation so far this year</t>
+          <t>Maharashtra Guardian Ministers List : तीन नेत्यांकडे सहा जिल्हे, कोल्हापूर अन् मुंबईसाठी दोन -दोन कारभारी,</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Maharashtra: Thousands Join Silent March In Kolhapur To Demand Return Of Elephant Mahadevi From Vantara</t>
+          <t>Kolhapur Politics: दोन कट्टर राजकीय विरोधक एका प्रश्नावर आले एकत्र!</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-thousands-join-silent-march-in-kolhapur-to-demand-return-of-elephant-mahadevi-from-vantara-video</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-mla-satej-patil-mla-amal-mahadik-kolhapur-airport-road-meeting-guardian-minister-prakash-abitkar-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>One more decision of Shiv Sena ex-min Tanaji Sawant clouded by controversy</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 24 जून 2025 | मंगळवार</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
+          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>How the transfer of an elephant in Kolhapur led to a boycott of Jio</t>
+          <t>Kolhapur Politics : अखेर 80 वर्षांच्या के. पी. पाटलांना अजितदादांनी स्वीकारलंच: पक्षप्रवेशासाठी कोल्हापूरमध्ये जंगी मेळावा</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/how-the-transfer-of-an-elephant-in-kolhapur-led-to-a-boycott-of-jio-10164145/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-mla-kp-patil-joins-ncp-ajit-pawar-kolhapur-visit-may-23-hn97</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome: An explainer as cases are on the rise in Maharashtra</t>
+          <t>Rahul Patil: काँग्रेस निष्ठावंतांचे पुत्र हाती घड्याळ बांधणार, करवीरचे राहुल पाटील राष्ट्रवादीत?</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-congress-leader-rahul-patil-to-join-ncp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Deenanath Mangeshkar Hospital Controversy Deepens</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 1 जून 2025 | रविवार</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Deenanath Mangeshkar Hospital Under Fire: BJP MLC’s PA’s Wife......</t>
+          <t>Agriculture University: कृषी विद्यापीठांचा फजितवाडा</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy-pregnant-woman-death</t>
+          <t>https://agrowon.esakal.com/sampadkiya/the-dilemma-of-agricultural-universities-article-on-agrowon-rat16</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>People staying within 100m periphery of Panhala fort fear displacement</t>
+          <t>Kolhapur Corona Update : महाराष्ट्राच्या आरोग्याची चावी हाती असलेल्या दोन मंत्र्यांच्या कोल्हापुरात</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>The Controversy of Mahadevi: A 36-Year-Old Elephant's Journey from Kolhapur to Gujarat</t>
+          <t>LMOTY 2025: हे चेहरे गाजवणार महाराष्ट्राचं पुढचं राजकारण; कोण ठरणार प्रॉमिसिंग राजकारणी?</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3526640-the-controversy-of-mahadevi-a-36-year-old-elephants-journey-from-kolhapur-to-gujarat</t>
+          <t>https://www.lokmat.com/maharashtra/lokmat-maharashtrian-of-the-year-awards-2025-here-are-the-nominations-for-promising-politician-category-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Guillain Barre: मुंबई में पहला संदिग्ध जीबीएस केस आया सामने, जानें कैसे करें इससे बचाव</t>
+          <t>Chandrahar Patil : चंद्रहार पाटील यांचे अखेर ठरले, ठाकरे सेनेला रामराम, सरकारसोबत जाणार; सांगलीच्या राजकारणात नवा ट्विस्ट</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://ndtv.in/health/1st-suspected-gbs-case-surfaced-in-mumbai-know-how-to-prevent-it-7662749</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway: शक्तिपीठ एक्सप्रेसवे के खिलाफ सड़क पर उतरे किसान, फडणवीस ने विधानसभा में गिनाए महामार्ग के फायदे-नुकसान</t>
+          <t>Kolhapur : कोल्हापुरात एकनाथ शिंदेंची 'जादू', एकाच वेळी काँग्रेस-भाजप आणि ताराराणी</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>महाराष्ट्र-कर्नाटक सीमा विवाद अब होगा हल! राज्य सरकार ने विपक्ष संग समिति का किया पुनर्गठन</t>
+          <t>Kolhapur APMC election | सभापती निवडीत पालकमंत्र्यांची एंट्री</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-government-reconstitutes-committee-resolve-border-dispute-karnataka-1260125.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-ministers-entry-in-kolhapur-agricultural-produce-market-committee-chairman-election-ap84</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Assembly election losers from MVA first pick in Mahayuti poaching spree</t>
+          <t>Gokul President Election : कोल्हापुरच्या राजकारणात मुश्रीफांची ताकद वाढली; जिल्हा बँक आणि गोकुळवर पितापुत्रांचं 'वर्चस्व', वाचा महिनाभरात काय काय घडलं?</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>‘पुढारी’कार डॉ. ग. गो. जाधव यांना अभिवादन</t>
+          <t>Chandrahar Patil : उद्धव ठाकरेंना मोठा धक्का! डबल महाराष्ट्र केसरी चंद्रहार पाटील आज शिंदेंच्या शिवसेनेत प्रवेश करणार</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/greetings-to-pudhari-dr-g-g-jadhav-ap84</t>
+          <t>https://www.lokshahi.com/maharashtra/lokshahi-politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>तुमच्यात काही मतभेद असतील तर सांगा, मी मिटवतो ! शाहू महाराजांची कोपरखळी, शिवसेना नेत्यांनाही हसू आवरेना</t>
+          <t>Almatty Dam : कर्नाटक भाजपचे महाराष्ट्राविरोधात वाकडे पाऊल, अलमट्टी धरणाची उंची वाढवण्यासाठी केंद्रीय मंत्र्यांच्या गाठीभेटी, वाद चिघळणार?</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/If-there-are-any-disagreements-among-you--tell-me--and-I-will-resolve-them--Shahu-Maharaj-s-jab-even-made-the-Shiv-Sena-leaders-unable-to-contain-their-laughter-</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/almatti-dam-height-increase-karnataka-bjp-mps-maharashtra-flood-risk-dispute-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Maharashtra Expands Cashless Treatment For Accident Victims Up To ₹1 Lakh</t>
+          <t>Almatti dam height : ‘आलमट्टी’वरून राजकीय वातावरण तापलं ; जलसंपदा मंत्री विखे पुन्हा घेणार सर्वपक्षीय बैठक!</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-expands-cashless-treatment-for-accident-victims-up-to-1-lakh</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/radhakrishna-vikhe-patil-to-hold-all-party-meeting-on-almatti-dam-height-water-dispute-maharashtra-karnataka-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : कोल्हापुरचं राजकारण फिरवणारे बंटी पाटील एकटे कसे पडले? 'घात' कुठे झाला?</t>
+          <t>Devendra Fadnavis : 'माधुरी'चा प्रश्न मार्गी लागणार? मंत्रिमंडळाच्या बैठकीत मुख्यमंत्री देवेंद्र फडणवीस यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-satej-patil-political-isolation-hasan-mushrif-chandradeep-narke-defection-congress-maharashtra-hn97</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers List : तीन नेत्यांकडे सहा जिल्हे, कोल्हापूर अन् मुंबईसाठी दोन -दोन कारभारी,</t>
+          <t>Maharashtra Guardian Ministers List : पालकमंत्र्यांची यादी जाहीर, बीड आणि पुण्याबाबत सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Kolhapur Politics: दोन कट्टर राजकीय विरोधक एका प्रश्नावर आले एकत्र!</t>
+          <t>Maharashtra Live Blog: माळेगाव सहकारी कारखाना निवडणुकीच्या मतमोजणीच्या प्रत्येक क्षणाचे वेगवान अपडेटस्, शरद पव</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-mla-satej-patil-mla-amal-mahadik-kolhapur-airport-road-meeting-guardian-minister-prakash-abitkar-mm76-rg93</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-beed-santosh-deshmukh-case-maharashtra-politics-malegaon-sahakari-sakhar-karkhana-election-2025-1365817</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : अखेर 80 वर्षांच्या के. पी. पाटलांना अजितदादांनी स्वीकारलंच: पक्षप्रवेशासाठी कोल्हापूरमध्ये जंगी मेळावा</t>
+          <t>Maharashtra Karnataka Border Dispute: सीमाप्रश्नी उच्चाधिकार समितीची पुनर्रचना</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-mla-kp-patil-joins-ncp-ajit-pawar-kolhapur-visit-may-23-hn97</t>
+          <t>https://agrowon.esakal.com/agro-special/reorganization-of-the-high-power-committee-on-border-issues-rat16</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 24 जून 2025 | मंगळवार</t>
+          <t>Maharashta Gurdian Ministers Full List : मुंबई ते गडचिरोली, बीड ते नागपूर, तुमच्या जिल्ह्याचा पालकमंत्री</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Gokul Politics : गोकुळमध्ये पुन्हा संघर्ष? वाढवलेल्या ठरावांचा नेता कोण? घमासान होण्याची चिन्हे</t>
+          <t>महादेवी हत्तीणीला परत आणण्यासाठी राज्य सरकार उचलणार मोठं पाऊल; मुख्यमंत्री देवेंद्र फडणवीसांनी सगळच सांगितलं</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/the-impact-of-1800-new-members-in-gokul-dairy-union-depends-on-upcoming-alliance-between-mahayuti-or-mva-as11-rg93</t>
+          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Hasan Mushrif : हसन मुश्रीफांना कोल्हापूर न देण्यामागचं कारण, दोस्ताना आला अंगलट?</t>
+          <t>India reports 2 more deaths from Guillain-Barre Syndrome, raising total to 3</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/why-hasan-mushrif-not-appointed-as-kolhapur-guardian-minister-as11-rg93</t>
+          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 1 जून 2025 | रविवार</t>
+          <t>More that 12k children died in Maharashtra between Apr last year and Feb 2025: Minister</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Rahul Patil: काँग्रेस निष्ठावंतांचे पुत्र हाती घड्याळ बांधणार, करवीरचे राहुल पाटील राष्ट्रवादीत?</t>
+          <t>Maharashtra govt to set up vigilance cells to stop illegal uterus removals among cane cutters</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-congress-leader-rahul-patil-to-join-ncp-mm76-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Agriculture University: कृषी विद्यापीठांचा फजितवाडा</t>
+          <t>Nurses’ strike leaves Sassoon wards deserted, administration struggles to find replacements</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/sampadkiya/the-dilemma-of-agricultural-universities-article-on-agrowon-rat16</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : मुख्यमंत्री देवेंद्र फडणवीस, शरद पवार एकाच समितीत, नेमकं काय काम करणार ?</t>
+          <t>Kolhapur celebrates I-Day, Janmashtami &amp; Dahi Handi</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/devendra-fadnavis-sharad-pawar-narayan-rane-prithvira-chavan-on-committee-to-resolve-maharashtra-karnataka-border-dispute-rm89</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Chandrahar Patil : चंद्रहार पाटील यांचे अखेर ठरले, ठाकरे सेनेला रामराम, सरकारसोबत जाणार; सांगलीच्या राजकारणात नवा ट्विस्ट</t>
+          <t>ZTCC, health minister honours families of deceased donors</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापुरात एकनाथ शिंदेंची 'जादू', एकाच वेळी काँग्रेस-भाजप आणि ताराराणी</t>
+          <t>Kolhapur IT Park &amp; employment initiatives announced at district investment summit</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Kolhapur APMC election | सभापती निवडीत पालकमंत्र्यांची एंट्री</t>
+          <t>Kolhapur district planning body okays 67cr to revamp zilla parishad schools</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-ministers-entry-in-kolhapur-agricultural-produce-market-committee-chairman-election-ap84</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Gokul President Election : कोल्हापुरच्या राजकारणात मुश्रीफांची ताकद वाढली; जिल्हा बँक आणि गोकुळवर पितापुत्रांचं 'वर्चस्व', वाचा महिनाभरात काय काय घडलं?</t>
+          <t>CA from Dhayari, 41, who died in Solapur, first GBS casualty; patient count in Pune touches 111</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Chandrahar Patil : उद्धव ठाकरेंना मोठा धक्का! डबल महाराष्ट्र केसरी चंद्रहार पाटील आज शिंदेंच्या शिवसेनेत प्रवेश करणार</t>
+          <t>Tender scam hits Akola women’s hospital, dist civil surgeon, two other top officials suspended</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/maharashtra/lokshahi-politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Almatty Dam : कर्नाटक भाजपचे महाराष्ट्राविरोधात वाकडे पाऊल, अलमट्टी धरणाची उंची वाढवण्यासाठी केंद्रीय मंत्र्यांच्या गाठीभेटी, वाद चिघळणार?</t>
+          <t>Patient records at 2,100 centres to be digitised</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/almatti-dam-height-increase-karnataka-bjp-mps-maharashtra-flood-risk-dispute-jap93-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Almatti dam height : ‘आलमट्टी’वरून राजकीय वातावरण तापलं ; जलसंपदा मंत्री विखे पुन्हा घेणार सर्वपक्षीय बैठक!</t>
+          <t>Maharashtra health department cancels deputation of Nashik civic body’s medical superintendent</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/radhakrishna-vikhe-patil-to-hold-all-party-meeting-on-almatti-dam-height-water-dispute-maharashtra-karnataka-msr87-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>kolhapur | जिल्ह्यातील सहकारावर कागलचे वर्चस्व</t>
+          <t>Bike ambulances, ICUs along wari routes: State health min</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mushrif-establishes-dominance-over-key-cooperative-institutions-in-district-ap84</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : 'माधुरी'चा प्रश्न मार्गी लागणार? मंत्रिमंडळाच्या बैठकीत मुख्यमंत्री देवेंद्र फडणवीस यांची मोठी घोषणा</t>
+          <t>Will Elephant Mahadevi Return To Kolhapur From Jamnagars Vantara? Details Inside</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
+          <t>https://www.freepressjournal.in/pune/will-elephant-mahadevi-return-to-kolhapur-from-jamnagars-vantara-details-inside</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers List : पालकमंत्र्यांची यादी जाहीर, बीड आणि पुण्याबाबत सरकारचा मोठा निर्णय</t>
+          <t>संपादकीय: सरकार कोई हल निकाले, किसानों की कर्ज माफी का मुद्दा ज्वलंत</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
+          <t>https://navbharatlive.com/special-coverage/high-level-committee-will-be-formed-within-15-days-to-take-a-decision-on-loan-waiver-1256403.html</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Maharashtra Live Blog: माळेगाव सहकारी कारखाना निवडणुकीच्या मतमोजणीच्या प्रत्येक क्षणाचे वेगवान अपडेटस्, शरद पव</t>
+          <t>NCP नेता हसन मुश्रीफ ने वाशिम के पालक मंत्री पद से दिया इस्तीफा, बोले- आने-जाने में होती हैं दिक्कत</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-beed-santosh-deshmukh-case-maharashtra-politics-malegaon-sahakari-sakhar-karkhana-election-2025-1365817</t>
+          <t>https://navbharatlive.com/maharashtra/washim/ncp-minister-hasan-mushrif-resigned-washim-guardian-minister-citing-travel-difficulties-1145083.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Shiv Sena : कोल्हापुरात शिवसेनेचं वादळ, एकनाथ शिंदेंचा बंटी पाटील आणि महाडिक दोन्ही गटांना धक्का</t>
+          <t>Maharashtra’s roadmap discussed at NDTV Marathi Manch</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
+          <t>https://bestmediainfo.com/mediainfo/mediainfo-marketing/maharashtras-roadmap-discussed-at-ndtv-marathi-manch-9009029</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Maharashtra Karnataka Border Dispute: सीमाप्रश्नी उच्चाधिकार समितीची पुनर्रचना</t>
+          <t>Maha govt launches organ donation fortnight, Minister Abitkar takes lead by filling form</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/reorganization-of-the-high-power-committee-on-border-issues-rat16</t>
+          <t>https://ianslive.in/maharashtra-govt-launches-organ-donation-fortnight--20250804092958</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Maharashta Gurdian Ministers Full List : मुंबई ते गडचिरोली, बीड ते नागपूर, तुमच्या जिल्ह्याचा पालकमंत्री</t>
+          <t>Mumbai Reports 53 Active COVID-19 Cases; 2 Deaths Linked To Co-Morbidities</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>"मी पहाटे ४ वाजता उठतो, फिरतो, व्यायाम करतो आणि..."; अजित पवारांनी सर्वच सांगितलं</t>
+          <t>Cases rise amid 1st GBS death; Central team reaches Pune</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/ajit-pawar-daily-routine-government-work-schedule/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदेंच्या वाढदिनी राज्यात उपमुख्यमंत्री वैद्यकीय मदत कक्षाची घोषणा</t>
+          <t>State to set up Maharashtra Public Health Infrastructure Corporation</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीणीला परत आणण्यासाठी राज्य सरकार उचलणार मोठं पाऊल; मुख्यमंत्री देवेंद्र फडणवीसांनी सगळच सांगितलं</t>
+          <t>Maharashtra to implement ‘No shortage, no wastage’ policy for blood management</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis: ग्रामीण आवासच्या 16.81 लाख घरकुलांना मंजुरी: मुख्यमंत्री - देशोन्नती</t>
+          <t>Medical health complex &amp; upgraded facilities inaugurated at govt hospitals in Kolhapur</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/cm-devendra-fadnavis-pm-awas-yojana/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>युवाशक्ती दहीहंडीला कोल्हापुरकरांनी मोठया संख्येने उपस्थित रहावे : खा. धनंजय महाडिक -</t>
+          <t>Maharashtra Gears Up for 68th National School Yoga Sports Championship Starting January 16</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
+          <t>https://impressivetimes.com/latest/news-3192/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>India reports 2 more deaths from Guillain-Barre Syndrome, raising total to 3</t>
+          <t>Pimpri Chinchwad News: PCMC Honoured with State Health Awards</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
+          <t>https://punemirror.com/city/pcmc/pimpri-chinchwad-news-pcmc-honoured-with-state-health-awards/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>More that 12k children died in Maharashtra between Apr last year and Feb 2025: Minister</t>
+          <t>Sanjeevani: Transforming Cancer Care Through Unity and Awareness</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
+          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Statewide awareness campaign on organ donation from Aug 3 to 15</t>
+          <t>Pune Observes World Malaria Day With Awareness Rally At Tadiwala Road</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
+          <t>https://www.freepressjournal.in/pune/pune-observes-world-malaria-day-with-awareness-rally-at-tadiwala-road</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Maharashtra govt to set up vigilance cells to stop illegal uterus removals among cane cutters</t>
+          <t>Deputy Chief Minister Ajit Pawar Inaugurates Special Health Screening Drive Under National Child Health Program In Pune</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
+          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Kolhapur celebrates I-Day, Janmashtami &amp; Dahi Handi</t>
+          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
+          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ZTCC, health minister honours families of deceased donors</t>
+          <t>Pune: Statewide Childrens Health Checkup Campaign Begins In Aundh Tomorrow</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
+          <t>https://www.freepressjournal.in/pune/pune-statewide-childrens-health-checkup-campaign-begins-in-aundh-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Kolhapur IT Park &amp; employment initiatives announced at district investment summit</t>
+          <t>Maharashtra School Education Minister Dadaji Bhuse Proposes Mobile App For Student Health Check-Ups Under RBSK</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-school-education-minister-dadaji-bhuse-proposes-mobile-app-for-student-health-check-ups-under-rbsk</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Kolhapur district planning body okays 67cr to revamp zilla parishad schools</t>
+          <t>Pune: Ajit Pawar Inaugurates 43 ‘Aapla Davakhana’ Clinics, Lays Foundation for State Family Welfare Building</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
+          <t>https://www.punekarnews.in/pune-ajit-pawar-inaugurates-43-aapla-davakhana-clinics-lays-foundation-for-state-family-welfare-building/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CA from Dhayari, 41, who died in Solapur, first GBS casualty; patient count in Pune touches 111</t>
+          <t>Maharashtra: Solapur man suspected to have died of Guillain-Barre syndrome; cases rise to 110 in Pune</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Shahu Maharaj’s 151st birth anniversary celebrated in Kolhapur</t>
+          <t>Maharashtra Announces Free Cancer Vaccination for Girls Aged 0-14 Amid Rising Cases</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
+          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Tender scam hits Akola women’s hospital, dist civil surgeon, two other top officials suspended</t>
+          <t>Over 14,000 women detected with cancer-like symptoms in Maharashtra</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-over-14000-women-detected-with-cancer-like-symptoms-in-hingoli-2753909-2025-07-10</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Patient records at 2,100 centres to be digitised</t>
+          <t>Maharashtra Faces Cancer Crisis: Over 14500 Women in Hingoli Show ‘Cancer-Like’ Symptoms During Govt Health Screening</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
+          <t>https://www.thehealthsite.com/news/maharashtra-faces-cancer-crisis-over-14500-women-in-hingoli-show-cancer-like-symptoms-during-govt-health-screening-1239129/</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Maharashtra health department cancels deputation of Nashik civic body’s medical superintendent</t>
+          <t>Ashadhi Wari 2025: Maharashtra Plans Safer, Greener Pilgrimage to Pandharpur</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Bike ambulances, ICUs along wari routes: State health min</t>
+          <t>Residents of 18 villages to observe bandh today to oppose merger into KMC limits</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Will Elephant Mahadevi Return To Kolhapur From Jamnagars Vantara? Details Inside</t>
+          <t>Another person dies in Maharashtra from Guillain-Barre syndrome: Death toll rises to 2, 16 new cases report...</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/will-elephant-mahadevi-return-to-kolhapur-from-jamnagars-vantara-details-inside</t>
+          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>संपादकीय: सरकार कोई हल निकाले, किसानों की कर्ज माफी का मुद्दा ज्वलंत</t>
+          <t>Maharashtra health minister pushes reforms, seeks new policy and faster recruitment</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/special-coverage/high-level-committee-will-be-formed-within-15-days-to-take-a-decision-on-loan-waiver-1256403.html</t>
+          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>NCP नेता हसन मुश्रीफ ने वाशिम के पालक मंत्री पद से दिया इस्तीफा, बोले- आने-जाने में होती हैं दिक्कत</t>
+          <t>शक्ति पीठ महामार्ग का प्रस्ताव … मलाई खाने के लिए भाजपा और शिंदे गुट में टकराव! … रु.२०,००० करोड़ के बजट पर है नजर</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/washim/ncp-minister-hasan-mushrif-resigned-washim-guardian-minister-citing-travel-difficulties-1145083.html</t>
+          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Maharashtra’s roadmap discussed at NDTV Marathi Manch</t>
+          <t>MoS Civil Aviation Shri Murlidhar Mohol inaugurates new ATC Tower cum Technical Block cum Fire Station at Kolhapur Airport</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://bestmediainfo.com/mediainfo/mediainfo-marketing/maharashtras-roadmap-discussed-at-ndtv-marathi-manch-9009029</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2128928</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Maha govt launches organ donation fortnight, Minister Abitkar takes lead by filling form</t>
+          <t>High-Tech ATC Tower Inaugurated at Kolhapur Airport</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://ianslive.in/maharashtra-govt-launches-organ-donation-fortnight--20250804092958</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/high-tech-atc-tower-inaugurated-at-kolhapur-airport/73773</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Mumbai Reports 53 Active COVID-19 Cases; 2 Deaths Linked To Co-Morbidities</t>
+          <t>Chief Justice Of India To Inaugurate Kolhapur Circuit Bench Of Bombay High Court</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
+          <t>https://www.livelaw.in/events/justice-bhushan-ramkrishna-gavai-kolhapur-circuit-bench-bombay-high-court-inaugration-events-300775</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Maharashtra to screen over 1.66 crore children in special drive | Latest News India</t>
+          <t>Shahu Maharaj’s 151st birth anniversary celebrated in Kolhapur</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-screen-over-1-66-crore-children-in-special-drive-101740770920444.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Cases rise amid 1st GBS death; Central team reaches Pune</t>
+          <t>राज्याच्या प्रगतीत कोल्हापूर जिल्हा अग्रभागी राहण्यासाठी सर्वजण सज्ज होऊया -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
+          <t>https://mahasamvad.in/164322/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>State to set up Maharashtra Public Health Infrastructure Corporation</t>
+          <t>Kolhapur Political News : काँग्रेसला मोठं भगदाड, 35 जणांची यादी तयार, मुंबईत होणार पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-elections-congress-35-leaders-will-join-shiv-sena-mumbai-entry-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Maharashtra to implement ‘No shortage, no wastage’ policy for blood management</t>
+          <t>Kolhapur : कोल्हापूर चित्रनगरीमधील चित्रीकरण स्थळांचं लोकार्पण व भूमिपूजन कार्यक्रम संपन्न</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
+          <t>https://www.navarashtra.com/videos/kolhapur-dedication-and-foundation-stone-laying-ceremony-of-filming-locations-in-kolhapur-chitranagari-concluded-914427.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Medical health complex &amp; upgraded facilities inaugurated at govt hospitals in Kolhapur</t>
+          <t>मुख्यमंत्री रोजगार निर्मिती कार्यक्रम : कोल्हापूर जिल्हा राज्यात अग्रस्थानी</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
+          <t>https://mahasamvad.in/170909/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Rs 1 Lakh Cashless Treatment for Accident Victims: Maharashtra Government’s New Move</t>
+          <t>Kolhapur Politics : शिंदेंचा बंटी पाटील अन् महाडिकांना धक्का; शारंगधर देशमुखांसह कोल्हापुरातील बड्या नेत्यांचा शिवसेनेत प्रवेश</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/04/19/rs-1-lakh-cashless-treatment-for-accident-victims-maharashtra-governments-new-move/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-congress-leaders-join-shivsena-kolhapur-shock-satej-patil-and-dhananjay-mahadik-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Maharashtra Gears Up for 68th National School Yoga Sports Championship Starting January 16</t>
+          <t>कोल्हापूर चित्रनगरीत मंत्री अॅड. आशिष शेलार यांच्या उपस्थितीत विविध विकासकामांचे उद्घाटन व लोकार्पण</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/news-3192/</t>
+          <t>https://mahasamvad.in/170610/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad News: PCMC Honoured with State Health Awards</t>
+          <t>Kolhapur Circuit Bench Inauguration |कोल्हापूर सर्किट बेंचचा 17 ऑगस्टला शानदार शुभारंभ</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pcmc/pimpri-chinchwad-news-pcmc-honoured-with-state-health-awards/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inauguration-17-august-chief-justice-gavai-arade-cm-grand-ceremony-5000-seating-sp96</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Sanjeevani: Transforming Cancer Care Through Unity and Awareness</t>
+          <t>ShivSena News : एकनाथ शिंदेंच्या 'मंगेशाची' आमदारकीसाठी मोर्चेबांधणी; चिवटेंना हवा 'गुरुजींचा' आशीर्वाद</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mangesh-chivate-mlc-election-pune-teachers-constituency-eknath-shinde-shiv-sena-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Deputy Chief Minister Ajit Pawar Inaugurates Special Health Screening Drive Under National Child Health Program In Pune</t>
+          <t>हद्दवाढीसाठी आज मुंबईत बैठक</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/meeting-in-mumbai-today-for-boundary-extension</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
+          <t>अंबाबाई, जोतिबा मंदिर विकासाच्या पहिल्या टप्प्याचे काम लवकरच सुरू</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/ambabai-jyotiba-temple-development-phase-one-to-begin-soon-dc95</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Pune: Statewide Childrens Health Checkup Campaign Begins In Aundh Tomorrow</t>
+          <t>...तर शिंदे शिवसेनाही स्वबळावर स्थानिक स्वराज्यच्या मैदानात</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-statewide-childrens-health-checkup-campaign-begins-in-aundh-tomorrow</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-municipal-corporation-election</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Pune: Ajit Pawar Inaugurates 43 ‘Aapla Davakhana’ Clinics, Lays Foundation for State Family Welfare Building</t>
+          <t>हद्दवाढीसंदर्भात सोमवारी मुंबईत उपमुख्यमंत्री शिंदे यांच्याकडे बैठक</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-ajit-pawar-inaugurates-43-aapla-davakhana-clinics-lays-foundation-for-state-family-welfare-building/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-shinde-to-hold-meeting-in-mumbai-on-monday-regarding-boundary-extension</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Maharashtra: Solapur man suspected to have died of Guillain-Barre syndrome; cases rise to 110 in Pune</t>
+          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/lokaraja-rajarshi-chhatrapati-shahu-jayanti-celebrations-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Maharashtra Announces Free Cancer Vaccination for Girls Aged 0-14 Amid Rising Cases</t>
+          <t>Maharashtra: 10,000 Farmers to Hold State-Wide March In Mumbai On March 12 Against 'Shaktipeeth Highway'</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Over 14,000 women detected with cancer-like symptoms in Maharashtra</t>
+          <t>Ajit Pawar’s Directive Clears Path for IT Hub in Kolhapur</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-over-14000-women-detected-with-cancer-like-symptoms-in-hingoli-2753909-2025-07-10</t>
+          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Ashadhi Wari 2025: Maharashtra Plans Safer, Greener Pilgrimage to Pandharpur</t>
+          <t>बाजार समिती सभापतिपद अजित पवार गटाकडे</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/market-committee-chairmanship-to-ajit-pawar-group-ap84</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Residents of 18 villages to observe bandh today to oppose merger into KMC limits</t>
+          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2105326</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Rs 1 lakh cash reward for informants, decoys helping bust illegal sex determination &amp; abortion rackets</t>
+          <t>Elephantiasis eradication drug campaign launched in 3 Vid districts</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rs-1-lakh-cash-reward-for-informants-decoys-helping-bust-illegal-sex-determination-abortion-rackets/articleshow/117612427.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Another person dies in Maharashtra from Guillain-Barre syndrome: Death toll rises to 2, 16 new cases report...</t>
+          <t>India Achieves Five Guinness World Records in Ayurveda</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
+          <t>https://observervoice.com/india-achieves-five-guinness-world-records-in-ayurveda-97959/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Maharashtra School Education Minister Dadaji Bhuse Proposes Mobile App For Student Health Check-Ups Under RBSK</t>
+          <t>चौदा वर्षे वयापर्यंतच्या मुलींना कर्करोगप्रतिबंधक लस देण्याचा विचार; अजित पवार यांची माहिती</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-school-education-minister-dadaji-bhuse-proposes-mobile-app-for-student-health-check-ups-under-rbsk</t>
+          <t>https://pudhari.news/maharashtra/pune/consideration-of-anti-cancer-vaccine-for-girls-up-to-fourteen-years-of-age-information-given-by-ajit-pawar</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Maharashtra health minister pushes reforms, seeks new policy and faster recruitment</t>
+          <t>सार्वजनिक आरोग्य पायाभूत सुविधा महामंडळ उभारणीसाठी कार्यवाही करावी- मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
+          <t>https://mahasamvad.in/160560/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>शक्ति पीठ महामार्ग का प्रस्ताव … मलाई खाने के लिए भाजपा और शिंदे गुट में टकराव! … रु.२०,००० करोड़ के बजट पर है नजर</t>
+          <t>ठाणे जिल्हा रुग्णालय एमएमआर मधील नागरिकांसाठी वरदान ठरणार – उपमुख्यमंत्री एकनाथ शिंदे</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
+          <t>https://mahasamvad.in/173688/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>MoS Civil Aviation Shri Murlidhar Mohol inaugurates new ATC Tower cum Technical Block cum Fire Station at Kolhapur Airport</t>
+          <t>माहिती व जनसंपर्क महासंचालनालय, महाराष्ट्र शासन | Page 523</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2128928</t>
+          <t>https://www.mahasamvad.in/page/523/?m=0</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>High-Tech ATC Tower Inaugurated at Kolhapur Airport</t>
+          <t>Government fully supports implementation of Jyotiba temple development plan: Fadnavis</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/high-tech-atc-tower-inaugurated-at-kolhapur-airport/73773</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Chief Justice Of India To Inaugurate Kolhapur Circuit Bench Of Bombay High Court</t>
+          <t>Maharashtra approves Rs 20,787 crores for Nagpur-Goa Shaktipeeth Expressway</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/events/justice-bhushan-ramkrishna-gavai-kolhapur-circuit-bench-bombay-high-court-inaugration-events-300775</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-nagpur-goa-shaktipeeth-expressway-land-acquisition-pilgrimage-tourism-2745741-2025-06-25</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Kolhapur Political News : काँग्रेसला मोठं भगदाड, 35 जणांची यादी तयार, मुंबईत होणार पक्षप्रवेश</t>
+          <t>Shiv Sena names 17 district liaison mins, escalates power battle in Mahayuti</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-elections-congress-35-leaders-will-join-shiv-sena-mumbai-entry-rm82-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापूर चित्रनगरीमधील चित्रीकरण स्थळांचं लोकार्पण व भूमिपूजन कार्यक्रम संपन्न</t>
+          <t>High-powered committee on Maharashtra-Karnataka boundary issue reconstituted</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/kolhapur-dedication-and-foundation-stone-laying-ceremony-of-filming-locations-in-kolhapur-chitranagari-concluded-914427.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री रोजगार निर्मिती कार्यक्रम : कोल्हापूर जिल्हा राज्यात अग्रस्थानी</t>
+          <t>‘Jt guardian post introduced to include more ministers’</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170909/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : शिंदेंचा बंटी पाटील अन् महाडिकांना धक्का; शारंगधर देशमुखांसह कोल्हापुरातील बड्या नेत्यांचा शिवसेनेत प्रवेश</t>
+          <t>MP Shrikant Shinde refutes Sanjay Raut’s ambulance scam allegations</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-congress-leaders-join-shivsena-kolhapur-shock-satej-patil-and-dhananjay-mahadik-as11-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>कोल्हापूर चित्रनगरीत मंत्री अॅड. आशिष शेलार यांच्या उपस्थितीत विविध विकासकामांचे उद्घाटन व लोकार्पण</t>
+          <t>Discord in Maharashtra govt over fund-shift to Ladki Bahin Yojana</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170610/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ShivSena News : एकनाथ शिंदेंच्या 'मंगेशाची' आमदारकीसाठी मोर्चेबांधणी; चिवटेंना हवा 'गुरुजींचा' आशीर्वाद</t>
+          <t>Fadnavis first Maha CM to become guardian minister</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mangesh-chivate-mlc-election-pune-teachers-constituency-eknath-shinde-shiv-sena-hn97-rg93</t>
+          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench Inauguration |कोल्हापूर सर्किट बेंचचा 17 ऑगस्टला शानदार शुभारंभ</t>
+          <t>Eknath Shinde's grand welcome : उपमुख्यमंत्री शिंदेंचं कोल्हापुरात ग्रँड वेलकम; आबिटकरांनी जाण ठेवत, स्वागतात सोडली नाही कुठलीच कसर!</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inauguration-17-august-chief-justice-gavai-arade-cm-grand-ceremony-5000-seating-sp96</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prakash-abitkar-grand-welcome-eknath-shinde-kolhapur-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>हद्दवाढीसाठी आज मुंबईत बैठक</t>
+          <t>MP राऊतांविषयी सवाल, MP Shrikant Shinde यांनी स्पष्टच केलं, कोण Sanjay Raut?</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/meeting-in-mumbai-today-for-boundary-extension</t>
+          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>अंबाबाई, जोतिबा मंदिर विकासाच्या पहिल्या टप्प्याचे काम लवकरच सुरू</t>
+          <t>Shivsena Politics: महाडिक, मुश्रीफ अन् सतेज पाटलांच्या बालेकिल्ल्यात शिंदे मोठा धमाका करणार; एक दोन नव्हे,तर 30 मात्तबर नेते ...</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/ambabai-jyotiba-temple-development-phase-one-to-begin-soon-dc95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-big-move-in-kolhapur-stronghold-of-dhananjay-mahadik-hasan-mushrif-satej-patil-30-leaders-to-join-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>...तर शिंदे शिवसेनाही स्वबळावर स्थानिक स्वराज्यच्या मैदानात</t>
+          <t>Kolhapur Ashokrao Mane : चर्चेचा विषय! आमदार अशोकराव माने नेमके कुणाचे? शिवसेना पक्ष कार्यालय उद्‌घाटनाला उपस्थित; राजकारण्यांना पडला प्रश्न</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-municipal-corporation-election</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/mla-ashokrao-mane-presence-at-a-shiv-sena-office-inauguration-has-stirred-political-debate-in-kolhapur-srs92</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>हद्दवाढीसंदर्भात सोमवारी मुंबईत उपमुख्यमंत्री शिंदे यांच्याकडे बैठक</t>
+          <t>मुश्रीफांनी सोडलं, अजित पवारांनी दत्ता मामांना घेरलं; कसा सुटला अखेर वाशिमच्या पालकमंत्रीपदाचा तिढा!</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-shinde-to-hold-meeting-in-mumbai-on-monday-regarding-boundary-extension</t>
+          <t>https://marathi.oneindia.com/maharashtra/datta-mama-bharne-appointed-as-guardian-minister-of-washim-district-ajit-pawar-hasan-mushrif-023877.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
+          <t>Maharashtra Health Department to set up committee for effective leprosy eradication</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/lokaraja-rajarshi-chhatrapati-shahu-jayanti-celebrations-today-ap84</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-health-department-to-set-up-committee-for-effective-leprosy-eradication/article69815684.ece</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Maharashtra: 10,000 Farmers to Hold State-Wide March In Mumbai On March 12 Against 'Shaktipeeth Highway'</t>
+          <t>111 Diagnosed With Guillain-Barre Syndrome In Maharashtra: Health Minister</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
+          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Ajit Pawar’s Directive Clears Path for IT Hub in Kolhapur</t>
+          <t>Health minister JP Nadda promises steady IVIG supply for Guillain-Barre Syndrome (GBS), say officials</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>बाजार समिती सभापतिपद अजित पवार गटाकडे</t>
+          <t>Pune: 76 Private Hospitals Issued Notices for Regulatory Violations</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/market-committee-chairmanship-to-ajit-pawar-group-ap84</t>
+          <t>https://www.thebridgechronicle.com/news/pune-76-private-hospitals-issued-notices-for-regulatory-violations</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Elephantiasis eradication drug campaign launched in 3 Vid districts</t>
+          <t>Guillain-Barré cases in Pune cross 100, health ministry sends expert team</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
+          <t>https://www.downtoearth.org.in/health/guillain-barr%C3%A9-cases-in-pune-cross-100-health-ministry-sends-expert-team-to-pune</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>India Achieves Five Guinness World Records in Ayurveda</t>
+          <t>State plans Maharashtra Institute of Virology, along the lines of NIV</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://observervoice.com/india-achieves-five-guinness-world-records-in-ayurveda-97959/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>चौदा वर्षे वयापर्यंतच्या मुलींना कर्करोगप्रतिबंधक लस देण्याचा विचार; अजित पवार यांची माहिती</t>
+          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/consideration-of-anti-cancer-vaccine-for-girls-up-to-fourteen-years-of-age-information-given-by-ajit-pawar</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>सार्वजनिक आरोग्य पायाभूत सुविधा महामंडळ उभारणीसाठी कार्यवाही करावी- मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Tally of nerve disorder GBS rises to 180 in Pune; Mumbai records first case</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160560/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ठाणे जिल्हा रुग्णालय एमएमआर मधील नागरिकांसाठी वरदान ठरणार – उपमुख्यमंत्री एकनाथ शिंदे</t>
+          <t>Nurses’ strike stalls health services at state-run hosps</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173688/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>माहिती व जनसंपर्क महासंचालनालय, महाराष्ट्र शासन | Page 523</t>
+          <t>Wildlife Protest Kolhapur: Thousands March to Demand Elephant Mahadevi's Return from Vantara</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/523/?m=0</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Government fully supports implementation of Jyotiba temple development plan: Fadnavis</t>
+          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Maharashtra approves Rs 20,787 crores for Nagpur-Goa Shaktipeeth Expressway</t>
+          <t>Accident victims to receive ₹1L cashless treatment, says health minister | Mumbai news</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-nagpur-goa-shaktipeeth-expressway-land-acquisition-pilgrimage-tourism-2745741-2025-06-25</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Shiv Sena names 17 district liaison mins, escalates power battle in Mahayuti</t>
+          <t>Nagpur Doctors Urge Govt to Simplify Hospital Renewal Process, Reduce Paperwork</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>High-powered committee on Maharashtra-Karnataka boundary issue reconstituted</t>
+          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>‘Jt guardian post introduced to include more ministers’</t>
+          <t>Maha govt signs two MoUs with PHFI, IMMAST for quality and capacity building in health sector</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
+          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>MP Shrikant Shinde refutes Sanjay Raut’s ambulance scam allegations</t>
+          <t>After 13-yr delay, govt says will open Nagpur District Hospital in 3 months</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Discord in Maharashtra govt over fund-shift to Ladki Bahin Yojana</t>
+          <t>Sewage from hotels, poultry farms near Khadakwasla under scanner: Health minister</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Fadnavis first Maha CM to become guardian minister</t>
+          <t>Maharashtra govt eyeing to make HPV vaccine available for girls: Ajit Pawar</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
+          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MP राऊतांविषयी सवाल, MP Shrikant Shinde यांनी स्पष्टच केलं, कोण Sanjay Raut?</t>
+          <t>Maha to amend Nursing Homes Registration rules</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Shivsena Politics: महाडिक, मुश्रीफ अन् सतेज पाटलांच्या बालेकिल्ल्यात शिंदे मोठा धमाका करणार; एक दोन नव्हे,तर 30 मात्तबर नेते ...</t>
+          <t>Aarogya Mitras in Maharashtra call off indefinite strike</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-big-move-in-kolhapur-stronghold-of-dhananjay-mahadik-hasan-mushrif-satej-patil-30-leaders-to-join-dk88-rg93</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Kolhapur Ashokrao Mane : चर्चेचा विषय! आमदार अशोकराव माने नेमके कुणाचे? शिवसेना पक्ष कार्यालय उद्‌घाटनाला उपस्थित; राजकारण्यांना पडला प्रश्न</t>
+          <t>Pune reports first death in GBS outbreak as cases surge</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/mla-ashokrao-mane-presence-at-a-shiv-sena-office-inauguration-has-stirred-political-debate-in-kolhapur-srs92</t>
+          <t>https://www.healthcareradius.in/clinical/covid-corner/gbs-claims-first-victim-in-pune-amid-rising-cases-central-team-dispatched-virus-outbreak-gbsvirus</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>111 Diagnosed With Guillain-Barre Syndrome In Maharashtra: Health Minister</t>
+          <t>Maharashtra Government Plans To Introduce Extensive Health Policy For Medical Tourism</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-plans-to-introduce-extensive-health-policy-for-medical-tourism</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Maharashtra Health Department to set up committee for effective leprosy eradication</t>
+          <t>Crores Sanctioned, No Compound Walls Built: Corruption Cloud Over Pune’s Yerawada Mental Hospital</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-health-department-to-set-up-committee-for-effective-leprosy-eradication/article69815684.ece</t>
+          <t>https://www.freepressjournal.in/pune/crores-sanctioned-no-compound-walls-built-corruption-cloud-over-punes-yerawada-mental-hospital</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Pune: 76 Private Hospitals Issued Notices for Regulatory Violations</t>
+          <t>Over 14,500 Women Detected With Cancer-Like Symptoms Post Screening In Maharashtra's Hingoli</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/pune-76-private-hospitals-issued-notices-for-regulatory-violations</t>
+          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>State to bring all diagnostic labs under health dept’s purview</t>
+          <t>Maharashtra govt framing policy to stop water contamination for prevention of illnesses: Minister</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Guillain-Barré cases in Pune cross 100, health ministry sends expert team</t>
+          <t>More than 14.5k women detected with cancer-like symptoms post screening in Hingoli</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.downtoearth.org.in/health/guillain-barr%C3%A9-cases-in-pune-cross-100-health-ministry-sends-expert-team-to-pune</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>State plans Maharashtra Institute of Virology, along the lines of NIV</t>
+          <t>Maharashtra Politics : लाडकी बहीण योजनेवरुन महायुतीत 'कसरत', आरोग्यमंत्र्यांचं मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
+          <t>मस्तवाल दीनानाथ मंगेशकर हॉस्पिटलमध्ये आमदाराच्या पीएच्या पत्नीचा जीव जाताच</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
+          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Tally of nerve disorder GBS rises to 180 in Pune; Mumbai records first case</t>
+          <t>Maharashtra Live Updates : सरकारी दवाख्यान्यात बोगस औषधांचा पुरवठा? आरोग्य मंत्री प्रकाश आबिटकरांचीही कबुली</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-updates-17-july-2025-assembly-monsoon-session-mahayuti-vs-mahavikas-aghadi-raj-thackeray-uddhav-thackeray-alliance-sambhaji-brigade-pravin-gaikwad-ncp-jayant-patil-shashikant-shinde-rohit-pawar-sharad-pwar-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Nurses’ strike stalls health services at state-run hosps</t>
+          <t>Jyotiba Chaitra Yatra : जोतिबा डोंगरावर दुपारी बारालाच निघणार सासनकाठी मिरवणूक; मंदिर 79 तास राहणार खुले</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/jyotiba-chaitra-yatra-sasan-kathi-miravnuk-minister-prakash-abitkar-jyotiba-dongar-kolhapur-bam92</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Wildlife Protest Kolhapur: Thousands March to Demand Elephant Mahadevi's Return from Vantara</t>
+          <t>Maharashtra Breaking News LIVE 9 January 2025 : राज्यपाल नियुक्त 12 आमदारांबाबतची याचिका फेटाळली</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
+          <t>Top Marathi News Today: अखेर कोकाटेंचं खातं बदललच;आता दिली 'या' खात्याची जबाबदारी</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Accident victims to receive ₹1L cashless treatment, says health minister | Mumbai news</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Maha govt signs two MoUs with PHFI, IMMAST for quality and capacity building in health sector</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Maharashtra govt eyeing to make HPV vaccine available for girls: Ajit Pawar</t>
+          <t>Mumbai: देवेंद्र फडणवीसांचा मोठा निर्णय, आता घरबसल्या करता येणार दस्त नोंदणी वन</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Maharashtra Faces Cancer Crisis: Over 14500 Women in Hingoli Show ‘Cancer-Like’ Symptoms During Govt Health Screening</t>
+          <t>Kolhapur News : कोल्हापुरात ढगफुटीसदृश्य पाऊस, ओढे-नाले तुडुंब, अनेक घरात पाणी शिरलं, जनजीवन विस्कळीत, शेतीचंही नुकसान</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.thehealthsite.com/news/maharashtra-faces-cancer-crisis-over-14500-women-in-hingoli-show-cancer-like-symptoms-during-govt-health-screening-1239129/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-heavy-rain-disrupts-daily-life-significant-damage-to-agriculture/articleshow/121814826.cms</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Maha to amend Nursing Homes Registration rules</t>
+          <t>Pahalgam Terror Attack: ...तर आमचीही नावं मृतांच्या यादीत असती! महाराष्ट्रातील २८ जण नाट्यमयरित्या थोडक्यात वाचले</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/bargain-and-delay-in-getting-horses-save-28-tourist-from-walking-into-pahalgam-terror-site/articleshow/120580319.cms</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Aarogya Mitras in Maharashtra call off indefinite strike</t>
+          <t>दीनानाथ मंगेशकर रुग्णालयावर कारवाई कधी? आरोग्य मंत्री प्रकाश आबिटकर यांनी दिले उत्तर</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-said-about-the-action-taken-by-dinanath-hospital-1387152.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Pune reports first death in GBS outbreak as cases surge</t>
+          <t>आता चिंता जलजन्य आजारांची; औषधांचा पुरेसा साठा राज्यात उपलब्ध करण्याचे आरोग्य मंत्री आबिटकर यांचे आदेश</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/clinical/covid-corner/gbs-claims-first-victim-in-pune-amid-rising-cases-central-team-dispatched-virus-outbreak-gbsvirus</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/waterborne-diseases-health-minister-abitkar-orders-medicine-stock</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Maharashtra Government Plans To Introduce Extensive Health Policy For Medical Tourism</t>
+          <t>केंद्रीय आरोग्य सेवा योजनेच्या दरांमध्ये सुधारणा करणार – केंद्रीय मंत्री मनसुख मांडविया</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-plans-to-introduce-extensive-health-policy-for-medical-tourism</t>
+          <t>https://mahasamvad.in/172749/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Maha Health Minister urges Mandaviya to revise income eligibility limit for ESIS beneficiaries</t>
+          <t>३ ते १५ ऑगस्ट २०२५ या कालावधीत अवयवदान पंधरवडा साजरा होणार – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/health/maha-health-minister-urges-mandaviya-to-revise-income-eligibility-limit-for-esis-beneficiaries</t>
+          <t>https://mahasamvad.in/173717/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Crores Sanctioned, No Compound Walls Built: Corruption Cloud Over Pune’s Yerawada Mental Hospital</t>
+          <t>विधानपरिषद प्रश्नोत्तरे</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/crores-sanctioned-no-compound-walls-built-corruption-cloud-over-punes-yerawada-mental-hospital</t>
+          <t>https://mahasamvad.in/172235/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Over 14,500 Women Detected With Cancer-Like Symptoms Post Screening In Maharashtra's Hingoli</t>
+          <t>Mahadevi Elephant: कोल्हापुर की 'महादेवी' हथिनी को वनतारा से वापस लाने की मांग तेज, लोगों ने किया मौन मार्च</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
+          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Maharashtra govt framing policy to stop water contamination for prevention of illnesses: Minister</t>
+          <t>पुणे से देश की आर्थिक राजधानी पहुंचा गिलियन बैरे सिंड्रोम, मुंबई में जीबीएस का पहला केस</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
+          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Health minister JP Nadda promises steady IVIG supply for Guillain-Barre Syndrome (GBS), say officials</t>
+          <t>‘वैद्यकीय अधिकाऱ्यांची रिक्त पदे तातडीने भरा’; आरोग्यमंत्री प्रकाश आबिटकर यांचे आदेश</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
+          <t>https://www.lokmat.com/maharashtra/fill-the-vacant-posts-of-medical-officers-immediately-says-health-minister-prakash-abitkar-a-a992/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Maharashtra Child Deaths: Over 12,000 Children Died Between April 2024 and Feb 2025</t>
+          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : सरकारी दवाख्यान्यात बोगस औषधांचा पुरवठा? आरोग्य मंत्री प्रकाश आबिटकरांचीही कबुली</t>
+          <t>Raj-Uddhav Thackeray Vijayi Rally : दोन भाऊ एकत्र आल्याने सुप्रिया सुळेंचा आनंद गगनात मावेना, मुश्रीफ बोलताच आबिटकरांनाही हसू आवरेना...</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-updates-17-july-2025-assembly-monsoon-session-mahayuti-vs-mahavikas-aghadi-raj-thackeray-uddhav-thackeray-alliance-sambhaji-brigade-pravin-gaikwad-ncp-jayant-patil-shashikant-shinde-rohit-pawar-sharad-pwar-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/raj-uddhav-thackeray-brothers-vijayi-rally-supriya-sule-criticized-by-hasan-mushrif-and-prakash-abitkar-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Eknath Shinde Department Scam: उपमुख्यमंत्री एकनाथ शिंदेंच्या खात्यात 'कुंपणानेच खाल्ले शेत', शासकीय तिजोरीवर अधिकाऱ्यांचा डल्ला?</t>
+          <t>Maharashtra Live Updates : ठाकरे बंधुंना फडणवीस यांचा टोला, बीड लैंगिक छळाप्रकरणात मोठी अपडेटसह वाचा महत्वाच्या घडामोडी</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/prashasan/sunil-mane-accuses-manisha-mhaiskar-corruption-eknath-shinde-pwd-gs97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-30-june-2025-live-updates-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-uddhav-thackeray-devendra-fadnavis-shivsena-ubt-kolhapur-vidarbha-as11</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE 9 January 2025 : राज्यपाल नियुक्त 12 आमदारांबाबतची याचिका फेटाळली</t>
+          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Top Marathi News Today: अखेर कोकाटेंचं खातं बदललच;आता दिली 'या' खात्याची जबाबदारी</t>
+          <t>येत्या काळात आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरु करणार - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
+          <t>https://mahasamvad.in/165634/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>आरोग्य क्षेत्रातील दर्जा व क्षमता वृद्धीसाठी पीएचएफआय, आयएमएमएएसटी यांच्यासोबत महाराष्ट्र शासनाचा सामंजस्य करार</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
+          <t>https://mahasamvad.in/173797/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>आता चिंता जलजन्य आजारांची; औषधांचा पुरेसा साठा राज्यात उपलब्ध करण्याचे आरोग्य मंत्री आबिटकर यांचे आदेश</t>
+          <t>अवयवदान इच्छा नोंदवणे ही एक जबाबदारी बनायला हवी - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री तथा पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/waterborne-diseases-health-minister-abitkar-orders-medicine-stock</t>
+          <t>https://mahasamvad.in/175714/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>केंद्रीय आरोग्य सेवा योजनेच्या दरांमध्ये सुधारणा करणार – केंद्रीय मंत्री मनसुख मांडविया</t>
+          <t>सर्वांगीण निरोगी महाराष्ट्र घडविण्यासाठी राज्य शासन कटिबद्ध- उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172749/</t>
+          <t>https://mahasamvad.in/163359/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>३ ते १५ ऑगस्ट २०२५ या कालावधीत अवयवदान पंधरवडा साजरा होणार – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>‘रुग्ण सेवा हीच ईश्वर सेवा; जनसामान्यांची सेवा हाच धर्म’ – उपमुख्यमंत्री एकनाथ शिंदे</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173717/</t>
+          <t>https://mahasamvad.in/155268/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>विधानपरिषद प्रश्नोत्तरे</t>
+          <t>राज्याच्या इतिहासात पहिल्यांदाच 'आरोग्य विषयक धोरण' : मंत्री प्रकाश आबिटकर -</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172235/</t>
+          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant: कोल्हापुर की 'महादेवी' हथिनी को वनतारा से वापस लाने की मांग तेज, लोगों ने किया मौन मार्च</t>
+          <t>Rain causes road closures, travel delays in Satara and Kolhapur districts</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>पुणे से देश की आर्थिक राजधानी पहुंचा गिलियन बैरे सिंड्रोम, मुंबई में जीबीएस का पहला केस</t>
+          <t>Kolhapur civic body yet to acquire Jayprabha Studio</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
+          <t>Double Maharashtra Kesari Chandrahar Patil Joins Shinde's Shiv Sena</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
+          <t>https://english.lokshahi.com/politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Raj-Uddhav Thackeray Vijayi Rally : दोन भाऊ एकत्र आल्याने सुप्रिया सुळेंचा आनंद गगनात मावेना, मुश्रीफ बोलताच आबिटकरांनाही हसू आवरेना...</t>
+          <t>Maharashtra's Rs 123 crore mortuary van project stuck, 132 new vehicles unused</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/raj-uddhav-thackeray-brothers-vijayi-rally-supriya-sule-criticized-by-hasan-mushrif-and-prakash-abitkar-as11-rg93</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : ठाकरे बंधुंना फडणवीस यांचा टोला, बीड लैंगिक छळाप्रकरणात मोठी अपडेटसह वाचा महत्वाच्या घडामोडी</t>
+          <t>Maharashtra Politics: Senior NCP Minister Hasan Mushrif Steps Down As Washims Guardian Minister</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-30-june-2025-live-updates-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-uddhav-thackeray-devendra-fadnavis-shivsena-ubt-kolhapur-vidarbha-as11</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-senior-ncp-minister-hasan-mushrif-steps-down-as-washims-guardian-minister</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
+          <t>Gokul Dudh Sangh : ‘गोकुळ’मध्ये पुन्हा अरुणोदय की नव्या रक्ताला संधी; नव्या अध्यक्ष निवडीसाठी घडामोडींना वेग, पाटील-मुश्रीफांचा पुढील डाव काय?</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-arun-dengle-get-president-of-gokul-dudh-sangh-or-will-give-a-chance-to-new-blood-vd83-rg-93</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>कोरोनाचा धोका नाही, पण नागरिकांनी काळजी घेणं गरजेचं - आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>kolhapur | जिल्ह्यातील सहकारावर कागलचे वर्चस्व</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/two-covid-patients-die-of-comorbidities-at-mumbai-kem-hospital-health-minister-prakash-abitkar-says-no-need-to-panic-maharashtra-news-mhs25052003840</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mushrif-establishes-dominance-over-key-cooperative-institutions-in-district-ap84</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>आरोग्य क्षेत्रातील दर्जा व क्षमता वृद्धीसाठी पीएचएफआय, आयएमएमएएसटी यांच्यासोबत महाराष्ट्र शासनाचा सामंजस्य करार</t>
+          <t>Kolhapur Politics : प्रकाश आबिटकरांना स्वकियांचेचं आव्हान, भाजप, अजित पवार गटाचा विरोध; जिल्हा नियोजन समितीवरून पडणार ठिणगी</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173797/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>सर्वांगीण निरोगी महाराष्ट्र घडविण्यासाठी राज्य शासन कटिबद्ध- उपमुख्यमंत्री अजित पवार</t>
+          <t>पुण्याची हद्दवाढ 27 वेळा, कोल्हापूरची एकदाही नाही; शहर-ग्रामीण विकासासाठी हद्दवाढ करावीच लागेल</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163359/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/inauguration-of-kolhapur-first-conference</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>‘रुग्ण सेवा हीच ईश्वर सेवा; जनसामान्यांची सेवा हाच धर्म’ – उपमुख्यमंत्री एकनाथ शिंदे</t>
+          <t>कोल्हापुरातील अंबाबाई मंदिराचा १,४९६, जोतिबाचा २६० कोटींचा विकास आराखडा मंजूर</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155268/</t>
+          <t>https://www.lokmat.com/kolhapur/development-plan-of-ambabai-temple-in-kolhapur-approved-at-rs-1496-crore-jyotiba-temple-at-rs-260-crore-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Rain causes road closures, travel delays in Satara and Kolhapur districts</t>
+          <t>विकासकामे दर्जात्मकच हवीत, तकलादू नकोत</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-ajit-pawar-said-about-the-kolhapur-development-works</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Kolhapur civic body yet to acquire Jayprabha Studio</t>
+          <t>‘कोल्हापूर फर्स्ट’ मधून कोल्हापूरच्या शाश्वत आणि सर्वांगीण विकासासाठी विचारमंथन</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
+          <t>https://mahasamvad.in/158746/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Double Maharashtra Kesari Chandrahar Patil Joins Shinde's Shiv Sena</t>
+          <t>भुदरगड तालुक्यातील सात धबधबे म्हणजे निसर्गात लपलेला अद्भुत खजिना – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
+          <t>https://mahasamvad.in/172859/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Maharashtra's Rs 123 crore mortuary van project stuck, 132 new vehicles unused</t>
+          <t>इचलकरंजीसह परिसराच्या विकासासाठी सर्वतोपरी मदत करु – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
+          <t>https://mahasamvad.in/166821/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Senior NCP Minister Hasan Mushrif Steps Down As Washims Guardian Minister</t>
+          <t>जिल्हा वार्षिक योजनेतील निधी गुणवत्ता पूर्ण कामांवरच खर्च करा-उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-senior-ncp-minister-hasan-mushrif-steps-down-as-washims-guardian-minister</t>
+          <t>https://mahasamvad.in/155119/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Kolhapur : 20 माजी नगरसेवक शिंदे शिवसेनेत; सतेज पाटील यांना धक्का</t>
+          <t>Madhuri Elephant Row: Fadnavis Backs Legal Move to Bring Elephant Back to Kolhapur</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/20-former-corporators-join-shinde-shivsena-setback-to-satej-patil-dc95</t>
+          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Gokul Dudh Sangh : ‘गोकुळ’मध्ये पुन्हा अरुणोदय की नव्या रक्ताला संधी; नव्या अध्यक्ष निवडीसाठी घडामोडींना वेग, पाटील-मुश्रीफांचा पुढील डाव काय?</t>
+          <t>"No one has to worry": Maharashtra Health Minister Prakash Abitkar on HMPV virus</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-arun-dengle-get-president-of-gokul-dudh-sangh-or-will-give-a-chance-to-new-blood-vd83-rg-93</t>
+          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>शक्तिपीठसाठी भूसंपादन केल्यास शिवसेना स्टाईलनं उत्तर देऊ; चंद्रहार पाटलांचा इशारा</t>
+          <t>Sassoon Hospital awarded for organ transplant efforts - Hindustan Times</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/after-kolhapur-the-project-is-also-being-opposed-from-sangli-therefore-if-land-is-acquired-for-highway-we-will-respond-in-shiv-sena-style-chandrahar-patil-maharashtra-news-mhs25012703384</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : प्रकाश आबिटकरांना स्वकियांचेचं आव्हान, भाजप, अजित पवार गटाचा विरोध; जिल्हा नियोजन समितीवरून पडणार ठिणगी</t>
+          <t>AIIMS Nagpur Bags 3 More Awards For Excellence In Organ Donation</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>कोल्हापुरातील अंबाबाई मंदिराचा १,४९६, जोतिबाचा २६० कोटींचा विकास आराखडा मंजूर</t>
+          <t>Preparations on in full swing after high court approved circuit bench in Kolhapur</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/development-plan-of-ambabai-temple-in-kolhapur-approved-at-rs-1496-crore-jyotiba-temple-at-rs-260-crore-a-a746/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>विकासकामे दर्जात्मकच हवीत, तकलादू नकोत</t>
+          <t>Kolhapur residents hold silent march, seek return of elephant Mahadevi from Gujarat’s Vantara</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-ajit-pawar-said-about-the-kolhapur-development-works</t>
+          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>‘कोल्हापूर फर्स्ट’ मधून कोल्हापूरच्या शाश्वत आणि सर्वांगीण विकासासाठी विचारमंथन</t>
+          <t>Maharashtra Live News 8th August 2025 : गोपीचंद पडळकर शरणू हांडेंच्या भेटीला रुग्णालयात</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158746/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>इचलकरंजीसह परिसराच्या विकासासाठी सर्वतोपरी मदत करु – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>राज्यात अवयवदान पंधरवड्याला प्रारंभ</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166821/</t>
+          <t>https://www.newsonair.gov.in/mr/organ-donation-fortnight-begins-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>जिल्हा वार्षिक योजनेतील निधी गुणवत्ता पूर्ण कामांवरच खर्च करा-उपमुख्यमंत्री अजित पवार</t>
+          <t>Maharashtra News: स्वातंत्र्य दिनाचा मुख्य शासकीय समारोह मुंबईत; पाहा कोण कुठे करणार ध्वजारोहण, संपूर्ण यादी Independence Day main government ceremony will be held in Mumbai; See who will hoist the flag where?</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155119/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>कोल्हापूर चित्रनगरीत पोस्ट प्रोडक्शनसाठी एफटीआयमार्फत चित्रपट शिक्षणाला सुरुवात होणार</t>
+          <t>Maharashtra Live Updates : पंकजा मुंडेंकडे दाद मागणाऱ्या आंदोलकाच्या कमरेत पोलिस अधिकाऱ्यानेच घातली लाथ</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170747/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-15-august-2025-latest-marathi-political-news-eknath-shinde-aaditya-thackeray-bdd-chawl-redevelopment-best-election-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-ajit-pawar-devendra-fadnavis-uddhav-thackeray-india-alliance-mns-shivsena-kabutarkhana-dhananjay-munde-pm-modi-speech-live-79th-independence-day</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Madhuri Elephant Row: Fadnavis Backs Legal Move to Bring Elephant Back to Kolhapur</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा झटपट आढावा</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>"No one has to worry": Maharashtra Health Minister Prakash Abitkar on HMPV virus</t>
+          <t>Independence Day 2025 : स्वातंत्र्यदिनानिमित्त तुमच्या जिल्ह्यात कोण करणार ध्वजारोहण?; वाचा यादी</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
+          <t>https://puneprimenews.com/pune/independence-day-2025-who-will-hoist-the-flag-in-your-district-on-independence-day-read-the-list/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Sassoon Hospital awarded for organ transplant efforts - Hindustan Times</t>
+          <t>Kolhapur Circuit Bench | कोल्हापूर सर्किट बेंचचे सरन्यायाधीशांच्या हस्ते दिमाखात उद्घाटन; कोल्हापुरात मोठा उत्साह</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inaugurated-by-the-chief-justice-great-excitement-in-kolhapur-an01</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>AIIMS Nagpur Bags 3 More Awards For Excellence In Organ Donation</t>
+          <t>Maharashtra Mumbai Rain Live Updates, 19 August 2025 : मुंबईला पावसाचा तडाखा, चेंबूरमध्ये मोनोरेल थांबली; बचावकार्याचा थरार जारी</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Preparations on in full swing after high court approved circuit bench in Kolhapur</t>
+          <t>Devendra Fadnavis : ‘आपले सरकार’ सेवांतील विलंबावर आळा घालण्यासाठी अधिकाऱ्यांवर दररोज दंड लावण्याचे निर्देश</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
+          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Kolhapur residents hold silent march, seek return of elephant Mahadevi from Gujarat’s Vantara</t>
+          <t>मिशन माधुरी हत्तीणीची घरवापसी! सतेज पाटलांच्या मोहिमेत 2 लाख 4 हजार 421 नागरिकांच्या</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/mission-madhuri-elephant-2-lakh-4-thousand-421-people-signatures-in-satej-patil-campaign-public-outrage-will-reach-the-president-marathi-news-update-1374246</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Maharashtra Live News 8th August 2025 : गोपीचंद पडळकर शरणू हांडेंच्या भेटीला रुग्णालयात</t>
+          <t>Madhuri Elephant | 'माधुरी हत्तीणी'साठी राज्य सरकार आणि मठ सुप्रीम कोर्टात याचिका दाखल करणार</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-government-and-nandani-math-will-file-petition-in-supreme-court-for-madhuri-elephant-db79</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>राज्यात अवयवदान पंधरवड्याला प्रारंभ</t>
+          <t>तिजोरीतील खडखडाटामुळे ५० वर्षानंतर सरकारनं घेतला महत्त्वाचा निर्णय, तळीरामांसह व्यावसायिकांसाठी नवीन संधी</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/organ-donation-fortnight-begins-in-the-state/</t>
+          <t>https://www.etvbharat.com/mr/!state/new-wine-shop-license-in-maharashtra-ajit-pawar-lead-committee-to-issue-new-liquor-licenses-to-328-wine-shops-to-increase-revenue-in-state-treasury-maharashtra-news-mhs25071302746</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Maharashtra News: स्वातंत्र्य दिनाचा मुख्य शासकीय समारोह मुंबईत; पाहा कोण कुठे करणार ध्वजारोहण, संपूर्ण यादी Independence Day main government ceremony will be held in Mumbai; See who will hoist the flag where?</t>
+          <t>नांदणी मठाची ‘माधुरी’ परत येणार? वनताराच्या CEO ने कोल्हापूरकरांना दिली ग्वाही</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : पंकजा मुंडेंकडे दाद मागणाऱ्या आंदोलकाच्या कमरेत पोलिस अधिकाऱ्यानेच घातली लाथ</t>
+          <t>हद्दवाढीचा प्रस्ताव महापालिकेकडून सरकारकडे सादर ! कोल्हापूरसाठी लवकरच तीन आनंदाच्या बातम्या !!</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-15-august-2025-latest-marathi-political-news-eknath-shinde-aaditya-thackeray-bdd-chawl-redevelopment-best-election-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-ajit-pawar-devendra-fadnavis-uddhav-thackeray-india-alliance-mns-shivsena-kabutarkhana-dhananjay-munde-pm-modi-speech-live-79th-independence-day</t>
+          <t>https://maharashtranews1.com/The-proposal-for-the-extension-has-been-sent-from-the-municipality-to-the-government--Three-good-news-coming-soon-for-Kolhapur--</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा झटपट आढावा</t>
+          <t>बेमुदत कामबंद आंदोलनास सुरुवात; NHM अंतर्गत १० हजारांहून अधिक अधिकारी-कर्मचारी रस्त्यावर</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
+          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Independence Day 2025 : स्वातंत्र्यदिनानिमित्त तुमच्या जिल्ह्यात कोण करणार ध्वजारोहण?; वाचा यादी</t>
+          <t>Madhuri Elephant | माधुरी हत्तीण परत येणार? कोल्हापुरकरांना मुख्यमंत्र्यांचा मोठा शब्द</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/independence-day-2025-who-will-hoist-the-flag-in-your-district-on-independence-day-read-the-list/</t>
+          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench | कोल्हापूर सर्किट बेंचचे सरन्यायाधीशांच्या हस्ते दिमाखात उद्घाटन; कोल्हापुरात मोठा उत्साह</t>
+          <t>युवाशक्ती दहीहंडीचा थरार २४ ऑगस्टला रंगणार, प्रथम क्रमांकाला ३ लाख रूपयांचे बक्षीस</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inaugurated-by-the-chief-justice-great-excitement-in-kolhapur-an01</t>
+          <t>https://maharashtranews1.com/The-excitement-of-Youth-Power-Dahi-Handi-will-take-place-on-August-24--with-a-prize-of-3-lakh-rupees-for-the-first-place-</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Maharashtra Mumbai Rain Live Updates, 19 August 2025 : मुंबईला पावसाचा तडाखा, चेंबूरमध्ये मोनोरेल थांबली; बचावकार्याचा थरार जारी</t>
+          <t>Kolhapur Circuit Bench : न्यायाच्या कोल्हापूर पर्वाला सुरुवात; सरन्यायाधीशांच्‍या उपस्थितीत सर्किट बेंचचे होणार उद्घाटन</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
+          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Maharashtra Live News Update: अंधेरीतून बस कोकणासाठी रवाना; गणेश भक्तांसाठी मनसेकडून विशेष सोय</t>
+          <t>Hindustani Bhau : 'तुम्ही जेवता ना @# तर नाही खात ना?'; माधुरी हत्तीण वादात हिंदुस्थानी भाऊची उडी, Video व्हायरल</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-24th-aug-2025-pm-narendra-modi-rahul-gandhi-maharashtra-politics-eknath-shinde-uddhav-thackeray-raj-thackeray-devendra-fadnavis-ajit-pawar-mumbai-thane-nagpur-pune-nashik-weather-forecast-rain-update-rains-live-news-today-pune-local-crime-top-headlines</t>
+          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>मिशन माधुरी हत्तीणीची घरवापसी! सतेज पाटलांच्या मोहिमेत 2 लाख 4 हजार 421 नागरिकांच्या</t>
+          <t>न्यायाच्या कोल्हापूर पर्वाला उद्यापासून सुरुवात</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mission-madhuri-elephant-2-lakh-4-thousand-421-people-signatures-in-satej-patil-campaign-public-outrage-will-reach-the-president-marathi-news-update-1374246</t>
+          <t>https://ratnagirikhabardar.com/news/74101/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : ‘आपले सरकार’ सेवांतील विलंबावर आळा घालण्यासाठी अधिकाऱ्यांवर दररोज दंड लावण्याचे निर्देश</t>
+          <t>रत्नागिरी : राष्ट्रीय आरोग्य अभियान (एनआरएचएम) कर्मचाऱ्यांचा उद्यापासून बेमुदत संप</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
+          <t>https://ratnagirikhabardar.com/news/74350/</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Madhuri Elephant | 'माधुरी हत्तीणी'साठी राज्य सरकार आणि मठ सुप्रीम कोर्टात याचिका दाखल करणार</t>
+          <t>कोल्हापूर सर्किट बेंच इमारतीचे दिमाखदार उद्घाटन</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-government-and-nandani-math-will-file-petition-in-supreme-court-for-madhuri-elephant-db79</t>
+          <t>https://ratnagirikhabardar.com/news/74156/</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>तिजोरीतील खडखडाटामुळे ५० वर्षानंतर सरकारनं घेतला महत्त्वाचा निर्णय, तळीरामांसह व्यावसायिकांसाठी नवीन संधी</t>
+          <t>Indian city faces rising cases of GBS disease</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/new-wine-shop-license-in-maharashtra-ajit-pawar-lead-committee-to-issue-new-liquor-licenses-to-328-wine-shops-to-increase-revenue-in-state-treasury-maharashtra-news-mhs25071302746</t>
+          <t>https://www.dw.com/en/indian-city-faces-rising-cases-of-gbs-disease/a-71430960</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>नांदणी मठाची ‘माधुरी’ परत येणार? वनताराच्या CEO ने कोल्हापूरकरांना दिली ग्वाही</t>
+          <t>Maharashtra records second suspected GBS death, cases rise to 127</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
+          <t>https://ddnews.gov.in/en/maharashtra-records-second-suspected-gbs-death-cases-rise-to-127/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>हद्दवाढीचा प्रस्ताव महापालिकेकडून सरकारकडे सादर ! कोल्हापूरसाठी लवकरच तीन आनंदाच्या बातम्या !!</t>
+          <t>NHM employees begin indefinite strike, healthcare services impacted</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-proposal-for-the-extension-has-been-sent-from-the-municipality-to-the-government--Three-good-news-coming-soon-for-Kolhapur--</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>बेमुदत कामबंद आंदोलनास सुरुवात; NHM अंतर्गत १० हजारांहून अधिक अधिकारी-कर्मचारी रस्त्यावर</t>
+          <t>Of 1.4L+ docs in Maha, only 10k opt in for ‘KYD’ QR code scheme</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Madhuri Elephant | माधुरी हत्तीण परत येणार? कोल्हापुरकरांना मुख्यमंत्र्यांचा मोठा शब्द</t>
+          <t>Daga hospital’s NICU ranked best in Maharashtra at state health awards</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/daga-hospitals-nicu-ranked-best-in-maharashtra-at-state-health-awards/articleshow/120074378.cms</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>युवाशक्ती दहीहंडीचा थरार २४ ऑगस्टला रंगणार, प्रथम क्रमांकाला ३ लाख रूपयांचे बक्षीस</t>
+          <t>Thousands participate in silent march to seek Mahadevi's return from Vantara</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-excitement-of-Youth-Power-Dahi-Handi-will-take-place-on-August-24--with-a-prize-of-3-lakh-rupees-for-the-first-place-</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench : न्यायाच्या कोल्हापूर पर्वाला सुरुवात; सरन्यायाधीशांच्‍या उपस्थितीत सर्किट बेंचचे होणार उद्घाटन</t>
+          <t>Exclusive: राज्यात राष्ट्रीय बाल स्वास्थ्य कार्यक्रमाची ऐसीतैसी!</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
+          <t>https://www.tendernama.com/scam-scanner/maharashtra-health-department-tender-scam</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Hindustani Bhau : 'तुम्ही जेवता ना @# तर नाही खात ना?'; माधुरी हत्तीण वादात हिंदुस्थानी भाऊची उडी, Video व्हायरल</t>
+          <t>गतवर्षी प्रमाणे यंदाही वारकरी दिंड्यांना सरकार अनुदान देणार : आचार्य तुषार भोसले</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>न्यायाच्या कोल्हापूर पर्वाला उद्यापासून सुरुवात</t>
+          <t>माधुरी हत्तीण परत आणण्याबाबत राज्य शासनाने घेतला ‘हा’ मोठा निर्णय; वाचा सविस्तर…</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74101/</t>
+          <t>https://puneprimenews.com/mumbai/the-state-government-took-this-big-decision-to-bring-back-madhuri-the-elephant-read-in-detail/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>रत्नागिरी : राष्ट्रीय आरोग्य अभियान (एनआरएचएम) कर्मचाऱ्यांचा उद्यापासून बेमुदत संप</t>
+          <t>अवयवदान पंधरवड्यास सुरुवात; आजपासून राज्यात जनजागृतीपर विविध उपक्रम</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74350/</t>
+          <t>https://mahasamvad.in/174294/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>कोल्हापूर सर्किट बेंच इमारतीचे दिमाखदार उद्घाटन</t>
+          <t>न्यायाच्या कोल्हापूर पर्वाला १७ ऑगस्टपासून सुरुवात</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74156/</t>
+          <t>https://mahasamvad.in/175429/</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Indian city faces rising cases of GBS disease</t>
+          <t>महादेवी हत्तीण परत नांदणीत येणार? राज्य सरकारचा सर्वोच्च न्यायालयात पुनरावलोकन याचिकेचा निर्णय</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.dw.com/en/indian-city-faces-rising-cases-of-gbs-disease/a-71430960</t>
+          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>NHM employees begin indefinite strike, healthcare services impacted</t>
+          <t>Delay in transfer of med head raises concerns over management of mental hospital</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Of 1.4L+ docs in Maha, only 10k opt in for ‘KYD’ QR code scheme</t>
+          <t>Maharashtra CM instructs Health Department to cover GBS treatment under State insurance scheme</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/chief-minister-instructs-health-department-to-cover-gbs-treatment-under-mjpjay/article69151508.ece</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Daga hospital’s NICU ranked best in Maharashtra at state health awards</t>
+          <t>Pregnant woman denied hospital treatment in Pune, dies; probe launched</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/daga-hospitals-nicu-ranked-best-in-maharashtra-at-state-health-awards/articleshow/120074378.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Thousands participate in silent march to seek Mahadevi's return from Vantara</t>
+          <t>Narayana Health SRCC Children’s Hospital observes World Child Obesity Day 2025 in collaboration with Gen-XL Foundation</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
+          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>First Phase of ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic 5 Guinness World Records</t>
+          <t>Latest Marathi News Updates : देश-विदेशासह राज्यात दिवसभरात काय घडलं? वाचा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/first-phase-of-desh-ka-prakriti-parikshan-abhiyaan-concludes-with-historic-5-guinness-world-records/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Exclusive: राज्यात राष्ट्रीय बाल स्वास्थ्य कार्यक्रमाची ऐसीतैसी!</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 25 मार्च 2025 | मंगळवार</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/scam-scanner/maharashtra-health-department-tender-scam</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-15-march-2025-eknath-shinde-ajit-pawar-maharashtra-politics-marathi-news-1351019</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>गतवर्षी प्रमाणे यंदाही वारकरी दिंड्यांना सरकार अनुदान देणार : आचार्य तुषार भोसले</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 12 मे 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>न्यायाच्या कोल्हापूर पर्वाला १७ ऑगस्टपासून सुरुवात</t>
+          <t>Breaking News Today : महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175429/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>माहिती व जनसंपर्क महासंचालनालय, महाराष्ट्र शासन | Page 81</t>
+          <t>अधिवेशनात गाजला बीड आरोग्य विभागातील घोटाळा; जिल्हा शल्य चिकित्सकांचं निलंबन</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/81/?m=0</t>
+          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>माहिती व जनसंपर्क महासंचालनालय, महाराष्ट्र शासन | Page 37</t>
+          <t>गुलाल खोबऱ्याची उधळण; जोतिबाच्या नावानं चांगभलंच्या गजरात चैत्र यात्रेला सुरुवात</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/37/?m=0</t>
+          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीण परत नांदणीत येणार? राज्य सरकारचा सर्वोच्च न्यायालयात पुनरावलोकन याचिकेचा निर्णय</t>
+          <t>पाच लाख भाविकांच्या उपस्थितीत दख्खनचा राजा जोतिबाची चैत्र यात्रा, डोंगरावर 'चांगभलं'चा गजर</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
+          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Maharashtra CM instructs Health Department to cover GBS treatment under State insurance scheme</t>
+          <t>राजर्षी छत्रपती शाहू महाराजांची जयंती उत्साहात साजरी; शरद पवारांसह विविध मान्यवरांनी केलं अभिवादन</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/chief-minister-instructs-health-department-to-cover-gbs-treatment-under-mjpjay/article69151508.ece</t>
+          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Pregnant woman denied hospital treatment in Pune, dies; probe launched</t>
+          <t>Maharashtra cancels registration of 258 Private Hospitals</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
+          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/maharashtra-cancels-registration-of-258-private-hospitals-152138</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Narayana Health SRCC Children’s Hospital observes World Child Obesity Day 2025 in collaboration with Gen-XL Foundation</t>
+          <t>Maharashtra govt to provide free cancer vaccine for girls, takes precautions against bird flu</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Kolhapur Corona Update : महाराष्ट्राच्या आरोग्याची चावी हाती असलेल्या दोन मंत्र्यांच्या कोल्हापुरात</t>
+          <t>First Phase of ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic 5 Guinness World Records</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
+          <t>https://pragativadi.com/first-phase-of-desh-ka-prakriti-parikshan-abhiyaan-concludes-with-historic-5-guinness-world-records/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>kolhapur News : अधिकार्‍यांनी नावीन्यतेसह गुणवत्तापूर्ण कामे करावीत</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-all-departments-in-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 25 मार्च 2025 | मंगळवार</t>
+          <t>Dairy Farming: आदर्श गोठा पुरस्काराचा राज्यभरात आदर्श घ्यावा; पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-15-march-2025-eknath-shinde-ajit-pawar-maharashtra-politics-marathi-news-1351019</t>
+          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Breaking News Today : महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
+          <t>कोल्हापूर : गावठाणाबाहेरील मिळकतींनाही मिळणार प्रॉपर्टी कार्ड</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-property-cards-for-non-gaothan-properties-dc95</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Mumbai: देवेंद्र फडणवीसांचा मोठा निर्णय, आता घरबसल्या करता येणार दस्त नोंदणी वन</t>
+          <t>पत्रकारांच्या आरोग्याच्या प्रश्नावर लवकरच बैठक घेणार – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
+          <t>https://mahasamvad.in/170017/</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>गुलाल खोबऱ्याची उधळण; जोतिबाच्या नावानं चांगभलंच्या गजरात चैत्र यात्रेला सुरुवात</t>
+          <t>PMC felicitated for ABDM Excellence</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
+          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Minister List: मुख्यमंत्री देवेंद्र फडणवीस यांच्याकडे कुठले पालकत्व, मुंडे यांना...</t>
+          <t>Cashless Treatment of Up to Rs 1 Lakh Announced for Accident Victims in Maharashtra</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/guardian-minister-of-devendra-fadnavis-government-announced-1336526.html</t>
+          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>मोठी बातमी! पालकमंत्र्यांची यादी जाहीर, धनंजय मुंडेंना मोठा धक्का, बीडचे नवे पालकमंत्री कोण?</t>
+          <t>मोठी बातमी ! अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार, आरोग्य खात्याचा महत्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/probable-list-of-guardian-minister-announced-dhananjay-munden-is-responsible-for-this-district-1336522.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-launches-cashless-accident-treatment-up-to-1-lakh-1387143.html</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Top Marathi News Today Live: PMPML बसदरवाढीवरून प्रवाश्यांमध्ये संताप, दर कमी करण्याची मागणी</t>
+          <t>महात्मा फुले जनआरोग्य योजनेबाबत आरोग्यमंत्र्यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-sports-crime-national-international-lifestyle-news-898945.html</t>
+          <t>https://www.loksatta.com/pune/health-minister-big-announcement-regarding-mahatma-phule-jan-arogya-yojana-pune-print-news-amy-95-5251004/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Kolhapur News: उद्योजकाच्या लेकाचा जीव गेला, १२ लाखांच्या बाईकचा चेंदामेंदा, ७० हजारांच्या हेल्मेटचा चुराडा</t>
+          <t>महात्मा ज्योतिराव फुले जन आरोग्य योजनेचा लाभ जास्तीत जास्त लाभार्थ्यांपर्यंत पोहोचवा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-businessman-son-died-in-horrifying-accident-with-car-expensive-bike-and-helmet-broken-into-pieces/articleshow/120491249.cms</t>
+          <t>https://mahasamvad.in/151398/</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>पाच लाख भाविकांच्या उपस्थितीत दख्खनचा राजा जोतिबाची चैत्र यात्रा, डोंगरावर 'चांगभलं'चा गजर</t>
+          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
+          <t>https://mahasamvad.in/154371/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>राजर्षी छत्रपती शाहू महाराजांची जयंती उत्साहात साजरी; शरद पवारांसह विविध मान्यवरांनी केलं अभिवादन</t>
+          <t>Maharashtra CM Fadnavis orders special arrangements for treating GBS patients</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>कौस्तुभ गणबोटे आणि संतोष जगदाळे यांच्या पार्थिवावर अंत्यसंस्कार; कुटुंबीयांचा आक्रोश, पाकिस्तानविरोधात घोषणाबाजी</t>
+          <t>Maharashtra Plans Bigger Organ Transplant Budget Under MJPJAY; Wadia Hospital Gets Pediatric Heart Transplant</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/last-rites-for-kaustubh-ganbote-and-santosh-jagdale-from-pune-who-died-in-pahalgam-terror-attack-maharashtra-news-mhs25042400578</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-plans-bigger-organ-transplant-budget-under-mjpjay-wadia-hospital-gets-pediatric-heart-transplant-license</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>गुलाल खोबऱ्याची उधळण, चांगभलं चा गजर, दख्खनचा राजा जोतिबाच्या यात्रेला सुरूवात</t>
+          <t>महात्मा जोतिराव फुले जनआरोग्य योजना ठप्प</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/jotiba-yatra-in-kolhapur-has-begun-from-today/articleshow/120201841.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mahatma-jyotirao-phule-janarogya-yojana-halted</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Maharashtra cancels registration of 258 Private Hospitals</t>
+          <t>जागतिक आरोग्य दिनी विविध आरोग्य योजनांचा शुभारंभ</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/maharashtra-cancels-registration-of-258-private-hospitals-152138</t>
+          <t>https://mahasamvad.in/161521/</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Maharashtra govt to provide free cancer vaccine for girls, takes precautions against bird flu</t>
+          <t>GBS Outbreak in Pune: Citizens Confront Central Health Team Over Alleged Inspection Failure</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
+          <t>https://www.thebridgechronicle.com/news/gbs-outbreak-in-pune-citizens-confront-central-health-team-over-alleged-inspection-failure</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>कोल्हापूर : गावठाणाबाहेरील मिळकतींनाही मिळणार प्रॉपर्टी कार्ड</t>
+          <t>Pune Pregnant Woman's Death: Preliminary Report Highlights Negligence by Deenanath Mangeshkar Hospital</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-property-cards-for-non-gaothan-properties-dc95</t>
+          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Dairy Farming: आदर्श गोठा पुरस्काराचा राज्यभरात आदर्श घ्यावा; पालकमंत्री आबिटकर</t>
+          <t>Pune: शहरात 76 खासगी रुग्णालयांना नोटीस</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
+          <t>https://pudhari.news/maharashtra/pune/notice-to-76-private-hospitals-in-the-city</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Cashless Treatment of Up to Rs 1 Lakh Announced for Accident Victims in Maharashtra</t>
+          <t>MLA Bhimrao Tapkir : सर्व पाणीपुरवठा स्त्रोतांचे नियमित क्लोरीनेशन करून त्यावर देखरेख ठेवा; जीबीएसबाबत उपाययोजनेचे दिले आदेश</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
+          <t>https://www.esakal.com/pune/regular-chlorination-of-all-water-supply-sources-ordered-by-gbs-for-safety-mla-bhimrao-tapkir-khadakwasla-pjp78</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>मोठी बातमी ! अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार, आरोग्य खात्याचा महत्वपूर्ण निर्णय</t>
+          <t>Pune hospital conferred 'Best BSD Award' and 'Best Organ Transplant Coordinator Award'</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-launches-cashless-accident-treatment-up-to-1-lakh-1387143.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>महात्मा फुले जनआरोग्य योजनेबाबत आरोग्यमंत्र्यांची मोठी घोषणा</t>
+          <t>Singapore tourism board partners with IndiGo to boost travel</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-big-announcement-regarding-mahatma-phule-jan-arogya-yojana-pune-print-news-amy-95-5251004/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>महात्मा ज्योतिराव फुले जन आरोग्य योजनेचा लाभ जास्तीत जास्त लाभार्थ्यांपर्यंत पोहोचवा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>अवयवदान सर्वश्रेष्ठ दान…</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151398/</t>
+          <t>https://mahasamvad.in/174716/</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Organ Donation Awareness | मरावे परी देह अन् अवयवरुपी उरावे</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154371/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/organ-donation-dr-prashant-wadikar-eight-lives-saved-sp96</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis orders special arrangements for treating GBS patients</t>
+          <t>७,५२२ अवयवदात्यांची प्रतिज्ञा; २४५ रुग्णांना नवजीवन</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
+          <t>https://www.lokmat.com/mumbai/mission-jeevan-donation-campaign-7522-donors-filled-out-an-organ-donation-pledge-and-submitted-it-to-lokmat-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Maharashtra Plans Bigger Organ Transplant Budget Under MJPJAY; Wadia Hospital Gets Pediatric Heart Transplant</t>
+          <t>विधानसभा इतर कामकाज</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-plans-bigger-organ-transplant-budget-under-mjpjay-wadia-hospital-gets-pediatric-heart-transplant-license</t>
+          <t>https://mahasamvad.in/172498/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>महात्मा जोतिराव फुले जनआरोग्य योजना ठप्प</t>
+          <t>Mahadevi Elephant Case: State Government Takes Proactive Role, Matter to Be Reconsidered in Supreme Court</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mahatma-jyotirao-phule-janarogya-yojana-halted</t>
+          <t>https://english.lokshahi.com/top-stories/mahadevi-elephant-state-governments-proactive-role-for-mahadevi-madhuri-elephant-will-be-reconsidered-in-the-supreme-court</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक; प्रस्ताव सादर करण्याचे मंत्री आबिटकर यांचे निर्देश</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/154371/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/workers-insurance-scheme-healthcare-infrastructure-prakash-abhitkar</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>जागतिक आरोग्य दिनी विविध आरोग्य योजनांचा शुभारंभ</t>
+          <t>वारी मार्गावर ९ लाखांहून अधिक वारकऱ्यांना आरोग्य सेवा</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161521/</t>
+          <t>https://mahasamvad.in/171744/</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>GBS Outbreak in Pune: Citizens Confront Central Health Team Over Alleged Inspection Failure</t>
+          <t>सार्वजनिक आरोग्य विभागाच्या जास्तीत जास्त सेवा ऑनलाईन करा – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/gbs-outbreak-in-pune-citizens-confront-central-health-team-over-alleged-inspection-failure</t>
+          <t>https://mahasamvad.in/171817/</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Delay in transfer of med head raises concerns over management of mental hospital</t>
+          <t>इंडियन इन्स्टिट्युट ऑफ पब्लिक हेल्थ आयआयटी, आयआयएमच्या धर्तीवर - Indian Institute of Public Health (IIPH) on the basis of IIT and IIM</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
+          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Pune Pregnant Woman's Death: Preliminary Report Highlights Negligence by Deenanath Mangeshkar Hospital</t>
+          <t>Maharashtra to file review petition to bring back elephant Madhuri to Kolhapur</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-to-file-review-petition-to-bring-back-elephant-madhuri-to-kolhapur-2766892-2025-08-06</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Pune: शहरात 76 खासगी रुग्णालयांना नोटीस</t>
+          <t>Kolhapur residents hold 45-km silent march for elephant’s return | Mumbai news</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/notice-to-76-private-hospitals-in-the-city</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>MLA Bhimrao Tapkir : सर्व पाणीपुरवठा स्त्रोतांचे नियमित क्लोरीनेशन करून त्यावर देखरेख ठेवा; जीबीएसबाबत उपाययोजनेचे दिले आदेश</t>
+          <t>Thousands Participate in a Silent March to Seek Mahadevi's Return from Vantara</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/regular-chlorination-of-all-water-supply-sources-ordered-by-gbs-for-safety-mla-bhimrao-tapkir-khadakwasla-pjp78</t>
+          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Pune hospital conferred 'Best BSD Award' and 'Best Organ Transplant Coordinator Award'</t>
+          <t>Kolhapur Rises for Mahadevi: Thousands Join Silent March Demanding Elephant's Return From Vantara</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
+          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Singapore tourism board partners with IndiGo to boost travel</t>
+          <t>Silent march in Kolhapur demands return of elephant Mahadevi from Vantara</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+          <t>https://www.dynamitenews.com/national/silent-march-in-kolhapur-demands-return-of-elephant-mahadevi-from-vantara</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>अवयवदान सर्वश्रेष्ठ दान…</t>
+          <t>“Madhuri Should Come Back To The Math”: Maharashtra To File Review Petition For Elephant’s Return, Says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174716/</t>
+          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Organ Donation Awareness | मरावे परी देह अन् अवयवरुपी उरावे</t>
+          <t>‘स्मार्ट’ अंतर्गत नोंदणीकृत प्रकल्प कालबद्धरितीने पूर्ण करा – कृषी मंत्री ॲड. माणिकराव कोकाटे</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/organ-donation-dr-prashant-wadikar-eight-lives-saved-sp96</t>
+          <t>https://mahasamvad.in/167140/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>७,५२२ अवयवदात्यांची प्रतिज्ञा; २४५ रुग्णांना नवजीवन</t>
+          <t>Blood Donation : 'ई-रक्तकोष पोर्टल' गरजूंना मिळवून देणार रक्त; अफवांवर विश्वास न ठेवता बिनधास्त करा रक्तदान, वाचा रक्तदानाचे फायदे !</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mission-jeevan-donation-campaign-7522-donors-filled-out-an-organ-donation-pledge-and-submitted-it-to-lokmat-a-a1001/</t>
+          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Maharashtra govt issues directives to strengthen healthcare system</t>
+          <t>Maharashtra rains: School wall collapses in Bhilar village</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-issues-directives-to-strengthen-healthcare-system/121275010</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-rains-school-wall-collapses-in-bhilar-village/articleshow/123403288.cms</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>विधानसभा इतर कामकाज</t>
+          <t>Kolhapur Circuit Bench: सर्किट बेंचच्या उद्घाटनासाठी करवीरनगरी सज्ज</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172498/</t>
+          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant Case: State Government Takes Proactive Role, Matter to Be Reconsidered in Supreme Court</t>
+          <t>Kolhapur Circuit Bench | सर्किट बेंचचे आज उद्घाटन</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/top-stories/mahadevi-elephant-state-governments-proactive-role-for-mahadevi-madhuri-elephant-will-be-reconsidered-in-the-supreme-court</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-inauguration-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>More than 14.5k women detected with cancer-like symptoms post screening in Hingoli</t>
+          <t>Bhushan Gavai: कोल्हापूर खंडपीठ देशातील सामाजिक आणि आर्थिक न्यायासाठी मैलाचा दगड, लवकरच</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
+          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक; प्रस्ताव सादर करण्याचे मंत्री आबिटकर यांचे निर्देश</t>
+          <t>Kolhapur Circuit Bench: रस्त्यांपासून पॅचवर्कपर्यंत ते वाहतूक व्यवस्थेपर्यंत सर्किंट बेंचच्या</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/workers-insurance-scheme-healthcare-infrastructure-prakash-abhitkar</t>
+          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>वारी मार्गावर ९ लाखांहून अधिक वारकऱ्यांना आरोग्य सेवा</t>
+          <t>रत्नागिरी : शिरगाव येथे उभारणार अत्याधुनिक ग्रामीण रुग्णालय</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171744/</t>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/modern-rural-hospital-to-be-built-shirgaon-ratnagiri-dc95</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>इंडियन इन्स्टिट्युट ऑफ पब्लिक हेल्थ आयआयटी, आयआयएमच्या धर्तीवर - Indian Institute of Public Health (IIPH) on the basis of IIT and IIM</t>
+          <t>In Photos Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंच आतून आहे तरी कसं? अत्याधुनिक कोर्ट रुमची पहिली झलक</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-what-is-the-inside-of-the-kolhapur-circuit-bench-like-first-glimpse-of-the-state-of-the-art-court-room-1377632</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Maharashtra to file review petition to bring back elephant Madhuri to Kolhapur</t>
+          <t>महायुतीत पुन्हा वाद पेटणार! १५ ऑगस्टला रायगडमध्ये अदिती तटकरेंच्या हस्ते होणार ध्वजारोहण, गोगावलेंना संधी नाहीच</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-to-file-review-petition-to-bring-back-elephant-madhuri-to-kolhapur-2766892-2025-08-06</t>
+          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Kolhapur residents hold 45-km silent march for elephant’s return | Mumbai news</t>
+          <t>लोकांच्या चाळीस वर्षाच्या लढयाला यश ! कोल्हापुरात सर्किट बेंच !!</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
+          <t>https://maharashtranews1.com/Success-to-the-people-s-forty-year-struggle--Circuit-bench-in-Kolhapur--</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Thousands Participate in a Silent March to Seek Mahadevi's Return from Vantara</t>
+          <t>Transfer 34 hectares of Shendapark Land for IT Hub in Kolhapur: Ajit Pawar</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Kolhapur Rises for Mahadevi: Thousands Join Silent March Demanding Elephant's Return From Vantara</t>
+          <t>स्वातंत्र्यदिनाचा मुख्य शासकीय समारोह मुंबईत; मुख्यमंत्र्यांच्या हस्ते ध्वजारोहण</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
+          <t>https://mahasamvad.in/174988/</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Silent march in Kolhapur demands return of elephant Mahadevi from Vantara</t>
+          <t>Maharashtra: Kolhapur Residents Appeal to President To Bring Back Beloved Elephant Mahadevi</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://www.dynamitenews.com/national/silent-march-in-kolhapur-demands-return-of-elephant-mahadevi-from-vantara</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>“Madhuri Should Come Back To The Math”: Maharashtra To File Review Petition For Elephant’s Return, Says CM Devendra Fadnavis</t>
+          <t>I am driven to bring prosperity to people:, says Maharashtra deputy chief minister Eknath Shinde</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>‘स्मार्ट’ अंतर्गत नोंदणीकृत प्रकल्प कालबद्धरितीने पूर्ण करा – कृषी मंत्री ॲड. माणिकराव कोकाटे</t>
+          <t>25 ऑगस्टला कोल्हापूरात मोठा निर्णय! भावकीचा वाद मिटणार? मेहुणे-पाहुणे एक दिलाने लढणार</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167140/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ajit-pawars-kolhapur-visit-on-august-25-hasan-mushrif-likely-to-resolve-kp-patil-ay-patil-dispute-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Blood Donation : 'ई-रक्तकोष पोर्टल' गरजूंना मिळवून देणार रक्त; अफवांवर विश्वास न ठेवता बिनधास्त करा रक्तदान, वाचा रक्तदानाचे फायदे !</t>
+          <t>Patient care remains hampered as govt contemplates nurses’ demands on day 6 of strike; over 500 surgeries</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Maharashtra rains: School wall collapses in Bhilar village</t>
+          <t>Speed up work on GMCs in Washim, Bhandara, Ambernath, Palghar: Fadnavis</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-rains-school-wall-collapses-in-bhilar-village/articleshow/123403288.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: सर्किट बेंचच्या उद्घाटनासाठी करवीरनगरी सज्ज</t>
+          <t>Farmers protest against Nagpur-Goa Shaktipeeth highway, vow to block land acquisition</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
+          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/farmers-protest-against-nagpur-goa-shaktipeeth-highway-vow-to-block-land-acquisition/118975130</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench | सर्किट बेंचचे आज उद्घाटन</t>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-inauguration-today-ap84</t>
+          <t>https://businessnewsthisweek.com/business/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Bhushan Gavai: कोल्हापूर खंडपीठ देशातील सामाजिक आणि आर्थिक न्यायासाठी मैलाचा दगड, लवकरच</t>
+          <t>Maharashtra To Convert All Govt Hospitals Into Organ Retrieval Centres To Boost Donations</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-convert-all-govt-hospitals-into-organ-retrieval-centres-to-boost-donations</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: रस्त्यांपासून पॅचवर्कपर्यंत ते वाहतूक व्यवस्थेपर्यंत सर्किंट बेंचच्या</t>
+          <t>लाडक्या बहिणीच्या नादात राज्यात आरोग्य व्यवस्थेच्या चिंधड्या राज्य सरकारकडून</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
+          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>रत्नागिरी : शिरगाव येथे उभारणार अत्याधुनिक ग्रामीण रुग्णालय</t>
+          <t>Maharashtra launches Inspection drive for blood banks</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/modern-rural-hospital-to-be-built-shirgaon-ratnagiri-dc95</t>
+          <t>https://medicaldialogues.in/news/health/maharashtra-launches-inspection-drive-for-blood-banks-146154</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>In Photos Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंच आतून आहे तरी कसं? अत्याधुनिक कोर्ट रुमची पहिली झलक</t>
+          <t>Maharashtra: Over 5,000 Hospitals Found Violating Nursing Act, Face Action</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-what-is-the-inside-of-the-kolhapur-circuit-bench-like-first-glimpse-of-the-state-of-the-art-court-room-1377632</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-over-5000-hospitals-found-violating-nursing-act-face-action</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>महायुतीत पुन्हा वाद पेटणार! १५ ऑगस्टला रायगडमध्ये अदिती तटकरेंच्या हस्ते होणार ध्वजारोहण, गोगावलेंना संधी नाहीच</t>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
+          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>'महादेवी' परत कधी येणार पालकमंत्र्यांनी जाहीर करावं: सतेज पाटलांचं आव्हान, सव्वा 2 लाख सह्यांच्या पत्रांनी राष्ट्रपतींना साकडं</t>
+          <t>Satej Patil Vs Shivsena : सतेज पाटलांचे शिलेदार शिंदेंनी स्वत:कडे वळवले, निवडणुकीच्या तोंडावर कोल्हापुरात सेनेचं पारडं जड?</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/people-movement-for-bring-back-elephant-mahadevi-to-kolhapur-from-vantara-writes-letter-to-president-maharashtra-news-mhs25080204198</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>लोकांच्या चाळीस वर्षाच्या लढयाला यश ! कोल्हापुरात सर्किट बेंच !!</t>
+          <t>Eknath Shinde gives meetings a miss as row over guardian ministership continues</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Success-to-the-people-s-forty-year-struggle--Circuit-bench-in-Kolhapur--</t>
+          <t>https://indianexpress.com/article/cities/mumbai/eknath-shinde-gives-meetings-a-miss-row-over-guardian-ministership-continues-9815527/</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>स्वातंत्र्यदिनाचा मुख्य शासकीय समारोह मुंबईत; मुख्यमंत्र्यांच्या हस्ते ध्वजारोहण</t>
+          <t>Maharashtra Govt Announces Guardian Ministers List; NCP's Dhananjay Munde Dropped | Full List</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174988/</t>
+          <t>https://www.outlookindia.com/national/maharashtra-govt-announces-guardian-ministers-list-ncps-dhananjay-munde-dropped-full-list</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Maharashtra: Kolhapur Residents Appeal to President To Bring Back Beloved Elephant Mahadevi</t>
+          <t>Maharashtra govt announces names of 36 guardian ministers: Dhananjay Munde not in list, CM Fadnavis gets Gadchiroli</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-announces-names-of-36-guardian-ministers-munde-not-in-list-9786173/</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Transfer 34 hectares of Shendapark Land for IT Hub in Kolhapur: Ajit Pawar</t>
+          <t>With new move, Eknath Shinde signals fresh tussle in Mahayuti govt</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>I am driven to bring prosperity to people:, says Maharashtra deputy chief minister Eknath Shinde</t>
+          <t>kolhapur | महायुतीची सत्ता आणण्यासाठी सज्ज राहा : खा. श्रीकांत शिंदे</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mp-shrikant-shinde-says-be-ready-to-bring-mahayuti-to-power-ap84</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>25 ऑगस्टला कोल्हापूरात मोठा निर्णय! भावकीचा वाद मिटणार? मेहुणे-पाहुणे एक दिलाने लढणार</t>
+          <t>Safety of warkaris is of prime importance, and police are alert to prevent any untoward incident: Shinde</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ajit-pawars-kolhapur-visit-on-august-25-hasan-mushrif-likely-to-resolve-kp-patil-ay-patil-dispute-as11-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Patient care remains hampered as govt contemplates nurses’ demands on day 6 of strike; over 500 surgeries</t>
+          <t>Govt shielding Deenanath Mangeshkar Hospital management in the Bhise death case: Danve</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Speed up work on GMCs in Washim, Bhandara, Ambernath, Palghar: Fadnavis</t>
+          <t>Wadia hospital to offer more affordable heart transplants to children</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>PMC felicitated for ABDM Excellence</t>
+          <t>DMER to start full-time nurse recruitment in August; MSNA calls off strike after state assurances</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Farmers protest against Nagpur-Goa Shaktipeeth highway, vow to block land acquisition</t>
+          <t>Over 14,500 Women Show Cancer-Like Symptoms After Screening Drive In Hingoli</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/farmers-protest-against-nagpur-goa-shaktipeeth-highway-vow-to-block-land-acquisition/118975130</t>
+          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Maharashtra To Convert All Govt Hospitals Into Organ Retrieval Centres To Boost Donations</t>
+          <t>Pune: University Road Flyover Partially Opens on May 1; Full Completion by August</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-convert-all-govt-hospitals-into-organ-retrieval-centres-to-boost-donations</t>
+          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणीच्या नादात राज्यात आरोग्य व्यवस्थेच्या चिंधड्या राज्य सरकारकडून</t>
+          <t>Pune: Ganesh Khind Road Flyover To Partially Open For Traffic On May 1, Full Completion Expected By August</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
+          <t>https://www.thedailyjagran.com/maharashtra/pune-ganesh-khind-university-road-flyover-to-partially-open-for-traffic-on-may-1-full-completion-likely-by-august-10226940</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Maharashtra launches Inspection drive for blood banks</t>
+          <t>Maharashtra Politics Update : राज्य सरकार एसटी महामंडळासह कामगारांच्या पाठिशी : अजित पवार</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/maharashtra-launches-inspection-drive-for-blood-banks-146154</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-01-august-2025-mahayuti-vs-mahavikas-aghadi-ncp-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi-ajit-pawar-sharad-pawar-devendra-fadnavis-shivsena-ubt-sharad-pawar-mahayuti-cabinet-reshuffle-datta-bharane-new-agriculture-minister-manikrao-kokate-donald-trump-tarrif</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Maharashtra: Over 5,000 Hospitals Found Violating Nursing Act, Face Action</t>
+          <t>या जिल्ह्यात हे पालकमंत्री स्वातंत्र्य दिनी ध्वजारोहण करणार</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-over-5000-hospitals-found-violating-nursing-act-face-action</t>
+          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+          <t>Eknath Shinde : कोल्हापूर सर्किट बेंचमुळे शेकडो मैल दूर असलेला न्याय घरापर्यंत आला; शिंदेंचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Satej Patil Vs Shivsena : सतेज पाटलांचे शिलेदार शिंदेंनी स्वत:कडे वळवले, निवडणुकीच्या तोंडावर कोल्हापुरात सेनेचं पारडं जड?</t>
+          <t>सार्वजनिक बांधकाम विभागांतर्गतची कामे दर्जेदार करा -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
+          <t>https://mahasamvad.in/158717/</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Eknath Shinde gives meetings a miss as row over guardian ministership continues</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/eknath-shinde-gives-meetings-a-miss-row-over-guardian-ministership-continues-9815527/</t>
+          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister-2/2710767/</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Announces Guardian Ministers List; NCP's Dhananjay Munde Dropped | Full List</t>
+          <t>‘अवयवदान पंधरवड्या’ला राज्यभरात सुरुवात</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
-        <is>
-          <t>https://www.outlookindia.com/national/maharashtra-govt-announces-guardian-ministers-list-ncps-dhananjay-munde-dropped-full-list</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>Maharashtra govt announces names of 36 guardian ministers: Dhananjay Munde not in list, CM Fadnavis gets Gadchiroli</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-announces-names-of-36-guardian-ministers-munde-not-in-list-9786173/</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>With new move, Eknath Shinde signals fresh tussle in Mahayuti govt</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>kolhapur | महायुतीची सत्ता आणण्यासाठी सज्ज राहा : खा. श्रीकांत शिंदे</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mp-shrikant-shinde-says-be-ready-to-bring-mahayuti-to-power-ap84</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>Safety of warkaris is of prime importance, and police are alert to prevent any untoward incident: Shinde</t>
-        </is>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>Govt shielding Deenanath Mangeshkar Hospital management in the Bhise death case: Danve</t>
-        </is>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>Wadia hospital to offer more affordable heart transplants to children</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>Nurses’ strike leaves Sassoon wards deserted, administration struggles to find replacements</t>
-        </is>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>DMER to start full-time nurse recruitment in August; MSNA calls off strike after state assurances</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>Over 14,500 Women Show Cancer-Like Symptoms After Screening Drive In Hingoli</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>Pune: University Road Flyover Partially Opens on May 1; Full Completion by August</t>
-        </is>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
-        </is>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>Pune: Ganesh Khind Road Flyover To Partially Open For Traffic On May 1, Full Completion Expected By August</t>
-        </is>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>https://www.thedailyjagran.com/maharashtra/pune-ganesh-khind-university-road-flyover-to-partially-open-for-traffic-on-may-1-full-completion-likely-by-august-10226940</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>500 Surgeries Delayed at Pune’s Sassoon Hospital as Nurses' Strike in Maharashtra Government Hospitals Enters Sixth Day</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>https://www.punekarnews.in/500-surgeries-delayed-at-punes-sassoon-hospital-as-nurses-strike-in-maharashtra-government-hospitals-enters-sixth-day/</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>Maharashtra Politics Update : राज्य सरकार एसटी महामंडळासह कामगारांच्या पाठिशी : अजित पवार</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-01-august-2025-mahayuti-vs-mahavikas-aghadi-ncp-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi-ajit-pawar-sharad-pawar-devendra-fadnavis-shivsena-ubt-sharad-pawar-mahayuti-cabinet-reshuffle-datta-bharane-new-agriculture-minister-manikrao-kokate-donald-trump-tarrif</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>या जिल्ह्यात हे पालकमंत्री स्वातंत्र्य दिनी ध्वजारोहण करणार</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>माजीमंत्री बाळासाहेब थोरात यांच्या प्रयत्नातून सुरू झालेल्या 100 बेड घुलेवाडी ग्रामीण रुग्णालयात आणखी सुविधा – आ.सत्यजित तांबे</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>https://ahmednagarlive24.com/ahilyanagar-news/more-facilities-at-the-100-bed-ghulewadi-rural-hospital-started-through-the-efforts-of-former-minister-balasaheb-thorat-asst-satyajit-tambe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister-2/2710767/</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>Maharashtra: CJI Bhushan Gavai inaugurates fifth bench of Bombay HC at Kolhapur</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278515631/maharashtra-cji-bhushan-gavai-inaugurates-fifth-bench-of-bombay-hc-at-kolhapur</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>Eknath Shinde : कोल्हापूर सर्किट बेंचमुळे शेकडो मैल दूर असलेला न्याय घरापर्यंत आला; शिंदेंचे प्रतिपादन</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>Arogya Mitras to go on indefinite statewide strike from Feb 12</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>https://businessnewsthisweek.com/business/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>‘अवयवदान पंधरवड्या’ला राज्यभरात सुरुवात</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
         <is>
           <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b26885-txt-mumbai-20250803041544</t>
         </is>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,600 +515,600 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Minister Prakash Abitkar acknowledges challenges in fund availability due to Ladki Bahin</t>
+          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-prakash-abitkar-acknowledges-challenges-in-fund-availability-due-to-ladki-bahin/articleshow/120857765.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Maharashtra to request Centre to include thalassemia under National Sickle Cell Disease Programme</t>
+          <t>Minister Prakash Abitkar acknowledges challenges in fund availability due to Ladki Bahin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-request-centre-thalassemia-national-sickle-cell-disease-programme-10169293/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-prakash-abitkar-acknowledges-challenges-in-fund-availability-due-to-ladki-bahin/articleshow/120857765.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>State assures policy for rare disorder after parents protest outside Mantralaya</t>
+          <t>Maharashtra to request Centre to include thalassemia under National Sickle Cell Disease Programme</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-assures-policy-for-rare-disorder-after-parents-protest-outside-mantralaya-101745351008595.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-request-centre-thalassemia-national-sickle-cell-disease-programme-10169293/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Law to empower health officials to take action against those contaminating drinking water on cards: Abitk</t>
+          <t>New app to ensure transparency, accountability in MJPJAY scheme: Abitkar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/law-to-empower-health-officials-to-take-action-against-those-contaminating-drinking-water-on-cards-abitkar/articleshow/117867170.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/new-app-to-ensure-transparency-accountability-in-mjpjay-scheme-abitkar-101746298903204.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>New app to ensure transparency, accountability in MJPJAY scheme: Abitkar</t>
+          <t>Law to empower health officials to take action against those contaminating drinking water on cards: Abitk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/new-app-to-ensure-transparency-accountability-in-mjpjay-scheme-abitkar-101746298903204.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/law-to-empower-health-officials-to-take-action-against-those-contaminating-drinking-water-on-cards-abitkar/articleshow/117867170.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Contaminated water source near Khadakwasla likely cause for Guillain-Barré syndrome, says health minister</t>
+          <t>State orders closure of 258 pvt hosps over violations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/contaminated-water-source-near-khadakwasla-likely-cause-for-guillain-barre-syndrome-says-health-minister-9802626/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-closure-of-258-pvt-hosps-over-violations-101752780027844.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESIC Hospital in Mumbai to open in Dec, says Maharashtra public health minister Prakash Abitkar</t>
+          <t>Contaminated water source near Khadakwasla likely cause for Guillain-Barré syndrome, says health minister</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/esic-hospital-in-mumbai-to-open-in-dec-says-maharashtra-public-health-minister-prakash-abitkar/articleshow/122256849.cms</t>
+          <t>https://indianexpress.com/article/cities/pune/contaminated-water-source-near-khadakwasla-likely-cause-for-guillain-barre-syndrome-says-health-minister-9802626/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>State orders closure of 258 pvt hosps over violations</t>
+          <t>ESIC Hospital in Mumbai to open in Dec, says Maharashtra public health minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-orders-closure-of-258-pvt-hosps-over-violations-101752780027844.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/esic-hospital-in-mumbai-to-open-in-dec-says-maharashtra-public-health-minister-prakash-abitkar/articleshow/122256849.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CM assures meeting on Kolhapur HC bench demand before March 15: Abitkar</t>
+          <t>Tanisha Bhise death: As in-laws take care of twin girls, husband in ‘a daze’, can’t understand how wife passed away</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-assures-meeting-on-kolhapur-hc-bench-demand-before-march-15-abitkar/articleshow/118538307.cms</t>
+          <t>https://indianexpress.com/article/cities/pune/tanisha-bhise-pune-hospital-death-in-laws-twin-girls-9925235/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Awaiting Centre's fund share to clear docs' salaries: Maharashtra health minister Prakash Abitkar</t>
+          <t>CM assures meeting on Kolhapur HC bench demand before March 15: Abitkar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/awaiting-centres-fund-share-to-clear-docs-salaries-maharashtra-health-minister-prakash-abitkar/articleshow/118661245.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cm-assures-meeting-on-kolhapur-hc-bench-demand-before-march-15-abitkar/articleshow/118538307.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cooperative movement in Kolhapur will be enriched with the support of Sahakar Darbar: Prakash Abitkar</t>
+          <t>Awaiting Centre's fund share to clear docs' salaries: Maharashtra health minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cooperative-movement-in-kolhapur-will-be-enriched-with-the-support-of-sahakar-darbar-prakash-abitkar/articleshow/120706181.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/awaiting-centres-fund-share-to-clear-docs-salaries-maharashtra-health-minister-prakash-abitkar/articleshow/118661245.cms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Beed civil surgeon suspended over misappropriation of funds during Covid pandemic, says Maharashtra healt</t>
+          <t>Cooperative movement in Kolhapur will be enriched with the support of Sahakar Darbar: Prakash Abitkar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/beed-civil-surgeon-suspended-over-misappropriation-of-funds-during-covid-pandemic-says-maharashtra-health-minister-prakash-abitkar/articleshow/119487972.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cooperative-movement-in-kolhapur-will-be-enriched-with-the-support-of-sahakar-darbar-prakash-abitkar/articleshow/120706181.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ordinance for Mahalaxmi temple DP in 8 days, will take citizens into confidence over 4.5-acre land acquis</t>
+          <t>Beed civil surgeon suspended over misappropriation of funds during Covid pandemic, says Maharashtra healt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/ordinance-for-mahalaxmi-temple-dp-in-8-days-will-take-citizens-into-confidence-over-4-5-acre-land-acquisition-abitkar/articleshow/121196282.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/beed-civil-surgeon-suspended-over-misappropriation-of-funds-during-covid-pandemic-says-maharashtra-health-minister-prakash-abitkar/articleshow/119487972.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CMO denies staying 3.2k cr contract of ex-health minister</t>
+          <t>Ordinance for Mahalaxmi temple DP in 8 days, will take citizens into confidence over 4.5-acre land acquis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/ordinance-for-mahalaxmi-temple-dp-in-8-days-will-take-citizens-into-confidence-over-4-5-acre-land-acquisition-abitkar/articleshow/121196282.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tanisha Bhise death: As in-laws take care of twin girls, husband in ‘a daze’, can’t understand how wife passed away</t>
+          <t>Charitable hospitals must implement govt schemes, will revise treatment rates: Minister</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/tanisha-bhise-pune-hospital-death-in-laws-twin-girls-9925235/</t>
+          <t>https://indianexpress.com/article/cities/pune/charitable-hospitals-must-implement-govt-schemes-will-revise-treatment-rates-minister-10145420/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
+          <t>Health dept. launches second probe into financial transactions at Regional Mental Hospital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Charitable hospitals must implement govt schemes, will revise treatment rates: Minister</t>
+          <t>Maharashtra to run organ donation drive across state from August 3 to 15: Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/charitable-hospitals-must-implement-govt-schemes-will-revise-treatment-rates-minister-10145420/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Health dept. launches second probe into financial transactions at Regional Mental Hospital</t>
+          <t>Abitkar attributes delay in loan waiver to Ladki Bahin scheme; no mention in BJP’s poll manifesto, says S</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maharashtra to run organ donation drive across state from August 3 to 15: Health Minister Prakash Abitkar</t>
+          <t>Soon, mandatory ‘no denial policy’ for hospitals in state: DCM Pawar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abitkar attributes delay in loan waiver to Ladki Bahin scheme; no mention in BJP’s poll manifesto, says S</t>
+          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
+          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Soon, mandatory ‘no denial policy’ for hospitals in state: DCM Pawar</t>
+          <t>Woman’s death after delivery in Pune: Maharashtra sets up probe committee</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
+          <t>https://indianexpress.com/article/cities/pune/pune-hospital-pregnant-woman-dies-probe-9924556/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Woman’s death after delivery in Pune: Maharashtra sets up probe committee</t>
+          <t>Maha to relax norms for nursing homes, hospitals with up to 10 beds</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/pune-hospital-pregnant-woman-dies-probe-9924556/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
+          <t>Major Health Boost for Nagpur And Vidarbha: Govt plans facilities, incentives for doctors in remote areas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Maha to relax norms for nursing homes, hospitals with up to 10 beds</t>
+          <t>GBS Outbreak Scare: Maharashtra Minister Announces New Law For Clean Water Supply, Fines For Polluters</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
+          <t>https://www.news18.com/india/gbs-outbreak-scare-maharashtra-minister-announces-new-law-for-clean-water-supply-fines-for-polluters-9218986.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Major Health Boost for Nagpur And Vidarbha: Govt plans facilities, incentives for doctors in remote areas</t>
+          <t>Rising obesity in children matter of grave concern, parents must take it seriously: Abitkar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GBS Outbreak Scare: Maharashtra Minister Announces New Law For Clean Water Supply, Fines For Polluters</t>
+          <t>Cashless treatment up to ₹1 lakh for accident victims in Maharashtra</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/gbs-outbreak-scare-maharashtra-minister-announces-new-law-for-clean-water-supply-fines-for-polluters-9218986.html</t>
+          <t>https://www.thehindu.com/news/national/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-1-lakh/article69463926.ece</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rising obesity in children matter of grave concern, parents must take it seriously: Abitkar</t>
+          <t>Mumbai's new 300-bed cancer center assures personalized, ai-powered treatment: Here's how</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
+          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cashless treatment up to ₹1 lakh for accident victims in Maharashtra</t>
+          <t>Maharashtra Government issues directives to strengthen healthcare system</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-1-lakh/article69463926.ece</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-government-issues-directives-to-strengthen-healthcare-system/article69593387.ece</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mumbai's new 300-bed cancer center assures personalized, ai-powered treatment: Here's how</t>
+          <t>Maharashtra to set up state-level committee for effective leprosy eradication: Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-set-up-state-level-committee-for-effective-leprosy-eradication-says-maharashtra-health-minister-prakash-abitkar-23584820</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maharashtra Government issues directives to strengthen healthcare system</t>
+          <t>Maharashtra to ask Centre to include Thalassemia in national health scheme: Prakash Abitkar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-government-issues-directives-to-strengthen-healthcare-system/article69593387.ece</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maharashtra to set up state-level committee for effective leprosy eradication: Health Minister Prakash Abitkar</t>
+          <t>Contaminated well suspected in GBS spike; Pune civic body now supplies clean water through tankers</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-set-up-state-level-committee-for-effective-leprosy-eradication-says-maharashtra-health-minister-prakash-abitkar-23584820</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/contaminated-well-suspected-in-gbs-spike-pune-civic-body-now-supplies-clean-water-through-tankers-101738005488804.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maharashtra to ask Centre to include Thalassemia in national health scheme: Prakash Abitkar</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
+          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister-2/2710767/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Contaminated well suspected in GBS spike; Pune civic body now supplies clean water through tankers</t>
+          <t>Mumbai reports 53 active Covid cases, government says situation under control</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/contaminated-well-suspected-in-gbs-spike-pune-civic-body-now-supplies-clean-water-through-tankers-101738005488804.html</t>
+          <t>https://www.indiatoday.in/cities/mumbai/story/covid-19-in-india-active-cases-in-mumbai-health-minister-prakash-abitkar-situation-under-control-2727629-2025-05-20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>State govt proposes to amend Bombay Nursing Home Act; health dept to hire legal firm</t>
+          <t>Maharashtra Accident Victims: Cashless Treatment up to Rs 1 Lakh in Emergency Hospitals</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mumbai reports 53 active Covid cases, government says situation under control</t>
+          <t>Maharashtra: Lab test ‘loot’ to end soon as govt plans price cap</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/cities/mumbai/story/covid-19-in-india-active-cases-in-mumbai-health-minister-prakash-abitkar-situation-under-control-2727629-2025-05-20</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Charitable hospitals must comply with govt health scheme GR: Minister</t>
+          <t>Mumbai Reports 53 Active COVID-19 Cases; 2 Deaths Linked To Co-Morbidities</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maharashtra: Lab test ‘loot’ to end soon as govt plans price cap</t>
+          <t>No sudden spike in GBS cases in Pune, situation under control: Health Minister</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
+          <t>https://indianexpress.com/article/cities/mumbai/no-sudden-spike-gbs-cases-pune-health-minister-9813822/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>No sudden spike in GBS cases in Pune, situation under control: Health Minister</t>
+          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/no-sudden-spike-gbs-cases-pune-health-minister-9813822/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GBS Cases In Pune Linked To Suspected Water Contamination, Says Maharashtra Minister</t>
+          <t>Maha to accredit private hospitals under Health Tourism Policy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/gbs-cases-in-pune-linked-to-suspected-water-contamination-says-maharashtra-minister-enn25012706765</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maharashtra government to provide free cancer vaccine for girls aged 0-14 across state</t>
+          <t>Mumbai: CM Fadnavis Holds High-Level Meeting on Public Health</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-across-state-latest-updates-bird-flu-precautions-2025-03-01-978584</t>
+          <t>https://impressivetimes.com/state/news-4249/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Maha Health Minister urges officials to submit Health Policy proposal</t>
+          <t>GBS Cases In Pune Linked To Suspected Water Contamination, Says Maharashtra Minister</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/state-news/maharashtra/maha-health-minister-urges-officials-to-submit-health-policy-proposal-148661</t>
+          <t>https://www.etvbharat.com/en/!state/gbs-cases-in-pune-linked-to-suspected-water-contamination-says-maharashtra-minister-enn25012706765</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Maharashtra government to provide free cancer vaccine for girls aged 0-14 across state</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/efforts-on-to-bring-back-%E2%80%98mahadevi%E2%80%99-from-vantara:-maharashtra-minister/2784707</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-across-state-latest-updates-bird-flu-precautions-2025-03-01-978584</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Contractual NHM staff may get permanent jobs; honorarium hike planned</t>
+          <t>Maha Health Minister urges officials to submit Health Policy proposal</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
+          <t>https://medicaldialogues.in/state-news/maharashtra/maha-health-minister-urges-officials-to-submit-health-policy-proposal-148661</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara Maharashtra minister</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister/2710544/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/01/bom39-mh-ld-elephant-minister.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Centre to revise CGHS rates soon, union minister assures</t>
+          <t>Contractual NHM staff may get permanent jobs; honorarium hike planned</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Maharashtra cancels Licenses of 258 Private Hospitals for Violations</t>
+          <t>Centre to revise CGHS rates soon, union minister assures</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HMPV Outbreak LIVE Updates: No cause for concern, says Maharashtra Health Minister Prakash Abitkar</t>
+          <t>Maharashtra cancels Licenses of 258 Private Hospitals for Violations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
+          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
+          <t>HMPV Outbreak LIVE Updates: No cause for concern, says Maharashtra Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
+          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara Maharashtra minister</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/01/bom39-mh-ld-elephant-minister.html</t>
+          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
         </is>
       </c>
     </row>
@@ -1127,396 +1127,396 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Accident victims in Maharashtra to receive cashless treatment up to Rs 1 lakh</t>
+          <t>Maharashtra approves inter and intra-district transfers for CHOs based on their requests</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh/articleshow/120402888.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maharashtra approves inter and intra-district transfers for CHOs based on their requests</t>
+          <t>Maharashtra: Accident victims to receive cashless treatment up to INR 1 lakh</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
+          <t>https://www.mumbailive.com/en/civic/accident-victims-of-maharashtra-to-receive-cashless-treatment-up-to-inr-1-lakh-88361</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Maharashtra: Accident victims to receive cashless treatment up to INR 1 lakh</t>
+          <t>Minister Abitkar leads the Maharashtra government's two-week organ donation campaign by filling the form</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/civic/accident-victims-of-maharashtra-to-receive-cashless-treatment-up-to-inr-1-lakh-88361</t>
+          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Minister Abitkar leads the Maharashtra government's two-week organ donation campaign by filling the form</t>
+          <t>Mumbai Reports First Suspected GBS Case Amid Rising Cases in Maharashtra</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
+          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mumbai Reports First Suspected GBS Case Amid Rising Cases in Maharashtra</t>
+          <t>Guillain-Barré Syndrome Outbreak: Maharashtra Health Minister Prakash Abitkar Visits Pune As Cases Cross 100</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
+          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-outbreak-maharashtra-health-minister-prakash-abitkar-visits-pune-as-cases-cross-100-videos</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome Outbreak: Maharashtra Health Minister Prakash Abitkar Visits Pune As Cases Cross 100</t>
+          <t>Health Minister Prakash Abitkar Promises Support To Private Doctors At Pune Dialogue</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-outbreak-maharashtra-health-minister-prakash-abitkar-visits-pune-as-cases-cross-100-videos</t>
+          <t>https://www.freepressjournal.in/pune/health-minister-prakash-abitkar-promises-support-to-private-doctors-at-pune-dialogue</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Health Minister Prakash Abitkar Promises Support To Private Doctors At Pune Dialogue</t>
+          <t>Guillain-Barré Syndrome In Kolhapur: Two Cases Of GBS Reported In Home District Of Health Minister Prakash</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/health-minister-prakash-abitkar-promises-support-to-private-doctors-at-pune-dialogue</t>
+          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-in-kolhapur-two-cases-of-gbs-reported-in-home-district-of-health-minister-prakash-abitkar-solapur-also-reports-cases</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome In Kolhapur: Two Cases Of GBS Reported In Home District Of Health Minister Prakash</t>
+          <t>Maharashtra To Urge Centre To Include Thalassemia In National Sickle Cell Programme</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-in-kolhapur-two-cases-of-gbs-reported-in-home-district-of-health-minister-prakash-abitkar-solapur-also-reports-cases</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-urge-centre-to-include-thalassemia-in-national-sickle-cell-programme</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Maharashtra To Urge Centre To Include Thalassemia In National Sickle Cell Programme</t>
+          <t>Health Minister Prakash Abitkar announces one lakh reward: Pricing for tip offs on fetal sex determination ...</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-urge-centre-to-include-thalassemia-in-national-sickle-cell-programme</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Health Minister Prakash Abitkar announces one lakh reward: Pricing for tip offs on fetal sex determination ...</t>
+          <t>Maharashtra Clears ₹20,000 Crore For Shaktipeeth Expressway Amid Fierce Farmer Opposition</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-clears-20000-crore-for-shaktipeeth-expressway-amid-fierce-farmer-opposition</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maharashtra Clears ₹20,000 Crore For Shaktipeeth Expressway Amid Fierce Farmer Opposition</t>
+          <t>Maharashtra Govt Launches Cashless Treatment Scheme For Accident Victims, Covers ₹1 Lakh Per Case</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-clears-20000-crore-for-shaktipeeth-expressway-amid-fierce-farmer-opposition</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-launches-cashless-treatment-scheme-for-accident-victims-covers-1-lakh-per-case</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Launches Cashless Treatment Scheme For Accident Victims, Covers ₹1 Lakh Per Case</t>
+          <t>Over 12,000 Child Deaths Reported In Maharashtra Between April 2024 And February 2025: Minister Prakash Abitka</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-launches-cashless-treatment-scheme-for-accident-victims-covers-1-lakh-per-case</t>
+          <t>https://www.freepressjournal.in/mumbai/over-12000-child-deaths-reported-in-maharashtra-between-april-2024-and-february-2025-minister-prakash-abitka</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Over 12,000 Child Deaths Reported In Maharashtra Between April 2024 And February 2025: Minister Prakash Abitka</t>
+          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/over-12000-child-deaths-reported-in-maharashtra-between-april-2024-and-february-2025-minister-prakash-abitka</t>
+          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
+          <t>महाराष्ट्र में गुइलेन-बैरे सिंड्रोम के 197 मरीज : स्वास्थ्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
+          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में गुइलेन-बैरे सिंड्रोम के 197 मरीज : स्वास्थ्य मंत्री प्रकाश आबिटकर</t>
+          <t>महाराष्ट्र में फिर कोरोना का डर? स्वास्थ्य मंत्री ने दिए अहम निर्देश, बोले- 'घबराएं</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में फिर कोरोना का डर? स्वास्थ्य मंत्री ने दिए अहम निर्देश, बोले- 'घबराएं</t>
+          <t>Cashless Treatment in Accident: दुर्घटनाग्रस्त के लिए 1 लाख तक फ्री इलाज</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
+          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cashless Treatment in Accident: दुर्घटनाग्रस्त के लिए 1 लाख तक फ्री इलाज</t>
+          <t>उद्धव ने जिसके लिए लिया था ‘पंजे’ से पंगा, अब उसी ने छोड़ा साथ, महायुति की ताकत बढ़ी</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>उद्धव ने जिसके लिए लिया था ‘पंजे’ से पंगा, अब उसी ने छोड़ा साथ, महायुति की ताकत बढ़ी</t>
+          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway: शक्तिपीठ एक्सप्रेसवे के खिलाफ सड़क पर उतरे किसान, फडणवीस ने विधानसभा में गिनाए महामार्ग के फायदे-नुकसान</t>
+          <t>Organ Donation: अंगदान को नया आयाम, महाराष्ट्र के अन्य चार शहरों में खुलेंगे ZTCC सेंटर</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
+          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की बेटियों के लिए किया ये ऐलान</t>
+          <t>Madhuri Elephant: हथिनी 'माधुरी' को वापस लाने के लिए मुख्यमंत्री देवेंद्र फडणवीस का बड़ा फैसला, राज्य सरकार भी सुप्रीम कोर्ट में दाखिल करेगी पुनर्विचार याचिका</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/devendra-fadnavis-government-announces-free-cancer-vaccine-for-girls-under-14-years-of-age-maharashtra-news/1088804/</t>
+          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Organ Donation: अंगदान को नया आयाम, महाराष्ट्र के अन्य चार शहरों में खुलेंगे ZTCC सेंटर</t>
+          <t>राज्य की स्वास्थ्य नीति के संदर्भ में तुरंत पेश करें प्रस्ताव - स्वास्थ्य मंत्री प्रकाश अबिटकर ने दिए निर्देश</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
+          <t>https://navbharatlive.com/maharashtra/health-minister-prakash-abitkar-instructions-to-submit-proposal-state-health-policy-5k-to-asha-workers-mumbai-1226342.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
+          <t>महाराष्ट्र सरकार का बड़ा फैसला, 0-14 साल की लड़कियों को मिलेगी मुफ्त कैंसर वैक्सीन</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Madhuri Elephant: हथिनी 'माधुरी' को वापस लाने के लिए मुख्यमंत्री देवेंद्र फडणवीस का बड़ा फैसला, राज्य सरकार भी सुप्रीम कोर्ट में दाखिल करेगी पुनर्विचार याचिका</t>
+          <t>Maharashtra Cancels Licences Of 258 Private Hospitals For Violating Healthcare Norms; Notices Sent To 5,134</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cancels-licences-of-258-private-hospitals-for-violating-healthcare-norms-notices-sent-to-5134-hospitals-says-state-health-minister</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>महाराष्ट्र सरकार का बड़ा फैसला, 0-14 साल की लड़कियों को मिलेगी मुफ्त कैंसर वैक्सीन</t>
+          <t>'Pune's GBS cases may be linked to suspected water contamination'</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
+          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Maharashtra Cancels Licences Of 258 Private Hospitals For Violating Healthcare Norms; Notices Sent To 5,134</t>
+          <t>Maharashtra health dept to probe into claim about Pune hospital's refusal to admit pregnant woman</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cancels-licences-of-258-private-hospitals-for-violating-healthcare-norms-notices-sent-to-5134-hospitals-says-state-health-minister</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>'Pune's GBS cases may be linked to suspected water contamination'</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
+          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister/2710544/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mumbai: CM Fadnavis Holds High-Level Meeting on Public Health</t>
+          <t>Maha Health Minister urges Mandaviya to revise income eligibility limit for ESIS beneficiaries</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/state/news-4249/</t>
+          <t>https://www.thehawk.in/news/health/maha-health-minister-urges-mandaviya-to-revise-income-eligibility-limit-for-esis-beneficiaries</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Maharashtra health dept to probe into claim about Pune hospital's refusal to admit pregnant woman</t>
+          <t>Prakash Abitkar: 'दादा नेहमी आमच्या परीक्षा घेतात अन् आमची अडचण होते', आरोग्यमंत्री प्रकाश</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
+          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maha Health Minister urges Mandaviya to revise income eligibility limit for ESIS beneficiaries</t>
+          <t>Prakash Abitkar News : आरोग्यमंत्री आबिटकरांची महत्त्वपूर्ण घोषणा, गर्भलिंगविरोधात खबऱ्यांना मिळणार मोठं बक्षीस</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/health/maha-health-minister-urges-mandaviya-to-revise-income-eligibility-limit-for-esis-beneficiaries</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-announces-reward-against-gender-testing-informants-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: 'दादा नेहमी आमच्या परीक्षा घेतात अन् आमची अडचण होते', आरोग्यमंत्री प्रकाश</t>
+          <t>आरोग्यमंत्री प्रकाश आबिटकर म्हणाले, काही बिघडणार…</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-on-inquiry-of-health-department-s-irregularity-pune-print-news-ggy-03-css-98-4923177/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री प्रकाश आबिटकर म्हणाले, काही बिघडणार…</t>
+          <t>कोल्हापूर शहराची हद्दवाढ, खंडपीठ होणारच; पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-on-inquiry-of-health-department-s-irregularity-pune-print-news-ggy-03-css-98-4923177/</t>
+          <t>https://www.lokmat.com/kolhapur/kolhapur-city-limits-to-be-expanded-bench-to-be-formed-says-guardian-minister-prakash-abitkar-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>कोल्हापूर शहराची हद्दवाढ, खंडपीठ होणारच; पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
+          <t>राज्यातील आरोग्यसंस्थांमध्ये दोन हजार पदनिर्मितीस मान्यता : आरोग्यमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/kolhapur-city-limits-to-be-expanded-bench-to-be-formed-says-guardian-minister-prakash-abitkar-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-health-department-2070-new-posts-approved</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>राज्यातील आरोग्यसंस्थांमध्ये दोन हजार पदनिर्मितीस मान्यता : आरोग्यमंत्री आबिटकर</t>
+          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-health-department-2070-new-posts-approved</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
         </is>
       </c>
     </row>
@@ -1535,96 +1535,96 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
+          <t>'जीबीएस' आजारानं रुग्णाचा मृत्यू होतो का? आरोग्यमंत्र्यांनी थेटच सांगितलं...</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
+          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>'जीबीएस' आजारानं रुग्णाचा मृत्यू होतो का? आरोग्यमंत्र्यांनी थेटच सांगितलं...</t>
+          <t>Tanisha Bhise Death Case : पैशांच्या डिपॉझिटसाठी उपचार नाकारणाऱ्या सर्व हॉस्पिटल्सवर कारवाई होणार? आरोग्यमंत्र्यांकडून महत्त्वाची माहिती</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tanisha Bhise Death Case : पैशांच्या डिपॉझिटसाठी उपचार नाकारणाऱ्या सर्व हॉस्पिटल्सवर कारवाई होणार? आरोग्यमंत्र्यांकडून महत्त्वाची माहिती</t>
+          <t>दीनानाथ मंगेशकर रुग्णालयावर कारवाई कधी? आरोग्य मंत्री प्रकाश आबिटकर यांनी दिले उत्तर</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-said-about-the-action-taken-by-dinanath-hospital-1387152.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : पालकमंत्री कोणावर होणार मेहरबान? भाजपमध्ये मोठी स्पर्धा</t>
+          <t>कोल्हापूरच्या राजकारणात आबिटकरांचे प्रकाशपर्व!</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/kolhapur-guardian-minister-prakash-abitkar-who-will-get-favor-bjp-big-competition-rg90-gs97</t>
+          <t>https://www.loksatta.com/kolhapur/prakash-abitkar-is-now-the-focus-of-kolhapur-politics-mrj-95-4843588/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या राजकारणात आबिटकरांचे प्रकाशपर्व!</t>
+          <t>कोल्हापूरच्या हद्दवाढीसाठी लवकरच मुख्यमंत्र्यांसोबत बैठक, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/prakash-abitkar-is-now-the-focus-of-kolhapur-politics-mrj-95-4843588/</t>
+          <t>https://www.lokmat.com/kolhapur/meeting-with-chief-minister-soon-for-extension-of-kolhapur-boundary-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या हद्दवाढीसाठी लवकरच मुख्यमंत्र्यांसोबत बैठक, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
+          <t>Corona virus in Maharashtra: राज्यातील कोरोना व्हायरसबाबत मोठी अपडेट, आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/meeting-with-chief-minister-soon-for-extension-of-kolhapur-boundary-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
+          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Corona virus in Maharashtra: राज्यातील कोरोना व्हायरसबाबत मोठी अपडेट, आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>राज्यात प्रथमच स्वतंत्र आरोग्य धोरण; आरोग्यमंत्री प्रकाश आबिटकर यांची घोषणा</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-announces-separate-health-policy-for-the-maharashtra-state-amy-95-4860385/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>राज्यात प्रथमच स्वतंत्र आरोग्य धोरण; आरोग्यमंत्री प्रकाश आबिटकर यांची घोषणा</t>
+          <t>‘वैद्यकीय अधिकाऱ्यांची रिक्त पदे तातडीने भरा’; आरोग्यमंत्री प्रकाश आबिटकर यांचे आदेश</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-announces-separate-health-policy-for-the-maharashtra-state-amy-95-4860385/</t>
+          <t>https://www.lokmat.com/maharashtra/fill-the-vacant-posts-of-medical-officers-immediately-says-health-minister-prakash-abitkar-a-a992/</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>वैद्यकीय प्रयोगशाळांच्या तपासणीसाठी कायदा; आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur News: पालकमंत्री प्रकाश आबिटकर शेताच्या बांधावर; भर पावसात चिखलगुट्टा करत भात रोपांची लागण</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
         </is>
       </c>
     </row>
@@ -1667,36 +1667,36 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्यापासून लंपी दूर ठेवा – प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : पालकमंत्री प्रकाश आबिटकरांकडून कोल्हापुरात ध्वजारोहण; म्हणाले, बहुमान मिळाल्याचा सार्थ अभिमान</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/lumpy-disease-under-controls-in-kolhapur-district-due-to-implementation-of-effective-vaccination-says-minister-prakash-abitkar-zws-70-5301296/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kolhapur News: पालकमंत्री प्रकाश आबिटकर शेताच्या बांधावर; भर पावसात चिखलगुट्टा करत भात रोपांची लागण</t>
+          <t>Prakash Abitkar : पालकमंत्री कोणावर होणार मेहरबान? भाजपमध्ये मोठी स्पर्धा</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/kolhapur-guardian-minister-prakash-abitkar-who-will-get-favor-bjp-big-competition-rg90-gs97</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : पालकमंत्री प्रकाश आबिटकरांकडून कोल्हापुरात ध्वजारोहण; म्हणाले, बहुमान मिळाल्याचा सार्थ अभिमान</t>
+          <t>Prakash Abitkar on Covid 19: कोरोनाची लक्षणं सौम्य, प्रकाश आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5122212/corona-symptoms-are-mild-prakash-abitkars-gave-detail-information/</t>
         </is>
       </c>
     </row>
@@ -1715,5952 +1715,6096 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : महाराष्ट्राच्या मंत्रिमंडळातला मोठा गौप्यस्फोट, मंत्र्यानेच सांगितली आतली बातमी</t>
+          <t>वैद्यकीय प्रयोगशाळांच्या तपासणीसाठी कायदा; आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
+          <t>Kolhapur Politics: पालकमंत्रीही उतरणार ‘गडहिंग्लज’च्या मैदानात !, मुश्रीफांचे बारकाईने लक्ष</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
+          <t>https://www.lokmat.com/kolhapur/guardian-minister-prakash-abitkar-will-also-contest-the-gadhinglaj-municipality-elections-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Madhuri Elephant News : ‘माधुरी हत्तीणी’च्या ‘नांदणी’वापसीचा मार्ग मोकळा! पण कायद्याचा अडसर; पालकमंत्री आबिटकरांची माहिती</t>
+          <t>कोल्हापूर जिल्ह्यापासून लंपी दूर ठेवा – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/madhuri-elephant-cleared-for-return-to-nandani-but-legal-hurdles-remain-says-minister-prakash-abitkar-rg84</t>
+          <t>https://www.loksatta.com/kolhapur/lumpy-disease-under-controls-in-kolhapur-district-due-to-implementation-of-effective-vaccination-says-minister-prakash-abitkar-zws-70-5301296/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Covid 19: कोरोनाची लक्षणं सौम्य, प्रकाश आबिटकर यांची माहिती</t>
+          <t>Maharashtra Politics : महाराष्ट्राच्या मंत्रिमंडळातला मोठा गौप्यस्फोट, मंत्र्यानेच सांगितली आतली बातमी</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5122212/corona-symptoms-are-mild-prakash-abitkars-gave-detail-information/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kolhapur city Extension : हद्दवाढीसाठी शहरवासियांनी न्यायदाता ठरवला, पालकमंत्री अबिटकरांनाच करणार म्होरक्या</t>
+          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-haddavadh-kruti-samitis-decision-to-approach-guardian-minister-prakash-abitkar-for-boundary-expansion-as11-rg93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Hospital : हॉस्पिटलच्या मनमानीला चाप लागणार पेशंट, नातेवाईकांची तक्रार थेट</t>
+          <t>Madhuri Elephant News : ‘माधुरी हत्तीणी’च्या ‘नांदणी’वापसीचा मार्ग मोकळा! पण कायद्याचा अडसर; पालकमंत्री आबिटकरांची माहिती</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/madhuri-elephant-cleared-for-return-to-nandani-but-legal-hurdles-remain-says-minister-prakash-abitkar-rg84</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: कोल्हापुरात महायुतीमध्ये शिवसेना हाच सर्वात मोठा पक्ष आगामी निवडणुकांसाठी</t>
+          <t>Maharashtra Politics : लाडकी बहीण योजनेवरुन महायुतीत 'कसरत', आरोग्यमंत्र्यांचं मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>महाराष्ट्राचे आरोग्यमंत्री अचानक रुग्णालयात धडकले, अधिकाऱ्यांवर भडकले, नेमकं काय घडलं?</t>
+          <t>Kolhapur city Extension : हद्दवाढीसाठी शहरवासियांनी न्यायदाता ठरवला, पालकमंत्री अबिटकरांनाच करणार म्होरक्या</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-haddavadh-kruti-samitis-decision-to-approach-guardian-minister-prakash-abitkar-for-boundary-expansion-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 108 अॅम्ब्युलन्स खरेदीच्या टेंडर प्रक्रियेत काय झालं? श्रीकांत शिंदेंचे</t>
+          <t>महाराष्ट्राचे आरोग्यमंत्री अचानक रुग्णालयात धडकले, अधिकाऱ्यांवर भडकले, नेमकं काय घडलं?</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kolhapur Political News | कॅरम खेळण्यात आबिटकर-महाडिक दंग; सोशल मीडियावर व्हिडिओ व्हायरल</t>
+          <t>राज्यात बॉम्बे नर्सिंग अँक्टची कठोर अमंलबजावणी होणार; आरोग्य मंत्री प्रकाश आबिटकर यांनी माहिती</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-leaders-dhanajay-mahadik-and-prakash-abitkar-sharangdhar-deshmukh-carrom-match-political-move-sd22</t>
+          <t>https://www.loksatta.com/maharashtra/health-minister-prakash-abitkar-has-informed-that-the-bombay-nursing-act-will-be-strictly-implemented-in-the-state-amy-95-4933697/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>राज्यात बॉम्बे नर्सिंग अँक्टची कठोर अमंलबजावणी होणार; आरोग्य मंत्री प्रकाश आबिटकर यांनी माहिती</t>
+          <t>Prakash Abitkar on Hospital : हॉस्पिटलच्या मनमानीला चाप लागणार पेशंट, नातेवाईकांची तक्रार थेट</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/health-minister-prakash-abitkar-has-informed-that-the-bombay-nursing-act-will-be-strictly-implemented-in-the-state-amy-95-4933697/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kolhapur Politics | कोल्हापूरचे पालकमंत्री आबिटकर थेट खासदार शाहू महाराजांच्या भेटीला; चर्चांना उधाण</t>
+          <t>Kolhapur Political News | कॅरम खेळण्यात आबिटकर-महाडिक दंग; सोशल मीडियावर व्हिडिओ व्हायरल</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-guardian-minister-prakash-abitkar-meets-congress-mp-shahu-maharaj-as80</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-leaders-dhanajay-mahadik-and-prakash-abitkar-sharangdhar-deshmukh-carrom-match-political-move-sd22</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kolhapur News: कोल्हापुरात ईएसआय रुग्णालयात आरोग्यमंत्र्यांकडून डॉक्टरांची झाडाझडती</t>
+          <t>Prakash Abitkar : 108 अॅम्ब्युलन्स खरेदीच्या टेंडर प्रक्रियेत काय झालं? श्रीकांत शिंदेंचे</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ई-रक्तकोषद्वारे गरजू रुग्णांना मिळणार रक्त उपलब्धतेची माहिती - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Politics | कोल्हापूरचे पालकमंत्री आबिटकर थेट खासदार शाहू महाराजांच्या भेटीला; चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159642/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-guardian-minister-prakash-abitkar-meets-congress-mp-shahu-maharaj-as80</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>अनुदान न मिळाल्याने रखडले ‘आरबीएसके’ पथकांचे वेतन; आरोग्यमंत्री प्रकाश आबिटकर यांची माहिती</t>
+          <t>Kolhapur News: कोल्हापुरात ईएसआय रुग्णालयात आरोग्यमंत्र्यांकडून डॉक्टरांची झाडाझडती</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/salary-of-rbsk-teams-stalled-due-to-non-receipt-of-grant</t>
+          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>‘अलमट्टी’ विरोधात महाराष्ट्राची; कायदेशीर लढाई – प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar: कोल्हापुरात महायुतीमध्ये शिवसेना हाच सर्वात मोठा पक्ष आगामी निवडणुकांसाठी</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/guardian-minister-prakash-abitkar-expressed-his-opinion-regarding-the-height-of-the-almatti-dam-while-talking-to-reporters-phm-00-5066152/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Almatti Dam : तर आम्हीही तशीच वकिलांची आणि जलतज्ञांची फौज उभा करू 'अलमट्टी'च्या</t>
+          <t>ई-रक्तकोषद्वारे गरजू रुग्णांना मिळणार रक्त उपलब्धतेची माहिती - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
+          <t>https://mahasamvad.in/159642/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Women Cancer Symptoms : खळबळजनक! महाराष्ट्रातील ‘या’ जिल्ह्यात तब्बल १४ हजारांहून अधिक महिलांमध्ये आढळली 'कॅन्सर'सारखी लक्षणे</t>
+          <t>अनुदान न मिळाल्याने रखडले ‘आरबीएसके’ पथकांचे वेतन; आरोग्यमंत्री प्रकाश आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/hingoli-women-cancer-symptoms-health-minister-prakash-abitkar-statement-14000-affected-msr87</t>
+          <t>https://pudhari.news/maharashtra/pune/salary-of-rbsk-teams-stalled-due-to-non-receipt-of-grant</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>कोल्हापूर हद्दवाढीवर लवकरच निर्णय</t>
+          <t>Prakash Abitkar on Almatti Dam : तर आम्हीही तशीच वकिलांची आणि जलतज्ञांची फौज उभा करू 'अलमट्टी'च्या</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-boundary-expansion-decision-soon-prakash-abitkar-ap84</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Prakash Abitkar | ग्रामीण भागात सेवा दिल्यानंतरच डॉक्टरांना प्रमाणपत्र मिळणार</t>
+          <t>‘अलमट्टी’ विरोधात महाराष्ट्राची; कायदेशीर लढाई – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/doctors-rural-service-bond-certificate-upload-health-minister-prakash-abitkar</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-prakash-abitkar-expressed-his-opinion-regarding-the-height-of-the-almatti-dam-while-talking-to-reporters-phm-00-5066152/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : विरोधकांच्या 108 रुग्णवाहिका घोटाळ्यावर आरोग्यमंत्र्यांचे स्पष्टीकरण, म्हणाले, "त्याचा शासनाशी सबंध नाही..."</t>
+          <t>Women Cancer Symptoms : खळबळजनक! महाराष्ट्रातील ‘या’ जिल्ह्यात तब्बल १४ हजारांहून अधिक महिलांमध्ये आढळली 'कॅन्सर'सारखी लक्षणे</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-108-ambulance-scam-health-minister-prakash-abitkar-clarification-jap93-rg93</t>
+          <t>https://www.esakal.com/maharashtra/hingoli-women-cancer-symptoms-health-minister-prakash-abitkar-statement-14000-affected-msr87</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: पहिल्यांदाच मंत्री अन् पालकमंत्रिपद मिळालं, आबिटकर यांच्यासमोर आता 'हे' मोठ आव्हान</t>
+          <t>पत्रकारांच्या आरोग्याच्या प्रश्नावर लवकरच बैठक घेणार – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-kolhapur-guardian-minister-prakash-abitkar-mahayuti-challenge-mm76-rg93</t>
+          <t>https://mahasamvad.in/170017/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांच्या सूचनेनुसारच हद्दवाढीची प्रक्रिया सुरू : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>कोल्हापूर हद्दवाढीवर लवकरच निर्णय</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/boundary-expansion-process-initiated-as-per-cm-directive-says-prakash-abitkar-ap84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-boundary-expansion-decision-soon-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>महिन्यातून किमान दोन वेळा आरोग्य संस्थांना अचानक भेटी द्या - आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar | ग्रामीण भागात सेवा दिल्यानंतरच डॉक्टरांना प्रमाणपत्र मिळणार</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/make-surprise-visits-to-health-institutions-at-least-twice-a-month-health-minister-prakash-abitkar-a-a1008/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/doctors-rural-service-bond-certificate-upload-health-minister-prakash-abitkar</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Pune GBS : पुण्यातील 'त्या' विहिरीमुळे पसरला गुईलेन बॅरे सिंड्रोम, आरोग्यमंत्र्यांनी दिली धक्कादायक माहिती</t>
+          <t>Prakash Abitkar : विरोधकांच्या 108 रुग्णवाहिका घोटाळ्यावर आरोग्यमंत्र्यांचे स्पष्टीकरण, म्हणाले, "त्याचा शासनाशी सबंध नाही..."</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-108-ambulance-scam-health-minister-prakash-abitkar-clarification-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>दोन कोटी शालेय विद्यार्थ्यांची आरोग्य तपासणी करणार – आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar: पहिल्यांदाच मंत्री अन् पालकमंत्रिपद मिळालं, आबिटकर यांच्यासमोर आता 'हे' मोठ आव्हान</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155891/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-kolhapur-guardian-minister-prakash-abitkar-mahayuti-challenge-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kolhapur Guardian Minister : मंत्री प्रकाश आबिटकर कोल्हापूरचे पालकमंत्री</t>
+          <t>मुख्यमंत्र्यांच्या सूचनेनुसारच हद्दवाढीची प्रक्रिया सुरू : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-appointed-as-guardian-minister-of-kolhapur-sdj87</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/boundary-expansion-process-initiated-as-per-cm-directive-says-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>flood control planning | पूर नियंत्रणाचे सूक्ष्म नियोजन करा : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>महिन्यातून किमान दोन वेळा आरोग्य संस्थांना अचानक भेटी द्या - आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/plan-micro-level-flood-control-says-minister-prakash-abitkar-ap84</t>
+          <t>https://www.lokmat.com/pune/make-surprise-visits-to-health-institutions-at-least-twice-a-month-health-minister-prakash-abitkar-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>अवैध गर्भपाताची माहिती देणाऱ्या महिलांच्या मानधनात वाढ – आबिटकर</t>
+          <t>कृषी विभागाच्या बैठकीवेळी पालकमंत्री प्रकाश आबिटकर यांनी मार्गदर्शन केले</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/increase-in-honorarium-of-women-who-provide-information-about-illegal-abortions-say-prakash-abitkar-mrj-95-4843272/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-guidance-during-the-agriculture-department-meeting-sud-02-5087323/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>आरोग्य सेवा बळकट करण्यासाठी आरोग्य मंत्र्यांचा सूचनांचा धडाका; आरोग्य भवनमध्ये सर्व अधिकाऱ्यांची बैठक</t>
+          <t>flood control planning | पूर नियंत्रणाचे सूक्ष्म नियोजन करा : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-suggestions-to-strengthen-healthcare-services-at-the-high-level-meeting-mumbai-print-news-zws-70-5104660/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/plan-micro-level-flood-control-says-minister-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>"कर्करोगापासून बचाव करण्यासाठी मुलींना मोफत लस...", नेमकं काय म्हणाले आरोग्य मंत्री?</t>
+          <t>दोन कोटी शालेय विद्यार्थ्यांची आरोग्य तपासणी करणार – आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
+          <t>https://mahasamvad.in/155891/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>‘महादेवी’परत करण्याबाबत ‘वनतारा’ व्यवस्थापन सकारात्मक; प्रकाश आबिटकर यांचा दावा</t>
+          <t>अवैध गर्भपाताची माहिती देणाऱ्या महिलांच्या मानधनात वाढ – आबिटकर</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-abitkar-claims-positive-response-from-vantara-over-elephant-rds-00-5274363/</t>
+          <t>https://www.loksatta.com/kolhapur/increase-in-honorarium-of-women-who-provide-information-about-illegal-abortions-say-prakash-abitkar-mrj-95-4843272/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GBS रुग्णांच्या उपचार करताना औषधांचा गैरवापर, जास्त पैसे पैसे घेतल्यास;आरोग्यमंत्री प्रकाश आबिटकर यांचा इशारा</t>
+          <t>Kolhapur Guardian Minister : मंत्री प्रकाश आबिटकर कोल्हापूरचे पालकमंत्री</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/beware-if-you-are-robbed-health-minister-prakash-abitkar-warns-a-a1008/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-appointed-as-guardian-minister-of-kolhapur-sdj87</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kolhapur Politics: 'गोकुळ'मध्ये मुश्रीफ, सतेज, आबिटकर, कोरे यांची एकी; डोंगळे एकाकी</t>
+          <t>"कर्करोगापासून बचाव करण्यासाठी मुलींना मोफत लस...", नेमकं काय म्हणाले आरोग्य मंत्री?</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/hasan-mushrif-satej-patil-prakash-abitkar-vinay-kore-are-united-in-gokul-dudh-sangh-politics-arun-dongle-is-alone-a-a746/</t>
+          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : आरोग्यमंत्र्यांच्या कोल्हापुरातच 'सलमान'ची चर्चा, प्रशासकीय अधिकारीही 'लाभार्थी'</t>
+          <t>Kolhapur Politics: 'गोकुळ'मध्ये मुश्रीफ, सतेज, आबिटकर, कोरे यांची एकी; डोंगळे एकाकी</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-advises-citizens-to-consult-professionals-that-time-some-officials-visit-salmans-hair-trainer-to-treatment-hair-problem-as11-rg93</t>
+          <t>https://www.lokmat.com/kolhapur/hasan-mushrif-satej-patil-prakash-abitkar-vinay-kore-are-united-in-gokul-dudh-sangh-politics-arun-dongle-is-alone-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>खासगी रुग्णालयांची नोंदणी आता ऑनलाईन, आरोग्य मंत्री प्रकाश आबिटकर यांची घोषणा</t>
+          <t>‘महादेवी’परत करण्याबाबत ‘वनतारा’ व्यवस्थापन सकारात्मक; प्रकाश आबिटकर यांचा दावा</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/registration-of-private-hospitals-now-online-health-minister-prakash-abitkar-announced-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-abitkar-claims-positive-response-from-vantara-over-elephant-rds-00-5274363/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>कर्करोग प्रतिबंधासाठी जनजागृती गरजेची – मंत्री प्रकाश आबिटकर</t>
+          <t>Mahadevi Elephant : नांदणीतील महादेवी परत येणार, मंत्री आबिटकरांनी दिली कायदेशीर प्रक्रियेची माहिती</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154597/</t>
+          <t>https://www.mymahanagar.com/maharashtra/mahadevi-elephant-in-nandani-will-return-minister-prakash-abitkar-gave-information-about-legal-process/907779/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>जिल्ह्याच्या सर्वांगिण विकासाचा संकल्प सर्वजण मिळून करू - पालकमंत्री प्रकाश आबिटकर यांचे जिल्हावासियांना आवाहन</t>
+          <t>Prakash Abitkar : आरोग्यमंत्र्यांच्या कोल्हापुरातच 'सलमान'ची चर्चा, प्रशासकीय अधिकारीही 'लाभार्थी'</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175693/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-advises-citizens-to-consult-professionals-that-time-some-officials-visit-salmans-hair-trainer-to-treatment-hair-problem-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>‘ईएसआयसी’ रुग्णालयात रुग्णसेवेच्या गुणवत्तेत वाढ करा – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Pune GBS : पुण्यातील 'त्या' विहिरीमुळे पसरला गुईलेन बॅरे सिंड्रोम, आरोग्यमंत्र्यांनी दिली धक्कादायक माहिती</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/170012/</t>
+          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>पालकमंत्री आबिटकर यांच्यासमोर नवे आव्हान!</t>
+          <t>खासगी रुग्णालयांची नोंदणी आता ऑनलाईन, आरोग्य मंत्री प्रकाश आबिटकर यांची घोषणा</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-faces-new-challenge</t>
+          <t>https://www.lokmat.com/kolhapur/registration-of-private-hospitals-now-online-health-minister-prakash-abitkar-announced-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री प्रकाश आबिटकर म्हणाले; शाकाहारी- मांसाहारीपेक्षा देशी प्रेम महत्त्वाचे!</t>
+          <t>कर्करोग प्रतिबंधासाठी जनजागृती गरजेची – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
+          <t>https://mahasamvad.in/154597/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pandharpur News | वारकर्‍यांची सेवा हीच पांडुरंगाची सेवा समजून काम करावे : मंत्री प्रकाश आबिटकर</t>
+          <t>जिल्ह्याच्या सर्वांगिण विकासाचा संकल्प सर्वजण मिळून करू - पालकमंत्री प्रकाश आबिटकर यांचे जिल्हावासियांना आवाहन</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/serve-warkaris-as-serving-pandurang-says-minister-prakash-abitkar-pandharpur-sk95</t>
+          <t>https://mahasamvad.in/175693/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर यांच्याकडून गुरुजनांना विधानसभेची हवाई सैर</t>
+          <t>‘ईएसआयसी’ रुग्णालयात रुग्णसेवेच्या गुणवत्तेत वाढ करा – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-minister-prakash-abitkar-takes-senior-citizens-on-air-trip-unique-guru-purnima-initiative-vsd-99-5224693/</t>
+          <t>https://www.mahasamvad.in/170012/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : राष्‍ट्रीय आरोग्‍य अभियानच्‍या कर्मचारी, अधिकारी यांचा पगार लवकरच</t>
+          <t>पालकमंत्री आबिटकर यांच्यासमोर नवे आव्हान!</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/salaries-of-national-health-mission-employees-and-officers-to-be-disbursed-soon-prakash-abitkar-pjp78</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-faces-new-challenge</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>‘जीबीएस’ वर उपचारांविषयी सर्वंकष उपाययोजना करा – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्य मंत्री प्रकाश आबिटकर म्हणाले; शाकाहारी- मांसाहारीपेक्षा देशी प्रेम महत्त्वाचे!</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153447/</t>
+          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>अरुण सरनाईक यांचा कलाविष्कार सदैव स्मरणात राहणारा : प्रकाश आबिटकर</t>
+          <t>प्रकाश आबिटकर यांच्याकडून गुरुजनांना विधानसभेची हवाई सैर</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-remembers-arun-sarnaiak-for-his-timeless-art-ocd-94-5177138/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-minister-prakash-abitkar-takes-senior-citizens-on-air-trip-unique-guru-purnima-initiative-vsd-99-5224693/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Kolhapur Shivsena: जिल्ह्यातील ठाकरे गट कोणाचाही दावणीला बांधू देणार नाही जुगार अड्डे</t>
+          <t>Prakash Abitkar : राष्‍ट्रीय आरोग्‍य अभियानच्‍या कर्मचारी, अधिकारी यांचा पगार लवकरच</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
+          <t>https://www.esakal.com/pune/salaries-of-national-health-mission-employees-and-officers-to-be-disbursed-soon-prakash-abitkar-pjp78</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री प्रकाश आबिटकर, राज्यमंत्री मेघना बोर्डीकर यांचा तामिळनाडू अभ्यास दौरा</t>
+          <t>‘जीबीएस’ वर उपचारांविषयी सर्वंकष उपाययोजना करा – आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157284/</t>
+          <t>https://mahasamvad.in/153447/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>अपघातग्रस्तांवर एक लाखांपर्यंत कॅशलेस उपचार करा; आरोग्यमंत्री आबिटकर यांचे निर्देश</t>
+          <t>GBS रुग्णांच्या उपचार करताना औषधांचा गैरवापर, जास्त पैसे पैसे घेतल्यास;आरोग्यमंत्री प्रकाश आबिटकर यांचा इशारा</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/cashless-treatment-up-to-one-lakh-for-accident-victims-health-minister-directive</t>
+          <t>https://www.lokmat.com/pune/beware-if-you-are-robbed-health-minister-prakash-abitkar-warns-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>आरोग्य विभागातील डॉक्टरांची रिक्त पदे तातडीने भरा- आरोग्यमंत्री</t>
+          <t>आरोग्यमंत्री प्रकाश आबिटकर, राज्यमंत्री मेघना बोर्डीकर यांचा तामिळनाडू अभ्यास दौरा</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fill-vacant-posts-of-doctors-in-health-department-immediately-says-health-minister-prakash-abitkar-mumbai-print-news-mrj-95-4857638/</t>
+          <t>https://mahasamvad.in/157284/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>राज्याच्या आरोग्य धोरणाबाबतचा प्रस्ताव तातडीने सादर करा – मंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Shivsena: जिल्ह्यातील ठाकरे गट कोणाचाही दावणीला बांधू देणार नाही जुगार अड्डे</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166367/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kolhapur | त्रुटीच इतक्या काढता, प्रस्ताव येणार कसे?</t>
+          <t>अपघातग्रस्तांवर एक लाखांपर्यंत कॅशलेस उपचार करा; आरोग्यमंत्री आबिटकर यांचे निर्देश</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-prakash-abitkar-pulls-up-forest-department-officials-ap84</t>
+          <t>https://pudhari.news/maharashtra/mumbai/cashless-treatment-up-to-one-lakh-for-accident-victims-health-minister-directive</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : मुश्रीफांना आबिटकरांचे वावडे? 'त्या' अहवालात स्थान देणं टाळलं; पालकमंत्री पदावरून नाराजी कायम</t>
+          <t>राज्यातील ग्रामीण रुग्णालय, प्राथमिक आरोग्य केंद्र इ.आरोग्य संस्थामध्ये दोन हजार पदनिर्मितीसाठी शासनाची मान्यता -आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-hasan-mushrif-prakash-abitkar-guardian-minister-rift-jap93-rg93</t>
+          <t>https://mahasamvad.in/156822/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरू करणार, मंत्री प्रकाश आबिटकर यांनी केली घोषणा</t>
+          <t>आरोग्य विभागातील डॉक्टरांची रिक्त पदे तातडीने भरा- आरोग्यमंत्री</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/awards-to-be-launched-for-all-departments-in-the-health-sector-health-minister-prakash-abitkar-announced-a-a746/</t>
+          <t>https://www.loksatta.com/mumbai/fill-vacant-posts-of-doctors-in-health-department-immediately-says-health-minister-prakash-abitkar-mumbai-print-news-mrj-95-4857638/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>हत्तीरोग मुक्त महाराष्ट्रासाठी औषधोपचार मोहिमेला सहकार्य करा – मंत्री प्रकाश आबिटकर</t>
+          <t>राज्यभरात कोरोना रुग्णसंख्येत वाढ; आरोग्य मंत्री प्रकाश आबिटकरांनी जनतेला केलं 'हे' आवाहन - PRAKASHRAO ABITKAR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/157564/</t>
+          <t>https://www.etvbharat.com/mr/!state/prakashrao-abitkar-reaction-on-maharashtra-corona-patient-shaktipeeth-highway-almatti-dam-water-chandrahar-patil-maharashtra-news-mhs25060905593</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी</t>
+          <t>kolhapur | त्रुटीच इतक्या काढता, प्रस्ताव येणार कसे?</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-prakash-abitkar-pulls-up-forest-department-officials-ap84</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Coronavirus : सिंगापूरनंतर राज्यात कोरोनाचा धोका वाढला? आरोग्यमंत्री म्हणाले...</t>
+          <t>Kolhapur Politics : मुश्रीफांना आबिटकरांचे वावडे? 'त्या' अहवालात स्थान देणं टाळलं; पालकमंत्री पदावरून नाराजी कायम</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/maharashtra-health-minister-on-corona-variants-situation-and-government-measures-nck90</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-hasan-mushrif-prakash-abitkar-guardian-minister-rift-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cashless Treatment : अपघातग्रस्तांना १ लाख रुपयांपर्यंत कॅशलेस उपचार मिळणार, राज्य सरकारचा मोठा निर्णय</t>
+          <t>हत्तीरोग मुक्त महाराष्ट्रासाठी औषधोपचार मोहिमेला सहकार्य करा – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/accident-victims-will-get-cashless-treatment-up-to-rs-1-lakh-big-decision-of-the-state-government-prakash-abitkar-gkt-96-5028935/</t>
+          <t>https://www.mahasamvad.in/157564/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
+          <t>आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरू करणार, मंत्री प्रकाश आबिटकर यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/abittkar-announced-guardian-minister-celebration-in-bhudargad</t>
+          <t>https://www.lokmat.com/kolhapur/awards-to-be-launched-for-all-departments-in-the-health-sector-health-minister-prakash-abitkar-announced-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>महादेवी हत्ती परत येणार?, वनतारा सीईओंसोबतच्या बैठकीतून मठाचे महास्वामी बाहेर पडले, नेमकं काय घडलं.. वाचा</t>
+          <t>Coronavirus : सिंगापूरनंतर राज्यात कोरोनाचा धोका वाढला? आरोग्यमंत्री म्हणाले...</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/now-a-legal-battle-for-the-mahadevi-elephant-of-nandani-math-guardian-minister-prakash-abitkar-gave-information-after-a-discussion-between-the-ceo-of-vanatara-and-the-mathadhis-a-a746/</t>
+          <t>https://saamtv.esakal.com/video/maharashtra-health-minister-on-corona-variants-situation-and-government-measures-nck90</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Prakashrao Abitkar : गर्भलिंग निदान सुरु असल्याची टीप देणाऱ्या खबरींना एका लाखाचं बक्षीस</t>
+          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेचा लाभ तळागाळातील गरजू कामगारांपर्यंत पोहोचवावा -सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Cashless Treatment : अपघातग्रस्तांना १ लाख रुपयांपर्यंत कॅशलेस उपचार मिळणार, राज्य सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173263/</t>
+          <t>https://www.loksatta.com/maharashtra/accident-victims-will-get-cashless-treatment-up-to-rs-1-lakh-big-decision-of-the-state-government-prakash-abitkar-gkt-96-5028935/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>‘अवयवदान’ ही मानवतेची व सामाजिक बदलाची चळवळ व्हावी – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/167252/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/abittkar-announced-guardian-minister-celebration-in-bhudargad</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्र्यांसमोरच दोन वैद्यकीय अधिकाऱ्यांमध्ये वाद: प्रकाश आबिटकरांनी दिली ईएसआयसी रुग्णालयाला अचानक भेट...</t>
+          <t>अलमट्टी, हिप्परगीच्या विसर्गावर लक्ष ठेवा, कोल्हापूरचे पालकमंत्री प्रकाश आबिटकर यांची सूचना</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/maharashtra-health-minister-prakash-abitkar-inspects-esic-hospital-kolhapur-135283124.html</t>
+          <t>https://www.lokmat.com/kolhapur/keep-an-eye-on-the-discharge-of-almatti-hippargi-dams-kolhapur-guardian-minister-prakash-abitkar-advice-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>तामिळनाडूच्या धर्तीवर सरकारी रुग्णालयांना मिळणार महात्मा फुले योजनेचा ५० टक्के निधी; राज्य सरकारचा महत्वपूर्ण निर्णय</t>
+          <t>महादेवी हत्ती परत येणार?, वनतारा सीईओंसोबतच्या बैठकीतून मठाचे महास्वामी बाहेर पडले, नेमकं काय घडलं.. वाचा</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-gave-an-explanation-in-the-legislative-council-phm-00-5212114/</t>
+          <t>https://www.lokmat.com/kolhapur/now-a-legal-battle-for-the-mahadevi-elephant-of-nandani-math-guardian-minister-prakash-abitkar-gave-information-after-a-discussion-between-the-ceo-of-vanatara-and-the-mathadhis-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Cashless Treatment in Hospital Maharashtra मोठी बातमी : अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार,</t>
+          <t>Prakashrao Abitkar : गर्भलिंग निदान सुरु असल्याची टीप देणाऱ्या खबरींना एका लाखाचं बक्षीस</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cashless-treatment-in-hospital-maharashtra-cashless-treatment-up-to-rs-1-lakh-for-accident-victims-big-decision-of-the-health-department-of-maharashtra-1354955</t>
+          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>कोल्हापूरचा क्रीडा विकास आराखडा तयार करावा – प्रकाश आबिटकर</t>
+          <t>राज्याच्या आरोग्य धोरणाबाबतचा प्रस्ताव तातडीने सादर करा – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-instructions-phm-00-5256184/</t>
+          <t>https://mahasamvad.in/166367/</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>दीनानाथ रुग्णालय अन् 10 लाखांच्या मागणी प्रकरणावर आरोग्य मंत्र्यांची पहिली प्रतिक्रिया, म्हणाले…</t>
+          <t>मस्तवाल दीनानाथ मंगेशकर हॉस्पिटलमध्ये आमदाराच्या पीएच्या पत्नीचा जीव जाताच</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-ordered-to-probe-and-inquiry-in-deenanath-mangeshkar-hospital-case-1378715.html</t>
+          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Shahu Maharaj Jayanti: शाहू महाराज यांचे काम देशाला दिशा देणारे: प्रकाश आबिटकर</t>
+          <t>‘अवयवदान’ ही मानवतेची व सामाजिक बदलाची चळवळ व्हावी – आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/shahu-maharajs-work-gave-direction-to-the-country-prakash-abitkar-prakash-abitkar</t>
+          <t>https://www.mahasamvad.in/167252/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी सुद्धा फॉर्म भरला; म्हणाले, अवयवदान इच्छा नोंदवणे जबाबदारी व्हायला हवी</t>
+          <t>kolhapur News : अधिकार्‍यांनी नावीन्यतेसह गुणवत्तापूर्ण कामे करावीत</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-all-departments-in-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : जुन्या पटावरची नवी समीकरणे, मंत्री आबीटकरांनी किमया केली, दोन राजकीय शत्रू आले एकत्र</t>
+          <t>Mahayuti Controversy: कोल्हापुरात 10 आमदार असलेल्या महायुतीत वादाचा भडका; आबिटकरांनाच विरोध,भाजपनं घातला थेट मुद्द्यालाच हात</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/friendship-buzz-between-congress-leader-sharangdhar-deshmukh-and-bjp-mp-dhananjay-mahadik-at-carrom-event-inaugurated-by-minister-prakash-abitkar-as11-rg93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-dispute-over-kolhapur-district-committee-bjp-ncp-vs-prakash-abitkar-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्यात क्रीडा क्षेत्रात मोठा वाव, क्रीडा संकुलासाठी अतिरिक्त निधी मिळावा म्हणून प्रयत्न करणार - पालकमंत्री प्रकाश आबिटकर</t>
+          <t>कामचुकारपणा आला अंगलट! आरोग्यमंत्र्यांचा दणका, हतरू आरोग्य केंद्रातील डॉक्टरसह चौघे निलंबित</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157463/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-primary-health-center-doctor-and-four-others-suspended</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : डॉक्टरांनी आरोग्य सेवा नाकारू नये; तनिषा भिसेच्या मृत्यूवर काय म्हणाले आरोग्यमंत्री?</t>
+          <t>Cashless Treatment in Hospital Maharashtra मोठी बातमी : अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार,</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cashless-treatment-in-hospital-maharashtra-cashless-treatment-up-to-rs-1-lakh-for-accident-victims-big-decision-of-the-health-department-of-maharashtra-1354955</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>कुष्ठरोग निर्मूलनाच्या प्रभावी अंमलबजावणीसाठी राज्यस्तरीय समिती स्थापन करणार -सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>तामिळनाडूच्या धर्तीवर सरकारी रुग्णालयांना मिळणार महात्मा फुले योजनेचा ५० टक्के निधी; राज्य सरकारचा महत्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172391/</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-gave-an-explanation-in-the-legislative-council-phm-00-5212114/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>अवयवदान मोठं पुण्याईच काम आहे… – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्यमंत्र्यांसमोरच दोन वैद्यकीय अधिकाऱ्यांमध्ये वाद: प्रकाश आबिटकरांनी दिली ईएसआयसी रुग्णालयाला अचानक भेट...</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174644/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/maharashtra-health-minister-prakash-abitkar-inspects-esic-hospital-kolhapur-135283124.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>आरोग्य शिबिरातून मोफत अत्याधुनिक वैद्यकीय सेवा उपलब्ध करून देणार - पालकमंत्री प्रकाश आबिटकर</t>
+          <t>दीनानाथ रुग्णालय अन् 10 लाखांच्या मागणी प्रकरणावर आरोग्य मंत्र्यांची पहिली प्रतिक्रिया, म्हणाले…</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173559/</t>
+          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-ordered-to-probe-and-inquiry-in-deenanath-mangeshkar-hospital-case-1378715.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीणीच्या परतीचा मार्ग मोकळा? जनभावना आणि वनताराच्या भूमिकेमुळे परतीची आशा</t>
+          <t>राज्य कामगार विमा योजनेचा लाभ तळागाळातील गरजू कामगारांपर्यंत पोहोचवावा -सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
+          <t>https://mahasamvad.in/173263/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>तानाजी सावंतांच्या कार्यकाळातील ३२०० कोटींचे टेंडर फडणवीसांकडून स्थगित, आरोग्यमंत्री म्हणाले…</t>
+          <t>कोल्हापूरचा क्रीडा विकास आराखडा तयार करावा – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/fadnavis-cancels-3200-crore-tender-during-tanaji-sawant-tenure-prakash-abitkar-reacts-a-a1008/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-instructions-phm-00-5256184/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>रुग्णालयांनी गरजू रुग्णांना शासकीय योजनांचा तत्परतेने लाभ द्यावा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Shahu Maharaj Jayanti: शाहू महाराज यांचे काम देशाला दिशा देणारे: प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173259/</t>
+          <t>https://agrowon.esakal.com/agro-special/shahu-maharajs-work-gave-direction-to-the-country-prakash-abitkar-prakash-abitkar</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>इंदिरा गांधी रुग्णालयात सुविधा पुरवणार – प्रकाश आबिटकर</t>
+          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी सुद्धा फॉर्म भरला; म्हणाले, अवयवदान इच्छा नोंदवणे जबाबदारी व्हायला हवी</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-assures-new-facilities-at-indira-gandhi-hospital-ocd-94-5247730/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>बचत गटांच्या चळवळीतून महिलांना आर्थिक सक्षम आणि साक्षर करूया – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Politics : जुन्या पटावरची नवी समीकरणे, मंत्री आबीटकरांनी किमया केली, दोन राजकीय शत्रू आले एकत्र</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166403/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/friendship-buzz-between-congress-leader-sharangdhar-deshmukh-and-bjp-mp-dhananjay-mahadik-at-carrom-event-inaugurated-by-minister-prakash-abitkar-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Kolhapur : सतर्क राहा; अलमट्टी, हिप्परगी विसर्गाबाबत समन्वय ठेवा</t>
+          <t>कोल्हापूर जिल्ह्यात क्रीडा क्षेत्रात मोठा वाव, क्रीडा संकुलासाठी अतिरिक्त निधी मिळावा म्हणून प्रयत्न करणार - पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-meeting-at-district-collector-office-dc95</t>
+          <t>https://mahasamvad.in/157463/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>५० हजार हक्काची घरे देण्यासाठी मिशन मोडवर काम करा -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : डॉक्टरांनी आरोग्य सेवा नाकारू नये; तनिषा भिसेच्या मृत्यूवर काय म्हणाले आरोग्यमंत्री?</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154283/</t>
+          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>विस्कळीत झालेली, १०२ रुग्णवाहिका सेवा पूर्ववत ?</t>
+          <t>Maharashtra | रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात ‘नो शॉर्टेज, नो वेस्टेज’ धोरण - आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-says-102-ambulance-service-restored-mumbai-print-news-ocd-94-5228346/</t>
+          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>मावळ तालुक्यातील आरोग्य संस्थांना आवश्यक सुविधा द्या - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>राज्याच्या प्रगतीत कोल्हापूर जिल्हा अग्रभागी राहण्यासाठी सर्वजण सज्ज होऊया -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174701/</t>
+          <t>https://mahasamvad.in/164322/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Pune News: प्रसुतीवेळी महिलेचा मृत्यू प्रकरणात आरोग्य मंत्र्यांचे कारवाईचे आदेश</t>
+          <t>आरोग्य शिबिरातून मोफत अत्याधुनिक वैद्यकीय सेवा उपलब्ध करून देणार - पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-health-minister-prakashrao-abitkar-orders-action-in-case-of-womans-death-during-childbirth-police-will-conduct-investigation-today-will-examine-cctv-along-with-statements-from-nurses-and-doctors-1352627</t>
+          <t>https://mahasamvad.in/173559/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Nandani Mahadevi Elephant : वनतारा सकारात्मक! नांदणी मठाची 'महादेवी' परत येण्याची शक्यता, पालकमंत्र्यांनी सांगितलं बैठकीत काय घडलं</t>
+          <t>तानाजी सावंतांच्या कार्यकाळातील ३२०० कोटींचे टेंडर फडणवीसांकडून स्थगित, आरोग्यमंत्री म्हणाले…</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
+          <t>https://www.lokmat.com/pune/fadnavis-cancels-3200-crore-tender-during-tanaji-sawant-tenure-prakash-abitkar-reacts-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : काेल्हापूर शहर हद्दवाढीची प्रक्रिया सुरू: प्रकाश आबिटकर ; मुख्यमंत्री, उपमुख्यमंत्री सकारात्मक</t>
+          <t>महादेवी हत्तीणीच्या परतीचा मार्ग मोकळा? जनभावना आणि वनताराच्या भूमिकेमुळे परतीची आशा</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-city-expansion-process-begins-cm-and-deputy-cm-supportive-abitkar-sdj87</t>
+          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Corona Cases In India : देशात कोरोनाची रुग्ण संख्या 257वर, तर राज्यात 53 कोरोना बाधित</t>
+          <t>कुष्ठरोग निर्मूलनाच्या प्रभावी अंमलबजावणीसाठी राज्यस्तरीय समिती स्थापन करणार -सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
+          <t>https://mahasamvad.in/172391/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Mahayuti News : 'स्थानिक'च्या निवडणुकीआधी महायुतीत नियुक्त्यांसाठी बिगफाईट; नेत्यांची डोकेदुखी वाढली...</t>
+          <t>अवयवदान मोठं पुण्याईच काम आहे… – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-leaders-lobby-for-kolhapur-dpdc-appointments-political-pressure-maharashtra-rm82-rg93</t>
+          <t>https://mahasamvad.in/174644/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>राष्ट्रीय आरोग्य अभियानाअंतर्गत कंत्राटी कर्मचाऱ्यांना नियमित करण्यासाठी कार्यवाही करा – ग्रामविकास मंत्री जयकुमार गोरे</t>
+          <t>Eknath Shinde's grand welcome : उपमुख्यमंत्री शिंदेंचं कोल्हापुरात ग्रँड वेलकम; आबिटकरांनी जाण ठेवत, स्वागतात सोडली नाही कुठलीच कसर!</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174852/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prakash-abitkar-grand-welcome-eknath-shinde-kolhapur-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री आबिटकर यांनी घेतले श्री विठ्ठल रुक्मिणी मातेचे दर्शन; VIP ट्रिटमेंट टाळत पायी जाणं केलं पसंत</t>
+          <t>बचत गटांच्या चळवळीतून महिलांना आर्थिक सक्षम आणि साक्षर करूया – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/health-minister-prakash-abitkar-took-darshan-of-shri-vitthal-rukmini-mata-temple-899077.html</t>
+          <t>https://mahasamvad.in/166403/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant : महादेवी हत्तीबाबत जिल्हाधिकारी कार्यालयात झालेल्या बैठकीवर पालकमंत्री आबिटकरांनी दिली सविस्तर माहिती</t>
+          <t>Kolhapur : सतर्क राहा; अलमट्टी, हिप्परगी विसर्गाबाबत समन्वय ठेवा</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-abitkar-shares-key-details-after-kolhapur-collector-office-meeting-on-mahadevi-elephant-issue-following-supreme-courts-controversial-order-srs92</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-meeting-at-district-collector-office-dc95</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>'महापुराच्या परिस्थितीला योग्य पद्धतीने सामोरं जाणार आहोत', Prakash Abitkar on Kolhapur Rainfall</t>
+          <t>Kolhapur Politics : ठरलं! महापालिका निवडणुकीत शिंदेंच्या शिवसेनेची सूत्रे अबिटकरांच्या हाती, तर राष्ट्रवादीची धुरा एकटे मुश्रीफ सांभाळणार</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/video/prakash-abitkar-kolhapur-rain-update-nrs96</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-ichalkaranji-municipal-election-political-strategies-party-alliance-hasan-mushrif-prakash-abitkar-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात 'नो शॉर्टेज, नो वेस्टेज' धोरण- मंत्री प्रकाश आबिटकर</t>
+          <t>विस्कळीत झालेली, १०२ रुग्णवाहिका सेवा पूर्ववत ?</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168889/</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-says-102-ambulance-service-restored-mumbai-print-news-ocd-94-5228346/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंचसाठी लगीनघाई; पुढील तीन दिवसात इमारतीचे हस्तांतरण, पालकमंत्र्यांकडून कामकाजाची पाहणी</t>
+          <t>येत्या काळात आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरु करणार - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
+          <t>https://mahasamvad.in/165634/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>वारसास्थळ यादीतील पन्हाळ्याचा समावेश अभिमानास्पद – आबिटकर</t>
+          <t>Nandani Mahadevi Elephant : वनतारा सकारात्मक! नांदणी मठाची 'महादेवी' परत येण्याची शक्यता, पालकमंत्र्यांनी सांगितलं बैठकीत काय घडलं</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/inclusion-of-panhala-in-the-heritage-site-list-is-a-matter-of-pride-says-prakash-abitkar-ssb-93-5224775/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Rural Housing Scheme : घरकुलांच्या उद्दिष्टपूर्तीत दिरंगाई नको ः प्रकाश आबिटकर</t>
+          <t>सार्वजनिक बांधकाम विभागांतर्गतची कामे दर्जेदार करा -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/no-delays-tolerated-in-housing-schemes-strict-action-warns-guardian-minister-mj18</t>
+          <t>https://mahasamvad.in/158717/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kolhapur |अत्याधुनिक सक्शन कम जेटिंग वाहनाचे पालकमंत्री आबिटकर यांच्या हस्ते लोकार्पण</t>
+          <t>Pune News: प्रसुतीवेळी महिलेचा मृत्यू प्रकरणात आरोग्य मंत्र्यांचे कारवाईचे आदेश</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-inaugurates-advanced-suction-cum-jetting-vehicle-ap84</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-health-minister-prakashrao-abitkar-orders-action-in-case-of-womans-death-during-childbirth-police-will-conduct-investigation-today-will-examine-cctv-along-with-statements-from-nurses-and-doctors-1352627</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>चांगल्या कामाचा लोक सन्मान करतात : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : काेल्हापूर शहर हद्दवाढीची प्रक्रिया सुरू: प्रकाश आबिटकर ; मुख्यमंत्री, उपमुख्यमंत्री सकारात्मक</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/rajarshi-shahu-awards-distributed-by-zilla-parishad-ap84</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-city-expansion-process-begins-cm-and-deputy-cm-supportive-abitkar-sdj87</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>बांधकाम पूर्ण झालेली रुग्णालये कार्यान्वित करून जनतेच्या सेवेत आणावीत- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Corona Cases In India : देशात कोरोनाची रुग्ण संख्या 257वर, तर राज्यात 53 कोरोना बाधित</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168802/</t>
+          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Chandrahar Patil: '...म्हणून चंद्रहार पाटलांनी ठाकरेंची साथ सोडली अन् शिंदेंच्या शिवसेनेत प्रवेश केला!'; 'या' मंत्र्यांचा मोठा दावा</t>
+          <t>अंधेरी येथील कामगार रुग्णालयातील आंतररुग्ण सुविधा नागरिकांसाठी उपलब्ध कराव्यात - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrahar-patil-switch-to-uddhav-thakceray-party-and-joining-eknath-shinde-shiv-sena-prakash-abitkar-big-claims-dk88</t>
+          <t>https://mahasamvad.in/168735/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant: 'माधुरी' लवकरच परतणार? नेमके काय म्हणाले पालकमंत्री प्रकाश आबिटकर? वाचाच...</t>
+          <t>भुदरगड तालुक्यातील सात धबधबे म्हणजे निसर्गात लपलेला अद्भुत खजिना – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/minister-prakash-abitkar-said-about-madhuri-mahadevi-elepahnt-nandni-math-vantara-947644.html</t>
+          <t>https://mahasamvad.in/172859/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>अनावश्यक गर्भाशय शस्त्रक्रिया करणाऱ्यांची गय करणार नाही, आरोग्य मंत्री प्रकाश आबिटकर यांचा इशारा</t>
+          <t>Mahayuti News : 'स्थानिक'च्या निवडणुकीआधी महायुतीत नियुक्त्यांसाठी बिगफाईट; नेत्यांची डोकेदुखी वाढली...</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-leaders-lobby-for-kolhapur-dpdc-appointments-political-pressure-maharashtra-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>बंधपत्रित वैद्यकीय अधिकाऱ्यांना ग्रामीण भागात सेवा देणे बंधनकारक - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>राष्ट्रीय आरोग्य अभियानाअंतर्गत कंत्राटी कर्मचाऱ्यांना नियमित करण्यासाठी कार्यवाही करा – ग्रामविकास मंत्री जयकुमार गोरे</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154909/</t>
+          <t>https://mahasamvad.in/174852/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : 'खंडपीठ'साठी माणिक पाटलांचं आंदोलन; समजुतीसाठी भाजप अन् शिवसेनेचा पुढाकार, तर राष्ट्रवादी...</t>
+          <t>राज्यातील कोरोना रूग्णांच्या संख्येत वाढ; आरोग्यमंत्री आबिटकरांनी दिली महत्त्वाची अपडेट</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-manik-patil-chuyekar-agitation-for-bench-court-was-stopped-in-the-presence-of-mp-dhananjay-mahadik-and-minister-prakashrao-abitkar-pp82-rg93</t>
+          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>कोल्हापूर खंडपीठ: १५ दिवसांत मुख्यमंत्र्यांसोबत भेट, पालकमंत्री आबिटकर यांचे आश्वासन</t>
+          <t>५० हजार हक्काची घरे देण्यासाठी मिशन मोडवर काम करा -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/meeting-with-cm-in-15-days-for-kolhapur-bench-guardian-minister-prakash-abitkar-assurance-a-a746/</t>
+          <t>https://mahasamvad.in/154283/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
+          <t>आरोग्यमंत्री आबिटकर यांनी घेतले श्री विठ्ठल रुक्मिणी मातेचे दर्शन; VIP ट्रिटमेंट टाळत पायी जाणं केलं पसंत</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
+          <t>https://www.navarashtra.com/maharashtra/health-minister-prakash-abitkar-took-darshan-of-shri-vitthal-rukmini-mata-temple-899077.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>मेगा रक्तदान शिबिराचे आयोजन करू नये; राज्य रक्त संक्रमण परिषदेच्या रक्तपेढ्यांना निर्देश</t>
+          <t>मावळ तालुक्यातील आरोग्य संस्थांना आवश्यक सुविधा द्या - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-health-department-prakash-abitkar-limits-mega-blood-donation-camps-mumbai-print-news-rds-00-5227011/</t>
+          <t>https://mahasamvad.in/174701/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या तीर्थक्षेत्रांना निधी कमी पडू देणार नाही</t>
+          <t>रायगड जिल्ह्यातील नागरिकांना उत्तम आरोग्य सुविधा देण्यासाठी शासन कटीबद्ध - मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/eknath-shinde-promises-funds-for-kolhapur-pilgrimage-sites</t>
+          <t>https://mahasamvad.in/158289/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Dr. Ashok Thorat : कोविड काळातील भ्रष्टाचार भोवला! बीड जिल्हा शल्य चिकित्सक अशोक थोरात यांचे निलंबन, प्रकाश आबिटकर यांची विधानसभेत घोषणा</t>
+          <t>Mahadevi Elephant : महादेवी हत्तीबाबत जिल्हाधिकारी कार्यालयात झालेल्या बैठकीवर पालकमंत्री आबिटकरांनी दिली सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/beed-district-surgeon-dr-ashok-thorat-suspended-health-minister-prakash-abitkar-announcement-in-vidhansabha-ymk86</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-abitkar-shares-key-details-after-kolhapur-collector-office-meeting-on-mahadevi-elephant-issue-following-supreme-courts-controversial-order-srs92</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>कोल्हापूरसह पाच जिल्ह्यांत १८ रोजी ‘सर्किट बेंच’ प्रारंभाचा आनंदोत्सव</t>
+          <t>'महापुराच्या परिस्थितीला योग्य पद्धतीने सामोरं जाणार आहोत', Prakash Abitkar on Kolhapur Rainfall</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/mumbai-high-court-circuit-bench-kolhapur-for-five-districts-prakash-abitkar-informed-css-98-5294507/</t>
+          <t>https://sarkarnama.esakal.com/video/prakash-abitkar-kolhapur-rain-update-nrs96</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kolhapur Politics | पालकमंत्र्यांच्या तालुक्यातूनच महायुतीत बंडखोरीचे वारे</t>
+          <t>रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात 'नो शॉर्टेज, नो वेस्टेज' धोरण- मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/ftii-to-deliver-film-making-courses-in-kolhapur-film-city-ap84-2</t>
+          <t>https://mahasamvad.in/168889/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Bandh: कोल्हापूर हद्दवाढीच्या विरोधात २० गावांत आज बंद; कृती समितीचा मंत्री आबिटकर, मुश्रीफांना इशारा</t>
+          <t>Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंचसाठी लगीनघाई; पुढील तीन दिवसात इमारतीचे हस्तांतरण, पालकमंत्र्यांकडून कामकाजाची पाहणी</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/20-villages-to-observe-bandh-today-against-kolhapur-boundary-extension-a-a746/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Sharangdhar Deshmukh : कोल्हापुरात कॉंग्रेसला खिंडार, माजी नगरसेवक करणार शिंदे सेनेत प्रवेश</t>
+          <t>Rural Housing Scheme : घरकुलांच्या उद्दिष्टपूर्तीत दिरंगाई नको ः प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
+          <t>https://agrowon.esakal.com/agro-special/no-delays-tolerated-in-housing-schemes-strict-action-warns-guardian-minister-mj18</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mahadevrao Mahadik : आप्पा महाडिकांनी दहीहंडी कार्यक्रमात आबिटकर, नरकेंशी केल्या कानगोष्टी; गोकुळ’ च्या राजकारणाला फुटणार उकळी, सतेज पाटलांचे काय?</t>
+          <t>सुपर स्पेशालिटीतील डॉक्टरांचे मानधन, ऑपरेशनचा निधी लवकरच मिळणार: आमदार खोडके यांनी उपस्थित केला प्रश्न; निध...</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/during-kolhapur-dahi-handi-event-appa-mahadik-was-seen-whispering-with-prakash-abitkar-and-chandradeep-narke-political-temperature-around-gokul-dudh-sangh-may-rise-whats-satej-patils-move-srs92</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/amravati/news/funds-for-super-specialty-doctors-honorarium-and-operations-will-be-available-soon-mla-khodke-raised-the-question-funds-will-be-provided-health-minister-abitkar-135398260.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>शाहू महाराजांच्या विचारांनी कोल्हापूरचे नाव उज्ज्वल करूया : पालकमंत्री आबिटकर</t>
+          <t>kolhapur |अत्याधुनिक सक्शन कम जेटिंग वाहनाचे पालकमंत्री आबिटकर यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/lets-glorify-kolhapur-with-shahu-maharajs-ideals-guardian-minister-abitkar-ap84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-inaugurates-advanced-suction-cum-jetting-vehicle-ap84</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Free cancer vaccine: राज्यातील 0-14 वयोगटातील मुलींना कॅन्सरविरोधी फ्री लस; कधी मिळणार लस, पाहा!</t>
+          <t>इंदिरा गांधी रुग्णालयात सुविधा पुरवणार – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/lifestyle/free-cancer-vaccine-for-girls-aged-0-14-in-the-state-check-when-it-will-be-available-sjk95</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-assures-new-facilities-at-indira-gandhi-hospital-ocd-94-5247730/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Medical Recruitment 2025: मोठी बातमी! राज्यात डॉक्टरांची मेगाभरती, सरकारी नोकरीची सुवर्णसंधी; १,५०० जागा भरल्या जाणार</t>
+          <t>चांगल्या कामाचा लोक सन्मान करतात : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/rajarshi-shahu-awards-distributed-by-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्गावरून कोल्हापुरातील मंत्र्यांमधील मतभेद चव्हाट्यावर</t>
+          <t>बांधकाम पूर्ण झालेली रुग्णालये कार्यान्वित करून जनतेच्या सेवेत आणावीत- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
+          <t>https://mahasamvad.in/168802/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा सोसायटीच्या रुग्णालयांमधून दर्जेदार आरोग्य सुविधा द्याव्यात- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Chandrahar Patil: '...म्हणून चंद्रहार पाटलांनी ठाकरेंची साथ सोडली अन् शिंदेंच्या शिवसेनेत प्रवेश केला!'; 'या' मंत्र्यांचा मोठा दावा</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151861/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrahar-patil-switch-to-uddhav-thakceray-party-and-joining-eknath-shinde-shiv-sena-prakash-abitkar-big-claims-dk88</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Maharashtra Government: अपघातग्रस्त रुग्णांना मिळणार १ लाख रुपयांपर्यंत कॅशलेस उपचार, फडणवीस सरकारचा मोठा निर्णय</t>
+          <t>अरुण सरनाईक यांचा कलाविष्कार सदैव स्मरणात राहणारा : प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/fadnavis-governments-big-move-maharashtra-govt-approves-rs-1-lakh-cashless-treatment-for-accident-victims-pvm91</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-remembers-arun-sarnaiak-for-his-timeless-art-ocd-94-5177138/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Kolhapur politics : कारे दुरावा कारे अबोला! मंत्री आबिटकर-मुश्रीफ यांच्यातील नाराजी उघड, बँकेच्या अहवालात पालकमंत्र्यांचा फोटोच नाही</t>
+          <t>Mahadevi Elephant: 'माधुरी' लवकरच परतणार? नेमके काय म्हणाले पालकमंत्री प्रकाश आबिटकर? वाचाच...</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/tension-between-ministers-abitkar-and-mushrif-continues-guardian-minister-prakashrao-abitkars-photo-missing-from-kdcc-bank-report-book-srs92</t>
+          <t>https://www.navarashtra.com/maharashtra/minister-prakash-abitkar-said-about-madhuri-mahadevi-elepahnt-nandni-math-vantara-947644.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Gokul Election : विधानसभा, लोकसभेचे उट्टे 'गोकुळ'मध्ये निघणार; मुश्रीफ-सतेज यांची कोंडी, आबिटकर-मंडलिकांसह नरके ठरणार निर्णायक</t>
+          <t>अनावश्यक गर्भाशय शस्त्रक्रिया करणाऱ्यांची गय करणार नाही, आरोग्य मंत्री प्रकाश आबिटकर यांचा इशारा</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/gokul-dudh-sangh-president-election-hasan-mushrif-satej-patil-prakash-abitkar-sanjay-mandlik-role-important-bam92</t>
+          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापूरच्या हद्दवाढीसाठी शासनाची पुढची स्टेप, पालकमंत्री आबिटकरांनी कायदेशीर त्रुटी दूर करण्यावर दिला भर</t>
+          <t>अवयवदान इच्छा नोंदवणे ही एक जबाबदारी बनायला हवी - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री तथा पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/governments-next-step-for-kolhapur-boundary-expansion-guardian-minister-abitkar-emphasizes-on-removing-legal-loopholes-srs92</t>
+          <t>https://mahasamvad.in/175714/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर यांची माहिती, दोन हजार पदनिर्मितीसाठी शासनाची मान्यता</t>
+          <t>कोल्हापूर खंडपीठ: १५ दिवसांत मुख्यमंत्र्यांसोबत भेट, पालकमंत्री आबिटकर यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
+          <t>https://www.lokmat.com/kolhapur/meeting-with-cm-in-15-days-for-kolhapur-bench-guardian-minister-prakash-abitkar-assurance-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>मंगेशकर रुग्णालय प्रकरणात कारवाई लवकरच; आरोग्यमंत्री आबिटकर यांची माहिती</t>
+          <t>Kolhapur Politics : 'खंडपीठ'साठी माणिक पाटलांचं आंदोलन; समजुतीसाठी भाजप अन् शिवसेनेचा पुढाकार, तर राष्ट्रवादी...</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-manik-patil-chuyekar-agitation-for-bench-court-was-stopped-in-the-presence-of-mp-dhananjay-mahadik-and-minister-prakashrao-abitkar-pp82-rg93</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री प्रकाश आबिटकर यांनी घेतली अवयवादानाची शपथ</t>
+          <t>अवयवदान पंधरवड्यास सुरुवात; आजपासून राज्यात जनजागृतीपर विविध उपक्रम</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
+          <t>https://mahasamvad.in/174294/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>आदर्श गोठा अभियानाच्या धर्तीवर आता जिल्ह्यात स्वच्छ - सुंदर घर अभियान -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>बंधपत्रित वैद्यकीय अधिकाऱ्यांना ग्रामीण भागात सेवा देणे बंधनकारक - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
+          <t>https://mahasamvad.in/154909/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Maharashtra | रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात ‘नो शॉर्टेज, नो वेस्टेज’ धोरण - आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
+          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>मोठी बातमी! राज्यात 1500 डॉक्टरांची भरती होणार, 10 एप्रिल रोजी जाहिरात निघणार</t>
+          <t>कोल्हापूरची ओळख ‘मेडिकल हब’ होईल : पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-will-become-medical-hub-guardian-minister-abitkar</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>राज्यातील कोरोना रूग्णांच्या संख्येत वाढ; आरोग्यमंत्री आबिटकरांनी दिली महत्त्वाची अपडेट</t>
+          <t>Dr. Ashok Thorat : कोविड काळातील भ्रष्टाचार भोवला! बीड जिल्हा शल्य चिकित्सक अशोक थोरात यांचे निलंबन, प्रकाश आबिटकर यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/major-update-on-coronavirus-in-maharashtra-health-minister-prakash-abitkar/</t>
+          <t>https://www.esakal.com/maharashtra/beed-district-surgeon-dr-ashok-thorat-suspended-health-minister-prakash-abitkar-announcement-in-vidhansabha-ymk86</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 4 कर्करोग रुग्णालयांची निर्मिती करणार; आरोग्यमंत्री प्रकाश आबिटकर यांनी केले जाहीर</t>
+          <t>कोल्हापूरसह पाच जिल्ह्यांत १८ रोजी ‘सर्किट बेंच’ प्रारंभाचा आनंदोत्सव</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
+          <t>https://www.loksatta.com/kolhapur/mumbai-high-court-circuit-bench-kolhapur-for-five-districts-prakash-abitkar-informed-css-98-5294507/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री Prakash Abitkar यांच्याकडून अवयवादानाची शपथ, राज्यात जनजागृतीपर विविध उपक्रम</t>
+          <t>मेगा रक्तदान शिबिराचे आयोजन करू नये; राज्य रक्त संक्रमण परिषदेच्या रक्तपेढ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/health-minister-prakash-abitkar-takes-oath-for-organ-donation-various-awareness-activities-in-the-state/128039/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-health-department-prakash-abitkar-limits-mega-blood-donation-camps-mumbai-print-news-rds-00-5227011/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Kolhapur City Extension : हद्दवाढ नाही तर निवडणूक नाही, कोल्हापूरची कृती समिती आक्रमक</t>
+          <t>कोल्हापूरच्या तीर्थक्षेत्रांना निधी कमी पडू देणार नाही</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-shahar-haddavad-samiti-warns-against-municipal-election-without-boundary-extension-as11-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/eknath-shinde-promises-funds-for-kolhapur-pilgrimage-sites</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>मोठी बातमी : सतेज पाटील आणि महाडिक यांच्यात पहिल्यांदाच एकमत, दोघेही एकाच फ्रेममध्ये!</t>
+          <t>महात्मा ज्योतिराव फुले जन आरोग्य योजनेचा लाभ जास्तीत जास्त लाभार्थ्यांपर्यंत पोहोचवा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
+          <t>https://mahasamvad.in/151398/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>येरवडा रुग्णालयातून '11 लाखांची अंतर्वस्त्रे गायब,' चौकशी समितीच्या अहवालातून कोणता घोटाळा समोर आलाय?</t>
+          <t>kolhapur Politics | पालकमंत्र्यांच्या तालुक्यातूनच महायुतीत बंडखोरीचे वारे</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/articles/c93n25pxqe1o</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/ftii-to-deliver-film-making-courses-in-kolhapur-film-city-ap84-2</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Almatti Dam Height : अलमट्टी उंची बाबत 15 दिवसांनी सर्व पक्षीयांसह पुन्हा बैठक आंदोलक आणि</t>
+          <t>मुख्यमंत्री-खंडपीठ कृती समिती यांच्यात लवकरच मुंबईत बैठक</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/meeting-between-chief-minister-and-khandepeeth-action-committee-to-be-held-soon-in-mumbai-ap84</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणीनंतर मुलींसाठी सरकारची मोठी घोषणा, 14 वर्षांपर्यंत मुलींना मोफत मिळणार ही गोष्ट</t>
+          <t>१०० जेसीबीमधून उपमुख्यमंत्री एकनाथ शिंदे यांच्यावर होणार फुलांची उधळण !</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/pune/maharashtra-government-to-provide-free-cancer-vaccine-for-girl-1358923.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/100-jcbs-to-shower-flowers-on-deputy-cm-eknath-shinde</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>नांदणी मठाची 'माधुरी' परत येणार? वनताराचे CEO म्हणाले, कोल्हापूरकरांना सर्व सहकार्य</t>
+          <t>Bandh: कोल्हापूर हद्दवाढीच्या विरोधात २० गावांत आज बंद; कृती समितीचा मंत्री आबिटकर, मुश्रीफांना इशारा</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
+          <t>https://www.lokmat.com/kolhapur/20-villages-to-observe-bandh-today-against-kolhapur-boundary-extension-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Pune Deenanath Mangeshkar Hospital Highlights: भाजपा कार्यकर्त्यांकडून डॉ. सुश्रुत घैसास यांच्या भावाच्या घराची तोडफोड</t>
+          <t>Sharangdhar Deshmukh : कोल्हापुरात कॉंग्रेसला खिंडार, माजी नगरसेवक करणार शिंदे सेनेत प्रवेश</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
+          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Nanded News : धक्कादायक! नांदेडच्या शासकीय ग्रामीण रुग्णालयात उंदरांचं साम्राज्य, चक्क</t>
+          <t>Mahadevrao Mahadik : आप्पा महाडिकांनी दहीहंडी कार्यक्रमात आबिटकर, नरकेंशी केल्या कानगोष्टी; गोकुळ’ च्या राजकारणाला फुटणार उकळी, सतेज पाटलांचे काय?</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/during-kolhapur-dahi-handi-event-appa-mahadik-was-seen-whispering-with-prakash-abitkar-and-chandradeep-narke-political-temperature-around-gokul-dudh-sangh-may-rise-whats-satej-patils-move-srs92</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway च्या भूसंपादनाला मंजुरी अन् 20 हजार कोटींची तरतूद, कोणत्या जिल्ह्यांमधून जाणार...</t>
+          <t>शाहू महाराजांच्या विचारांनी कोल्हापूरचे नाव उज्ज्वल करूया : पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/lets-glorify-kolhapur-with-shahu-maharajs-ideals-guardian-minister-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking LIVE: देश-विदेशातील महत्त्वाच्या घडामोडींचा आढावा फक्त एका क्लिकवर...</t>
+          <t>Free cancer vaccine: राज्यातील 0-14 वयोगटातील मुलींना कॅन्सरविरोधी फ्री लस; कधी मिळणार लस, पाहा!</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
+          <t>https://saamtv.esakal.com/lifestyle/free-cancer-vaccine-for-girls-aged-0-14-in-the-state-check-when-it-will-be-available-sjk95</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर आणि जयकुमार गोरे यांचे आदेश, कंत्राटी कर्मचाऱ्यांना नियमित करा</t>
+          <t>कोल्हापूर जिल्ह्याला प्रथमच 2 पालकमंत्री</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-district-gets-2-guardian-ministers-for-the-first-time</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : घाबरून न जाऊ नका, लोकांना पॅनिक करू नका – आरोग्यमंत्री अबिटकर</t>
+          <t>Medical Recruitment 2025: मोठी बातमी! राज्यात डॉक्टरांची मेगाभरती, सरकारी नोकरीची सुवर्णसंधी; १,५०० जागा भरल्या जाणार</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Prakash Abitkar | Corona ला घाबरून न जाऊ नका, लोकांना पॅनिक करू नका : आरोग्यमंत्री</t>
+          <t>शक्तिपीठ महामार्गावरून कोल्हापुरातील मंत्र्यांमधील मतभेद चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
+          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Shaktipeeth Highway : सांगली, हिंगोलीसह 10 जिल्ह्यात शक्तीपीठ महामार्गाला कडवा विरोध; कोल्हापुरबाबत पालकमंत्र्यांनी दिले संकेत</t>
+          <t>राज्य कामगार विमा सोसायटीच्या रुग्णालयांमधून दर्जेदार आरोग्य सुविधा द्याव्यात- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-minister-prakash-abitkar-confirms-cancellation-of-shaktipeeth-highway-as11</t>
+          <t>https://mahasamvad.in/151861/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्गास 2 मंत्र्यांचा विरोध, मंत्रिमंडळ बैठकीत पडसाद राजू शेट्टी</t>
+          <t>Maharashtra Government: अपघातग्रस्त रुग्णांना मिळणार १ लाख रुपयांपर्यंत कॅशलेस उपचार, फडणवीस सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
+          <t>https://saamtv.esakal.com/maharashtra/fadnavis-governments-big-move-maharashtra-govt-approves-rs-1-lakh-cashless-treatment-for-accident-victims-pvm91</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Maharashtra: Beed Surgeon Suspended For 'Embezzling Crores In Medicine Procurement During COVID-19'</t>
+          <t>kolhapur | पालकमंत्र्यांकडे जाणार्‍या फायली सहपालकमंत्र्यांमार्फत</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shinde-shiv-sena-vs-bjp-kolhapur-political-clash-ap84</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Lack of voluntary blood donations help ‘red market’ thrive</t>
+          <t>Kolhapur politics : कारे दुरावा कारे अबोला! मंत्री आबिटकर-मुश्रीफ यांच्यातील नाराजी उघड, बँकेच्या अहवालात पालकमंत्र्यांचा फोटोच नाही</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/tension-between-ministers-abitkar-and-mushrif-continues-guardian-minister-prakashrao-abitkars-photo-missing-from-kdcc-bank-report-book-srs92</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की लड़कियों को फ्री में दी जाएगी कैंसर की वैक्सीन</t>
+          <t>Kolhapur : कोल्हापूरच्या हद्दवाढीसाठी शासनाची पुढची स्टेप, पालकमंत्री आबिटकरांनी कायदेशीर त्रुटी दूर करण्यावर दिला भर</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/governments-next-step-for-kolhapur-boundary-expansion-guardian-minister-abitkar-emphasizes-on-removing-legal-loopholes-srs92</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार की 20,787 करोड़ रुपये की मंजूरी, तैयार होगा नागपुर-गोवा शक्तिपीठ एक्सप्रेसवे!</t>
+          <t>प्रकाश आबिटकर यांची माहिती, दोन हजार पदनिर्मितीसाठी शासनाची मान्यता</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Central team focuses on source, diagnosis amid GBS cases surge | Latest News India - Hindustan Times</t>
+          <t>मंगेशकर रुग्णालय प्रकरणात कारवाई लवकरच; आरोग्यमंत्री आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
+          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GBS Outbreak: First fatality confirmed in Pune as cases surge</t>
+          <t>आरोग्य मंत्री प्रकाश आबिटकर यांनी घेतली अवयवादानाची शपथ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>खौफनाक: महाराष्ट्र में एक जिले में 14000 महिलाओं में मिले कैंसर के लक्षण, क्या बोले स्वास्थ्य मंत्री?</t>
+          <t>आदर्श गोठा अभियानाच्या धर्तीवर आता जिल्ह्यात स्वच्छ - सुंदर घर अभियान -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
+          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>State to bring all diagnostic labs under health dept’s purview</t>
+          <t>मोठी बातमी! राज्यात 1500 डॉक्टरांची भरती होणार, 10 एप्रिल रोजी जाहिरात निघणार</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
+          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>No one has to worry, says Maharashtra Health Minister Abitkar on HMPV</t>
+          <t>Prakash Abitkar : 4 कर्करोग रुग्णालयांची निर्मिती करणार; आरोग्यमंत्री प्रकाश आबिटकर यांनी केले जाहीर</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
+          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Maharashtra Accident Victims: Cashless Treatment up to Rs 1 Lakh in Emergency Hospitals</t>
+          <t>Maharashtra News Live Updates: कोरोनाचे लक्षण सौम्य असून काळजी घेणे गरजेचं - मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-rs-1-lakh-3499736</t>
+          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-live-news-updates-29-may-2025-heavy-rainfall-alert-across-maharashtra-mumbai-pune-red-alert-rains-weather-forecast-live-news-today-maharashtra-politics-corona-update-mumbai-pune-local-entertainment-sports-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Statewide awareness campaign on organ donation from Aug 3 to 15</t>
+          <t>मोठी बातमी : सतेज पाटील आणि महाडिक यांच्यात पहिल्यांदाच एकमत, दोघेही एकाच फ्रेममध्ये!</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Maharashtra cabinet approves Mahalaxmi &amp; Jotiba temple development plans</t>
+          <t>Kolhapur City Extension : हद्दवाढ नाही तर निवडणूक नाही, कोल्हापूरची कृती समिती आक्रमक</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-shahar-haddavad-samiti-warns-against-municipal-election-without-boundary-extension-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>One Day for Farmer initiative implemented in Kolhapur district</t>
+          <t>येरवडा रुग्णालयातून '11 लाखांची अंतर्वस्त्रे गायब,' चौकशी समितीच्या अहवालातून कोणता घोटाळा समोर आलाय?</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
+          <t>https://www.bbc.com/marathi/articles/c93n25pxqe1o</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Maharashtra: Child Health Drive Faces Backlash Over Unpaid RBSK Medical Teams</t>
+          <t>Almatti Dam Height : अलमट्टी उंची बाबत 15 दिवसांनी सर्व पक्षीयांसह पुन्हा बैठक आंदोलक आणि</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/maharashtra-child-health-drive-faces-backlash-over-unpaid-rbsk-medical-teams</t>
+          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Maha to accredit private hospitals under Health Tourism Policy</t>
+          <t>लाडक्या बहिणीनंतर मुलींसाठी सरकारची मोठी घोषणा, 14 वर्षांपर्यंत मुलींना मोफत मिळणार ही गोष्ट</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/pune/maharashtra-government-to-provide-free-cancer-vaccine-for-girl-1358923.html</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Maharashtra To Launch Statewide Organ Donation Drive From August 3 To 15</t>
+          <t>नांदणी मठाची 'माधुरी' परत येणार? वनताराचे CEO म्हणाले, कोल्हापूरकरांना सर्व सहकार्य</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-launch-statewide-organ-donation-drive-from-august-3-to-15</t>
+          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Pune: Yerawada Mental Hospital Extends OPD Timing Till 5PM</t>
+          <t>Pune Deenanath Mangeshkar Hospital Highlights: भाजपा कार्यकर्त्यांकडून डॉ. सुश्रुत घैसास यांच्या भावाच्या घराची तोडफोड</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-yerawada-mental-hospital-extends-opd-timing-till-5pm</t>
+          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Mushrif appeals to Gokul chairman Arun Dongale to resign</t>
+          <t>Shaktipeeth Expressway च्या भूसंपादनाला मंजुरी अन् 20 हजार कोटींची तरतूद, कोणत्या जिल्ह्यांमधून जाणार...</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
+          <t>Maharashtra Breaking LIVE: देश-विदेशातील महत्त्वाच्या घडामोडींचा आढावा फक्त एका क्लिकवर...</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Spell out measures taken to prevent children deaths in Maharashtra: NCP (SP) to govt | Latest News India</t>
+          <t>प्रकाश आबिटकर आणि जयकुमार गोरे यांचे आदेश, कंत्राटी कर्मचाऱ्यांना नियमित करा</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
+          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Health dept to focus on doorstep services amid Covid cases, monsoon</t>
+          <t>Prakash Abitkar : घाबरून न जाऊ नका, लोकांना पॅनिक करू नका – आरोग्यमंत्री अबिटकर</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
+          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>With 1.6L units till May, Pune dist ahead in blood donation so far this year</t>
+          <t>Prakash Abitkar | Corona ला घाबरून न जाऊ नका, लोकांना पॅनिक करू नका : आरोग्यमंत्री</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Maharashtra: Thousands Join Silent March In Kolhapur To Demand Return Of Elephant Mahadevi From Vantara</t>
+          <t>Shaktipeeth Highway : सांगली, हिंगोलीसह 10 जिल्ह्यात शक्तीपीठ महामार्गाला कडवा विरोध; कोल्हापुरबाबत पालकमंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-thousands-join-silent-march-in-kolhapur-to-demand-return-of-elephant-mahadevi-from-vantara-video</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-minister-prakash-abitkar-confirms-cancellation-of-shaktipeeth-highway-as11</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>One more decision of Shiv Sena ex-min Tanaji Sawant clouded by controversy</t>
+          <t>शक्तिपीठ महामार्गास 2 मंत्र्यांचा विरोध, मंत्रिमंडळ बैठकीत पडसाद राजू शेट्टी</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
+          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>How the transfer of an elephant in Kolhapur led to a boycott of Jio</t>
+          <t>Maharashtra: Beed Surgeon Suspended For 'Embezzling Crores In Medicine Procurement During COVID-19'</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/how-the-transfer-of-an-elephant-in-kolhapur-led-to-a-boycott-of-jio-10164145/</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome: An explainer as cases are on the rise in Maharashtra</t>
+          <t>GBS Outbreak: First fatality confirmed in Pune as cases surge</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
+          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Deenanath Mangeshkar Hospital Controversy Deepens</t>
+          <t>Lack of voluntary blood donations help ‘red market’ thrive</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Deenanath Mangeshkar Hospital Under Fire: BJP MLC’s PA’s Wife......</t>
+          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की लड़कियों को फ्री में दी जाएगी कैंसर की वैक्सीन</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy-pregnant-woman-death</t>
+          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>People staying within 100m periphery of Panhala fort fear displacement</t>
+          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की बेटियों के लिए किया ये ऐलान</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
+          <t>https://hindi.news24online.com/state/mumbai/devendra-fadnavis-government-announces-free-cancer-vaccine-for-girls-under-14-years-of-age-maharashtra-news/1088804/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>The Controversy of Mahadevi: A 36-Year-Old Elephant's Journey from Kolhapur to Gujarat</t>
+          <t>फडणवीस सरकार की 20,787 करोड़ रुपये की मंजूरी, तैयार होगा नागपुर-गोवा शक्तिपीठ एक्सप्रेसवे!</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3526640-the-controversy-of-mahadevi-a-36-year-old-elephants-journey-from-kolhapur-to-gujarat</t>
+          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Guillain Barre: मुंबई में पहला संदिग्ध जीबीएस केस आया सामने, जानें कैसे करें इससे बचाव</t>
+          <t>Central team focuses on source, diagnosis amid GBS cases surge | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://ndtv.in/health/1st-suspected-gbs-case-surfaced-in-mumbai-know-how-to-prevent-it-7662749</t>
+          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>महाराष्ट्र-कर्नाटक सीमा विवाद अब होगा हल! राज्य सरकार ने विपक्ष संग समिति का किया पुनर्गठन</t>
+          <t>CMO denies staying 3.2k cr contract of ex-health minister</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-government-reconstitutes-committee-resolve-border-dispute-karnataka-1260125.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>शिंदे-दादा के क्षेत्र में सर्वाधिक फर्जी लाडली बहनें!</t>
+          <t>Charitable hospitals must comply with govt health scheme GR: Minister</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Assembly election losers from MVA first pick in Mahayuti poaching spree</t>
+          <t>State to set up Maharashtra Public Health Infrastructure Corporation</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Kolhapur politics : वडील उद्धव ठाकरेंसोबत तर मुलगा मात्र अजित पवारांच्या राष्ट्रवादीच्या स्टेजवर; कोल्हापूरचं हटके राजकारण!</t>
+          <t>खौफनाक: महाराष्ट्र में एक जिले में 14000 महिलाओं में मिले कैंसर के लक्षण, क्या बोले स्वास्थ्य मंत्री?</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-kp-patil-with-uddhav-thackeray-son-ranjit-patil-on-ajit-pawar-stage-msr87-rg93</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>‘पुढारी’कार डॉ. ग. गो. जाधव यांना अभिवादन</t>
+          <t>No one has to worry, says Maharashtra Health Minister Abitkar on HMPV</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/greetings-to-pudhari-dr-g-g-jadhav-ap84</t>
+          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>तुमच्यात काही मतभेद असतील तर सांगा, मी मिटवतो ! शाहू महाराजांची कोपरखळी, शिवसेना नेत्यांनाही हसू आवरेना</t>
+          <t>Statewide awareness campaign on organ donation from Aug 3 to 15</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/If-there-are-any-disagreements-among-you--tell-me--and-I-will-resolve-them--Shahu-Maharaj-s-jab-even-made-the-Shiv-Sena-leaders-unable-to-contain-their-laughter-</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Maharashtra Government To Provide Free Cancer Vaccine For Girls Aged 0-14</t>
+          <t>Maharashtra cabinet approves Mahalaxmi &amp; Jotiba temple development plans</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-7825621</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Maharashtra Expands Cashless Treatment For Accident Victims Up To ₹1 Lakh</t>
+          <t>One Day for Farmer initiative implemented in Kolhapur district</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-expands-cashless-treatment-for-accident-victims-up-to-1-lakh</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : कोल्हापुरचं राजकारण फिरवणारे बंटी पाटील एकटे कसे पडले? 'घात' कुठे झाला?</t>
+          <t>Maharashtra: Child Health Drive Faces Backlash Over Unpaid RBSK Medical Teams</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-satej-patil-political-isolation-hasan-mushrif-chandradeep-narke-defection-congress-maharashtra-hn97</t>
+          <t>https://www.thebridgechronicle.com/news/maharashtra-child-health-drive-faces-backlash-over-unpaid-rbsk-medical-teams</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers List : तीन नेत्यांकडे सहा जिल्हे, कोल्हापूर अन् मुंबईसाठी दोन -दोन कारभारी,</t>
+          <t>Maharashtra To Launch Statewide Organ Donation Drive From August 3 To 15</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-launch-statewide-organ-donation-drive-from-august-3-to-15</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Kolhapur Politics: दोन कट्टर राजकीय विरोधक एका प्रश्नावर आले एकत्र!</t>
+          <t>Pune: Yerawada Mental Hospital Extends OPD Timing Till 5PM</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-mla-satej-patil-mla-amal-mahadik-kolhapur-airport-road-meeting-guardian-minister-prakash-abitkar-mm76-rg93</t>
+          <t>https://www.freepressjournal.in/pune/pune-yerawada-mental-hospital-extends-opd-timing-till-5pm</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 24 जून 2025 | मंगळवार</t>
+          <t>JP Nadda Launches National Mass Drug Administration Round for Elimination of Lymphatic Filariasis</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
+          <t>https://pragativadi.com/jp-nadda-launches-national-mass-drug-administration-round-for-elimination-of-lymphatic-filariasis/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : अखेर 80 वर्षांच्या के. पी. पाटलांना अजितदादांनी स्वीकारलंच: पक्षप्रवेशासाठी कोल्हापूरमध्ये जंगी मेळावा</t>
+          <t>Mushrif appeals to Gokul chairman Arun Dongale to resign</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-mla-kp-patil-joins-ncp-ajit-pawar-kolhapur-visit-may-23-hn97</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Rahul Patil: काँग्रेस निष्ठावंतांचे पुत्र हाती घड्याळ बांधणार, करवीरचे राहुल पाटील राष्ट्रवादीत?</t>
+          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-congress-leader-rahul-patil-to-join-ncp-mm76-rg93</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 1 जून 2025 | रविवार</t>
+          <t>Spell out measures taken to prevent children deaths in Maharashtra: NCP (SP) to govt | Latest News India</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
+          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Agriculture University: कृषी विद्यापीठांचा फजितवाडा</t>
+          <t>Health dept to focus on doorstep services amid Covid cases, monsoon</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/sampadkiya/the-dilemma-of-agricultural-universities-article-on-agrowon-rat16</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Kolhapur Corona Update : महाराष्ट्राच्या आरोग्याची चावी हाती असलेल्या दोन मंत्र्यांच्या कोल्हापुरात</t>
+          <t>With 1.6L units till May, Pune dist ahead in blood donation so far this year</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>LMOTY 2025: हे चेहरे गाजवणार महाराष्ट्राचं पुढचं राजकारण; कोण ठरणार प्रॉमिसिंग राजकारणी?</t>
+          <t>Maharashtra: Thousands Join Silent March In Kolhapur To Demand Return Of Elephant Mahadevi From Vantara</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/lokmat-maharashtrian-of-the-year-awards-2025-here-are-the-nominations-for-promising-politician-category-a-a301/</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-thousands-join-silent-march-in-kolhapur-to-demand-return-of-elephant-mahadevi-from-vantara-video</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Chandrahar Patil : चंद्रहार पाटील यांचे अखेर ठरले, ठाकरे सेनेला रामराम, सरकारसोबत जाणार; सांगलीच्या राजकारणात नवा ट्विस्ट</t>
+          <t>One more decision of Shiv Sena ex-min Tanaji Sawant clouded by controversy</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापुरात एकनाथ शिंदेंची 'जादू', एकाच वेळी काँग्रेस-भाजप आणि ताराराणी</t>
+          <t>How the transfer of an elephant in Kolhapur led to a boycott of Jio</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
+          <t>https://indianexpress.com/article/cities/pune/how-the-transfer-of-an-elephant-in-kolhapur-led-to-a-boycott-of-jio-10164145/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Kolhapur APMC election | सभापती निवडीत पालकमंत्र्यांची एंट्री</t>
+          <t>Guillain-Barré Syndrome: An explainer as cases are on the rise in Maharashtra</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-ministers-entry-in-kolhapur-agricultural-produce-market-committee-chairman-election-ap84</t>
+          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Gokul President Election : कोल्हापुरच्या राजकारणात मुश्रीफांची ताकद वाढली; जिल्हा बँक आणि गोकुळवर पितापुत्रांचं 'वर्चस्व', वाचा महिनाभरात काय काय घडलं?</t>
+          <t>Deenanath Mangeshkar Hospital Controversy Deepens</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
+          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Chandrahar Patil : उद्धव ठाकरेंना मोठा धक्का! डबल महाराष्ट्र केसरी चंद्रहार पाटील आज शिंदेंच्या शिवसेनेत प्रवेश करणार</t>
+          <t>Deenanath Mangeshkar Hospital Under Fire: BJP MLC’s PA’s Wife......</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/maharashtra/lokshahi-politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
+          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy-pregnant-woman-death</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Almatty Dam : कर्नाटक भाजपचे महाराष्ट्राविरोधात वाकडे पाऊल, अलमट्टी धरणाची उंची वाढवण्यासाठी केंद्रीय मंत्र्यांच्या गाठीभेटी, वाद चिघळणार?</t>
+          <t>People staying within 100m periphery of Panhala fort fear displacement</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/almatti-dam-height-increase-karnataka-bjp-mps-maharashtra-flood-risk-dispute-jap93-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Almatti dam height : ‘आलमट्टी’वरून राजकीय वातावरण तापलं ; जलसंपदा मंत्री विखे पुन्हा घेणार सर्वपक्षीय बैठक!</t>
+          <t>Vikhe Patil to irrigation dept: Study concerns on Almatti dam</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/radhakrishna-vikhe-patil-to-hold-all-party-meeting-on-almatti-dam-height-water-dispute-maharashtra-karnataka-msr87-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vikhe-patil-to-irrigation-dept-study-concerns-on-almatti-dam/articleshow/121323044.cms</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : 'माधुरी'चा प्रश्न मार्गी लागणार? मंत्रिमंडळाच्या बैठकीत मुख्यमंत्री देवेंद्र फडणवीस यांची मोठी घोषणा</t>
+          <t>Shaktipeeth Expressway: शक्तिपीठ एक्सप्रेसवे के खिलाफ सड़क पर उतरे किसान, फडणवीस ने विधानसभा में गिनाए महामार्ग के फायदे-नुकसान</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers List : पालकमंत्र्यांची यादी जाहीर, बीड आणि पुण्याबाबत सरकारचा मोठा निर्णय</t>
+          <t>शिंदे-दादा के क्षेत्र में सर्वाधिक फर्जी लाडली बहनें!</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
+          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Maharashtra Live Blog: माळेगाव सहकारी कारखाना निवडणुकीच्या मतमोजणीच्या प्रत्येक क्षणाचे वेगवान अपडेटस्, शरद पव</t>
+          <t>महाराष्ट्र-कर्नाटक सीमा विवाद अब होगा हल! राज्य सरकार ने विपक्ष संग समिति का किया पुनर्गठन</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-beed-santosh-deshmukh-case-maharashtra-politics-malegaon-sahakari-sakhar-karkhana-election-2025-1365817</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-government-reconstitutes-committee-resolve-border-dispute-karnataka-1260125.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Maharashtra Karnataka Border Dispute: सीमाप्रश्नी उच्चाधिकार समितीची पुनर्रचना</t>
+          <t>Assembly election losers from MVA first pick in Mahayuti poaching spree</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/reorganization-of-the-high-power-committee-on-border-issues-rat16</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Maharashta Gurdian Ministers Full List : मुंबई ते गडचिरोली, बीड ते नागपूर, तुमच्या जिल्ह्याचा पालकमंत्री</t>
+          <t>Kolhapur politics : वडील उद्धव ठाकरेंसोबत तर मुलगा मात्र अजित पवारांच्या राष्ट्रवादीच्या स्टेजवर; कोल्हापूरचं हटके राजकारण!</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-kp-patil-with-uddhav-thackeray-son-ranjit-patil-on-ajit-pawar-stage-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीणीला परत आणण्यासाठी राज्य सरकार उचलणार मोठं पाऊल; मुख्यमंत्री देवेंद्र फडणवीसांनी सगळच सांगितलं</t>
+          <t>‘पुढारी’कार डॉ. ग. गो. जाधव यांना अभिवादन</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/greetings-to-pudhari-dr-g-g-jadhav-ap84</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>India reports 2 more deaths from Guillain-Barre Syndrome, raising total to 3</t>
+          <t>तुमच्यात काही मतभेद असतील तर सांगा, मी मिटवतो ! शाहू महाराजांची कोपरखळी, शिवसेना नेत्यांनाही हसू आवरेना</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
+          <t>https://maharashtranews1.com/If-there-are-any-disagreements-among-you--tell-me--and-I-will-resolve-them--Shahu-Maharaj-s-jab-even-made-the-Shiv-Sena-leaders-unable-to-contain-their-laughter-</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>More that 12k children died in Maharashtra between Apr last year and Feb 2025: Minister</t>
+          <t>Maharashtra Expands Cashless Treatment For Accident Victims Up To ₹1 Lakh</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-expands-cashless-treatment-for-accident-victims-up-to-1-lakh</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Maharashtra govt to set up vigilance cells to stop illegal uterus removals among cane cutters</t>
+          <t>Kolhapur Politics : कोल्हापुरचं राजकारण फिरवणारे बंटी पाटील एकटे कसे पडले? 'घात' कुठे झाला?</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-satej-patil-political-isolation-hasan-mushrif-chandradeep-narke-defection-congress-maharashtra-hn97</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Nurses’ strike leaves Sassoon wards deserted, administration struggles to find replacements</t>
+          <t>Maharashtra Guardian Ministers List : तीन नेत्यांकडे सहा जिल्हे, कोल्हापूर अन् मुंबईसाठी दोन -दोन कारभारी,</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Kolhapur celebrates I-Day, Janmashtami &amp; Dahi Handi</t>
+          <t>Kolhapur Politics : अखेर 80 वर्षांच्या के. पी. पाटलांना अजितदादांनी स्वीकारलंच: पक्षप्रवेशासाठी कोल्हापूरमध्ये जंगी मेळावा</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-mla-kp-patil-joins-ncp-ajit-pawar-kolhapur-visit-may-23-hn97</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ZTCC, health minister honours families of deceased donors</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 24 जून 2025 | मंगळवार</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
+          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Kolhapur IT Park &amp; employment initiatives announced at district investment summit</t>
+          <t>Gokul Politics : गोकुळमध्ये पुन्हा संघर्ष? वाढवलेल्या ठरावांचा नेता कोण? घमासान होण्याची चिन्हे</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/the-impact-of-1800-new-members-in-gokul-dairy-union-depends-on-upcoming-alliance-between-mahayuti-or-mva-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Kolhapur district planning body okays 67cr to revamp zilla parishad schools</t>
+          <t>Hasan Mushrif : हसन मुश्रीफांना कोल्हापूर न देण्यामागचं कारण, दोस्ताना आला अंगलट?</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/why-hasan-mushrif-not-appointed-as-kolhapur-guardian-minister-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>CA from Dhayari, 41, who died in Solapur, first GBS casualty; patient count in Pune touches 111</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 1 जून 2025 | रविवार</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Tender scam hits Akola women’s hospital, dist civil surgeon, two other top officials suspended</t>
+          <t>kolhapur | मेहुणे-पाहुण्यांचा राजकीय संघर्ष मुश्रीफांमुळे संपणार</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/political-conflict-between-k-p-patil-and-a-y-patil-will-end-due-to-mushrif-ap84</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Patient records at 2,100 centres to be digitised</t>
+          <t>Rahul Patil: काँग्रेस निष्ठावंतांचे पुत्र हाती घड्याळ बांधणार, करवीरचे राहुल पाटील राष्ट्रवादीत?</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-congress-leader-rahul-patil-to-join-ncp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Maharashtra health department cancels deputation of Nashik civic body’s medical superintendent</t>
+          <t>Agriculture University: कृषी विद्यापीठांचा फजितवाडा</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
+          <t>https://agrowon.esakal.com/sampadkiya/the-dilemma-of-agricultural-universities-article-on-agrowon-rat16</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Bike ambulances, ICUs along wari routes: State health min</t>
+          <t>Kolhapur Corona Update : महाराष्ट्राच्या आरोग्याची चावी हाती असलेल्या दोन मंत्र्यांच्या कोल्हापुरात</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Will Elephant Mahadevi Return To Kolhapur From Jamnagars Vantara? Details Inside</t>
+          <t>Chandrahar Patil : चंद्रहार पाटील यांचे अखेर ठरले, ठाकरे सेनेला रामराम, सरकारसोबत जाणार; सांगलीच्या राजकारणात नवा ट्विस्ट</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/will-elephant-mahadevi-return-to-kolhapur-from-jamnagars-vantara-details-inside</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>संपादकीय: सरकार कोई हल निकाले, किसानों की कर्ज माफी का मुद्दा ज्वलंत</t>
+          <t>Shivsena Politics: कोल्हापूरच्या राजकीय आखाड्यात शिंदेंच्या शिवसेनेला 'अच्छे दिन',इच्छुकांच्या रांगा; पण 'ही' असणार टांगती तलवार</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/special-coverage/high-level-committee-will-be-formed-within-15-days-to-take-a-decision-on-loan-waiver-1256403.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-shiv-sena-gains-in-kolhapur-amid-rebellion-fears-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>NCP नेता हसन मुश्रीफ ने वाशिम के पालक मंत्री पद से दिया इस्तीफा, बोले- आने-जाने में होती हैं दिक्कत</t>
+          <t>LMOTY 2025: हे चेहरे गाजवणार महाराष्ट्राचं पुढचं राजकारण; कोण ठरणार प्रॉमिसिंग राजकारणी?</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/washim/ncp-minister-hasan-mushrif-resigned-washim-guardian-minister-citing-travel-difficulties-1145083.html</t>
+          <t>https://www.lokmat.com/maharashtra/lokmat-maharashtrian-of-the-year-awards-2025-here-are-the-nominations-for-promising-politician-category-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Maharashtra’s roadmap discussed at NDTV Marathi Manch</t>
+          <t>Kolhapur : कोल्हापुरात एकनाथ शिंदेंची 'जादू', एकाच वेळी काँग्रेस-भाजप आणि ताराराणी</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://bestmediainfo.com/mediainfo/mediainfo-marketing/maharashtras-roadmap-discussed-at-ndtv-marathi-manch-9009029</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Maha govt launches organ donation fortnight, Minister Abitkar takes lead by filling form</t>
+          <t>Top Marathi News Today: अखेर कोकाटेंचं खातं बदललच;आता दिली 'या' खात्याची जबाबदारी</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://ianslive.in/maharashtra-govt-launches-organ-donation-fortnight--20250804092958</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Mumbai Reports 53 Active COVID-19 Cases; 2 Deaths Linked To Co-Morbidities</t>
+          <t>Kolhapur APMC election | सभापती निवडीत पालकमंत्र्यांची एंट्री</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-ministers-entry-in-kolhapur-agricultural-produce-market-committee-chairman-election-ap84</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Cases rise amid 1st GBS death; Central team reaches Pune</t>
+          <t>Gokul President Election : कोल्हापुरच्या राजकारणात मुश्रीफांची ताकद वाढली; जिल्हा बँक आणि गोकुळवर पितापुत्रांचं 'वर्चस्व', वाचा महिनाभरात काय काय घडलं?</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>State to set up Maharashtra Public Health Infrastructure Corporation</t>
+          <t>Kolhapur : महायुतीच्या ‘रडार’वर काँग्रेस; सत्तेसाठी लावणार कस</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-political-move-to-keep-congress-out-of-kolhapur-municipal-corporation-dc95</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Maharashtra to implement ‘No shortage, no wastage’ policy for blood management</t>
+          <t>Chandrahar Patil : उद्धव ठाकरेंना मोठा धक्का! डबल महाराष्ट्र केसरी चंद्रहार पाटील आज शिंदेंच्या शिवसेनेत प्रवेश करणार</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
+          <t>https://www.lokshahi.com/maharashtra/lokshahi-politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Medical health complex &amp; upgraded facilities inaugurated at govt hospitals in Kolhapur</t>
+          <t>Almatty Dam : कर्नाटक भाजपचे महाराष्ट्राविरोधात वाकडे पाऊल, अलमट्टी धरणाची उंची वाढवण्यासाठी केंद्रीय मंत्र्यांच्या गाठीभेटी, वाद चिघळणार?</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/almatti-dam-height-increase-karnataka-bjp-mps-maharashtra-flood-risk-dispute-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Maharashtra Gears Up for 68th National School Yoga Sports Championship Starting January 16</t>
+          <t>Almatti dam height : ‘आलमट्टी’वरून राजकीय वातावरण तापलं ; जलसंपदा मंत्री विखे पुन्हा घेणार सर्वपक्षीय बैठक!</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/news-3192/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/radhakrishna-vikhe-patil-to-hold-all-party-meeting-on-almatti-dam-height-water-dispute-maharashtra-karnataka-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad News: PCMC Honoured with State Health Awards</t>
+          <t>Devendra Fadnavis : 'माधुरी'चा प्रश्न मार्गी लागणार? मंत्रिमंडळाच्या बैठकीत मुख्यमंत्री देवेंद्र फडणवीस यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pcmc/pimpri-chinchwad-news-pcmc-honoured-with-state-health-awards/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Sanjeevani: Transforming Cancer Care Through Unity and Awareness</t>
+          <t>kolhapur | जिल्ह्यातील सहकारावर कागलचे वर्चस्व</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mushrif-establishes-dominance-over-key-cooperative-institutions-in-district-ap84</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Pune Observes World Malaria Day With Awareness Rally At Tadiwala Road</t>
+          <t>Maharashtra Guardian Ministers List : पालकमंत्र्यांची यादी जाहीर, बीड आणि पुण्याबाबत सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-observes-world-malaria-day-with-awareness-rally-at-tadiwala-road</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Deputy Chief Minister Ajit Pawar Inaugurates Special Health Screening Drive Under National Child Health Program In Pune</t>
+          <t>Shiv Sena : कोल्हापुरात शिवसेनेचं वादळ, एकनाथ शिंदेंचा बंटी पाटील आणि महाडिक दोन्ही गटांना धक्का</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
+          <t>Maharashtra Karnataka Border Dispute: सीमाप्रश्नी उच्चाधिकार समितीची पुनर्रचना</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
+          <t>https://agrowon.esakal.com/agro-special/reorganization-of-the-high-power-committee-on-border-issues-rat16</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Pune: Statewide Childrens Health Checkup Campaign Begins In Aundh Tomorrow</t>
+          <t>Maharashta Gurdian Ministers Full List : मुंबई ते गडचिरोली, बीड ते नागपूर, तुमच्या जिल्ह्याचा पालकमंत्री</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-statewide-childrens-health-checkup-campaign-begins-in-aundh-tomorrow</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Maharashtra School Education Minister Dadaji Bhuse Proposes Mobile App For Student Health Check-Ups Under RBSK</t>
+          <t>Mahayuti clash: महायुतीत पुन्हा धुसफूस, शिंदेंच्या मंत्र्यांच्या फाईल्स CMO मध्ये अडकल्या,</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-school-education-minister-dadaji-bhuse-proposes-mobile-app-for-student-health-check-ups-under-rbsk</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-shivsena-cabinet-ministers-get-angry-on-devendra-fadnavis-cmo-office-over-pa-and-osd-appointment-delay-1343532</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Pune: Ajit Pawar Inaugurates 43 ‘Aapla Davakhana’ Clinics, Lays Foundation for State Family Welfare Building</t>
+          <t>एकनाथ शिंदेंच्या वाढदिनी राज्यात उपमुख्यमंत्री वैद्यकीय मदत कक्षाची घोषणा</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-ajit-pawar-inaugurates-43-aapla-davakhana-clinics-lays-foundation-for-state-family-welfare-building/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Maharashtra: Solapur man suspected to have died of Guillain-Barre syndrome; cases rise to 110 in Pune</t>
+          <t>महादेवी हत्तीणीला परत आणण्यासाठी राज्य सरकार उचलणार मोठं पाऊल; मुख्यमंत्री देवेंद्र फडणवीसांनी सगळच सांगितलं</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
+          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Maharashtra Announces Free Cancer Vaccination for Girls Aged 0-14 Amid Rising Cases</t>
+          <t>युवाशक्ती दहीहंडीला कोल्हापुरकरांनी मोठया संख्येने उपस्थित रहावे : खा. धनंजय महाडिक -</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
+          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Over 14,000 women detected with cancer-like symptoms in Maharashtra</t>
+          <t>Nandani Math Mahadevi Elephant : नांदणी मठाची ‘माधुरी’ परत येणार? वनताराचे CEO काय म्हणाले?</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-over-14000-women-detected-with-cancer-like-symptoms-in-hingoli-2753909-2025-07-10</t>
+          <t>https://www.timemaharashtra.com/trending/nandani-math-mahadevi-elephant-will-nandani-maths-madhuri-return-what-did-vantaras-ceo-say/127830/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Maharashtra Faces Cancer Crisis: Over 14500 Women in Hingoli Show ‘Cancer-Like’ Symptoms During Govt Health Screening</t>
+          <t>India reports 2 more deaths from Guillain-Barre Syndrome, raising total to 3</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.thehealthsite.com/news/maharashtra-faces-cancer-crisis-over-14500-women-in-hingoli-show-cancer-like-symptoms-during-govt-health-screening-1239129/</t>
+          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ashadhi Wari 2025: Maharashtra Plans Safer, Greener Pilgrimage to Pandharpur</t>
+          <t>More that 12k children died in Maharashtra between Apr last year and Feb 2025: Minister</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Residents of 18 villages to observe bandh today to oppose merger into KMC limits</t>
+          <t>Maharashtra govt to set up vigilance cells to stop illegal uterus removals among cane cutters</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Another person dies in Maharashtra from Guillain-Barre syndrome: Death toll rises to 2, 16 new cases report...</t>
+          <t>State govt proposes to amend Bombay Nursing Home Act; health dept to hire legal firm</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Maharashtra health minister pushes reforms, seeks new policy and faster recruitment</t>
+          <t>Nurses’ strike leaves Sassoon wards deserted, administration struggles to find replacements</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>शक्ति पीठ महामार्ग का प्रस्ताव … मलाई खाने के लिए भाजपा और शिंदे गुट में टकराव! … रु.२०,००० करोड़ के बजट पर है नजर</t>
+          <t>ZTCC, health minister honours families of deceased donors</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>MoS Civil Aviation Shri Murlidhar Mohol inaugurates new ATC Tower cum Technical Block cum Fire Station at Kolhapur Airport</t>
+          <t>Kolhapur IT Park &amp; employment initiatives announced at district investment summit</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2128928</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>High-Tech ATC Tower Inaugurated at Kolhapur Airport</t>
+          <t>Kolhapur district planning body okays 67cr to revamp zilla parishad schools</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/high-tech-atc-tower-inaugurated-at-kolhapur-airport/73773</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Chief Justice Of India To Inaugurate Kolhapur Circuit Bench Of Bombay High Court</t>
+          <t>CA from Dhayari, 41, who died in Solapur, first GBS casualty; patient count in Pune touches 111</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/events/justice-bhushan-ramkrishna-gavai-kolhapur-circuit-bench-bombay-high-court-inaugration-events-300775</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Shahu Maharaj’s 151st birth anniversary celebrated in Kolhapur</t>
+          <t>Tender scam hits Akola women’s hospital, dist civil surgeon, two other top officials suspended</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>राज्याच्या प्रगतीत कोल्हापूर जिल्हा अग्रभागी राहण्यासाठी सर्वजण सज्ज होऊया -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Patient records at 2,100 centres to be digitised</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164322/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Kolhapur Political News : काँग्रेसला मोठं भगदाड, 35 जणांची यादी तयार, मुंबईत होणार पक्षप्रवेश</t>
+          <t>Maharashtra health department cancels deputation of Nashik civic body’s medical superintendent</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-elections-congress-35-leaders-will-join-shiv-sena-mumbai-entry-rm82-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापूर चित्रनगरीमधील चित्रीकरण स्थळांचं लोकार्पण व भूमिपूजन कार्यक्रम संपन्न</t>
+          <t>Bike ambulances, ICUs along wari routes: State health min</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/kolhapur-dedication-and-foundation-stone-laying-ceremony-of-filming-locations-in-kolhapur-chitranagari-concluded-914427.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री रोजगार निर्मिती कार्यक्रम : कोल्हापूर जिल्हा राज्यात अग्रस्थानी</t>
+          <t>Will Elephant Mahadevi Return To Kolhapur From Jamnagars Vantara? Details Inside</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170909/</t>
+          <t>https://www.freepressjournal.in/pune/will-elephant-mahadevi-return-to-kolhapur-from-jamnagars-vantara-details-inside</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : शिंदेंचा बंटी पाटील अन् महाडिकांना धक्का; शारंगधर देशमुखांसह कोल्हापुरातील बड्या नेत्यांचा शिवसेनेत प्रवेश</t>
+          <t>संपादकीय: सरकार कोई हल निकाले, किसानों की कर्ज माफी का मुद्दा ज्वलंत</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-congress-leaders-join-shivsena-kolhapur-shock-satej-patil-and-dhananjay-mahadik-as11-rg93</t>
+          <t>https://navbharatlive.com/special-coverage/high-level-committee-will-be-formed-within-15-days-to-take-a-decision-on-loan-waiver-1256403.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>कोल्हापूर चित्रनगरीत मंत्री अॅड. आशिष शेलार यांच्या उपस्थितीत विविध विकासकामांचे उद्घाटन व लोकार्पण</t>
+          <t>महाराष्ट्र में मेडिकल व्यवस्था हुई 'बीमार', 200 से अधिक नए स्वास्थ्य केंद्रों पर लटका ताला</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170610/</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-more-than-200-newly-built-health-centres-locked-1224919.html</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench Inauguration |कोल्हापूर सर्किट बेंचचा 17 ऑगस्टला शानदार शुभारंभ</t>
+          <t>NCP नेता हसन मुश्रीफ ने वाशिम के पालक मंत्री पद से दिया इस्तीफा, बोले- आने-जाने में होती हैं दिक्कत</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inauguration-17-august-chief-justice-gavai-arade-cm-grand-ceremony-5000-seating-sp96</t>
+          <t>https://navbharatlive.com/maharashtra/washim/ncp-minister-hasan-mushrif-resigned-washim-guardian-minister-citing-travel-difficulties-1145083.html</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ShivSena News : एकनाथ शिंदेंच्या 'मंगेशाची' आमदारकीसाठी मोर्चेबांधणी; चिवटेंना हवा 'गुरुजींचा' आशीर्वाद</t>
+          <t>Maharashtra’s roadmap discussed at NDTV Marathi Manch</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mangesh-chivate-mlc-election-pune-teachers-constituency-eknath-shinde-shiv-sena-hn97-rg93</t>
+          <t>https://bestmediainfo.com/mediainfo/mediainfo-marketing/maharashtras-roadmap-discussed-at-ndtv-marathi-manch-9009029</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>हद्दवाढीसाठी आज मुंबईत बैठक</t>
+          <t>Maha govt launches organ donation fortnight, Minister Abitkar takes lead by filling form</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/meeting-in-mumbai-today-for-boundary-extension</t>
+          <t>https://ianslive.in/maharashtra-govt-launches-organ-donation-fortnight--20250804092958</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>अंबाबाई, जोतिबा मंदिर विकासाच्या पहिल्या टप्प्याचे काम लवकरच सुरू</t>
+          <t>Cases rise amid 1st GBS death; Central team reaches Pune</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/ambabai-jyotiba-temple-development-phase-one-to-begin-soon-dc95</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>...तर शिंदे शिवसेनाही स्वबळावर स्थानिक स्वराज्यच्या मैदानात</t>
+          <t>Maharashtra to implement ‘No shortage, no wastage’ policy for blood management</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-municipal-corporation-election</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>हद्दवाढीसंदर्भात सोमवारी मुंबईत उपमुख्यमंत्री शिंदे यांच्याकडे बैठक</t>
+          <t>Medical health complex &amp; upgraded facilities inaugurated at govt hospitals in Kolhapur</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-shinde-to-hold-meeting-in-mumbai-on-monday-regarding-boundary-extension</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
+          <t>Maharashtra Gears Up for 68th National School Yoga Sports Championship Starting January 16</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/lokaraja-rajarshi-chhatrapati-shahu-jayanti-celebrations-today-ap84</t>
+          <t>https://impressivetimes.com/latest/news-3192/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Maharashtra: 10,000 Farmers to Hold State-Wide March In Mumbai On March 12 Against 'Shaktipeeth Highway'</t>
+          <t>Pimpri Chinchwad News: PCMC Honoured with State Health Awards</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
+          <t>https://punemirror.com/city/pcmc/pimpri-chinchwad-news-pcmc-honoured-with-state-health-awards/</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Ajit Pawar’s Directive Clears Path for IT Hub in Kolhapur</t>
+          <t>Sanjeevani: Transforming Cancer Care Through Unity and Awareness</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
+          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>बाजार समिती सभापतिपद अजित पवार गटाकडे</t>
+          <t>Pune Observes World Malaria Day With Awareness Rally At Tadiwala Road</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/market-committee-chairmanship-to-ajit-pawar-group-ap84</t>
+          <t>https://www.freepressjournal.in/pune/pune-observes-world-malaria-day-with-awareness-rally-at-tadiwala-road</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
+          <t>Deputy Chief Minister Ajit Pawar Inaugurates Special Health Screening Drive Under National Child Health Program In Pune</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=2105326</t>
+          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Elephantiasis eradication drug campaign launched in 3 Vid districts</t>
+          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
+          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>India Achieves Five Guinness World Records in Ayurveda</t>
+          <t>Pune: Statewide Childrens Health Checkup Campaign Begins In Aundh Tomorrow</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://observervoice.com/india-achieves-five-guinness-world-records-in-ayurveda-97959/</t>
+          <t>https://www.freepressjournal.in/pune/pune-statewide-childrens-health-checkup-campaign-begins-in-aundh-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>चौदा वर्षे वयापर्यंतच्या मुलींना कर्करोगप्रतिबंधक लस देण्याचा विचार; अजित पवार यांची माहिती</t>
+          <t>Maharashtra: Solapur man suspected to have died of Guillain-Barre syndrome; cases rise to 110 in Pune</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/consideration-of-anti-cancer-vaccine-for-girls-up-to-fourteen-years-of-age-information-given-by-ajit-pawar</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>सार्वजनिक आरोग्य पायाभूत सुविधा महामंडळ उभारणीसाठी कार्यवाही करावी- मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Maharashtra Announces Free Cancer Vaccination for Girls Aged 0-14 Amid Rising Cases</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160560/</t>
+          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ठाणे जिल्हा रुग्णालय एमएमआर मधील नागरिकांसाठी वरदान ठरणार – उपमुख्यमंत्री एकनाथ शिंदे</t>
+          <t>Over 14,000 women detected with cancer-like symptoms in Maharashtra</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173688/</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-over-14000-women-detected-with-cancer-like-symptoms-in-hingoli-2753909-2025-07-10</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>माहिती व जनसंपर्क महासंचालनालय, महाराष्ट्र शासन | Page 523</t>
+          <t>Maharashtra Faces Cancer Crisis: Over 14500 Women in Hingoli Show ‘Cancer-Like’ Symptoms During Govt Health Screening</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/523/?m=0</t>
+          <t>https://www.thehealthsite.com/news/maharashtra-faces-cancer-crisis-over-14500-women-in-hingoli-show-cancer-like-symptoms-during-govt-health-screening-1239129/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Government fully supports implementation of Jyotiba temple development plan: Fadnavis</t>
+          <t>Ashadhi Wari 2025: Maharashtra Plans Safer, Greener Pilgrimage to Pandharpur</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Maharashtra approves Rs 20,787 crores for Nagpur-Goa Shaktipeeth Expressway</t>
+          <t>Residents of 18 villages to observe bandh today to oppose merger into KMC limits</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-nagpur-goa-shaktipeeth-expressway-land-acquisition-pilgrimage-tourism-2745741-2025-06-25</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Shiv Sena names 17 district liaison mins, escalates power battle in Mahayuti</t>
+          <t>Another person dies in Maharashtra from Guillain-Barre syndrome: Death toll rises to 2, 16 new cases report...</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
+          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>High-powered committee on Maharashtra-Karnataka boundary issue reconstituted</t>
+          <t>Maharashtra School Education Minister Dadaji Bhuse Proposes Mobile App For Student Health Check-Ups Under RBSK</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-school-education-minister-dadaji-bhuse-proposes-mobile-app-for-student-health-check-ups-under-rbsk</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>‘Jt guardian post introduced to include more ministers’</t>
+          <t>Maharashtra health minister pushes reforms, seeks new policy and faster recruitment</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
+          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>MP Shrikant Shinde refutes Sanjay Raut’s ambulance scam allegations</t>
+          <t>शक्ति पीठ महामार्ग का प्रस्ताव … मलाई खाने के लिए भाजपा और शिंदे गुट में टकराव! … रु.२०,००० करोड़ के बजट पर है नजर</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
+          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Discord in Maharashtra govt over fund-shift to Ladki Bahin Yojana</t>
+          <t>MoS Civil Aviation Shri Murlidhar Mohol inaugurates new ATC Tower cum Technical Block cum Fire Station at Kolhapur Airport</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2128928</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Fadnavis first Maha CM to become guardian minister</t>
+          <t>Chief Justice Of India To Inaugurate Kolhapur Circuit Bench Of Bombay High Court</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
+          <t>https://www.livelaw.in/events/justice-bhushan-ramkrishna-gavai-kolhapur-circuit-bench-bombay-high-court-inaugration-events-300775</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Eknath Shinde's grand welcome : उपमुख्यमंत्री शिंदेंचं कोल्हापुरात ग्रँड वेलकम; आबिटकरांनी जाण ठेवत, स्वागतात सोडली नाही कुठलीच कसर!</t>
+          <t>Kolhapur celebrates I-Day, Janmashtami &amp; Dahi Handi</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prakash-abitkar-grand-welcome-eknath-shinde-kolhapur-msr87-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>MP राऊतांविषयी सवाल, MP Shrikant Shinde यांनी स्पष्टच केलं, कोण Sanjay Raut?</t>
+          <t>Shahu Maharaj’s 151st birth anniversary celebrated in Kolhapur</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Shivsena Politics: महाडिक, मुश्रीफ अन् सतेज पाटलांच्या बालेकिल्ल्यात शिंदे मोठा धमाका करणार; एक दोन नव्हे,तर 30 मात्तबर नेते ...</t>
+          <t>Kolhapur : कोल्हापूर चित्रनगरीमधील चित्रीकरण स्थळांचं लोकार्पण व भूमिपूजन कार्यक्रम संपन्न</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-big-move-in-kolhapur-stronghold-of-dhananjay-mahadik-hasan-mushrif-satej-patil-30-leaders-to-join-dk88-rg93</t>
+          <t>https://www.navarashtra.com/videos/kolhapur-dedication-and-foundation-stone-laying-ceremony-of-filming-locations-in-kolhapur-chitranagari-concluded-914427.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Kolhapur Ashokrao Mane : चर्चेचा विषय! आमदार अशोकराव माने नेमके कुणाचे? शिवसेना पक्ष कार्यालय उद्‌घाटनाला उपस्थित; राजकारण्यांना पडला प्रश्न</t>
+          <t>मुख्यमंत्री रोजगार निर्मिती कार्यक्रम : कोल्हापूर जिल्हा राज्यात अग्रस्थानी</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/mla-ashokrao-mane-presence-at-a-shiv-sena-office-inauguration-has-stirred-political-debate-in-kolhapur-srs92</t>
+          <t>https://mahasamvad.in/170909/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>मुश्रीफांनी सोडलं, अजित पवारांनी दत्ता मामांना घेरलं; कसा सुटला अखेर वाशिमच्या पालकमंत्रीपदाचा तिढा!</t>
+          <t>Kolhapur Political News : काँग्रेसला मोठं भगदाड, 35 जणांची यादी तयार, मुंबईत होणार पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/datta-mama-bharne-appointed-as-guardian-minister-of-washim-district-ajit-pawar-hasan-mushrif-023877.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-elections-congress-35-leaders-will-join-shiv-sena-mumbai-entry-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Maharashtra Health Department to set up committee for effective leprosy eradication</t>
+          <t>कोल्हापूर चित्रनगरीत मंत्री अॅड. आशिष शेलार यांच्या उपस्थितीत विविध विकासकामांचे उद्घाटन व लोकार्पण</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-health-department-to-set-up-committee-for-effective-leprosy-eradication/article69815684.ece</t>
+          <t>https://mahasamvad.in/170610/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>111 Diagnosed With Guillain-Barre Syndrome In Maharashtra: Health Minister</t>
+          <t>Kolhapur Politics : शिंदेंचा बंटी पाटील अन् महाडिकांना धक्का; शारंगधर देशमुखांसह कोल्हापुरातील बड्या नेत्यांचा शिवसेनेत प्रवेश</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-congress-leaders-join-shivsena-kolhapur-shock-satej-patil-and-dhananjay-mahadik-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Health minister JP Nadda promises steady IVIG supply for Guillain-Barre Syndrome (GBS), say officials</t>
+          <t>Kolhapur Circuit Bench Inauguration |कोल्हापूर सर्किट बेंचचा 17 ऑगस्टला शानदार शुभारंभ</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inauguration-17-august-chief-justice-gavai-arade-cm-grand-ceremony-5000-seating-sp96</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Pune: 76 Private Hospitals Issued Notices for Regulatory Violations</t>
+          <t>हद्दवाढीसाठी आज मुंबईत बैठक</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/pune-76-private-hospitals-issued-notices-for-regulatory-violations</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/meeting-in-mumbai-today-for-boundary-extension</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Guillain-Barré cases in Pune cross 100, health ministry sends expert team</t>
+          <t>ShivSena News : एकनाथ शिंदेंच्या 'मंगेशाची' आमदारकीसाठी मोर्चेबांधणी; चिवटेंना हवा 'गुरुजींचा' आशीर्वाद</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.downtoearth.org.in/health/guillain-barr%C3%A9-cases-in-pune-cross-100-health-ministry-sends-expert-team-to-pune</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mangesh-chivate-mlc-election-pune-teachers-constituency-eknath-shinde-shiv-sena-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>State plans Maharashtra Institute of Virology, along the lines of NIV</t>
+          <t>अंबाबाई, जोतिबा मंदिर विकासाच्या पहिल्या टप्प्याचे काम लवकरच सुरू</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/ambabai-jyotiba-temple-development-phase-one-to-begin-soon-dc95</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
+          <t>...तर शिंदे शिवसेनाही स्वबळावर स्थानिक स्वराज्यच्या मैदानात</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-municipal-corporation-election</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Tally of nerve disorder GBS rises to 180 in Pune; Mumbai records first case</t>
+          <t>हद्दवाढीसंदर्भात सोमवारी मुंबईत उपमुख्यमंत्री शिंदे यांच्याकडे बैठक</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-shinde-to-hold-meeting-in-mumbai-on-monday-regarding-boundary-extension</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Nurses’ strike stalls health services at state-run hosps</t>
+          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/lokaraja-rajarshi-chhatrapati-shahu-jayanti-celebrations-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Wildlife Protest Kolhapur: Thousands March to Demand Elephant Mahadevi's Return from Vantara</t>
+          <t>हद्दवाढीचा प्रस्ताव महापालिकेकडून सरकारकडे सादर ! कोल्हापूरसाठी लवकरच तीन आनंदाच्या बातम्या !!</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
+          <t>https://maharashtranews1.com/The-proposal-for-the-extension-has-been-sent-from-the-municipality-to-the-government--Three-good-news-coming-soon-for-Kolhapur--</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
+          <t>Maharashtra: 10,000 Farmers to Hold State-Wide March In Mumbai On March 12 Against 'Shaktipeeth Highway'</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Accident victims to receive ₹1L cashless treatment, says health minister | Mumbai news</t>
+          <t>Ajit Pawar’s Directive Clears Path for IT Hub in Kolhapur</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
+          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Nagpur Doctors Urge Govt to Simplify Hospital Renewal Process, Reduce Paperwork</t>
+          <t>बाजार समिती सभापतिपद अजित पवार गटाकडे</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/market-committee-chairmanship-to-ajit-pawar-group-ap84</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
+          <t>Elephantiasis eradication drug campaign launched in 3 Vid districts</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Maha govt signs two MoUs with PHFI, IMMAST for quality and capacity building in health sector</t>
+          <t>India Achieves Five Guinness World Records in Ayurveda</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
+          <t>https://observervoice.com/india-achieves-five-guinness-world-records-in-ayurveda-97959/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>After 13-yr delay, govt says will open Nagpur District Hospital in 3 months</t>
+          <t>चौदा वर्षे वयापर्यंतच्या मुलींना कर्करोगप्रतिबंधक लस देण्याचा विचार; अजित पवार यांची माहिती</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/consideration-of-anti-cancer-vaccine-for-girls-up-to-fourteen-years-of-age-information-given-by-ajit-pawar</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Sewage from hotels, poultry farms near Khadakwasla under scanner: Health minister</t>
+          <t>सार्वजनिक आरोग्य पायाभूत सुविधा महामंडळ उभारणीसाठी कार्यवाही करावी- मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
+          <t>https://mahasamvad.in/160560/</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Maharashtra govt eyeing to make HPV vaccine available for girls: Ajit Pawar</t>
+          <t>प्रत्येक बालकाला सशक्त आणि निरोगी जीवनाची हमी देण्याचे काम करुया – उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
+          <t>https://mahasamvad.in/157898/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Maha to amend Nursing Homes Registration rules</t>
+          <t>ठाणे जिल्हा रुग्णालय एमएमआर मधील नागरिकांसाठी वरदान ठरणार – उपमुख्यमंत्री एकनाथ शिंदे</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
+          <t>https://mahasamvad.in/173688/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Aarogya Mitras in Maharashtra call off indefinite strike</t>
+          <t>Government fully supports implementation of Jyotiba temple development plan: Fadnavis</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Pune reports first death in GBS outbreak as cases surge</t>
+          <t>Maharashtra approves Rs 20,787 crores for Nagpur-Goa Shaktipeeth Expressway</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/clinical/covid-corner/gbs-claims-first-victim-in-pune-amid-rising-cases-central-team-dispatched-virus-outbreak-gbsvirus</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-nagpur-goa-shaktipeeth-expressway-land-acquisition-pilgrimage-tourism-2745741-2025-06-25</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Maharashtra Government Plans To Introduce Extensive Health Policy For Medical Tourism</t>
+          <t>Shiv Sena names 17 district liaison mins, escalates power battle in Mahayuti</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-plans-to-introduce-extensive-health-policy-for-medical-tourism</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Crores Sanctioned, No Compound Walls Built: Corruption Cloud Over Pune’s Yerawada Mental Hospital</t>
+          <t>High-powered committee on Maharashtra-Karnataka boundary issue reconstituted</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/crores-sanctioned-no-compound-walls-built-corruption-cloud-over-punes-yerawada-mental-hospital</t>
+          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Over 14,500 Women Detected With Cancer-Like Symptoms Post Screening In Maharashtra's Hingoli</t>
+          <t>‘Jt guardian post introduced to include more ministers’</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Maharashtra govt framing policy to stop water contamination for prevention of illnesses: Minister</t>
+          <t>MP Shrikant Shinde refutes Sanjay Raut’s ambulance scam allegations</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>More than 14.5k women detected with cancer-like symptoms post screening in Hingoli</t>
+          <t>Discord in Maharashtra govt over fund-shift to Ladki Bahin Yojana</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : लाडकी बहीण योजनेवरुन महायुतीत 'कसरत', आरोग्यमंत्र्यांचं मोठं वक्तव्य</t>
+          <t>Fadnavis first Maha CM to become guardian minister</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>मस्तवाल दीनानाथ मंगेशकर हॉस्पिटलमध्ये आमदाराच्या पीएच्या पत्नीचा जीव जाताच</t>
+          <t>MP राऊतांविषयी सवाल, MP Shrikant Shinde यांनी स्पष्टच केलं, कोण Sanjay Raut?</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
+          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : सरकारी दवाख्यान्यात बोगस औषधांचा पुरवठा? आरोग्य मंत्री प्रकाश आबिटकरांचीही कबुली</t>
+          <t>Shivsena Politics: महाडिक, मुश्रीफ अन् सतेज पाटलांच्या बालेकिल्ल्यात शिंदे मोठा धमाका करणार; एक दोन नव्हे,तर 30 मात्तबर नेते ...</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-updates-17-july-2025-assembly-monsoon-session-mahayuti-vs-mahavikas-aghadi-raj-thackeray-uddhav-thackeray-alliance-sambhaji-brigade-pravin-gaikwad-ncp-jayant-patil-shashikant-shinde-rohit-pawar-sharad-pwar-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-big-move-in-kolhapur-stronghold-of-dhananjay-mahadik-hasan-mushrif-satej-patil-30-leaders-to-join-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Jyotiba Chaitra Yatra : जोतिबा डोंगरावर दुपारी बारालाच निघणार सासनकाठी मिरवणूक; मंदिर 79 तास राहणार खुले</t>
+          <t>Kolhapur Ashokrao Mane : चर्चेचा विषय! आमदार अशोकराव माने नेमके कुणाचे? शिवसेना पक्ष कार्यालय उद्‌घाटनाला उपस्थित; राजकारण्यांना पडला प्रश्न</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/jyotiba-chaitra-yatra-sasan-kathi-miravnuk-minister-prakash-abitkar-jyotiba-dongar-kolhapur-bam92</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/mla-ashokrao-mane-presence-at-a-shiv-sena-office-inauguration-has-stirred-political-debate-in-kolhapur-srs92</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE 9 January 2025 : राज्यपाल नियुक्त 12 आमदारांबाबतची याचिका फेटाळली</t>
+          <t>मुश्रीफांनी सोडलं, अजित पवारांनी दत्ता मामांना घेरलं; कसा सुटला अखेर वाशिमच्या पालकमंत्रीपदाचा तिढा!</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/datta-mama-bharne-appointed-as-guardian-minister-of-washim-district-ajit-pawar-hasan-mushrif-023877.html</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Top Marathi News Today: अखेर कोकाटेंचं खातं बदललच;आता दिली 'या' खात्याची जबाबदारी</t>
+          <t>Maharashtra Health Department to set up committee for effective leprosy eradication</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-health-department-to-set-up-committee-for-effective-leprosy-eradication/article69815684.ece</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>111 Diagnosed With Guillain-Barre Syndrome In Maharashtra: Health Minister</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
+          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>Health minister JP Nadda promises steady IVIG supply for Guillain-Barre Syndrome (GBS), say officials</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Mumbai: देवेंद्र फडणवीसांचा मोठा निर्णय, आता घरबसल्या करता येणार दस्त नोंदणी वन</t>
+          <t>Pune: 76 Private Hospitals Issued Notices for Regulatory Violations</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
+          <t>https://www.thebridgechronicle.com/news/pune-76-private-hospitals-issued-notices-for-regulatory-violations</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Kolhapur News : कोल्हापुरात ढगफुटीसदृश्य पाऊस, ओढे-नाले तुडुंब, अनेक घरात पाणी शिरलं, जनजीवन विस्कळीत, शेतीचंही नुकसान</t>
+          <t>State to bring all diagnostic labs under health dept’s purview</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-heavy-rain-disrupts-daily-life-significant-damage-to-agriculture/articleshow/121814826.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Pahalgam Terror Attack: ...तर आमचीही नावं मृतांच्या यादीत असती! महाराष्ट्रातील २८ जण नाट्यमयरित्या थोडक्यात वाचले</t>
+          <t>Guillain-Barré cases in Pune cross 100, health ministry sends expert team</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/bargain-and-delay-in-getting-horses-save-28-tourist-from-walking-into-pahalgam-terror-site/articleshow/120580319.cms</t>
+          <t>https://www.downtoearth.org.in/health/guillain-barr%C3%A9-cases-in-pune-cross-100-health-ministry-sends-expert-team-to-pune</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>दीनानाथ मंगेशकर रुग्णालयावर कारवाई कधी? आरोग्य मंत्री प्रकाश आबिटकर यांनी दिले उत्तर</t>
+          <t>State plans Maharashtra Institute of Virology, along the lines of NIV</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-said-about-the-action-taken-by-dinanath-hospital-1387152.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>आता चिंता जलजन्य आजारांची; औषधांचा पुरेसा साठा राज्यात उपलब्ध करण्याचे आरोग्य मंत्री आबिटकर यांचे आदेश</t>
+          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/waterborne-diseases-health-minister-abitkar-orders-medicine-stock</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>केंद्रीय आरोग्य सेवा योजनेच्या दरांमध्ये सुधारणा करणार – केंद्रीय मंत्री मनसुख मांडविया</t>
+          <t>Tally of nerve disorder GBS rises to 180 in Pune; Mumbai records first case</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172749/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>३ ते १५ ऑगस्ट २०२५ या कालावधीत अवयवदान पंधरवडा साजरा होणार – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>Nurses’ strike stalls health services at state-run hosps</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173717/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>विधानपरिषद प्रश्नोत्तरे</t>
+          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172235/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant: कोल्हापुर की 'महादेवी' हथिनी को वनतारा से वापस लाने की मांग तेज, लोगों ने किया मौन मार्च</t>
+          <t>Accident victims to receive ₹1L cashless treatment, says health minister | Mumbai news</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>पुणे से देश की आर्थिक राजधानी पहुंचा गिलियन बैरे सिंड्रोम, मुंबई में जीबीएस का पहला केस</t>
+          <t>Wildlife Protest Kolhapur: Thousands March to Demand Elephant Mahadevi's Return from Vantara</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>‘वैद्यकीय अधिकाऱ्यांची रिक्त पदे तातडीने भरा’; आरोग्यमंत्री प्रकाश आबिटकर यांचे आदेश</t>
+          <t>Nagpur Doctors Urge Govt to Simplify Hospital Renewal Process, Reduce Paperwork</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/fill-the-vacant-posts-of-medical-officers-immediately-says-health-minister-prakash-abitkar-a-a992/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
+          <t>Maha govt signs two MoUs with PHFI, IMMAST for quality and capacity building in health sector</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
+          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Raj-Uddhav Thackeray Vijayi Rally : दोन भाऊ एकत्र आल्याने सुप्रिया सुळेंचा आनंद गगनात मावेना, मुश्रीफ बोलताच आबिटकरांनाही हसू आवरेना...</t>
+          <t>After 13-yr delay, govt says will open Nagpur District Hospital in 3 months</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/raj-uddhav-thackeray-brothers-vijayi-rally-supriya-sule-criticized-by-hasan-mushrif-and-prakash-abitkar-as11-rg93</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : ठाकरे बंधुंना फडणवीस यांचा टोला, बीड लैंगिक छळाप्रकरणात मोठी अपडेटसह वाचा महत्वाच्या घडामोडी</t>
+          <t>Sewage from hotels, poultry farms near Khadakwasla under scanner: Health minister</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-30-june-2025-live-updates-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-uddhav-thackeray-devendra-fadnavis-shivsena-ubt-kolhapur-vidarbha-as11</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
+          <t>Maharashtra govt eyeing to make HPV vaccine available for girls: Ajit Pawar</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
+          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>येत्या काळात आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरु करणार - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Maha to amend Nursing Homes Registration rules</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165634/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>आरोग्य क्षेत्रातील दर्जा व क्षमता वृद्धीसाठी पीएचएफआय, आयएमएमएएसटी यांच्यासोबत महाराष्ट्र शासनाचा सामंजस्य करार</t>
+          <t>Aarogya Mitras in Maharashtra call off indefinite strike</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173797/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>अवयवदान इच्छा नोंदवणे ही एक जबाबदारी बनायला हवी - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री तथा पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Maharashtra Government Plans To Introduce Extensive Health Policy For Medical Tourism</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175714/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-plans-to-introduce-extensive-health-policy-for-medical-tourism</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>सर्वांगीण निरोगी महाराष्ट्र घडविण्यासाठी राज्य शासन कटिबद्ध- उपमुख्यमंत्री अजित पवार</t>
+          <t>Crores Sanctioned, No Compound Walls Built: Corruption Cloud Over Pune’s Yerawada Mental Hospital</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163359/</t>
+          <t>https://www.freepressjournal.in/pune/crores-sanctioned-no-compound-walls-built-corruption-cloud-over-punes-yerawada-mental-hospital</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>‘रुग्ण सेवा हीच ईश्वर सेवा; जनसामान्यांची सेवा हाच धर्म’ – उपमुख्यमंत्री एकनाथ शिंदे</t>
+          <t>Over 14,500 Women Detected With Cancer-Like Symptoms Post Screening In Maharashtra's Hingoli</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155268/</t>
+          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>राज्याच्या इतिहासात पहिल्यांदाच 'आरोग्य विषयक धोरण' : मंत्री प्रकाश आबिटकर -</t>
+          <t>Maharashtra govt framing policy to stop water contamination for prevention of illnesses: Minister</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Rain causes road closures, travel delays in Satara and Kolhapur districts</t>
+          <t>Maharashtra Child Deaths: Over 12,000 Children Died Between April 2024 and Feb 2025</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Kolhapur civic body yet to acquire Jayprabha Studio</t>
+          <t>Maharashtra Live Updates : सरकारी दवाख्यान्यात बोगस औषधांचा पुरवठा? आरोग्य मंत्री प्रकाश आबिटकरांचीही कबुली</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-updates-17-july-2025-assembly-monsoon-session-mahayuti-vs-mahavikas-aghadi-raj-thackeray-uddhav-thackeray-alliance-sambhaji-brigade-pravin-gaikwad-ncp-jayant-patil-shashikant-shinde-rohit-pawar-sharad-pwar-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Double Maharashtra Kesari Chandrahar Patil Joins Shinde's Shiv Sena</t>
+          <t>Jyotiba Chaitra Yatra : जोतिबा डोंगरावर दुपारी बारालाच निघणार सासनकाठी मिरवणूक; मंदिर 79 तास राहणार खुले</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/jyotiba-chaitra-yatra-sasan-kathi-miravnuk-minister-prakash-abitkar-jyotiba-dongar-kolhapur-bam92</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Maharashtra's Rs 123 crore mortuary van project stuck, 132 new vehicles unused</t>
+          <t>आता चिंता जलजन्य आजारांची; औषधांचा पुरेसा साठा राज्यात उपलब्ध करण्याचे आरोग्य मंत्री आबिटकर यांचे आदेश</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/waterborne-diseases-health-minister-abitkar-orders-medicine-stock</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Senior NCP Minister Hasan Mushrif Steps Down As Washims Guardian Minister</t>
+          <t>केंद्रीय आरोग्य सेवा योजनेच्या दरांमध्ये सुधारणा करणार – केंद्रीय मंत्री मनसुख मांडविया</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-senior-ncp-minister-hasan-mushrif-steps-down-as-washims-guardian-minister</t>
+          <t>https://mahasamvad.in/172749/</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Gokul Dudh Sangh : ‘गोकुळ’मध्ये पुन्हा अरुणोदय की नव्या रक्ताला संधी; नव्या अध्यक्ष निवडीसाठी घडामोडींना वेग, पाटील-मुश्रीफांचा पुढील डाव काय?</t>
+          <t>३ ते १५ ऑगस्ट २०२५ या कालावधीत अवयवदान पंधरवडा साजरा होणार – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-arun-dengle-get-president-of-gokul-dudh-sangh-or-will-give-a-chance-to-new-blood-vd83-rg-93</t>
+          <t>https://mahasamvad.in/173717/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>kolhapur | जिल्ह्यातील सहकारावर कागलचे वर्चस्व</t>
+          <t>विधानपरिषद प्रश्नोत्तरे</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mushrif-establishes-dominance-over-key-cooperative-institutions-in-district-ap84</t>
+          <t>https://mahasamvad.in/172235/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : प्रकाश आबिटकरांना स्वकियांचेचं आव्हान, भाजप, अजित पवार गटाचा विरोध; जिल्हा नियोजन समितीवरून पडणार ठिणगी</t>
+          <t>Mahadevi Elephant: कोल्हापुर की 'महादेवी' हथिनी को वनतारा से वापस लाने की मांग तेज, लोगों ने किया मौन मार्च</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
+          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>पुण्याची हद्दवाढ 27 वेळा, कोल्हापूरची एकदाही नाही; शहर-ग्रामीण विकासासाठी हद्दवाढ करावीच लागेल</t>
+          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/inauguration-of-kolhapur-first-conference</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>कोल्हापुरातील अंबाबाई मंदिराचा १,४९६, जोतिबाचा २६० कोटींचा विकास आराखडा मंजूर</t>
+          <t>Raj-Uddhav Thackeray Vijayi Rally : दोन भाऊ एकत्र आल्याने सुप्रिया सुळेंचा आनंद गगनात मावेना, मुश्रीफ बोलताच आबिटकरांनाही हसू आवरेना...</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/development-plan-of-ambabai-temple-in-kolhapur-approved-at-rs-1496-crore-jyotiba-temple-at-rs-260-crore-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/raj-uddhav-thackeray-brothers-vijayi-rally-supriya-sule-criticized-by-hasan-mushrif-and-prakash-abitkar-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>विकासकामे दर्जात्मकच हवीत, तकलादू नकोत</t>
+          <t>Maharashtra Live Updates : ठाकरे बंधुंना फडणवीस यांचा टोला, बीड लैंगिक छळाप्रकरणात मोठी अपडेटसह वाचा महत्वाच्या घडामोडी</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-ajit-pawar-said-about-the-kolhapur-development-works</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-30-june-2025-live-updates-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-uddhav-thackeray-devendra-fadnavis-shivsena-ubt-kolhapur-vidarbha-as11</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>‘कोल्हापूर फर्स्ट’ मधून कोल्हापूरच्या शाश्वत आणि सर्वांगीण विकासासाठी विचारमंथन</t>
+          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>भुदरगड तालुक्यातील सात धबधबे म्हणजे निसर्गात लपलेला अद्भुत खजिना – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्य क्षेत्रातील दर्जा व क्षमता वृद्धीसाठी पीएचएफआय, आयएमएमएएसटी यांच्यासोबत महाराष्ट्र शासनाचा सामंजस्य करार</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172859/</t>
+          <t>https://mahasamvad.in/173797/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>इचलकरंजीसह परिसराच्या विकासासाठी सर्वतोपरी मदत करु – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>सर्वांगीण निरोगी महाराष्ट्र घडविण्यासाठी राज्य शासन कटिबद्ध- उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166821/</t>
+          <t>https://mahasamvad.in/163359/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>जिल्हा वार्षिक योजनेतील निधी गुणवत्ता पूर्ण कामांवरच खर्च करा-उपमुख्यमंत्री अजित पवार</t>
+          <t>‘रुग्ण सेवा हीच ईश्वर सेवा; जनसामान्यांची सेवा हाच धर्म’ – उपमुख्यमंत्री एकनाथ शिंदे</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155119/</t>
+          <t>https://mahasamvad.in/155268/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Madhuri Elephant Row: Fadnavis Backs Legal Move to Bring Elephant Back to Kolhapur</t>
+          <t>Rain causes road closures, travel delays in Satara and Kolhapur districts</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>"No one has to worry": Maharashtra Health Minister Prakash Abitkar on HMPV virus</t>
+          <t>Kolhapur civic body yet to acquire Jayprabha Studio</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Sassoon Hospital awarded for organ transplant efforts - Hindustan Times</t>
+          <t>Double Maharashtra Kesari Chandrahar Patil Joins Shinde's Shiv Sena</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
+          <t>https://english.lokshahi.com/politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>AIIMS Nagpur Bags 3 More Awards For Excellence In Organ Donation</t>
+          <t>Maharashtra's Rs 123 crore mortuary van project stuck, 132 new vehicles unused</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Preparations on in full swing after high court approved circuit bench in Kolhapur</t>
+          <t>Maharashtra Politics: Senior NCP Minister Hasan Mushrif Steps Down As Washims Guardian Minister</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-senior-ncp-minister-hasan-mushrif-steps-down-as-washims-guardian-minister</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Kolhapur residents hold silent march, seek return of elephant Mahadevi from Gujarat’s Vantara</t>
+          <t>Gokul Dudh Sangh : ‘गोकुळ’मध्ये पुन्हा अरुणोदय की नव्या रक्ताला संधी; नव्या अध्यक्ष निवडीसाठी घडामोडींना वेग, पाटील-मुश्रीफांचा पुढील डाव काय?</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-arun-dengle-get-president-of-gokul-dudh-sangh-or-will-give-a-chance-to-new-blood-vd83-rg-93</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Maharashtra Live News 8th August 2025 : गोपीचंद पडळकर शरणू हांडेंच्या भेटीला रुग्णालयात</t>
+          <t>Kolhapur Politics : प्रकाश आबिटकरांना स्वकियांचेचं आव्हान, भाजप, अजित पवार गटाचा विरोध; जिल्हा नियोजन समितीवरून पडणार ठिणगी</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>राज्यात अवयवदान पंधरवड्याला प्रारंभ</t>
+          <t>पुण्याची हद्दवाढ 27 वेळा, कोल्हापूरची एकदाही नाही; शहर-ग्रामीण विकासासाठी हद्दवाढ करावीच लागेल</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/organ-donation-fortnight-begins-in-the-state/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/inauguration-of-kolhapur-first-conference</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Maharashtra News: स्वातंत्र्य दिनाचा मुख्य शासकीय समारोह मुंबईत; पाहा कोण कुठे करणार ध्वजारोहण, संपूर्ण यादी Independence Day main government ceremony will be held in Mumbai; See who will hoist the flag where?</t>
+          <t>कोल्हापुरातील अंबाबाई मंदिराचा १,४९६, जोतिबाचा २६० कोटींचा विकास आराखडा मंजूर</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://www.lokmat.com/kolhapur/development-plan-of-ambabai-temple-in-kolhapur-approved-at-rs-1496-crore-jyotiba-temple-at-rs-260-crore-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : पंकजा मुंडेंकडे दाद मागणाऱ्या आंदोलकाच्या कमरेत पोलिस अधिकाऱ्यानेच घातली लाथ</t>
+          <t>विकासकामे दर्जात्मकच हवीत, तकलादू नकोत</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-15-august-2025-latest-marathi-political-news-eknath-shinde-aaditya-thackeray-bdd-chawl-redevelopment-best-election-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-ajit-pawar-devendra-fadnavis-uddhav-thackeray-india-alliance-mns-shivsena-kabutarkhana-dhananjay-munde-pm-modi-speech-live-79th-independence-day</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-ajit-pawar-said-about-the-kolhapur-development-works</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा झटपट आढावा</t>
+          <t>‘कोल्हापूर फर्स्ट’ मधून कोल्हापूरच्या शाश्वत आणि सर्वांगीण विकासासाठी विचारमंथन</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
+          <t>https://mahasamvad.in/158746/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Independence Day 2025 : स्वातंत्र्यदिनानिमित्त तुमच्या जिल्ह्यात कोण करणार ध्वजारोहण?; वाचा यादी</t>
+          <t>इचलकरंजीसह परिसराच्या विकासासाठी सर्वतोपरी मदत करु – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/independence-day-2025-who-will-hoist-the-flag-in-your-district-on-independence-day-read-the-list/</t>
+          <t>https://mahasamvad.in/166821/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench | कोल्हापूर सर्किट बेंचचे सरन्यायाधीशांच्या हस्ते दिमाखात उद्घाटन; कोल्हापुरात मोठा उत्साह</t>
+          <t>जिल्हा वार्षिक योजनेतील निधी गुणवत्ता पूर्ण कामांवरच खर्च करा-उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inaugurated-by-the-chief-justice-great-excitement-in-kolhapur-an01</t>
+          <t>https://mahasamvad.in/155119/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Maharashtra Mumbai Rain Live Updates, 19 August 2025 : मुंबईला पावसाचा तडाखा, चेंबूरमध्ये मोनोरेल थांबली; बचावकार्याचा थरार जारी</t>
+          <t>Madhuri Elephant Row: Fadnavis Backs Legal Move to Bring Elephant Back to Kolhapur</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/fadnavis-backs-efforts-to-bring-elephant-madhuri-back-to-kolhapur-from-vantara-3666063</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : ‘आपले सरकार’ सेवांतील विलंबावर आळा घालण्यासाठी अधिकाऱ्यांवर दररोज दंड लावण्याचे निर्देश</t>
+          <t>"No one has to worry": Maharashtra Health Minister Prakash Abitkar on HMPV virus</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
+          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>मिशन माधुरी हत्तीणीची घरवापसी! सतेज पाटलांच्या मोहिमेत 2 लाख 4 हजार 421 नागरिकांच्या</t>
+          <t>Sassoon Hospital awarded for organ transplant efforts - Hindustan Times</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mission-madhuri-elephant-2-lakh-4-thousand-421-people-signatures-in-satej-patil-campaign-public-outrage-will-reach-the-president-marathi-news-update-1374246</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Madhuri Elephant | 'माधुरी हत्तीणी'साठी राज्य सरकार आणि मठ सुप्रीम कोर्टात याचिका दाखल करणार</t>
+          <t>AIIMS Nagpur Bags 3 More Awards For Excellence In Organ Donation</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-government-and-nandani-math-will-file-petition-in-supreme-court-for-madhuri-elephant-db79</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>तिजोरीतील खडखडाटामुळे ५० वर्षानंतर सरकारनं घेतला महत्त्वाचा निर्णय, तळीरामांसह व्यावसायिकांसाठी नवीन संधी</t>
+          <t>Kolhapur residents hold silent march, seek return of elephant Mahadevi from Gujarat’s Vantara</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/new-wine-shop-license-in-maharashtra-ajit-pawar-lead-committee-to-issue-new-liquor-licenses-to-328-wine-shops-to-increase-revenue-in-state-treasury-maharashtra-news-mhs25071302746</t>
+          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>नांदणी मठाची ‘माधुरी’ परत येणार? वनताराच्या CEO ने कोल्हापूरकरांना दिली ग्वाही</t>
+          <t>Maharashtra Live News 8th August 2025 : गोपीचंद पडळकर शरणू हांडेंच्या भेटीला रुग्णालयात</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>हद्दवाढीचा प्रस्ताव महापालिकेकडून सरकारकडे सादर ! कोल्हापूरसाठी लवकरच तीन आनंदाच्या बातम्या !!</t>
+          <t>राज्यात अवयवदान पंधरवड्याला प्रारंभ</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-proposal-for-the-extension-has-been-sent-from-the-municipality-to-the-government--Three-good-news-coming-soon-for-Kolhapur--</t>
+          <t>https://www.newsonair.gov.in/mr/organ-donation-fortnight-begins-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>बेमुदत कामबंद आंदोलनास सुरुवात; NHM अंतर्गत १० हजारांहून अधिक अधिकारी-कर्मचारी रस्त्यावर</t>
+          <t>Maharashtra Live Updates : पंकजा मुंडेंकडे दाद मागणाऱ्या आंदोलकाच्या कमरेत पोलिस अधिकाऱ्यानेच घातली लाथ</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-15-august-2025-latest-marathi-political-news-eknath-shinde-aaditya-thackeray-bdd-chawl-redevelopment-best-election-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-ajit-pawar-devendra-fadnavis-uddhav-thackeray-india-alliance-mns-shivsena-kabutarkhana-dhananjay-munde-pm-modi-speech-live-79th-independence-day</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Madhuri Elephant | माधुरी हत्तीण परत येणार? कोल्हापुरकरांना मुख्यमंत्र्यांचा मोठा शब्द</t>
+          <t>Maharashtra News: स्वातंत्र्य दिनाचा मुख्य शासकीय समारोह मुंबईत; पाहा कोण कुठे करणार ध्वजारोहण, संपूर्ण यादी Independence Day main government ceremony will be held in Mumbai; See who will hoist the flag where?</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>युवाशक्ती दहीहंडीचा थरार २४ ऑगस्टला रंगणार, प्रथम क्रमांकाला ३ लाख रूपयांचे बक्षीस</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा झटपट आढावा</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-excitement-of-Youth-Power-Dahi-Handi-will-take-place-on-August-24--with-a-prize-of-3-lakh-rupees-for-the-first-place-</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench : न्यायाच्या कोल्हापूर पर्वाला सुरुवात; सरन्यायाधीशांच्‍या उपस्थितीत सर्किट बेंचचे होणार उद्घाटन</t>
+          <t>Independence Day 2025 : स्वातंत्र्यदिनानिमित्त तुमच्या जिल्ह्यात कोण करणार ध्वजारोहण?; वाचा यादी</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
+          <t>https://puneprimenews.com/pune/independence-day-2025-who-will-hoist-the-flag-in-your-district-on-independence-day-read-the-list/</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Hindustani Bhau : 'तुम्ही जेवता ना @# तर नाही खात ना?'; माधुरी हत्तीण वादात हिंदुस्थानी भाऊची उडी, Video व्हायरल</t>
+          <t>Kolhapur Circuit Bench | कोल्हापूर सर्किट बेंचचे सरन्यायाधीशांच्या हस्ते दिमाखात उद्घाटन; कोल्हापुरात मोठा उत्साह</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inaugurated-by-the-chief-justice-great-excitement-in-kolhapur-an01</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>न्यायाच्या कोल्हापूर पर्वाला उद्यापासून सुरुवात</t>
+          <t>Maharashtra Mumbai Rain Live Updates, 19 August 2025 : मुंबईला पावसाचा तडाखा, चेंबूरमध्ये मोनोरेल थांबली; बचावकार्याचा थरार जारी</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74101/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>रत्नागिरी : राष्ट्रीय आरोग्य अभियान (एनआरएचएम) कर्मचाऱ्यांचा उद्यापासून बेमुदत संप</t>
+          <t>Maharashtra Live Blog: माळेगाव सहकारी कारखाना निवडणुकीच्या मतमोजणीच्या प्रत्येक क्षणाचे वेगवान अपडेटस्, शरद पव</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74350/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-beed-santosh-deshmukh-case-maharashtra-politics-malegaon-sahakari-sakhar-karkhana-election-2025-1365817</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>कोल्हापूर सर्किट बेंच इमारतीचे दिमाखदार उद्घाटन</t>
+          <t>Nanded News : धक्कादायक! नांदेडच्या शासकीय ग्रामीण रुग्णालयात उंदरांचं साम्राज्य, चक्क</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74156/</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Indian city faces rising cases of GBS disease</t>
+          <t>Devendra Fadnavis : ‘आपले सरकार’ सेवांतील विलंबावर आळा घालण्यासाठी अधिकाऱ्यांवर दररोज दंड लावण्याचे निर्देश</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.dw.com/en/indian-city-faces-rising-cases-of-gbs-disease/a-71430960</t>
+          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Maharashtra records second suspected GBS death, cases rise to 127</t>
+          <t>Madhuri Elephant | 'माधुरी हत्तीणी'साठी राज्य सरकार आणि मठ सुप्रीम कोर्टात याचिका दाखल करणार</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://ddnews.gov.in/en/maharashtra-records-second-suspected-gbs-death-cases-rise-to-127/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-government-and-nandani-math-will-file-petition-in-supreme-court-for-madhuri-elephant-db79</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>NHM employees begin indefinite strike, healthcare services impacted</t>
+          <t>नांदणी मठाची ‘माधुरी’ परत येणार? वनताराच्या CEO ने कोल्हापूरकरांना दिली ग्वाही</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
+          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Of 1.4L+ docs in Maha, only 10k opt in for ‘KYD’ QR code scheme</t>
+          <t>बेमुदत कामबंद आंदोलनास सुरुवात; NHM अंतर्गत १० हजारांहून अधिक अधिकारी-कर्मचारी रस्त्यावर</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
+          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Daga hospital’s NICU ranked best in Maharashtra at state health awards</t>
+          <t>Madhuri Elephant | माधुरी हत्तीण परत येणार? कोल्हापुरकरांना मुख्यमंत्र्यांचा मोठा शब्द</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/daga-hospitals-nicu-ranked-best-in-maharashtra-at-state-health-awards/articleshow/120074378.cms</t>
+          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Thousands participate in silent march to seek Mahadevi's return from Vantara</t>
+          <t>युवाशक्ती दहीहंडीचा थरार २४ ऑगस्टला रंगणार, प्रथम क्रमांकाला ३ लाख रूपयांचे बक्षीस</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
+          <t>https://maharashtranews1.com/The-excitement-of-Youth-Power-Dahi-Handi-will-take-place-on-August-24--with-a-prize-of-3-lakh-rupees-for-the-first-place-</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Exclusive: राज्यात राष्ट्रीय बाल स्वास्थ्य कार्यक्रमाची ऐसीतैसी!</t>
+          <t>Kolhapur Circuit Bench : न्यायाच्या कोल्हापूर पर्वाला सुरुवात; सरन्यायाधीशांच्‍या उपस्थितीत सर्किट बेंचचे होणार उद्घाटन</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/scam-scanner/maharashtra-health-department-tender-scam</t>
+          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>गतवर्षी प्रमाणे यंदाही वारकरी दिंड्यांना सरकार अनुदान देणार : आचार्य तुषार भोसले</t>
+          <t>न्यायाच्या कोल्हापूर पर्वाला उद्यापासून सुरुवात</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
+          <t>https://ratnagirikhabardar.com/news/74101/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>माधुरी हत्तीण परत आणण्याबाबत राज्य शासनाने घेतला ‘हा’ मोठा निर्णय; वाचा सविस्तर…</t>
+          <t>रत्नागिरी : राष्ट्रीय आरोग्य अभियान (एनआरएचएम) कर्मचाऱ्यांचा उद्यापासून बेमुदत संप</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/the-state-government-took-this-big-decision-to-bring-back-madhuri-the-elephant-read-in-detail/</t>
+          <t>https://ratnagirikhabardar.com/news/74350/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>अवयवदान पंधरवड्यास सुरुवात; आजपासून राज्यात जनजागृतीपर विविध उपक्रम</t>
+          <t>Indian city faces rising cases of GBS disease</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174294/</t>
+          <t>https://www.dw.com/en/indian-city-faces-rising-cases-of-gbs-disease/a-71430960</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>न्यायाच्या कोल्हापूर पर्वाला १७ ऑगस्टपासून सुरुवात</t>
+          <t>NHM employees begin indefinite strike, healthcare services impacted</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175429/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीण परत नांदणीत येणार? राज्य सरकारचा सर्वोच्च न्यायालयात पुनरावलोकन याचिकेचा निर्णय</t>
+          <t>Of 1.4L+ docs in Maha, only 10k opt in for ‘KYD’ QR code scheme</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Delay in transfer of med head raises concerns over management of mental hospital</t>
+          <t>Thousands participate in silent march to seek Mahadevi's return from Vantara</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Maharashtra CM instructs Health Department to cover GBS treatment under State insurance scheme</t>
+          <t>Exclusive: राज्यात राष्ट्रीय बाल स्वास्थ्य कार्यक्रमाची ऐसीतैसी!</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/chief-minister-instructs-health-department-to-cover-gbs-treatment-under-mjpjay/article69151508.ece</t>
+          <t>https://www.tendernama.com/scam-scanner/maharashtra-health-department-tender-scam</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Pregnant woman denied hospital treatment in Pune, dies; probe launched</t>
+          <t>गतवर्षी प्रमाणे यंदाही वारकरी दिंड्यांना सरकार अनुदान देणार : आचार्य तुषार भोसले</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Narayana Health SRCC Children’s Hospital observes World Child Obesity Day 2025 in collaboration with Gen-XL Foundation</t>
+          <t>माधुरी हत्तीण परत आणण्याबाबत राज्य शासनाने घेतला ‘हा’ मोठा निर्णय; वाचा सविस्तर…</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
+          <t>https://puneprimenews.com/mumbai/the-state-government-took-this-big-decision-to-bring-back-madhuri-the-elephant-read-in-detail/</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Latest Marathi News Updates : देश-विदेशासह राज्यात दिवसभरात काय घडलं? वाचा एका क्लिकवर</t>
+          <t>न्यायाच्या कोल्हापूर पर्वाला १७ ऑगस्टपासून सुरुवात</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://mahasamvad.in/175429/</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 25 मार्च 2025 | मंगळवार</t>
+          <t>महादेवी हत्तीण परत नांदणीत येणार? राज्य सरकारचा सर्वोच्च न्यायालयात पुनरावलोकन याचिकेचा निर्णय</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-15-march-2025-eknath-shinde-ajit-pawar-maharashtra-politics-marathi-news-1351019</t>
+          <t>https://www.timemaharashtra.com/maharashtra/will-mahadevi-elephant-return-to-nandani-state-governments-decision-on-review-petition-in-supreme-court/128244/</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 12 मे 2025 | सोमवार</t>
+          <t>12k kid deaths in 11 months</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/12k-kid-deaths-in-11-months/articleshow/122305129.cms</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Breaking News Today : महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
+          <t>Safety of warkaris is of prime importance, and police are alert to prevent any untoward incident: Shinde</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>अधिवेशनात गाजला बीड आरोग्य विभागातील घोटाळा; जिल्हा शल्य चिकित्सकांचं निलंबन</t>
+          <t>Delay in transfer of med head raises concerns over management of mental hospital</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/delay-in-transfer-of-med-head-raises-concerns-over-management-of-mental-hospital-101742005148858.html</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>गुलाल खोबऱ्याची उधळण; जोतिबाच्या नावानं चांगभलंच्या गजरात चैत्र यात्रेला सुरुवात</t>
+          <t>Maharashtra CM instructs Health Department to cover GBS treatment under State insurance scheme</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/chief-minister-instructs-health-department-to-cover-gbs-treatment-under-mjpjay/article69151508.ece</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>पाच लाख भाविकांच्या उपस्थितीत दख्खनचा राजा जोतिबाची चैत्र यात्रा, डोंगरावर 'चांगभलं'चा गजर</t>
+          <t>Pregnant woman denied hospital treatment in Pune, dies; probe launched</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pregnant-woman-denied-hospital-treatment-in-pune-dies-probe-launched-101743794142506.html</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>राजर्षी छत्रपती शाहू महाराजांची जयंती उत्साहात साजरी; शरद पवारांसह विविध मान्यवरांनी केलं अभिवादन</t>
+          <t>Narayana Health SRCC Children’s Hospital observes World Child Obesity Day 2025 in collaboration with Gen-XL Foundation</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
+          <t>https://www.expresshealthcare.in/amp/news/narayana-health-srcc-childrens-hospital-observes-world-child-obesity-day-2025-in-collaboration-with-gen-xl-foundation/449213/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Maharashtra cancels registration of 258 Private Hospitals</t>
+          <t>Maharashtra Breaking News LIVE 9 January 2025 : राज्यपाल नियुक्त 12 आमदारांबाबतची याचिका फेटाळली</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/maharashtra-cancels-registration-of-258-private-hospitals-152138</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Maharashtra govt to provide free cancer vaccine for girls, takes precautions against bird flu</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>First Phase of ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic 5 Guinness World Records</t>
+          <t>Latest Marathi News Updates : देश-विदेशासह राज्यात दिवसभरात काय घडलं? वाचा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/first-phase-of-desh-ka-prakriti-parikshan-abhiyaan-concludes-with-historic-5-guinness-world-records/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>kolhapur News : अधिकार्‍यांनी नावीन्यतेसह गुणवत्तापूर्ण कामे करावीत</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-all-departments-in-zilla-parishad-ap84</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Dairy Farming: आदर्श गोठा पुरस्काराचा राज्यभरात आदर्श घ्यावा; पालकमंत्री आबिटकर</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 12 मे 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>कोल्हापूर : गावठाणाबाहेरील मिळकतींनाही मिळणार प्रॉपर्टी कार्ड</t>
+          <t>Breaking News Today : महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-property-cards-for-non-gaothan-properties-dc95</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>पत्रकारांच्या आरोग्याच्या प्रश्नावर लवकरच बैठक घेणार – मंत्री प्रकाश आबिटकर</t>
+          <t>Mumbai: देवेंद्र फडणवीसांचा मोठा निर्णय, आता घरबसल्या करता येणार दस्त नोंदणी वन</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170017/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>PMC felicitated for ABDM Excellence</t>
+          <t>अधिवेशनात गाजला बीड आरोग्य विभागातील घोटाळा; जिल्हा शल्य चिकित्सकांचं निलंबन</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
+          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Cashless Treatment of Up to Rs 1 Lakh Announced for Accident Victims in Maharashtra</t>
+          <t>गुलाल खोबऱ्याची उधळण; जोतिबाच्या नावानं चांगभलंच्या गजरात चैत्र यात्रेला सुरुवात</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
+          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>मोठी बातमी ! अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार, आरोग्य खात्याचा महत्वपूर्ण निर्णय</t>
+          <t>Kolhapur News: उद्योजकाच्या लेकाचा जीव गेला, १२ लाखांच्या बाईकचा चेंदामेंदा, ७० हजारांच्या हेल्मेटचा चुराडा</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-launches-cashless-accident-treatment-up-to-1-lakh-1387143.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-businessman-son-died-in-horrifying-accident-with-car-expensive-bike-and-helmet-broken-into-pieces/articleshow/120491249.cms</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>महात्मा फुले जनआरोग्य योजनेबाबत आरोग्यमंत्र्यांची मोठी घोषणा</t>
+          <t>पाच लाख भाविकांच्या उपस्थितीत दख्खनचा राजा जोतिबाची चैत्र यात्रा, डोंगरावर 'चांगभलं'चा गजर - JOTIBA CHAITRA YATRA 2025</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-big-announcement-regarding-mahatma-phule-jan-arogya-yojana-pune-print-news-amy-95-5251004/</t>
+          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>महात्मा ज्योतिराव फुले जन आरोग्य योजनेचा लाभ जास्तीत जास्त लाभार्थ्यांपर्यंत पोहोचवा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>राजर्षी छत्रपती शाहू महाराजांची जयंती उत्साहात साजरी; शरद पवारांसह विविध मान्यवरांनी केलं अभिवादन</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151398/</t>
+          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>शक्तिपीठ महामार्ग कोल्हापूर जिल्हा वगळून गोव्याला नेणार कसा? शेतकऱ्यांचा सवाल; जिल्हाधिकारी कार्यालयासमोर धरणे आंदोलन</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154371/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-farmers-question-mahayuti-government-over-nagpur-goa-shaktipeeth-highway-bam92</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis orders special arrangements for treating GBS patients</t>
+          <t>Maharashtra cancels registration of 258 Private Hospitals</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
+          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/maharashtra-cancels-registration-of-258-private-hospitals-152138</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Maharashtra Plans Bigger Organ Transplant Budget Under MJPJAY; Wadia Hospital Gets Pediatric Heart Transplant</t>
+          <t>Maharashtra govt to provide free cancer vaccine for girls, takes precautions against bird flu</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-plans-bigger-organ-transplant-budget-under-mjpjay-wadia-hospital-gets-pediatric-heart-transplant-license</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>महात्मा जोतिराव फुले जनआरोग्य योजना ठप्प</t>
+          <t>Dairy Farming: आदर्श गोठा पुरस्काराचा राज्यभरात आदर्श घ्यावा; पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mahatma-jyotirao-phule-janarogya-yojana-halted</t>
+          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>जागतिक आरोग्य दिनी विविध आरोग्य योजनांचा शुभारंभ</t>
+          <t>कोल्हापूर : गावठाणाबाहेरील मिळकतींनाही मिळणार प्रॉपर्टी कार्ड</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161521/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-property-cards-for-non-gaothan-properties-dc95</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>GBS Outbreak in Pune: Citizens Confront Central Health Team Over Alleged Inspection Failure</t>
+          <t>PMC felicitated for ABDM Excellence</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/gbs-outbreak-in-pune-citizens-confront-central-health-team-over-alleged-inspection-failure</t>
+          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Pune Pregnant Woman's Death: Preliminary Report Highlights Negligence by Deenanath Mangeshkar Hospital</t>
+          <t>Cashless Treatment of Up to Rs 1 Lakh Announced for Accident Victims in Maharashtra</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
+          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Pune: शहरात 76 खासगी रुग्णालयांना नोटीस</t>
+          <t>मोठी बातमी ! अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार, आरोग्य खात्याचा महत्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/notice-to-76-private-hospitals-in-the-city</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-launches-cashless-accident-treatment-up-to-1-lakh-1387143.html</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MLA Bhimrao Tapkir : सर्व पाणीपुरवठा स्त्रोतांचे नियमित क्लोरीनेशन करून त्यावर देखरेख ठेवा; जीबीएसबाबत उपाययोजनेचे दिले आदेश</t>
+          <t>महात्मा फुले जनआरोग्य योजनेबाबत आरोग्यमंत्र्यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/regular-chlorination-of-all-water-supply-sources-ordered-by-gbs-for-safety-mla-bhimrao-tapkir-khadakwasla-pjp78</t>
+          <t>https://www.loksatta.com/pune/health-minister-big-announcement-regarding-mahatma-phule-jan-arogya-yojana-pune-print-news-amy-95-5251004/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Pune hospital conferred 'Best BSD Award' and 'Best Organ Transplant Coordinator Award'</t>
+          <t>महात्मा जोतिराव फुले जनआरोग्य योजना ठप्प</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mahatma-jyotirao-phule-janarogya-yojana-halted</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Singapore tourism board partners with IndiGo to boost travel</t>
+          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+          <t>https://www.mahasamvad.in/154371/</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>अवयवदान सर्वश्रेष्ठ दान…</t>
+          <t>‘लाडकी बहीण’मुळे आरोग्याचा खेळखंडोबा</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174716/</t>
+          <t>https://dainikekmat.com/%E0%A4%B2%E0%A4%BE%E0%A4%A1%E0%A4%95%E0%A5%80-%E0%A4%AC%E0%A4%B9%E0%A5%80%E0%A4%A3%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8B%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%BE/96992/</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Organ Donation Awareness | मरावे परी देह अन् अवयवरुपी उरावे</t>
+          <t>Maharashtra CM Fadnavis orders special arrangements for treating GBS patients</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/organ-donation-dr-prashant-wadikar-eight-lives-saved-sp96</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>७,५२२ अवयवदात्यांची प्रतिज्ञा; २४५ रुग्णांना नवजीवन</t>
+          <t>Maharashtra Plans Bigger Organ Transplant Budget Under MJPJAY; Wadia Hospital Gets Pediatric Heart Transplant</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mission-jeevan-donation-campaign-7522-donors-filled-out-an-organ-donation-pledge-and-submitted-it-to-lokmat-a-a1001/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-plans-bigger-organ-transplant-budget-under-mjpjay-wadia-hospital-gets-pediatric-heart-transplant-license</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>विधानसभा इतर कामकाज</t>
+          <t>जागतिक आरोग्य दिनी विविध आरोग्य योजनांचा शुभारंभ</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172498/</t>
+          <t>https://mahasamvad.in/161521/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant Case: State Government Takes Proactive Role, Matter to Be Reconsidered in Supreme Court</t>
+          <t>GBS Outbreak in Pune: Citizens Confront Central Health Team Over Alleged Inspection Failure</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/top-stories/mahadevi-elephant-state-governments-proactive-role-for-mahadevi-madhuri-elephant-will-be-reconsidered-in-the-supreme-court</t>
+          <t>https://www.thebridgechronicle.com/news/gbs-outbreak-in-pune-citizens-confront-central-health-team-over-alleged-inspection-failure</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक; प्रस्ताव सादर करण्याचे मंत्री आबिटकर यांचे निर्देश</t>
+          <t>Pune Pregnant Woman's Death: Preliminary Report Highlights Negligence by Deenanath Mangeshkar Hospital</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/workers-insurance-scheme-healthcare-infrastructure-prakash-abhitkar</t>
+          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>वारी मार्गावर ९ लाखांहून अधिक वारकऱ्यांना आरोग्य सेवा</t>
+          <t>Pune: शहरात 76 खासगी रुग्णालयांना नोटीस</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171744/</t>
+          <t>https://pudhari.news/maharashtra/pune/notice-to-76-private-hospitals-in-the-city</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>सार्वजनिक आरोग्य विभागाच्या जास्तीत जास्त सेवा ऑनलाईन करा – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>MLA Bhimrao Tapkir : सर्व पाणीपुरवठा स्त्रोतांचे नियमित क्लोरीनेशन करून त्यावर देखरेख ठेवा; जीबीएसबाबत उपाययोजनेचे दिले आदेश</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171817/</t>
+          <t>https://www.esakal.com/pune/regular-chlorination-of-all-water-supply-sources-ordered-by-gbs-for-safety-mla-bhimrao-tapkir-khadakwasla-pjp78</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>इंडियन इन्स्टिट्युट ऑफ पब्लिक हेल्थ आयआयटी, आयआयएमच्या धर्तीवर - Indian Institute of Public Health (IIPH) on the basis of IIT and IIM</t>
+          <t>Organ Donation Awareness | मरावे परी देह अन् अवयवरुपी उरावे</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/organ-donation-dr-prashant-wadikar-eight-lives-saved-sp96</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Maharashtra to file review petition to bring back elephant Madhuri to Kolhapur</t>
+          <t>अवयवदान सर्वश्रेष्ठ दान…</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-to-file-review-petition-to-bring-back-elephant-madhuri-to-kolhapur-2766892-2025-08-06</t>
+          <t>https://mahasamvad.in/174716/</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Kolhapur residents hold 45-km silent march for elephant’s return | Mumbai news</t>
+          <t>७,५२२ अवयवदात्यांची प्रतिज्ञा; २४५ रुग्णांना नवजीवन</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
+          <t>https://www.lokmat.com/mumbai/mission-jeevan-donation-campaign-7522-donors-filled-out-an-organ-donation-pledge-and-submitted-it-to-lokmat-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Thousands Participate in a Silent March to Seek Mahadevi's Return from Vantara</t>
+          <t>राज्यात ३ ते १५ ऑगस्ट या कालावधीत अवयवदान पंधरवडा साजरा होणार</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
+          <t>https://ratnagirikhabardar.com/news/70580/</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Kolhapur Rises for Mahadevi: Thousands Join Silent March Demanding Elephant's Return From Vantara</t>
+          <t>विधानसभा इतर कामकाज</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
+          <t>https://mahasamvad.in/172498/</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Silent march in Kolhapur demands return of elephant Mahadevi from Vantara</t>
+          <t>Mahadevi Elephant Case: State Government Takes Proactive Role, Matter to Be Reconsidered in Supreme Court</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://www.dynamitenews.com/national/silent-march-in-kolhapur-demands-return-of-elephant-mahadevi-from-vantara</t>
+          <t>https://english.lokshahi.com/top-stories/mahadevi-elephant-state-governments-proactive-role-for-mahadevi-madhuri-elephant-will-be-reconsidered-in-the-supreme-court</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>“Madhuri Should Come Back To The Math”: Maharashtra To File Review Petition For Elephant’s Return, Says CM Devendra Fadnavis</t>
+          <t>More than 14.5k women detected with cancer-like symptoms post screening in Hingoli</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>‘स्मार्ट’ अंतर्गत नोंदणीकृत प्रकल्प कालबद्धरितीने पूर्ण करा – कृषी मंत्री ॲड. माणिकराव कोकाटे</t>
+          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक; प्रस्ताव सादर करण्याचे मंत्री आबिटकर यांचे निर्देश</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167140/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/workers-insurance-scheme-healthcare-infrastructure-prakash-abhitkar</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Blood Donation : 'ई-रक्तकोष पोर्टल' गरजूंना मिळवून देणार रक्त; अफवांवर विश्वास न ठेवता बिनधास्त करा रक्तदान, वाचा रक्तदानाचे फायदे !</t>
+          <t>वारी मार्गावर ९ लाखांहून अधिक वारकऱ्यांना आरोग्य सेवा</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
+          <t>https://mahasamvad.in/171744/</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Maharashtra rains: School wall collapses in Bhilar village</t>
+          <t>इंडियन इन्स्टिट्युट ऑफ पब्लिक हेल्थ आयआयटी, आयआयएमच्या धर्तीवर - Indian Institute of Public Health (IIPH) on the basis of IIT and IIM</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-rains-school-wall-collapses-in-bhilar-village/articleshow/123403288.cms</t>
+          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: सर्किट बेंचच्या उद्घाटनासाठी करवीरनगरी सज्ज</t>
+          <t>Maharashtra to file review petition to bring back elephant Madhuri to Kolhapur</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-to-file-review-petition-to-bring-back-elephant-madhuri-to-kolhapur-2766892-2025-08-06</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench | सर्किट बेंचचे आज उद्घाटन</t>
+          <t>Kolhapur residents hold 45-km silent march for elephant’s return | Mumbai news</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-inauguration-today-ap84</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Bhushan Gavai: कोल्हापूर खंडपीठ देशातील सामाजिक आणि आर्थिक न्यायासाठी मैलाचा दगड, लवकरच</t>
+          <t>Thousands Participate in a Silent March to Seek Mahadevi's Return from Vantara</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
+          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: रस्त्यांपासून पॅचवर्कपर्यंत ते वाहतूक व्यवस्थेपर्यंत सर्किंट बेंचच्या</t>
+          <t>Kolhapur Rises for Mahadevi: Thousands Join Silent March Demanding Elephant's Return From Vantara</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
+          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>रत्नागिरी : शिरगाव येथे उभारणार अत्याधुनिक ग्रामीण रुग्णालय</t>
+          <t>Silent march in Kolhapur demands return of elephant Mahadevi from Vantara</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/modern-rural-hospital-to-be-built-shirgaon-ratnagiri-dc95</t>
+          <t>https://www.dynamitenews.com/national/silent-march-in-kolhapur-demands-return-of-elephant-mahadevi-from-vantara</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>In Photos Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंच आतून आहे तरी कसं? अत्याधुनिक कोर्ट रुमची पहिली झलक</t>
+          <t>“Madhuri Should Come Back To The Math”: Maharashtra To File Review Petition For Elephant’s Return, Says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-what-is-the-inside-of-the-kolhapur-circuit-bench-like-first-glimpse-of-the-state-of-the-art-court-room-1377632</t>
+          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>महायुतीत पुन्हा वाद पेटणार! १५ ऑगस्टला रायगडमध्ये अदिती तटकरेंच्या हस्ते होणार ध्वजारोहण, गोगावलेंना संधी नाहीच</t>
+          <t>‘स्मार्ट’ अंतर्गत नोंदणीकृत प्रकल्प कालबद्धरितीने पूर्ण करा – कृषी मंत्री ॲड. माणिकराव कोकाटे</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
+          <t>https://mahasamvad.in/167140/</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>लोकांच्या चाळीस वर्षाच्या लढयाला यश ! कोल्हापुरात सर्किट बेंच !!</t>
+          <t>Blood Donation : 'ई-रक्तकोष पोर्टल' गरजूंना मिळवून देणार रक्त; अफवांवर विश्वास न ठेवता बिनधास्त करा रक्तदान, वाचा रक्तदानाचे फायदे !</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Success-to-the-people-s-forty-year-struggle--Circuit-bench-in-Kolhapur--</t>
+          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Transfer 34 hectares of Shendapark Land for IT Hub in Kolhapur: Ajit Pawar</t>
+          <t>Maharashtra rains: School wall collapses in Bhilar village</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-rains-school-wall-collapses-in-bhilar-village/articleshow/123403288.cms</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>स्वातंत्र्यदिनाचा मुख्य शासकीय समारोह मुंबईत; मुख्यमंत्र्यांच्या हस्ते ध्वजारोहण</t>
+          <t>Preparations on in full swing after high court approved circuit bench in Kolhapur</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174988/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Maharashtra: Kolhapur Residents Appeal to President To Bring Back Beloved Elephant Mahadevi</t>
+          <t>Kolhapur Circuit Bench: सर्किट बेंचच्या उद्घाटनासाठी करवीरनगरी सज्ज</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
+          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>I am driven to bring prosperity to people:, says Maharashtra deputy chief minister Eknath Shinde</t>
+          <t>Kolhapur Circuit Bench | सर्किट बेंचचे आज उद्घाटन</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-inauguration-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>25 ऑगस्टला कोल्हापूरात मोठा निर्णय! भावकीचा वाद मिटणार? मेहुणे-पाहुणे एक दिलाने लढणार</t>
+          <t>Bhushan Gavai: कोल्हापूर खंडपीठ देशातील सामाजिक आणि आर्थिक न्यायासाठी मैलाचा दगड, लवकरच</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ajit-pawars-kolhapur-visit-on-august-25-hasan-mushrif-likely-to-resolve-kp-patil-ay-patil-dispute-as11-rg93</t>
+          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Patient care remains hampered as govt contemplates nurses’ demands on day 6 of strike; over 500 surgeries</t>
+          <t>Kolhapur Circuit Bench: रस्त्यांपासून पॅचवर्कपर्यंत ते वाहतूक व्यवस्थेपर्यंत सर्किंट बेंचच्या</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Speed up work on GMCs in Washim, Bhandara, Ambernath, Palghar: Fadnavis</t>
+          <t>रत्नागिरी : शिरगाव येथे उभारणार अत्याधुनिक ग्रामीण रुग्णालय</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/modern-rural-hospital-to-be-built-shirgaon-ratnagiri-dc95</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Farmers protest against Nagpur-Goa Shaktipeeth highway, vow to block land acquisition</t>
+          <t>महायुतीत पुन्हा वाद पेटणार! १५ ऑगस्टला रायगडमध्ये अदिती तटकरेंच्या हस्ते होणार ध्वजारोहण, गोगावलेंना संधी नाहीच</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://infra.economictimes.indiatimes.com/news/roads-highways/farmers-protest-against-nagpur-goa-shaktipeeth-highway-vow-to-block-land-acquisition/118975130</t>
+          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+          <t>लोकांच्या चाळीस वर्षाच्या लढयाला यश ! कोल्हापुरात सर्किट बेंच !!</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://businessnewsthisweek.com/business/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/</t>
+          <t>https://maharashtranews1.com/Success-to-the-people-s-forty-year-struggle--Circuit-bench-in-Kolhapur--</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Maharashtra To Convert All Govt Hospitals Into Organ Retrieval Centres To Boost Donations</t>
+          <t>कोल्हापूर सर्किट बेंच इमारतीचे दिमाखदार उद्घाटन</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-convert-all-govt-hospitals-into-organ-retrieval-centres-to-boost-donations</t>
+          <t>https://ratnagirikhabardar.com/news/74156/</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणीच्या नादात राज्यात आरोग्य व्यवस्थेच्या चिंधड्या राज्य सरकारकडून</t>
+          <t>Transfer 34 hectares of Shendapark Land for IT Hub in Kolhapur: Ajit Pawar</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Maharashtra launches Inspection drive for blood banks</t>
+          <t>25 ऑगस्टला कोल्हापूरात मोठा निर्णय! भावकीचा वाद मिटणार? मेहुणे-पाहुणे एक दिलाने लढणार</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/maharashtra-launches-inspection-drive-for-blood-banks-146154</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ajit-pawars-kolhapur-visit-on-august-25-hasan-mushrif-likely-to-resolve-kp-patil-ay-patil-dispute-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Maharashtra: Over 5,000 Hospitals Found Violating Nursing Act, Face Action</t>
+          <t>स्वातंत्र्यदिनाचा मुख्य शासकीय समारोह मुंबईत; मुख्यमंत्र्यांच्या हस्ते ध्वजारोहण</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-over-5000-hospitals-found-violating-nursing-act-face-action</t>
+          <t>https://mahasamvad.in/174988/</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+          <t>Maharashtra: Kolhapur Residents Appeal to President To Bring Back Beloved Elephant Mahadevi</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Satej Patil Vs Shivsena : सतेज पाटलांचे शिलेदार शिंदेंनी स्वत:कडे वळवले, निवडणुकीच्या तोंडावर कोल्हापुरात सेनेचं पारडं जड?</t>
+          <t>I am driven to bring prosperity to people:, says Maharashtra deputy chief minister Eknath Shinde</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Eknath Shinde gives meetings a miss as row over guardian ministership continues</t>
+          <t>Patient care remains hampered as govt contemplates nurses’ demands on day 6 of strike; over 500 surgeries</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/eknath-shinde-gives-meetings-a-miss-row-over-guardian-ministership-continues-9815527/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/patient-care-remains-hampered-as-govt-contemplates-nurses-demands-on-day-6-of-strike-over-500-surgeries-postponed-at-sassoon/articleshow/122866730.cms</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Announces Guardian Ministers List; NCP's Dhananjay Munde Dropped | Full List</t>
+          <t>Speed up work on GMCs in Washim, Bhandara, Ambernath, Palghar: Fadnavis</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://www.outlookindia.com/national/maharashtra-govt-announces-guardian-ministers-list-ncps-dhananjay-munde-dropped-full-list</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/speed-up-work-on-gmcs-in-washim-bhandara-ambernath-palghar-fadnavis/articleshow/122372814.cms</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Maharashtra govt announces names of 36 guardian ministers: Dhananjay Munde not in list, CM Fadnavis gets Gadchiroli</t>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-announces-names-of-36-guardian-ministers-munde-not-in-list-9786173/</t>
+          <t>https://businessnewsthisweek.com/business/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>With new move, Eknath Shinde signals fresh tussle in Mahayuti govt</t>
+          <t>Pune hospital conferred 'Best BSD Award' and 'Best Organ Transplant Coordinator Award'</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>kolhapur | महायुतीची सत्ता आणण्यासाठी सज्ज राहा : खा. श्रीकांत शिंदे</t>
+          <t>Maharashtra To Convert All Govt Hospitals Into Organ Retrieval Centres To Boost Donations</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mp-shrikant-shinde-says-be-ready-to-bring-mahayuti-to-power-ap84</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-convert-all-govt-hospitals-into-organ-retrieval-centres-to-boost-donations</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Safety of warkaris is of prime importance, and police are alert to prevent any untoward incident: Shinde</t>
+          <t>लाडक्या बहिणीच्या नादात राज्यात आरोग्य व्यवस्थेच्या चिंधड्या राज्य सरकारकडून</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/safety-of-warkaris-is-of-prime-importance-and-police-are-alert-to-prevent-any-untoward-incident-shinde/articleshow/122234617.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Govt shielding Deenanath Mangeshkar Hospital management in the Bhise death case: Danve</t>
+          <t>Maharashtra launches Inspection drive for blood banks</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
+          <t>https://medicaldialogues.in/news/health/maharashtra-launches-inspection-drive-for-blood-banks-146154</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Wadia hospital to offer more affordable heart transplants to children</t>
+          <t>Maharashtra: Over 5,000 Hospitals Found Violating Nursing Act, Face Action</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-over-5000-hospitals-found-violating-nursing-act-face-action</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>DMER to start full-time nurse recruitment in August; MSNA calls off strike after state assurances</t>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
+          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Over 14,500 Women Show Cancer-Like Symptoms After Screening Drive In Hingoli</t>
+          <t>Satej Patil Vs Shivsena : सतेज पाटलांचे शिलेदार शिंदेंनी स्वत:कडे वळवले, निवडणुकीच्या तोंडावर कोल्हापुरात सेनेचं पारडं जड?</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Pune: University Road Flyover Partially Opens on May 1; Full Completion by August</t>
+          <t>Maharashtra govt announces names of 36 guardian ministers: Dhananjay Munde not in list, CM Fadnavis gets Gadchiroli</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-announces-names-of-36-guardian-ministers-munde-not-in-list-9786173/</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Pune: Ganesh Khind Road Flyover To Partially Open For Traffic On May 1, Full Completion Expected By August</t>
+          <t>SDMA structure to be changed to accommodate Maharashtra deputy CMs</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/pune-ganesh-khind-university-road-flyover-to-partially-open-for-traffic-on-may-1-full-completion-likely-by-august-10226940</t>
+          <t>https://www.deccanherald.com/india/maharashtra/sdma-structure-to-be-changed-to-accommodate-maharashtra-deputy-cms-3400638</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Update : राज्य सरकार एसटी महामंडळासह कामगारांच्या पाठिशी : अजित पवार</t>
+          <t>Maharashtra Govt Announces Guardian Ministers List; NCP's Dhananjay Munde Dropped | Full List</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-01-august-2025-mahayuti-vs-mahavikas-aghadi-ncp-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi-ajit-pawar-sharad-pawar-devendra-fadnavis-shivsena-ubt-sharad-pawar-mahayuti-cabinet-reshuffle-datta-bharane-new-agriculture-minister-manikrao-kokate-donald-trump-tarrif</t>
+          <t>https://www.outlookindia.com/national/maharashtra-govt-announces-guardian-ministers-list-ncps-dhananjay-munde-dropped-full-list</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>या जिल्ह्यात हे पालकमंत्री स्वातंत्र्य दिनी ध्वजारोहण करणार</t>
+          <t>With new move, Eknath Shinde signals fresh tussle in Mahayuti govt</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Eknath Shinde : कोल्हापूर सर्किट बेंचमुळे शेकडो मैल दूर असलेला न्याय घरापर्यंत आला; शिंदेंचे प्रतिपादन</t>
+          <t>kolhapur | महायुतीची सत्ता आणण्यासाठी सज्ज राहा : खा. श्रीकांत शिंदे</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mp-shrikant-shinde-says-be-ready-to-bring-mahayuti-to-power-ap84</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>सार्वजनिक बांधकाम विभागांतर्गतची कामे दर्जेदार करा -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Govt shielding Deenanath Mangeshkar Hospital management in the Bhise death case: Danve</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158717/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Wadia hospital to offer more affordable heart transplants to children</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister-2/2710767/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
+          <t>DMER to start full-time nurse recruitment in August; MSNA calls off strike after state assurances</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Over 14,500 Women Show Cancer-Like Symptoms After Screening Drive In Hingoli</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Pune: University Road Flyover Partially Opens on May 1; Full Completion by August</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Pune: Ganesh Khind Road Flyover To Partially Open For Traffic On May 1, Full Completion Expected By August</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>https://www.thedailyjagran.com/maharashtra/pune-ganesh-khind-university-road-flyover-to-partially-open-for-traffic-on-may-1-full-completion-likely-by-august-10226940</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics Update : राज्य सरकार एसटी महामंडळासह कामगारांच्या पाठिशी : अजित पवार</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-01-august-2025-mahayuti-vs-mahavikas-aghadi-ncp-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi-ajit-pawar-sharad-pawar-devendra-fadnavis-shivsena-ubt-sharad-pawar-mahayuti-cabinet-reshuffle-datta-bharane-new-agriculture-minister-manikrao-kokate-donald-trump-tarrif</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>या जिल्ह्यात हे पालकमंत्री स्वातंत्र्य दिनी ध्वजारोहण करणार</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Eknath Shinde : कोल्हापूर सर्किट बेंचमुळे शेकडो मैल दूर असलेला न्याय घरापर्यंत आला; शिंदेंचे प्रतिपादन</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Arogya Mitras to go on indefinite statewide strike from Feb 12</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Maharashtra: CM Devendra Fadnavis instructs to make special arrangement for treatment of GBS patients</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-instructs-to-make-special-arrangement-for-treatment-of-gbs-patients20250128191358/</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Singapore tourism board partners with IndiGo to boost travel</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278523385/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-acrob-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
           <t>‘अवयवदान पंधरवड्या’ला राज्यभरात सुरुवात</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B614" t="inlineStr">
         <is>
           <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b26885-txt-mumbai-20250803041544</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>सार्वजनिक आरोग्य विभागाच्या जास्तीत जास्त सेवा ऑनलाईन करा – मुख्यमंत्री देवेंद्र फडणवीस</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/171817/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,12 +515,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
+          <t>Maharashtra to ask Centre to include Thalassemia in national health scheme: Prakash Abitkar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
         </is>
       </c>
     </row>
@@ -683,168 +683,168 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Charitable hospitals must implement govt schemes, will revise treatment rates: Minister</t>
+          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/charitable-hospitals-must-implement-govt-schemes-will-revise-treatment-rates-minister-10145420/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-will-take-strict-action-against-unnecessary-hysterectomies-says-state-health-minister-prakash-abitkar-23565034</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Health dept. launches second probe into financial transactions at Regional Mental Hospital</t>
+          <t>Charitable hospitals must implement govt schemes, will revise treatment rates: Minister</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
+          <t>https://indianexpress.com/article/cities/pune/charitable-hospitals-must-implement-govt-schemes-will-revise-treatment-rates-minister-10145420/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maharashtra to run organ donation drive across state from August 3 to 15: Health Minister Prakash Abitkar</t>
+          <t>Health dept. launches second probe into financial transactions at Regional Mental Hospital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-launches-second-probe-into-financial-transactions-at-regional-mental-hospital-101736964694048.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Abitkar attributes delay in loan waiver to Ladki Bahin scheme; no mention in BJP’s poll manifesto, says S</t>
+          <t>Maharashtra to run organ donation drive across state from August 3 to 15: Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-run-organ-donation-drive-across-state-from-august-3-to-15-says-state-health-minister-prakash-abitkar-23587112</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Soon, mandatory ‘no denial policy’ for hospitals in state: DCM Pawar</t>
+          <t>Abitkar attributes delay in loan waiver to Ladki Bahin scheme; no mention in BJP’s poll manifesto, says S</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/abitkar-attributes-delay-in-loan-waiver-to-ladki-bahin-scheme-no-mention-in-bjps-poll-manifesto-says-save/articleshow/121855174.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
+          <t>Woman’s death after delivery in Pune: Maharashtra sets up probe committee</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
+          <t>https://indianexpress.com/article/cities/pune/pune-hospital-pregnant-woman-dies-probe-9924556/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Woman’s death after delivery in Pune: Maharashtra sets up probe committee</t>
+          <t>Soon, mandatory ‘no denial policy’ for hospitals in state: DCM Pawar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/pune-hospital-pregnant-woman-dies-probe-9924556/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/soon-mandatory-no-denial-policy-for-hospitals-in-state-dcm-pawar-101745606848690.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maha to relax norms for nursing homes, hospitals with up to 10 beds</t>
+          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
+          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Major Health Boost for Nagpur And Vidarbha: Govt plans facilities, incentives for doctors in remote areas</t>
+          <t>Maha to relax norms for nursing homes, hospitals with up to 10 beds</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-relax-norms-for-nursing-homes-hospitals-with-up-to-10-beds-101741632130994.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GBS Outbreak Scare: Maharashtra Minister Announces New Law For Clean Water Supply, Fines For Polluters</t>
+          <t>Rising obesity in children matter of grave concern, parents must take it seriously: Abitkar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/gbs-outbreak-scare-maharashtra-minister-announces-new-law-for-clean-water-supply-fines-for-polluters-9218986.html</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rising obesity in children matter of grave concern, parents must take it seriously: Abitkar</t>
+          <t>GBS Outbreak Scare: Maharashtra Minister Announces New Law For Clean Water Supply, Fines For Polluters</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/urgent-action-needed-rising-childhood-obesity-crisis-in-maharashtra/121377468</t>
+          <t>https://www.news18.com/india/gbs-outbreak-scare-maharashtra-minister-announces-new-law-for-clean-water-supply-fines-for-polluters-9218986.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cashless treatment up to ₹1 lakh for accident victims in Maharashtra</t>
+          <t>Mumbai's new 300-bed cancer center assures personalized, ai-powered treatment: Here's how</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-1-lakh/article69463926.ece</t>
+          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mumbai's new 300-bed cancer center assures personalized, ai-powered treatment: Here's how</t>
+          <t>Maharashtra Government issues directives to strengthen healthcare system</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.healthcareradius.in/awareness-and-promotion/mumbais-new-300-bed-cancer-center-assures-personalized-ai-powered-treatment-heres-how</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-government-issues-directives-to-strengthen-healthcare-system/article69593387.ece</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maharashtra Government issues directives to strengthen healthcare system</t>
+          <t>Cashless treatment up to ₹1 lakh for accident victims in Maharashtra</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-government-issues-directives-to-strengthen-healthcare-system/article69593387.ece</t>
+          <t>https://www.thehindu.com/news/national/accident-victims-in-maharashtra-to-receive-cashless-treatment-up-to-1-lakh/article69463926.ece</t>
         </is>
       </c>
     </row>
@@ -863,48 +863,48 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maharashtra to ask Centre to include Thalassemia in national health scheme: Prakash Abitkar</t>
+          <t>Contaminated well suspected in GBS spike; Pune civic body now supplies clean water through tankers</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-ask-centre-to-include-thalassemia-in-national-health-scheme-maharashtra-health-minister-prakash-abitkar-23587287</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/contaminated-well-suspected-in-gbs-spike-pune-civic-body-now-supplies-clean-water-through-tankers-101738005488804.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Contaminated well suspected in GBS spike; Pune civic body now supplies clean water through tankers</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/contaminated-well-suspected-in-gbs-spike-pune-civic-body-now-supplies-clean-water-through-tankers-101738005488804.html</t>
+          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister-2/2710767/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Mumbai reports 53 active Covid cases, government says situation under control</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister-2/2710767/</t>
+          <t>https://www.indiatoday.in/cities/mumbai/story/covid-19-in-india-active-cases-in-mumbai-health-minister-prakash-abitkar-situation-under-control-2727629-2025-05-20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mumbai reports 53 active Covid cases, government says situation under control</t>
+          <t>Maharashtra: Lab test ‘loot’ to end soon as govt plans price cap</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/cities/mumbai/story/covid-19-in-india-active-cases-in-mumbai-health-minister-prakash-abitkar-situation-under-control-2727629-2025-05-20</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
         </is>
       </c>
     </row>
@@ -923,1920 +923,1920 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maharashtra: Lab test ‘loot’ to end soon as govt plans price cap</t>
+          <t>Mumbai Reports 53 Active COVID-19 Cases; 2 Deaths Linked To Co-Morbidities</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-govt-to-cap-diagnostic-test-prices-soon-23502807</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mumbai Reports 53 Active COVID-19 Cases; 2 Deaths Linked To Co-Morbidities</t>
+          <t>No sudden spike in GBS cases in Pune, situation under control: Health Minister</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-reports-53-active-covid-19-cases-2-deaths-linked-to-co-morbidities-article-151683398</t>
+          <t>https://indianexpress.com/article/cities/mumbai/no-sudden-spike-gbs-cases-pune-health-minister-9813822/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>No sudden spike in GBS cases in Pune, situation under control: Health Minister</t>
+          <t>Maha to accredit private hospitals under Health Tourism Policy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/no-sudden-spike-gbs-cases-pune-health-minister-9813822/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
+          <t>Maharashtra government to provide free cancer vaccine for girls aged 0-14 across state</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-across-state-latest-updates-bird-flu-precautions-2025-03-01-978584</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maha to accredit private hospitals under Health Tourism Policy</t>
+          <t>GBS Cases In Pune Linked To Suspected Water Contamination, Says Maharashtra Minister</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-accredit-private-hospitals-under-health-tourism-policy-101738951583297.html</t>
+          <t>https://www.etvbharat.com/en/!state/gbs-cases-in-pune-linked-to-suspected-water-contamination-says-maharashtra-minister-enn25012706765</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mumbai: CM Fadnavis Holds High-Level Meeting on Public Health</t>
+          <t>Maha Health Minister urges officials to submit Health Policy proposal</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/state/news-4249/</t>
+          <t>https://medicaldialogues.in/state-news/maharashtra/maha-health-minister-urges-officials-to-submit-health-policy-proposal-148661</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GBS Cases In Pune Linked To Suspected Water Contamination, Says Maharashtra Minister</t>
+          <t>First Phase of the ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic Five Guinness World Records</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/gbs-cases-in-pune-linked-to-suspected-water-contamination-says-maharashtra-minister-enn25012706765</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2105326</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maharashtra government to provide free cancer vaccine for girls aged 0-14 across state</t>
+          <t>Contractual NHM staff may get permanent jobs; honorarium hike planned</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-across-state-latest-updates-bird-flu-precautions-2025-03-01-978584</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Maha Health Minister urges officials to submit Health Policy proposal</t>
+          <t>Maharashtra health dept to probe into claim about Pune hospital's refusal to admit pregnant woman</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/state-news/maharashtra/maha-health-minister-urges-officials-to-submit-health-policy-proposal-148661</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara Maharashtra minister</t>
+          <t>Centre to revise CGHS rates soon, union minister assures</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/01/bom39-mh-ld-elephant-minister.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Contractual NHM staff may get permanent jobs; honorarium hike planned</t>
+          <t>HMPV Outbreak LIVE Updates: No cause for concern, says Maharashtra Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/contractual-nhm-staff-may-get-permanent-jobs-honorarium-hike-planned/articleshow/121276552.cms</t>
+          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Centre to revise CGHS rates soon, union minister assures</t>
+          <t>Alert After Covid Cases Rise | Maharashtra Health Minister: “No Need To Panic”</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/centre-to-revise-cghs-rates-soon-union-minister-assures-101752782006201.html</t>
+          <t>https://www.businesstoday.in/bt-tv/video/alert-after-covid-cases-rise-maharashtra-health-minister-no-need-to-panic-477235-2025-05-21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Maharashtra cancels Licenses of 258 Private Hospitals for Violations</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
+          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HMPV Outbreak LIVE Updates: No cause for concern, says Maharashtra Health Minister Prakash Abitkar</t>
+          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/live-blog/hmpv-outbreak-live-updates-symptoms-prevention-guidelines-cases-in-india-health-ministry-18331190</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>Maharashtra approves inter and intra-district transfers for CHOs based on their requests</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/states/Efforts-on-to-bring-back-%E2%80%98Mahadevi%E2%80%99-from-Vantara--Maharashtra-minister/2784129</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
+          <t>Maharashtra: Accident victims to receive cashless treatment up to INR 1 lakh</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-maharashtra-to-form-leprosy-eradication-committee--106388</t>
+          <t>https://www.mumbailive.com/en/civic/accident-victims-of-maharashtra-to-receive-cashless-treatment-up-to-inr-1-lakh-88361</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alert After Covid Cases Rise | Maharashtra Health Minister: “No Need To Panic”</t>
+          <t>Minister Abitkar leads the Maharashtra government's two-week organ donation campaign by filling the form</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/alert-after-covid-cases-rise-maharashtra-health-minister-no-need-to-panic-477235-2025-05-21</t>
+          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Maharashtra approves inter and intra-district transfers for CHOs based on their requests</t>
+          <t>Mumbai Reports First Suspected GBS Case Amid Rising Cases in Maharashtra</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-approves-inter-and-intra-district-transfers-for-chos-based-on-their-requests-23558258</t>
+          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maharashtra: Accident victims to receive cashless treatment up to INR 1 lakh</t>
+          <t>Guillain-Barré Syndrome Outbreak: Maharashtra Health Minister Prakash Abitkar Visits Pune As Cases Cross 100</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/civic/accident-victims-of-maharashtra-to-receive-cashless-treatment-up-to-inr-1-lakh-88361</t>
+          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-outbreak-maharashtra-health-minister-prakash-abitkar-visits-pune-as-cases-cross-100-videos</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Minister Abitkar leads the Maharashtra government's two-week organ donation campaign by filling the form</t>
+          <t>Health Minister Prakash Abitkar Promises Support To Private Doctors At Pune Dialogue</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://assamtribune.com/national/minister-abitkar-leads-the-maharashtra-governments-two-week-organ-donation-campaign-by-filling-the-form-1587216</t>
+          <t>https://www.freepressjournal.in/pune/health-minister-prakash-abitkar-promises-support-to-private-doctors-at-pune-dialogue</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mumbai Reports First Suspected GBS Case Amid Rising Cases in Maharashtra</t>
+          <t>Guillain-Barré Syndrome In Kolhapur: Two Cases Of GBS Reported In Home District Of Health Minister Prakash</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://ehealth.eletsonline.com/2025/02/mumbai-reports-first-suspected-gbs-case-amid-rising-cases-in-maharashtra/</t>
+          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-in-kolhapur-two-cases-of-gbs-reported-in-home-district-of-health-minister-prakash-abitkar-solapur-also-reports-cases</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome Outbreak: Maharashtra Health Minister Prakash Abitkar Visits Pune As Cases Cross 100</t>
+          <t>Health Minister Prakash Abitkar announces one lakh reward: Pricing for tip offs on fetal sex determination ...</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-outbreak-maharashtra-health-minister-prakash-abitkar-visits-pune-as-cases-cross-100-videos</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Health Minister Prakash Abitkar Promises Support To Private Doctors At Pune Dialogue</t>
+          <t>Maharashtra To Urge Centre To Include Thalassemia In National Sickle Cell Programme</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/health-minister-prakash-abitkar-promises-support-to-private-doctors-at-pune-dialogue</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-urge-centre-to-include-thalassemia-in-national-sickle-cell-programme</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome In Kolhapur: Two Cases Of GBS Reported In Home District Of Health Minister Prakash</t>
+          <t>Maharashtra Clears ₹20,000 Crore For Shaktipeeth Expressway Amid Fierce Farmer Opposition</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/guillain-barr-syndrome-in-kolhapur-two-cases-of-gbs-reported-in-home-district-of-health-minister-prakash-abitkar-solapur-also-reports-cases</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-clears-20000-crore-for-shaktipeeth-expressway-amid-fierce-farmer-opposition</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Maharashtra To Urge Centre To Include Thalassemia In National Sickle Cell Programme</t>
+          <t>Maharashtra Govt Launches Cashless Treatment Scheme For Accident Victims, Covers ₹1 Lakh Per Case</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-urge-centre-to-include-thalassemia-in-national-sickle-cell-programme</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-launches-cashless-treatment-scheme-for-accident-victims-covers-1-lakh-per-case</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Health Minister Prakash Abitkar announces one lakh reward: Pricing for tip offs on fetal sex determination ...</t>
+          <t>Over 12,000 Child Deaths Reported In Maharashtra Between April 2024 And February 2025: Minister Prakash Abitka</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/health-minister-prakash-abitkar-announces-one-lakh-reward-134351424.html</t>
+          <t>https://www.freepressjournal.in/mumbai/over-12000-child-deaths-reported-in-maharashtra-between-april-2024-and-february-2025-minister-prakash-abitka</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maharashtra Clears ₹20,000 Crore For Shaktipeeth Expressway Amid Fierce Farmer Opposition</t>
+          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-clears-20000-crore-for-shaktipeeth-expressway-amid-fierce-farmer-opposition</t>
+          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Launches Cashless Treatment Scheme For Accident Victims, Covers ₹1 Lakh Per Case</t>
+          <t>Maharashtra: Govt Cancels Licenses Of 258 Private Hospitals For Violations</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-launches-cashless-treatment-scheme-for-accident-victims-covers-1-lakh-per-case</t>
+          <t>https://globalgreenews.com/2025/07/18/maharashtra-govt-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Over 12,000 Child Deaths Reported In Maharashtra Between April 2024 And February 2025: Minister Prakash Abitka</t>
+          <t>महाराष्ट्र में गुइलेन-बैरे सिंड्रोम के 197 मरीज : स्वास्थ्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/over-12000-child-deaths-reported-in-maharashtra-between-april-2024-and-february-2025-minister-prakash-abitka</t>
+          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CGHS Rates To Be Revised Soon, Says Mandaviya; Focus On Upgrading ESIS Hospitals Across Maharashtra</t>
+          <t>महाराष्ट्र में फिर कोरोना का डर? स्वास्थ्य मंत्री ने दिए अहम निर्देश, बोले- 'घबराएं</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/cghs-rates-to-be-revised-soon-says-mandaviya-focus-on-upgrading-esis-hospitals-across-maharashtra</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में गुइलेन-बैरे सिंड्रोम के 197 मरीज : स्वास्थ्य मंत्री प्रकाश आबिटकर</t>
+          <t>Cashless Treatment in Accident: दुर्घटनाग्रस्त के लिए 1 लाख तक फ्री इलाज</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/states/there-are-197-patients-of-guillain-barre-syndrome-in-maharashtra-health-minister-prakash-abitkar-534784-1</t>
+          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में फिर कोरोना का डर? स्वास्थ्य मंत्री ने दिए अहम निर्देश, बोले- 'घबराएं</t>
+          <t>उद्धव ने जिसके लिए लिया था ‘पंजे’ से पंगा, अब उसी ने छोड़ा साथ, महायुति की ताकत बढ़ी</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-corona-cases-health-minister-prakash-abitkar-said-do-not-panic-about-covid-19-ann-2957290</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cashless Treatment in Accident: दुर्घटनाग्रस्त के लिए 1 लाख तक फ्री इलाज</t>
+          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/cashless-treatment-in-road-accident-maharashtra-hindi/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>उद्धव ने जिसके लिए लिया था ‘पंजे’ से पंगा, अब उसी ने छोड़ा साथ, महायुति की ताकत बढ़ी</t>
+          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की बेटियों के लिए किया ये ऐलान</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-politics-uddhav-thackeray-shiv-sena-leader-chandrahar-patil-join-mahayuti-soon-19656309</t>
+          <t>https://hindi.news24online.com/state/mumbai/devendra-fadnavis-government-announces-free-cancer-vaccine-for-girls-under-14-years-of-age-maharashtra-news/1088804/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
+          <t>Organ Donation: अंगदान को नया आयाम, महाराष्ट्र के अन्य चार शहरों में खुलेंगे ZTCC सेंटर</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Organ Donation: अंगदान को नया आयाम, महाराष्ट्र के अन्य चार शहरों में खुलेंगे ZTCC सेंटर</t>
+          <t>Madhuri Elephant: हथिनी 'माधुरी' को वापस लाने के लिए मुख्यमंत्री देवेंद्र फडणवीस का बड़ा फैसला, राज्य सरकार भी सुप्रीम कोर्ट में दाखिल करेगी पुनर्विचार याचिका</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/more-ztcc-maharashtra-organ-donation-hindi/</t>
+          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Madhuri Elephant: हथिनी 'माधुरी' को वापस लाने के लिए मुख्यमंत्री देवेंद्र फडणवीस का बड़ा फैसला, राज्य सरकार भी सुप्रीम कोर्ट में दाखिल करेगी पुनर्विचार याचिका</t>
+          <t>राज्य की स्वास्थ्य नीति के संदर्भ में तुरंत पेश करें प्रस्ताव - स्वास्थ्य मंत्री प्रकाश अबिटकर ने दिए निर्देश</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/devendra-fadnavis-madhuri-elephant-return-nandani-math-hindi/</t>
+          <t>https://navbharatlive.com/maharashtra/health-minister-prakash-abitkar-instructions-to-submit-proposal-state-health-policy-5k-to-asha-workers-mumbai-1226342.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>राज्य की स्वास्थ्य नीति के संदर्भ में तुरंत पेश करें प्रस्ताव - स्वास्थ्य मंत्री प्रकाश अबिटकर ने दिए निर्देश</t>
+          <t>Maharashtra Cancels Licences Of 258 Private Hospitals For Violating Healthcare Norms; Notices Sent To 5,134</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/health-minister-prakash-abitkar-instructions-to-submit-proposal-state-health-policy-5k-to-asha-workers-mumbai-1226342.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cancels-licences-of-258-private-hospitals-for-violating-healthcare-norms-notices-sent-to-5134-hospitals-says-state-health-minister</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>महाराष्ट्र सरकार का बड़ा फैसला, 0-14 साल की लड़कियों को मिलेगी मुफ्त कैंसर वैक्सीन</t>
+          <t>'Pune's GBS cases may be linked to suspected water contamination'</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.humsamvet.com/national/maharashtra-governments-big-decision-girls-aged-0-14-years-will-get-free-cancer-vaccine-32953</t>
+          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Maharashtra Cancels Licences Of 258 Private Hospitals For Violating Healthcare Norms; Notices Sent To 5,134</t>
+          <t>Efforts on to bring back ‘Mahadevi’ from Vantara Maharashtra minister</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cancels-licences-of-258-private-hospitals-for-violating-healthcare-norms-notices-sent-to-5134-hospitals-says-state-health-minister</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/01/bom39-mh-ld-elephant-minister.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>'Pune's GBS cases may be linked to suspected water contamination'</t>
+          <t>Prakash Abitkar: 'दादा नेहमी आमच्या परीक्षा घेतात अन् आमची अडचण होते', आरोग्यमंत्री प्रकाश</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/health/pune-s-gbs-cases-linked-to-suspected-water-contamination-prakash-abitkar-125012701436_1.html</t>
+          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Maharashtra health dept to probe into claim about Pune hospital's refusal to admit pregnant woman</t>
+          <t>Prakash Abitkar News : आरोग्यमंत्री आबिटकरांची महत्त्वपूर्ण घोषणा, गर्भलिंगविरोधात खबऱ्यांना मिळणार मोठं बक्षीस</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-health-dept-to-probe-into-claim-about-pune-hospitals-refusal-to-admit-pregnant-woman-3477956</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-announces-reward-against-gender-testing-informants-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Efforts on to bring back ‘Mahadevi’ from Vantara: Maharashtra minister</t>
+          <t>आरोग्यमंत्री प्रकाश आबिटकर म्हणाले, काही बिघडणार…</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/efforts-on-to-bring-back-mahadevi-from-vantara-maharashtra-minister/2710544/</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-on-inquiry-of-health-department-s-irregularity-pune-print-news-ggy-03-css-98-4923177/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Maha Health Minister urges Mandaviya to revise income eligibility limit for ESIS beneficiaries</t>
+          <t>पारदर्शी कारभारासाठी चौकशी होणे योग्यच : आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/health/maha-health-minister-urges-mandaviya-to-revise-income-eligibility-limit-for-esis-beneficiaries</t>
+          <t>https://pudhari.news/pimpri-chinchwad/an-inquiry-is-right-for-transparent-governance-says-prakash-abitakar</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: 'दादा नेहमी आमच्या परीक्षा घेतात अन् आमची अडचण होते', आरोग्यमंत्री प्रकाश</t>
+          <t>कोल्हापूर शहराची हद्दवाढ, खंडपीठ होणारच; पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/health-minister-prakash-abitkar-on-dcm-ajit-pawar-pune-hindu-hrudaysamrat-balasaheb-thakrey-aapla-dawakhana-1356102</t>
+          <t>https://www.lokmat.com/kolhapur/kolhapur-city-limits-to-be-expanded-bench-to-be-formed-says-guardian-minister-prakash-abitkar-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Prakash Abitkar News : आरोग्यमंत्री आबिटकरांची महत्त्वपूर्ण घोषणा, गर्भलिंगविरोधात खबऱ्यांना मिळणार मोठं बक्षीस</t>
+          <t>Prakashrao Abitkar | मंत्री प्रकाश आबिटकर यांचा अजेंडा काय? जाणून घ्या...</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-announces-reward-against-gender-testing-informants-dk88-rg93</t>
+          <t>https://www.lokshahi.com/news/what-is-minister-prakash-abitkars-agenda-find-out</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री प्रकाश आबिटकर म्हणाले, काही बिघडणार…</t>
+          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-on-inquiry-of-health-department-s-irregularity-pune-print-news-ggy-03-css-98-4923177/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>कोल्हापूर शहराची हद्दवाढ, खंडपीठ होणारच; पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
+          <t>'जीबीएस' आजारानं रुग्णाचा मृत्यू होतो का? आरोग्यमंत्र्यांनी थेटच सांगितलं...</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/kolhapur-city-limits-to-be-expanded-bench-to-be-formed-says-guardian-minister-prakash-abitkar-a-a746/</t>
+          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>राज्यातील आरोग्यसंस्थांमध्ये दोन हजार पदनिर्मितीस मान्यता : आरोग्यमंत्री आबिटकर</t>
+          <t>Tanisha Bhise Death Case : पैशांच्या डिपॉझिटसाठी उपचार नाकारणाऱ्या सर्व हॉस्पिटल्सवर कारवाई होणार? आरोग्यमंत्र्यांकडून महत्त्वाची माहिती</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-health-department-2070-new-posts-approved</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
+          <t>कोल्हापूरच्या राजकारणात आबिटकरांचे प्रकाशपर्व!</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%A6-%E0%A4%A8-%E0%A4%B5-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%AD%E0%A5%81%E0%A4%A6%E0%A4%B0%E0%A4%97%E0%A4%A1-%E0%A4%A4-%E0%A4%B2%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%9C%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%B7/ar-AA1xqYL9</t>
+          <t>https://www.loksatta.com/kolhapur/prakash-abitkar-is-now-the-focus-of-kolhapur-politics-mrj-95-4843588/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Prakashrao Abitkar | मंत्री प्रकाश आबिटकर यांचा अजेंडा काय? जाणून घ्या...</t>
+          <t>राज्यातील आरोग्यसंस्थांमध्ये दोन हजार पदनिर्मितीस मान्यता : आरोग्यमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/what-is-minister-prakash-abitkars-agenda-find-out</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-health-department-2070-new-posts-approved</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>'जीबीएस' आजारानं रुग्णाचा मृत्यू होतो का? आरोग्यमंत्र्यांनी थेटच सांगितलं...</t>
+          <t>कोल्हापूरच्या हद्दवाढीसाठी लवकरच मुख्यमंत्र्यांसोबत बैठक, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/gbs-disease-does-not-cause-death-health-minister-prakash-abitkar-clarifies-in-pune-maharashtra-news-mhs25012706012</t>
+          <t>https://www.lokmat.com/kolhapur/meeting-with-chief-minister-soon-for-extension-of-kolhapur-boundary-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tanisha Bhise Death Case : पैशांच्या डिपॉझिटसाठी उपचार नाकारणाऱ्या सर्व हॉस्पिटल्सवर कारवाई होणार? आरोग्यमंत्र्यांकडून महत्त्वाची माहिती</t>
+          <t>Corona virus in Maharashtra: राज्यातील कोरोना व्हायरसबाबत मोठी अपडेट, आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-health-minister-prakash-abitkar-on-tanisha-bhise-death-case/articleshow/119980632.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>दीनानाथ मंगेशकर रुग्णालयावर कारवाई कधी? आरोग्य मंत्री प्रकाश आबिटकर यांनी दिले उत्तर</t>
+          <t>राज्यात प्रथमच स्वतंत्र आरोग्य धोरण; आरोग्यमंत्री प्रकाश आबिटकर यांची घोषणा</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-said-about-the-action-taken-by-dinanath-hospital-1387152.html</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-announces-separate-health-policy-for-the-maharashtra-state-amy-95-4860385/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या राजकारणात आबिटकरांचे प्रकाशपर्व!</t>
+          <t>‘वैद्यकीय अधिकाऱ्यांची रिक्त पदे तातडीने भरा’; आरोग्यमंत्री प्रकाश आबिटकर यांचे आदेश</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/prakash-abitkar-is-now-the-focus-of-kolhapur-politics-mrj-95-4843588/</t>
+          <t>https://www.lokmat.com/maharashtra/fill-the-vacant-posts-of-medical-officers-immediately-says-health-minister-prakash-abitkar-a-a992/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या हद्दवाढीसाठी लवकरच मुख्यमंत्र्यांसोबत बैठक, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
+          <t>Prakash Abitkar : कोल्हापुरातील दिव्यांगांचा एकही प्रश्न शिल्लक ठेवायचा नाही प्रकाश</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/meeting-with-chief-minister-soon-for-extension-of-kolhapur-boundary-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-prakash-abitkar-instructions-no-issue-of-the-disabled-should-be-left-unsolved-marathi-news-1358401</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Corona virus in Maharashtra: राज्यातील कोरोना व्हायरसबाबत मोठी अपडेट, आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>विधानसभेत आरोग्यमंत्र्यांची मोठी घोषणा, बीड जिल्हा रुग्णालयातील बडा डॉक्टर</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/corona-virus-covid-19-patients-increases-in-maharashtra-updates-health-minister-prakash-abitkar-1360086</t>
+          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>राज्यात प्रथमच स्वतंत्र आरोग्य धोरण; आरोग्यमंत्री प्रकाश आबिटकर यांची घोषणा</t>
+          <t>Kolhapur News: पालकमंत्री प्रकाश आबिटकर शेताच्या बांधावर; भर पावसात चिखलगुट्टा करत भात रोपांची लागण</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-announces-separate-health-policy-for-the-maharashtra-state-amy-95-4860385/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>‘वैद्यकीय अधिकाऱ्यांची रिक्त पदे तातडीने भरा’; आरोग्यमंत्री प्रकाश आबिटकर यांचे आदेश</t>
+          <t>Prakash Abitkar : पालकमंत्री प्रकाश आबिटकरांकडून कोल्हापुरात ध्वजारोहण; म्हणाले, बहुमान मिळाल्याचा सार्थ अभिमान</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/fill-the-vacant-posts-of-medical-officers-immediately-says-health-minister-prakash-abitkar-a-a992/</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : कोल्हापुरातील दिव्यांगांचा एकही प्रश्न शिल्लक ठेवायचा नाही प्रकाश</t>
+          <t>Prakash Abitkar : पालकमंत्री कोणावर होणार मेहरबान? भाजपमध्ये मोठी स्पर्धा</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-prakash-abitkar-instructions-no-issue-of-the-disabled-should-be-left-unsolved-marathi-news-1358401</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/kolhapur-guardian-minister-prakash-abitkar-who-will-get-favor-bjp-big-competition-rg90-gs97</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kolhapur News: पालकमंत्री प्रकाश आबिटकर शेताच्या बांधावर; भर पावसात चिखलगुट्टा करत भात रोपांची लागण</t>
+          <t>Prakash Abitkar on Covid 19: कोरोनाची लक्षणं सौम्य, प्रकाश आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-guardian-minister-prakash-abitkar-on-the-farm-planting-rice-seedlings-by-making-mud-puddles-in-heavy-rain-1368103</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5122212/corona-symptoms-are-mild-prakash-abitkars-gave-detail-information/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>विधानसभेत आरोग्यमंत्र्यांची मोठी घोषणा, बीड जिल्हा रुग्णालयातील बडा डॉक्टर</t>
+          <t>Prakash Abitkar : सामान्य नागरिकांना त्रास देणाऱ्यांना रस्त्यावर फटके द्या; गांजा आणि सावकारीवरून पालकमंत्री प्रकाश आबिटकरांचे निर्देश</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/health-minister-prakash-abitkar-announces-beed-district-civil-surgeon-ashok-thorat-suspended-in-vidhan-sabha-maharashtra-budget-session-marathi-news-1350939</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : पालकमंत्री प्रकाश आबिटकरांकडून कोल्हापुरात ध्वजारोहण; म्हणाले, बहुमान मिळाल्याचा सार्थ अभिमान</t>
+          <t>वैद्यकीय प्रयोगशाळांच्या तपासणीसाठी कायदा; आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-prakash-abitkar-said-that-he-is-rightly-proud-to-have-received-this-honor-as-the-guardian-minister-of-kolhapur-district-1340809</t>
+          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : पालकमंत्री कोणावर होणार मेहरबान? भाजपमध्ये मोठी स्पर्धा</t>
+          <t>कोल्हापूर जिल्ह्यापासून लंपी दूर ठेवा – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/kolhapur-guardian-minister-prakash-abitkar-who-will-get-favor-bjp-big-competition-rg90-gs97</t>
+          <t>https://www.loksatta.com/kolhapur/lumpy-disease-under-controls-in-kolhapur-district-due-to-implementation-of-effective-vaccination-says-minister-prakash-abitkar-zws-70-5301296/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Covid 19: कोरोनाची लक्षणं सौम्य, प्रकाश आबिटकर यांची माहिती</t>
+          <t>Maharashtra Politics : महाराष्ट्राच्या मंत्रिमंडळातला मोठा गौप्यस्फोट, मंत्र्यानेच सांगितली आतली बातमी</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5122212/corona-symptoms-are-mild-prakash-abitkars-gave-detail-information/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : सामान्य नागरिकांना त्रास देणाऱ्यांना रस्त्यावर फटके द्या; गांजा आणि सावकारीवरून पालकमंत्री प्रकाश आबिटकरांचे निर्देश</t>
+          <t>Kolhapur Politics: पालकमंत्रीही उतरणार ‘गडहिंग्लज’च्या मैदानात !, मुश्रीफांचे बारकाईने लक्ष</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-whip-those-who-harass-ordinary-citizens-on-the-streets-guardian-minister-prakash-abitkar-instructions-on-ganja-and-moneylender-maharashtra-marathi-news-update-1357053</t>
+          <t>https://www.lokmat.com/kolhapur/guardian-minister-prakash-abitkar-will-also-contest-the-gadhinglaj-municipality-elections-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>वैद्यकीय प्रयोगशाळांच्या तपासणीसाठी कायदा; आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-prakash-abitkar-told-the-legislative-assembly-that-the-process-of-drafting-the-law-is-underway-pune-print-news-phm-00-5219873/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kolhapur Politics: पालकमंत्रीही उतरणार ‘गडहिंग्लज’च्या मैदानात !, मुश्रीफांचे बारकाईने लक्ष</t>
+          <t>Madhuri Elephant News : ‘माधुरी हत्तीणी’च्या ‘नांदणी’वापसीचा मार्ग मोकळा! पण कायद्याचा अडसर; पालकमंत्री आबिटकरांची माहिती</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/guardian-minister-prakash-abitkar-will-also-contest-the-gadhinglaj-municipality-elections-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/madhuri-elephant-cleared-for-return-to-nandani-but-legal-hurdles-remain-says-minister-prakash-abitkar-rg84</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्यापासून लंपी दूर ठेवा – प्रकाश आबिटकर</t>
+          <t>Maharashtra Politics : लाडकी बहीण योजनेवरुन महायुतीत 'कसरत', आरोग्यमंत्र्यांचं मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/lumpy-disease-under-controls-in-kolhapur-district-due-to-implementation-of-effective-vaccination-says-minister-prakash-abitkar-zws-70-5301296/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : महाराष्ट्राच्या मंत्रिमंडळातला मोठा गौप्यस्फोट, मंत्र्यानेच सांगितली आतली बातमी</t>
+          <t>Kolhapur city Extension : हद्दवाढीसाठी शहरवासियांनी न्यायदाता ठरवला, पालकमंत्री अबिटकरांनाच करणार म्होरक्या</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/minister-prakash-abitkars-big-revelation-in-maharashtra-politics-delay-in-farmers-loan-waiver-due-to-ladki-bahin-scheme/articleshow/121847611.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-haddavadh-kruti-samitis-decision-to-approach-guardian-minister-prakash-abitkar-for-boundary-expansion-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
+          <t>महाराष्ट्राचे आरोग्यमंत्री अचानक रुग्णालयात धडकले, अधिकाऱ्यांवर भडकले, नेमकं काय घडलं?</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Madhuri Elephant News : ‘माधुरी हत्तीणी’च्या ‘नांदणी’वापसीचा मार्ग मोकळा! पण कायद्याचा अडसर; पालकमंत्री आबिटकरांची माहिती</t>
+          <t>Kolhapur Political News | कॅरम खेळण्यात आबिटकर-महाडिक दंग; सोशल मीडियावर व्हिडिओ व्हायरल</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/madhuri-elephant-cleared-for-return-to-nandani-but-legal-hurdles-remain-says-minister-prakash-abitkar-rg84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-leaders-dhanajay-mahadik-and-prakash-abitkar-sharangdhar-deshmukh-carrom-match-political-move-sd22</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : लाडकी बहीण योजनेवरुन महायुतीत 'कसरत', आरोग्यमंत्र्यांचं मोठं वक्तव्य</t>
+          <t>राज्यात बॉम्बे नर्सिंग अँक्टची कठोर अमंलबजावणी होणार; आरोग्य मंत्री प्रकाश आबिटकर यांनी माहिती</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-big-statement-on-ladki-bahin-yojana/articleshow/120848813.cms</t>
+          <t>https://www.loksatta.com/maharashtra/health-minister-prakash-abitkar-has-informed-that-the-bombay-nursing-act-will-be-strictly-implemented-in-the-state-amy-95-4933697/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kolhapur city Extension : हद्दवाढीसाठी शहरवासियांनी न्यायदाता ठरवला, पालकमंत्री अबिटकरांनाच करणार म्होरक्या</t>
+          <t>Prakash Abitkar on Hospital : हॉस्पिटलच्या मनमानीला चाप लागणार पेशंट, नातेवाईकांची तक्रार थेट</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-haddavadh-kruti-samitis-decision-to-approach-guardian-minister-prakash-abitkar-for-boundary-expansion-as11-rg93</t>
+          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>महाराष्ट्राचे आरोग्यमंत्री अचानक रुग्णालयात धडकले, अधिकाऱ्यांवर भडकले, नेमकं काय घडलं?</t>
+          <t>Kolhapur Politics | कोल्हापूरचे पालकमंत्री आबिटकर थेट खासदार शाहू महाराजांच्या भेटीला; चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/health-minister-prakash-abitkar-surprise-visit-to-hospital-anger-over-management-dispute-among-officials/articleshow/121994682.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-guardian-minister-prakash-abitkar-meets-congress-mp-shahu-maharaj-as80</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>राज्यात बॉम्बे नर्सिंग अँक्टची कठोर अमंलबजावणी होणार; आरोग्य मंत्री प्रकाश आबिटकर यांनी माहिती</t>
+          <t>कोल्हापूर जिल्ह्यातील ३५७ प्राथमिक शाळांसाठी ११० कोटींचा निधी, पालकमंत्री प्रकाश आबिटकर यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/health-minister-prakash-abitkar-has-informed-that-the-bombay-nursing-act-will-be-strictly-implemented-in-the-state-amy-95-4933697/</t>
+          <t>https://www.lokmat.com/kolhapur/fund-of-rs-110-crores-for-357-primary-schools-in-kolhapur-district-guardian-minister-prakash-abitkar-gave-information-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Hospital : हॉस्पिटलच्या मनमानीला चाप लागणार पेशंट, नातेवाईकांची तक्रार थेट</t>
+          <t>Prakash Abitkar : 108 अॅम्ब्युलन्स खरेदीच्या टेंडर प्रक्रियेत काय झालं? श्रीकांत शिंदेंचे</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/prakash-abitkar-on-hospital-1357379</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kolhapur Political News | कॅरम खेळण्यात आबिटकर-महाडिक दंग; सोशल मीडियावर व्हिडिओ व्हायरल</t>
+          <t>Kolhapur News: कोल्हापुरात ईएसआय रुग्णालयात आरोग्यमंत्र्यांकडून डॉक्टरांची झाडाझडती</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-leaders-dhanajay-mahadik-and-prakash-abitkar-sharangdhar-deshmukh-carrom-match-political-move-sd22</t>
+          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 108 अॅम्ब्युलन्स खरेदीच्या टेंडर प्रक्रियेत काय झालं? श्रीकांत शिंदेंचे</t>
+          <t>Prakash Abitkar: कोल्हापुरात महायुतीमध्ये शिवसेना हाच सर्वात मोठा पक्ष आगामी निवडणुकांसाठी</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-clarification-on-maharashtra-108-ambulance-tender-corruption-allegation-on-shrikant-eknath-shinde-kolhapur-news-1372811</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Kolhapur Politics | कोल्हापूरचे पालकमंत्री आबिटकर थेट खासदार शाहू महाराजांच्या भेटीला; चर्चांना उधाण</t>
+          <t>अनुदान न मिळाल्याने रखडले ‘आरबीएसके’ पथकांचे वेतन; आरोग्यमंत्री प्रकाश आबिटकर यांची माहिती</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-guardian-minister-prakash-abitkar-meets-congress-mp-shahu-maharaj-as80</t>
+          <t>https://pudhari.news/maharashtra/pune/salary-of-rbsk-teams-stalled-due-to-non-receipt-of-grant</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kolhapur News: कोल्हापुरात ईएसआय रुग्णालयात आरोग्यमंत्र्यांकडून डॉक्टरांची झाडाझडती</t>
+          <t>‘अलमट्टी’ विरोधात महाराष्ट्राची; कायदेशीर लढाई – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/health-minister-prakash-abitkar-at-esi-hospital-in-kolhapur-two-medical-officers-have-a-verbal-clash-marathi-news-update-1365376</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-prakash-abitkar-expressed-his-opinion-regarding-the-height-of-the-almatti-dam-while-talking-to-reporters-phm-00-5066152/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: कोल्हापुरात महायुतीमध्ये शिवसेना हाच सर्वात मोठा पक्ष आगामी निवडणुकांसाठी</t>
+          <t>Prakash Abitkar on Almatti Dam : तर आम्हीही तशीच वकिलांची आणि जलतज्ञांची फौज उभा करू 'अलमट्टी'च्या</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-guardian-minister-prakash-abitkar-has-categorically-stated-that-shiv-sena-is-the-largest-party-in-the-mahayuti-in-the-district-marathi-news-update-1372685</t>
+          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ई-रक्तकोषद्वारे गरजू रुग्णांना मिळणार रक्त उपलब्धतेची माहिती - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>Women Cancer Symptoms : खळबळजनक! महाराष्ट्रातील ‘या’ जिल्ह्यात तब्बल १४ हजारांहून अधिक महिलांमध्ये आढळली 'कॅन्सर'सारखी लक्षणे</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159642/</t>
+          <t>https://www.esakal.com/maharashtra/hingoli-women-cancer-symptoms-health-minister-prakash-abitkar-statement-14000-affected-msr87</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>अनुदान न मिळाल्याने रखडले ‘आरबीएसके’ पथकांचे वेतन; आरोग्यमंत्री प्रकाश आबिटकर यांची माहिती</t>
+          <t>गर्भलिंग निदानाची माहिती देणार्‍यास एक लाखाचे बक्षीस</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/salary-of-rbsk-teams-stalled-due-to-non-receipt-of-grant</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/reward-of-1-lakh-for-informing-about-fetal-sex-diagnosis</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Prakash Abitkar on Almatti Dam : तर आम्हीही तशीच वकिलांची आणि जलतज्ञांची फौज उभा करू 'अलमट्टी'च्या</t>
+          <t>ई-रक्तकोषद्वारे गरजू रुग्णांना मिळणार रक्त उपलब्धतेची माहिती - सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/prakash-abitkar-warning-to-karnataka-from-the-height-of-almatti-maharashtra-marathi-news-update-1357399</t>
+          <t>https://mahasamvad.in/159642/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>‘अलमट्टी’ विरोधात महाराष्ट्राची; कायदेशीर लढाई – प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : विरोधकांच्या 108 रुग्णवाहिका घोटाळ्यावर आरोग्यमंत्र्यांचे स्पष्टीकरण, म्हणाले, "त्याचा शासनाशी सबंध नाही..."</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/guardian-minister-prakash-abitkar-expressed-his-opinion-regarding-the-height-of-the-almatti-dam-while-talking-to-reporters-phm-00-5066152/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-108-ambulance-scam-health-minister-prakash-abitkar-clarification-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Women Cancer Symptoms : खळबळजनक! महाराष्ट्रातील ‘या’ जिल्ह्यात तब्बल १४ हजारांहून अधिक महिलांमध्ये आढळली 'कॅन्सर'सारखी लक्षणे</t>
+          <t>कोल्हापूर हद्दवाढीवर लवकरच निर्णय</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/hingoli-women-cancer-symptoms-health-minister-prakash-abitkar-statement-14000-affected-msr87</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-boundary-expansion-decision-soon-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>पत्रकारांच्या आरोग्याच्या प्रश्नावर लवकरच बैठक घेणार – मंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar | ग्रामीण भागात सेवा दिल्यानंतरच डॉक्टरांना प्रमाणपत्र मिळणार</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170017/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/doctors-rural-service-bond-certificate-upload-health-minister-prakash-abitkar</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>कोल्हापूर हद्दवाढीवर लवकरच निर्णय</t>
+          <t>पत्रकारांच्या आरोग्याच्या प्रश्नावर लवकरच बैठक घेणार – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-boundary-expansion-decision-soon-prakash-abitkar-ap84</t>
+          <t>https://mahasamvad.in/170017/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Prakash Abitkar | ग्रामीण भागात सेवा दिल्यानंतरच डॉक्टरांना प्रमाणपत्र मिळणार</t>
+          <t>Prakash Abitkar: पहिल्यांदाच मंत्री अन् पालकमंत्रिपद मिळालं, आबिटकर यांच्यासमोर आता 'हे' मोठ आव्हान</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/doctors-rural-service-bond-certificate-upload-health-minister-prakash-abitkar</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-kolhapur-guardian-minister-prakash-abitkar-mahayuti-challenge-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : विरोधकांच्या 108 रुग्णवाहिका घोटाळ्यावर आरोग्यमंत्र्यांचे स्पष्टीकरण, म्हणाले, "त्याचा शासनाशी सबंध नाही..."</t>
+          <t>मुख्यमंत्र्यांच्या सूचनेनुसारच हद्दवाढीची प्रक्रिया सुरू : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-108-ambulance-scam-health-minister-prakash-abitkar-clarification-jap93-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/boundary-expansion-process-initiated-as-per-cm-directive-says-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Prakash Abitkar: पहिल्यांदाच मंत्री अन् पालकमंत्रिपद मिळालं, आबिटकर यांच्यासमोर आता 'हे' मोठ आव्हान</t>
+          <t>Pune GBS : पुण्यातील 'त्या' विहिरीमुळे पसरला गुईलेन बॅरे सिंड्रोम, आरोग्यमंत्र्यांनी दिली धक्कादायक माहिती</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-kolhapur-guardian-minister-prakash-abitkar-mahayuti-challenge-mm76-rg93</t>
+          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांच्या सूचनेनुसारच हद्दवाढीची प्रक्रिया सुरू : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>कृषी विभागाच्या बैठकीवेळी पालकमंत्री प्रकाश आबिटकर यांनी मार्गदर्शन केले</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/boundary-expansion-process-initiated-as-per-cm-directive-says-prakash-abitkar-ap84</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-guidance-during-the-agriculture-department-meeting-sud-02-5087323/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>महिन्यातून किमान दोन वेळा आरोग्य संस्थांना अचानक भेटी द्या - आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>flood control planning | पूर नियंत्रणाचे सूक्ष्म नियोजन करा : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/make-surprise-visits-to-health-institutions-at-least-twice-a-month-health-minister-prakash-abitkar-a-a1008/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/plan-micro-level-flood-control-says-minister-prakash-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>कृषी विभागाच्या बैठकीवेळी पालकमंत्री प्रकाश आबिटकर यांनी मार्गदर्शन केले</t>
+          <t>दोन कोटी शालेय विद्यार्थ्यांची आरोग्य तपासणी करणार – आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-guidance-during-the-agriculture-department-meeting-sud-02-5087323/</t>
+          <t>https://mahasamvad.in/155891/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>flood control planning | पूर नियंत्रणाचे सूक्ष्म नियोजन करा : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Guardian Minister : मंत्री प्रकाश आबिटकर कोल्हापूरचे पालकमंत्री</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/plan-micro-level-flood-control-says-minister-prakash-abitkar-ap84</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-appointed-as-guardian-minister-of-kolhapur-sdj87</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>दोन कोटी शालेय विद्यार्थ्यांची आरोग्य तपासणी करणार – आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>अवैध गर्भपाताची माहिती देणाऱ्या महिलांच्या मानधनात वाढ – आबिटकर</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155891/</t>
+          <t>https://www.loksatta.com/kolhapur/increase-in-honorarium-of-women-who-provide-information-about-illegal-abortions-say-prakash-abitkar-mrj-95-4843272/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>अवैध गर्भपाताची माहिती देणाऱ्या महिलांच्या मानधनात वाढ – आबिटकर</t>
+          <t>"कर्करोगापासून बचाव करण्यासाठी मुलींना मोफत लस...", नेमकं काय म्हणाले आरोग्य मंत्री? - CANCER VACCINE FOR GIRLS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/increase-in-honorarium-of-women-who-provide-information-about-illegal-abortions-say-prakash-abitkar-mrj-95-4843272/</t>
+          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kolhapur Guardian Minister : मंत्री प्रकाश आबिटकर कोल्हापूरचे पालकमंत्री</t>
+          <t>Kolhapur Politics: 'गोकुळ'मध्ये मुश्रीफ, सतेज, आबिटकर, कोरे यांची एकी; डोंगळे एकाकी</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-appointed-as-guardian-minister-of-kolhapur-sdj87</t>
+          <t>https://www.lokmat.com/kolhapur/hasan-mushrif-satej-patil-prakash-abitkar-vinay-kore-are-united-in-gokul-dudh-sangh-politics-arun-dongle-is-alone-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>"कर्करोगापासून बचाव करण्यासाठी मुलींना मोफत लस...", नेमकं काय म्हणाले आरोग्य मंत्री?</t>
+          <t>Mahadevi Elephant : नांदणीतील महादेवी परत येणार, मंत्री आबिटकरांनी दिली कायदेशीर प्रक्रियेची माहिती</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/hpv-vaccination-in-maharashtra-health-minister-prakash-abitkar-informed-that-cancer-vaccine-will-be-given-free-to-girls-up-to-age-of-14-maharashtra-news-mhs25030200577</t>
+          <t>https://www.mymahanagar.com/maharashtra/mahadevi-elephant-in-nandani-will-return-minister-prakash-abitkar-gave-information-about-legal-process/907779/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Kolhapur Politics: 'गोकुळ'मध्ये मुश्रीफ, सतेज, आबिटकर, कोरे यांची एकी; डोंगळे एकाकी</t>
+          <t>‘महादेवी’परत करण्याबाबत ‘वनतारा’ व्यवस्थापन सकारात्मक; प्रकाश आबिटकर यांचा दावा</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/hasan-mushrif-satej-patil-prakash-abitkar-vinay-kore-are-united-in-gokul-dudh-sangh-politics-arun-dongle-is-alone-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-abitkar-claims-positive-response-from-vantara-over-elephant-rds-00-5274363/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>‘महादेवी’परत करण्याबाबत ‘वनतारा’ व्यवस्थापन सकारात्मक; प्रकाश आबिटकर यांचा दावा</t>
+          <t>Prakash Abitkar : आरोग्यमंत्र्यांच्या कोल्हापुरातच 'सलमान'ची चर्चा, प्रशासकीय अधिकारीही 'लाभार्थी'</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-abitkar-claims-positive-response-from-vantara-over-elephant-rds-00-5274363/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-advises-citizens-to-consult-professionals-that-time-some-officials-visit-salmans-hair-trainer-to-treatment-hair-problem-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant : नांदणीतील महादेवी परत येणार, मंत्री आबिटकरांनी दिली कायदेशीर प्रक्रियेची माहिती</t>
+          <t>कर्करोग प्रतिबंधासाठी जनजागृती गरजेची – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/mahadevi-elephant-in-nandani-will-return-minister-prakash-abitkar-gave-information-about-legal-process/907779/</t>
+          <t>https://mahasamvad.in/154597/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : आरोग्यमंत्र्यांच्या कोल्हापुरातच 'सलमान'ची चर्चा, प्रशासकीय अधिकारीही 'लाभार्थी'</t>
+          <t>खासगी रुग्णालयांची नोंदणी आता ऑनलाईन, आरोग्य मंत्री प्रकाश आबिटकर यांची घोषणा</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/health-minister-prakash-abitkar-advises-citizens-to-consult-professionals-that-time-some-officials-visit-salmans-hair-trainer-to-treatment-hair-problem-as11-rg93</t>
+          <t>https://www.lokmat.com/kolhapur/registration-of-private-hospitals-now-online-health-minister-prakash-abitkar-announced-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pune GBS : पुण्यातील 'त्या' विहिरीमुळे पसरला गुईलेन बॅरे सिंड्रोम, आरोग्यमंत्र्यांनी दिली धक्कादायक माहिती</t>
+          <t>जिल्ह्याच्या सर्वांगिण विकासाचा संकल्प सर्वजण मिळून करू - पालकमंत्री प्रकाश आबिटकर यांचे जिल्हावासियांना आवाहन</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/gbs-patients-have-increased-due-to-the-contaminated-water-in-well-say-health-minister-prakash-abitkar-7575460</t>
+          <t>https://mahasamvad.in/175693/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>खासगी रुग्णालयांची नोंदणी आता ऑनलाईन, आरोग्य मंत्री प्रकाश आबिटकर यांची घोषणा</t>
+          <t>‘ईएसआयसी’ रुग्णालयात रुग्णसेवेच्या गुणवत्तेत वाढ करा – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/registration-of-private-hospitals-now-online-health-minister-prakash-abitkar-announced-a-a746/</t>
+          <t>https://www.mahasamvad.in/170012/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>कर्करोग प्रतिबंधासाठी जनजागृती गरजेची – मंत्री प्रकाश आबिटकर</t>
+          <t>पालकमंत्री आबिटकर यांच्यासमोर नवे आव्हान!</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154597/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-faces-new-challenge</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>जिल्ह्याच्या सर्वांगिण विकासाचा संकल्प सर्वजण मिळून करू - पालकमंत्री प्रकाश आबिटकर यांचे जिल्हावासियांना आवाहन</t>
+          <t>आरोग्य मंत्री प्रकाश आबिटकर म्हणाले; शाकाहारी- मांसाहारीपेक्षा देशी प्रेम महत्त्वाचे!</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175693/</t>
+          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>‘ईएसआयसी’ रुग्णालयात रुग्णसेवेच्या गुणवत्तेत वाढ करा – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : राष्‍ट्रीय आरोग्‍य अभियानच्‍या कर्मचारी, अधिकारी यांचा पगार लवकरच</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/170012/</t>
+          <t>https://www.esakal.com/pune/salaries-of-national-health-mission-employees-and-officers-to-be-disbursed-soon-prakash-abitkar-pjp78</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>पालकमंत्री आबिटकर यांच्यासमोर नवे आव्हान!</t>
+          <t>Prakash Abitkar : 'GBS आजारावर सर्वंकष उपाययोजना करा'; आरोग्यमंत्री आबिटकरांचे संबंधित प्रशासनाला महत्त्वपूर्ण निर्देश</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-faces-new-challenge</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/health-minister-prakash-abitkar-instructions-to-take-measures-regarding-gbs-disease-bam92</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री प्रकाश आबिटकर म्हणाले; शाकाहारी- मांसाहारीपेक्षा देशी प्रेम महत्त्वाचे!</t>
+          <t>GBS रुग्णांच्या उपचार करताना औषधांचा गैरवापर, जास्त पैसे पैसे घेतल्यास;आरोग्यमंत्री प्रकाश आबिटकर यांचा इशारा</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kalhapur-prakash-abitkar-calls-for-unity-in-celebrating-independence-day-with-diverse-event-over-veg-nonveg-debate-rds-00-5306948/</t>
+          <t>https://www.lokmat.com/pune/beware-if-you-are-robbed-health-minister-prakash-abitkar-warns-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर यांच्याकडून गुरुजनांना विधानसभेची हवाई सैर</t>
+          <t>Kolhapur Shivsena: जिल्ह्यातील ठाकरे गट कोणाचाही दावणीला बांधू देणार नाही जुगार अड्डे</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-minister-prakash-abitkar-takes-senior-citizens-on-air-trip-unique-guru-purnima-initiative-vsd-99-5224693/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : राष्‍ट्रीय आरोग्‍य अभियानच्‍या कर्मचारी, अधिकारी यांचा पगार लवकरच</t>
+          <t>‘जीबीएस’ वर उपचारांविषयी सर्वंकष उपाययोजना करा – आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/salaries-of-national-health-mission-employees-and-officers-to-be-disbursed-soon-prakash-abitkar-pjp78</t>
+          <t>https://mahasamvad.in/153447/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>‘जीबीएस’ वर उपचारांविषयी सर्वंकष उपाययोजना करा – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>अपघातग्रस्तांवर एक लाखांपर्यंत कॅशलेस उपचार करा; आरोग्यमंत्री आबिटकर यांचे निर्देश</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153447/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/cashless-treatment-up-to-one-lakh-for-accident-victims-health-minister-directive</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GBS रुग्णांच्या उपचार करताना औषधांचा गैरवापर, जास्त पैसे पैसे घेतल्यास;आरोग्यमंत्री प्रकाश आबिटकर यांचा इशारा</t>
+          <t>राज्यभरात कोरोना रुग्णसंख्येत वाढ; आरोग्य मंत्री प्रकाश आबिटकरांनी जनतेला केलं 'हे' आवाहन - PRAKASHRAO ABITKAR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/beware-if-you-are-robbed-health-minister-prakash-abitkar-warns-a-a1008/</t>
+          <t>https://www.etvbharat.com/mr/!state/prakashrao-abitkar-reaction-on-maharashtra-corona-patient-shaktipeeth-highway-almatti-dam-water-chandrahar-patil-maharashtra-news-mhs25060905593</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री प्रकाश आबिटकर, राज्यमंत्री मेघना बोर्डीकर यांचा तामिळनाडू अभ्यास दौरा</t>
+          <t>Coronavirus : सिंगापूरनंतर राज्यात कोरोनाचा धोका वाढला? आरोग्यमंत्री म्हणाले...</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157284/</t>
+          <t>https://saamtv.esakal.com/video/maharashtra-health-minister-on-corona-variants-situation-and-government-measures-nck90</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Kolhapur Shivsena: जिल्ह्यातील ठाकरे गट कोणाचाही दावणीला बांधू देणार नाही जुगार अड्डे</t>
+          <t>आरोग्य विभागातील डॉक्टरांची रिक्त पदे तातडीने भरा- आरोग्यमंत्री</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/ravikiran-ingavale-says-those-who-run-gambling-dens-are-seen-with-the-guardian-minister-prakash-abitkar-and-cm-shinde-1367502</t>
+          <t>https://www.loksatta.com/mumbai/fill-vacant-posts-of-doctors-in-health-department-immediately-says-health-minister-prakash-abitkar-mumbai-print-news-mrj-95-4857638/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>अपघातग्रस्तांवर एक लाखांपर्यंत कॅशलेस उपचार करा; आरोग्यमंत्री आबिटकर यांचे निर्देश</t>
+          <t>Kolhapur Politics : मुश्रीफांना आबिटकरांचे वावडे? 'त्या' अहवालात स्थान देणं टाळलं; पालकमंत्री पदावरून नाराजी कायम</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/cashless-treatment-up-to-one-lakh-for-accident-victims-health-minister-directive</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-hasan-mushrif-prakash-abitkar-guardian-minister-rift-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>राज्यातील ग्रामीण रुग्णालय, प्राथमिक आरोग्य केंद्र इ.आरोग्य संस्थामध्ये दोन हजार पदनिर्मितीसाठी शासनाची मान्यता -आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>kolhapur | त्रुटीच इतक्या काढता, प्रस्ताव येणार कसे?</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/156822/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-prakash-abitkar-pulls-up-forest-department-officials-ap84</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>आरोग्य विभागातील डॉक्टरांची रिक्त पदे तातडीने भरा- आरोग्यमंत्री</t>
+          <t>आरोग्यमंत्री प्रकाश आबिटकर, राज्यमंत्री मेघना बोर्डीकर यांचा तामिळनाडू अभ्यास दौरा</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fill-vacant-posts-of-doctors-in-health-department-immediately-says-health-minister-prakash-abitkar-mumbai-print-news-mrj-95-4857638/</t>
+          <t>https://mahasamvad.in/157284/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>राज्यभरात कोरोना रुग्णसंख्येत वाढ; आरोग्य मंत्री प्रकाश आबिटकरांनी जनतेला केलं 'हे' आवाहन - PRAKASHRAO ABITKAR</t>
+          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/prakashrao-abitkar-reaction-on-maharashtra-corona-patient-shaktipeeth-highway-almatti-dam-water-chandrahar-patil-maharashtra-news-mhs25060905593</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kolhapur | त्रुटीच इतक्या काढता, प्रस्ताव येणार कसे?</t>
+          <t>आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरू करणार, मंत्री प्रकाश आबिटकर यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-prakash-abitkar-pulls-up-forest-department-officials-ap84</t>
+          <t>https://www.lokmat.com/kolhapur/awards-to-be-launched-for-all-departments-in-the-health-sector-health-minister-prakash-abitkar-announced-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : मुश्रीफांना आबिटकरांचे वावडे? 'त्या' अहवालात स्थान देणं टाळलं; पालकमंत्री पदावरून नाराजी कायम</t>
+          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-hasan-mushrif-prakash-abitkar-guardian-minister-rift-jap93-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/abittkar-announced-guardian-minister-celebration-in-bhudargad</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>हत्तीरोग मुक्त महाराष्ट्रासाठी औषधोपचार मोहिमेला सहकार्य करा – मंत्री प्रकाश आबिटकर</t>
+          <t>राज्यातील ग्रामीण रुग्णालय, प्राथमिक आरोग्य केंद्र इ.आरोग्य संस्थामध्ये दोन हजार पदनिर्मितीसाठी शासनाची मान्यता -आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/157564/</t>
+          <t>https://mahasamvad.in/156822/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>आरोग्य क्षेत्रातील सर्वच विभागांसाठी पुरस्कार सुरू करणार, मंत्री प्रकाश आबिटकर यांनी केली घोषणा</t>
+          <t>अलमट्टी, हिप्परगीच्या विसर्गावर लक्ष ठेवा, कोल्हापूरचे पालकमंत्री प्रकाश आबिटकर यांची सूचना</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/awards-to-be-launched-for-all-departments-in-the-health-sector-health-minister-prakash-abitkar-announced-a-a746/</t>
+          <t>https://www.lokmat.com/kolhapur/keep-an-eye-on-the-discharge-of-almatti-hippargi-dams-kolhapur-guardian-minister-prakash-abitkar-advice-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Coronavirus : सिंगापूरनंतर राज्यात कोरोनाचा धोका वाढला? आरोग्यमंत्री म्हणाले...</t>
+          <t>राज्याच्या आरोग्य धोरणाबाबतचा प्रस्ताव तातडीने सादर करा – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/maharashtra-health-minister-on-corona-variants-situation-and-government-measures-nck90</t>
+          <t>https://mahasamvad.in/166367/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी</t>
+          <t>मस्तवाल दीनानाथ मंगेशकर हॉस्पिटलमध्ये आमदाराच्या पीएच्या पत्नीचा जीव जाताच</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-ranks-first-in-organ-donation-guardian-minister-prakash-abitkar-also-filled-the-form-said-egistering-the-wish-to-donate-organs-should-be-a-responsibility-1377281</t>
+          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cashless Treatment : अपघातग्रस्तांना १ लाख रुपयांपर्यंत कॅशलेस उपचार मिळणार, राज्य सरकारचा मोठा निर्णय</t>
+          <t>Prakashrao Abitkar : गर्भलिंग निदान सुरु असल्याची टीप देणाऱ्या खबरींना एका लाखाचं बक्षीस</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/accident-victims-will-get-cashless-treatment-up-to-rs-1-lakh-big-decision-of-the-state-government-prakash-abitkar-gkt-96-5028935/</t>
+          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ना.आबिटकर यांचे पालकमंत्रीपदी नाव जाहीर होताच भुदरगड तालुक्यात जल्लोष</t>
+          <t>‘अवयवदान’ ही मानवतेची व सामाजिक बदलाची चळवळ व्हावी – आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/abittkar-announced-guardian-minister-celebration-in-bhudargad</t>
+          <t>https://www.mahasamvad.in/167252/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>अलमट्टी, हिप्परगीच्या विसर्गावर लक्ष ठेवा, कोल्हापूरचे पालकमंत्री प्रकाश आबिटकर यांची सूचना</t>
+          <t>हत्तीरोग मुक्त महाराष्ट्रासाठी औषधोपचार मोहिमेला सहकार्य करा – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/keep-an-eye-on-the-discharge-of-almatti-hippargi-dams-kolhapur-guardian-minister-prakash-abitkar-advice-a-a746/</t>
+          <t>https://www.mahasamvad.in/157564/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>महादेवी हत्ती परत येणार?, वनतारा सीईओंसोबतच्या बैठकीतून मठाचे महास्वामी बाहेर पडले, नेमकं काय घडलं.. वाचा</t>
+          <t>कामचुकारपणा आला अंगलट! आरोग्यमंत्र्यांचा दणका, हतरू आरोग्य केंद्रातील डॉक्टरसह चौघे निलंबित</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/now-a-legal-battle-for-the-mahadevi-elephant-of-nandani-math-guardian-minister-prakash-abitkar-gave-information-after-a-discussion-between-the-ceo-of-vanatara-and-the-mathadhis-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-primary-health-center-doctor-and-four-others-suspended</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Prakashrao Abitkar : गर्भलिंग निदान सुरु असल्याची टीप देणाऱ्या खबरींना एका लाखाचं बक्षीस</t>
+          <t>Mahayuti Controversy: कोल्हापुरात 10 आमदार असलेल्या महायुतीत वादाचा भडका; आबिटकरांनाच विरोध,भाजपनं घातला थेट मुद्द्यालाच हात</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/prakashrao-abitkar-says-a-reward-of-one-lakh-will-be-given-to-informers-who-tip-off-that-pregnancy-diagnosis-is-in-progress-a-big-announcement-by-the-health-minister-prakashrao-abitkar-in-kolhapur-maharashtra-politics-marathi-news-1340501</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-dispute-over-kolhapur-district-committee-bjp-ncp-vs-prakash-abitkar-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>राज्याच्या आरोग्य धोरणाबाबतचा प्रस्ताव तातडीने सादर करा – मंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्यमंत्र्यांसमोरच दोन वैद्यकीय अधिकाऱ्यांमध्ये वाद: प्रकाश आबिटकरांनी दिली ईएसआयसी रुग्णालयाला अचानक भेट...</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166367/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/maharashtra-health-minister-prakash-abitkar-inspects-esic-hospital-kolhapur-135283124.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>मस्तवाल दीनानाथ मंगेशकर हॉस्पिटलमध्ये आमदाराच्या पीएच्या पत्नीचा जीव जाताच</t>
+          <t>Cashless Treatment in Hospital Maharashtra मोठी बातमी : अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार,</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-tanisha-bhise-death-case-four-member-committee-to-investigate-dinanath-hospital-prakash-abitkar-madhuri-misal-decision-maharashtra-marathi-news-1352646</t>
+          <t>https://marathi.abplive.com/news/maharashtra/cashless-treatment-in-hospital-maharashtra-cashless-treatment-up-to-rs-1-lakh-for-accident-victims-big-decision-of-the-health-department-of-maharashtra-1354955</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>‘अवयवदान’ ही मानवतेची व सामाजिक बदलाची चळवळ व्हावी – आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>कोल्हापूरचा क्रीडा विकास आराखडा तयार करावा – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/167252/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-instructions-phm-00-5256184/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kolhapur News : अधिकार्‍यांनी नावीन्यतेसह गुणवत्तापूर्ण कामे करावीत</t>
+          <t>कोल्हापूर प्राधिकरणातील अधिकाऱ्यांची पेन्शन थांबवा, पालकमंत्र्यांच्या सूचना</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-all-departments-in-zilla-parishad-ap84</t>
+          <t>https://www.lokmat.com/kolhapur/stop-the-pension-of-kolhapur-authority-officials-instructions-from-the-guardian-minister-prakash-abitkar-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mahayuti Controversy: कोल्हापुरात 10 आमदार असलेल्या महायुतीत वादाचा भडका; आबिटकरांनाच विरोध,भाजपनं घातला थेट मुद्द्यालाच हात</t>
+          <t>दीनानाथ रुग्णालय अन् 10 लाखांच्या मागणी प्रकरणावर आरोग्य मंत्र्यांची पहिली प्रतिक्रिया, म्हणाले…</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-dispute-over-kolhapur-district-committee-bjp-ncp-vs-prakash-abitkar-dk88-rg93</t>
+          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-ordered-to-probe-and-inquiry-in-deenanath-mangeshkar-hospital-case-1378715.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>कामचुकारपणा आला अंगलट! आरोग्यमंत्र्यांचा दणका, हतरू आरोग्य केंद्रातील डॉक्टरसह चौघे निलंबित</t>
+          <t>तामिळनाडूच्या धर्तीवर सरकारी रुग्णालयांना मिळणार महात्मा फुले योजनेचा ५० टक्के निधी; राज्य सरकारचा महत्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-primary-health-center-doctor-and-four-others-suspended</t>
+          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-gave-an-explanation-in-the-legislative-council-phm-00-5212114/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Cashless Treatment in Hospital Maharashtra मोठी बातमी : अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार,</t>
+          <t>राज्य कामगार विमा योजनेचा लाभ तळागाळातील गरजू कामगारांपर्यंत पोहोचवावा -सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/cashless-treatment-in-hospital-maharashtra-cashless-treatment-up-to-rs-1-lakh-for-accident-victims-big-decision-of-the-health-department-of-maharashtra-1354955</t>
+          <t>https://mahasamvad.in/173263/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>तामिळनाडूच्या धर्तीवर सरकारी रुग्णालयांना मिळणार महात्मा फुले योजनेचा ५० टक्के निधी; राज्य सरकारचा महत्वपूर्ण निर्णय</t>
+          <t>Shahu Maharaj Jayanti: शाहू महाराज यांचे काम देशाला दिशा देणारे: प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/health-minister-prakash-abitkar-gave-an-explanation-in-the-legislative-council-phm-00-5212114/</t>
+          <t>https://agrowon.esakal.com/agro-special/shahu-maharajs-work-gave-direction-to-the-country-prakash-abitkar-prakash-abitkar</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्र्यांसमोरच दोन वैद्यकीय अधिकाऱ्यांमध्ये वाद: प्रकाश आबिटकरांनी दिली ईएसआयसी रुग्णालयाला अचानक भेट...</t>
+          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी सुद्धा फॉर्म भरला; म्हणाले, अवयवदान इच्छा नोंदवणे जबाबदारी व्हायला हवी</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/maharashtra-health-minister-prakash-abitkar-inspects-esic-hospital-kolhapur-135283124.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>दीनानाथ रुग्णालय अन् 10 लाखांच्या मागणी प्रकरणावर आरोग्य मंत्र्यांची पहिली प्रतिक्रिया, म्हणाले…</t>
+          <t>Kolhapur Politics : जुन्या पटावरची नवी समीकरणे, मंत्री आबीटकरांनी किमया केली, दोन राजकीय शत्रू आले एकत्र</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-ordered-to-probe-and-inquiry-in-deenanath-mangeshkar-hospital-case-1378715.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/friendship-buzz-between-congress-leader-sharangdhar-deshmukh-and-bjp-mp-dhananjay-mahadik-at-carrom-event-inaugurated-by-minister-prakash-abitkar-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेचा लाभ तळागाळातील गरजू कामगारांपर्यंत पोहोचवावा -सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>कोल्हापूर जिल्ह्यात क्रीडा क्षेत्रात मोठा वाव, क्रीडा संकुलासाठी अतिरिक्त निधी मिळावा म्हणून प्रयत्न करणार - पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173263/</t>
+          <t>https://mahasamvad.in/157463/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>कोल्हापूरचा क्रीडा विकास आराखडा तयार करावा – प्रकाश आबिटकर</t>
+          <t>Prakash Abitkar : डॉक्टरांनी आरोग्य सेवा नाकारू नये; तनिषा भिसेच्या मृत्यूवर काय म्हणाले आरोग्यमंत्री?</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-guardian-minister-prakash-abitkar-gave-instructions-phm-00-5256184/</t>
+          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Shahu Maharaj Jayanti: शाहू महाराज यांचे काम देशाला दिशा देणारे: प्रकाश आबिटकर</t>
+          <t>Maharashtra | रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात ‘नो शॉर्टेज, नो वेस्टेज’ धोरण - आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/shahu-maharajs-work-gave-direction-to-the-country-prakash-abitkar-prakash-abitkar</t>
+          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>अवयवदानात कोल्हापूर राज्यात प्रथम क्रमांकावर, पालकमंत्री प्रकाश आबिटकरांनी सुद्धा फॉर्म भरला; म्हणाले, अवयवदान इच्छा नोंदवणे जबाबदारी व्हायला हवी</t>
+          <t>राज्याच्या प्रगतीत कोल्हापूर जिल्हा अग्रभागी राहण्यासाठी सर्वजण सज्ज होऊया -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%A4-%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE-%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%95-%E0%A4%B5%E0%A4%B0-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%A6%E0%A5%8D%E0%A4%A7-%E0%A4%AB-%E0%A4%B0%E0%A5%8D%E0%A4%AE-%E0%A4%AD%E0%A4%B0%E0%A4%B2-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B5%E0%A4%AF%E0%A4%B5%E0%A4%A6-%E0%A4%A8-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%B5%E0%A4%A3%E0%A5%87-%E0%A4%9C%E0%A4%AC-%E0%A4%AC%E0%A4%A6-%E0%A4%B0-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5/ar-AA1KzWZR</t>
+          <t>https://mahasamvad.in/164322/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : जुन्या पटावरची नवी समीकरणे, मंत्री आबीटकरांनी किमया केली, दोन राजकीय शत्रू आले एकत्र</t>
+          <t>आरोग्य शिबिरातून मोफत अत्याधुनिक वैद्यकीय सेवा उपलब्ध करून देणार - पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/friendship-buzz-between-congress-leader-sharangdhar-deshmukh-and-bjp-mp-dhananjay-mahadik-at-carrom-event-inaugurated-by-minister-prakash-abitkar-as11-rg93</t>
+          <t>https://mahasamvad.in/173559/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्यात क्रीडा क्षेत्रात मोठा वाव, क्रीडा संकुलासाठी अतिरिक्त निधी मिळावा म्हणून प्रयत्न करणार - पालकमंत्री प्रकाश आबिटकर</t>
+          <t>महादेवी हत्तीणीच्या परतीचा मार्ग मोकळा? जनभावना आणि वनताराच्या भूमिकेमुळे परतीची आशा</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157463/</t>
+          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : डॉक्टरांनी आरोग्य सेवा नाकारू नये; तनिषा भिसेच्या मृत्यूवर काय म्हणाले आरोग्यमंत्री?</t>
+          <t>तानाजी सावंतांच्या कार्यकाळातील ३२०० कोटींचे टेंडर फडणवीसांकडून स्थगित, आरोग्यमंत्री म्हणाले…</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/health-minister-prakash-abitkar-clarified-that-doctors-should-not-refuse-health-services/871013/</t>
+          <t>https://www.lokmat.com/pune/fadnavis-cancels-3200-crore-tender-during-tanaji-sawant-tenure-prakash-abitkar-reacts-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Maharashtra | रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात ‘नो शॉर्टेज, नो वेस्टेज’ धोरण - आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>कुष्ठरोग निर्मूलनाच्या प्रभावी अंमलबजावणीसाठी राज्यस्तरीय समिती स्थापन करणार -सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/maharashtra-or-no-shortage-no-waste-policy-in-the-state-for-planned-management-of-blood-collection-health-minister/</t>
+          <t>https://mahasamvad.in/172391/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>राज्याच्या प्रगतीत कोल्हापूर जिल्हा अग्रभागी राहण्यासाठी सर्वजण सज्ज होऊया -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>... तर मंगेशकर रुग्णालयावर कठोर कारवाई करणार; आरोग्यमंत्र्यांसह जिल्हाधिकारी नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164322/</t>
+          <t>https://www.lokmat.com/pune/strict-action-will-be-taken-against-mangeshkar-hospital-health-minister-and-the-district-collector-reaction-a-a992/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>आरोग्य शिबिरातून मोफत अत्याधुनिक वैद्यकीय सेवा उपलब्ध करून देणार - पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Eknath Shinde's grand welcome : उपमुख्यमंत्री शिंदेंचं कोल्हापुरात ग्रँड वेलकम; आबिटकरांनी जाण ठेवत, स्वागतात सोडली नाही कुठलीच कसर!</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173559/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prakash-abitkar-grand-welcome-eknath-shinde-kolhapur-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>तानाजी सावंतांच्या कार्यकाळातील ३२०० कोटींचे टेंडर फडणवीसांकडून स्थगित, आरोग्यमंत्री म्हणाले…</t>
+          <t>अवयवदान मोठं पुण्याईच काम आहे… – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/fadnavis-cancels-3200-crore-tender-during-tanaji-sawant-tenure-prakash-abitkar-reacts-a-a1008/</t>
+          <t>https://mahasamvad.in/174644/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीणीच्या परतीचा मार्ग मोकळा? जनभावना आणि वनताराच्या भूमिकेमुळे परतीची आशा</t>
+          <t>बचत गटांच्या चळवळीतून महिलांना आर्थिक सक्षम आणि साक्षर करूया – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/vantara-ready-to-return-mahadevi-elephant-if-court-orders-guardian-minister-prakash-abitkar-maharashtra-news-mhs25080105913</t>
+          <t>https://mahasamvad.in/166403/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>कुष्ठरोग निर्मूलनाच्या प्रभावी अंमलबजावणीसाठी राज्यस्तरीय समिती स्थापन करणार -सार्वजनिक आरोग्यमंत्री प्रकाश आबिटकर</t>
+          <t>इंदिरा गांधी रुग्णालयात सुविधा पुरवणार – प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172391/</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-assures-new-facilities-at-indira-gandhi-hospital-ocd-94-5247730/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>अवयवदान मोठं पुण्याईच काम आहे… – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>महात्मा गांधी स्मारक रुग्णालयाला सर्वोत्तम कामगार रुग्णालय बनविणार – मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174644/</t>
+          <t>https://mahasamvad.in/169637/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Eknath Shinde's grand welcome : उपमुख्यमंत्री शिंदेंचं कोल्हापुरात ग्रँड वेलकम; आबिटकरांनी जाण ठेवत, स्वागतात सोडली नाही कुठलीच कसर!</t>
+          <t>Kolhapur : सतर्क राहा; अलमट्टी, हिप्परगी विसर्गाबाबत समन्वय ठेवा</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prakash-abitkar-grand-welcome-eknath-shinde-kolhapur-msr87-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-meeting-at-district-collector-office-dc95</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>बचत गटांच्या चळवळीतून महिलांना आर्थिक सक्षम आणि साक्षर करूया – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Politics : ठरलं! महापालिका निवडणुकीत शिंदेंच्या शिवसेनेची सूत्रे अबिटकरांच्या हाती, तर राष्ट्रवादीची धुरा एकटे मुश्रीफ सांभाळणार</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/166403/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-ichalkaranji-municipal-election-political-strategies-party-alliance-hasan-mushrif-prakash-abitkar-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Kolhapur : सतर्क राहा; अलमट्टी, हिप्परगी विसर्गाबाबत समन्वय ठेवा</t>
+          <t>Prakash Abitkar: आरोग्य मंत्र्यांच्या जिल्ह्याचे आरोग्य बिघडले, काय आहे परिस्थिती?</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-meeting-at-district-collector-office-dc95</t>
+          <t>https://www.tarunbharat.com/prakash-abitkar-cpr-gaganbawda-dead-7-year-old-baby-pregnancy-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : ठरलं! महापालिका निवडणुकीत शिंदेंच्या शिवसेनेची सूत्रे अबिटकरांच्या हाती, तर राष्ट्रवादीची धुरा एकटे मुश्रीफ सांभाळणार</t>
+          <t>खंडपीठासाठी कालबद्ध कार्यक्रम; 15 मार्चपूर्वी मुख्यमंत्र्यांसमवेत बैठक</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-ichalkaranji-municipal-election-political-strategies-party-alliance-hasan-mushrif-prakash-abitkar-jap93-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-said-about-the-kolhapur-bench</t>
         </is>
       </c>
     </row>
@@ -2867,108 +2867,108 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Nandani Mahadevi Elephant : वनतारा सकारात्मक! नांदणी मठाची 'महादेवी' परत येण्याची शक्यता, पालकमंत्र्यांनी सांगितलं बैठकीत काय घडलं</t>
+          <t>सार्वजनिक बांधकाम विभागांतर्गतची कामे दर्जेदार करा -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
+          <t>https://mahasamvad.in/158717/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>सार्वजनिक बांधकाम विभागांतर्गतची कामे दर्जेदार करा -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Corona Cases In India : देशात कोरोनाची रुग्ण संख्या 257वर, तर राज्यात 53 कोरोना बाधित</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158717/</t>
+          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Pune News: प्रसुतीवेळी महिलेचा मृत्यू प्रकरणात आरोग्य मंत्र्यांचे कारवाईचे आदेश</t>
+          <t>Prakash Abitkar : काेल्हापूर शहर हद्दवाढीची प्रक्रिया सुरू: प्रकाश आबिटकर ; मुख्यमंत्री, उपमुख्यमंत्री सकारात्मक</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-health-minister-prakashrao-abitkar-orders-action-in-case-of-womans-death-during-childbirth-police-will-conduct-investigation-today-will-examine-cctv-along-with-statements-from-nurses-and-doctors-1352627</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-city-expansion-process-begins-cm-and-deputy-cm-supportive-abitkar-sdj87</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : काेल्हापूर शहर हद्दवाढीची प्रक्रिया सुरू: प्रकाश आबिटकर ; मुख्यमंत्री, उपमुख्यमंत्री सकारात्मक</t>
+          <t>अंधेरी येथील कामगार रुग्णालयातील आंतररुग्ण सुविधा नागरिकांसाठी उपलब्ध कराव्यात - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-city-expansion-process-begins-cm-and-deputy-cm-supportive-abitkar-sdj87</t>
+          <t>https://mahasamvad.in/168735/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Corona Cases In India : देशात कोरोनाची रुग्ण संख्या 257वर, तर राज्यात 53 कोरोना बाधित</t>
+          <t>भुदरगड तालुक्यातील सात धबधबे म्हणजे निसर्गात लपलेला अद्भुत खजिना – पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/covid-cases-rise-singapore-hongkong-india-alert-mumbai-health-minister-prakash-abitkar-statement-1408354.html</t>
+          <t>https://mahasamvad.in/172859/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>अंधेरी येथील कामगार रुग्णालयातील आंतररुग्ण सुविधा नागरिकांसाठी उपलब्ध कराव्यात - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>Mahayuti News : 'स्थानिक'च्या निवडणुकीआधी महायुतीत नियुक्त्यांसाठी बिगफाईट; नेत्यांची डोकेदुखी वाढली...</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168735/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-leaders-lobby-for-kolhapur-dpdc-appointments-political-pressure-maharashtra-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>भुदरगड तालुक्यातील सात धबधबे म्हणजे निसर्गात लपलेला अद्भुत खजिना – पालकमंत्री प्रकाश आबिटकर</t>
+          <t>राष्ट्रीय आरोग्य अभियानाअंतर्गत कंत्राटी कर्मचाऱ्यांना नियमित करण्यासाठी कार्यवाही करा – ग्रामविकास मंत्री जयकुमार गोरे</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172859/</t>
+          <t>https://mahasamvad.in/174852/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mahayuti News : 'स्थानिक'च्या निवडणुकीआधी महायुतीत नियुक्त्यांसाठी बिगफाईट; नेत्यांची डोकेदुखी वाढली...</t>
+          <t>५० हजार हक्काची घरे देण्यासाठी मिशन मोडवर काम करा -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mahayuti-leaders-lobby-for-kolhapur-dpdc-appointments-political-pressure-maharashtra-rm82-rg93</t>
+          <t>https://mahasamvad.in/154283/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>राष्ट्रीय आरोग्य अभियानाअंतर्गत कंत्राटी कर्मचाऱ्यांना नियमित करण्यासाठी कार्यवाही करा – ग्रामविकास मंत्री जयकुमार गोरे</t>
+          <t>Nandani Mahadevi Elephant : वनतारा सकारात्मक! नांदणी मठाची 'महादेवी' परत येण्याची शक्यता, पालकमंत्र्यांनी सांगितलं बैठकीत काय घडलं</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174852/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/nandani-mahadevi-elephant-stay-in-vantara-to-be-reconsidered-by-high-level-meeting-here-is-what-happened/articleshow/123045763.cms</t>
         </is>
       </c>
     </row>
@@ -2987,60 +2987,60 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>५० हजार हक्काची घरे देण्यासाठी मिशन मोडवर काम करा -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>मावळ तालुक्यातील आरोग्य संस्थांना आवश्यक सुविधा द्या - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154283/</t>
+          <t>https://mahasamvad.in/174701/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>आरोग्यमंत्री आबिटकर यांनी घेतले श्री विठ्ठल रुक्मिणी मातेचे दर्शन; VIP ट्रिटमेंट टाळत पायी जाणं केलं पसंत</t>
+          <t>रायगड जिल्ह्यातील नागरिकांना उत्तम आरोग्य सुविधा देण्यासाठी शासन कटीबद्ध - मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/health-minister-prakash-abitkar-took-darshan-of-shri-vitthal-rukmini-mata-temple-899077.html</t>
+          <t>https://mahasamvad.in/158289/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>मावळ तालुक्यातील आरोग्य संस्थांना आवश्यक सुविधा द्या - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>Mahadevi Elephant : महादेवी हत्तीबाबत जिल्हाधिकारी कार्यालयात झालेल्या बैठकीवर पालकमंत्री आबिटकरांनी दिली सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174701/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-abitkar-shares-key-details-after-kolhapur-collector-office-meeting-on-mahadevi-elephant-issue-following-supreme-courts-controversial-order-srs92</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>रायगड जिल्ह्यातील नागरिकांना उत्तम आरोग्य सुविधा देण्यासाठी शासन कटीबद्ध - मंत्री प्रकाश आबिटकर</t>
+          <t>आरोग्यमंत्री आबिटकर यांनी घेतले श्री विठ्ठल रुक्मिणी मातेचे दर्शन; VIP ट्रिटमेंट टाळत पायी जाणं केलं पसंत</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158289/</t>
+          <t>https://www.navarashtra.com/maharashtra/health-minister-prakash-abitkar-took-darshan-of-shri-vitthal-rukmini-mata-temple-899077.html</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant : महादेवी हत्तीबाबत जिल्हाधिकारी कार्यालयात झालेल्या बैठकीवर पालकमंत्री आबिटकरांनी दिली सविस्तर माहिती</t>
+          <t>रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात 'नो शॉर्टेज, नो वेस्टेज' धोरण- मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-abitkar-shares-key-details-after-kolhapur-collector-office-meeting-on-mahadevi-elephant-issue-following-supreme-courts-controversial-order-srs92</t>
+          <t>https://mahasamvad.in/168889/</t>
         </is>
       </c>
     </row>
@@ -3059,2916 +3059,2916 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>रक्तसंकलनाचे नियोजनबद्ध व्यवस्थापनासाठी राज्यात 'नो शॉर्टेज, नो वेस्टेज' धोरण- मंत्री प्रकाश आबिटकर</t>
+          <t>सुपर स्पेशालिटीतील डॉक्टरांचे मानधन, ऑपरेशनचा निधी लवकरच मिळणार: आमदार खोडके यांनी उपस्थित केला प्रश्न; निध...</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168889/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/amravati/news/funds-for-super-specialty-doctors-honorarium-and-operations-will-be-available-soon-mla-khodke-raised-the-question-funds-will-be-provided-health-minister-abitkar-135398260.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंचसाठी लगीनघाई; पुढील तीन दिवसात इमारतीचे हस्तांतरण, पालकमंत्र्यांकडून कामकाजाची पाहणी</t>
+          <t>kolhapur |अत्याधुनिक सक्शन कम जेटिंग वाहनाचे पालकमंत्री आबिटकर यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-inaugurates-advanced-suction-cum-jetting-vehicle-ap84</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Rural Housing Scheme : घरकुलांच्या उद्दिष्टपूर्तीत दिरंगाई नको ः प्रकाश आबिटकर</t>
+          <t>चांगल्या कामाचा लोक सन्मान करतात : पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/no-delays-tolerated-in-housing-schemes-strict-action-warns-guardian-minister-mj18</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/rajarshi-shahu-awards-distributed-by-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>सुपर स्पेशालिटीतील डॉक्टरांचे मानधन, ऑपरेशनचा निधी लवकरच मिळणार: आमदार खोडके यांनी उपस्थित केला प्रश्न; निध...</t>
+          <t>Chandrahar Patil: '...म्हणून चंद्रहार पाटलांनी ठाकरेंची साथ सोडली अन् शिंदेंच्या शिवसेनेत प्रवेश केला!'; 'या' मंत्र्यांचा मोठा दावा</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/amravati/news/funds-for-super-specialty-doctors-honorarium-and-operations-will-be-available-soon-mla-khodke-raised-the-question-funds-will-be-provided-health-minister-abitkar-135398260.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrahar-patil-switch-to-uddhav-thakceray-party-and-joining-eknath-shinde-shiv-sena-prakash-abitkar-big-claims-dk88</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kolhapur |अत्याधुनिक सक्शन कम जेटिंग वाहनाचे पालकमंत्री आबिटकर यांच्या हस्ते लोकार्पण</t>
+          <t>बांधकाम पूर्ण झालेली रुग्णालये कार्यान्वित करून जनतेच्या सेवेत आणावीत- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-inaugurates-advanced-suction-cum-jetting-vehicle-ap84</t>
+          <t>https://mahasamvad.in/168802/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>इंदिरा गांधी रुग्णालयात सुविधा पुरवणार – प्रकाश आबिटकर</t>
+          <t>अरुण सरनाईक यांचा कलाविष्कार सदैव स्मरणात राहणारा : प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-assures-new-facilities-at-indira-gandhi-hospital-ocd-94-5247730/</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-remembers-arun-sarnaiak-for-his-timeless-art-ocd-94-5177138/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>चांगल्या कामाचा लोक सन्मान करतात : पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur Circuit Bench: कोल्हापूर सर्किट बेंचसाठी लगीनघाई; पुढील तीन दिवसात इमारतीचे हस्तांतरण, पालकमंत्र्यांकडून कामकाजाची पाहणी</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/rajarshi-shahu-awards-distributed-by-zilla-parishad-ap84</t>
+          <t>https://marathi.abplive.com/photo-gallery/news/kolhapur-kolhapur-circuit-bench-building-to-be-transferred-in-next-three-days-guardian-minister-prakash-abitkar-to-inspect-work-1375914</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>बांधकाम पूर्ण झालेली रुग्णालये कार्यान्वित करून जनतेच्या सेवेत आणावीत- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Mahadevi Elephant: 'माधुरी' लवकरच परतणार? नेमके काय म्हणाले पालकमंत्री प्रकाश आबिटकर? वाचाच...</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/168802/</t>
+          <t>https://www.navarashtra.com/maharashtra/minister-prakash-abitkar-said-about-madhuri-mahadevi-elepahnt-nandni-math-vantara-947644.html</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Chandrahar Patil: '...म्हणून चंद्रहार पाटलांनी ठाकरेंची साथ सोडली अन् शिंदेंच्या शिवसेनेत प्रवेश केला!'; 'या' मंत्र्यांचा मोठा दावा</t>
+          <t>अनावश्यक गर्भाशय शस्त्रक्रिया करणाऱ्यांची गय करणार नाही, आरोग्य मंत्री प्रकाश आबिटकर यांचा इशारा</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrahar-patil-switch-to-uddhav-thakceray-party-and-joining-eknath-shinde-shiv-sena-prakash-abitkar-big-claims-dk88</t>
+          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>अरुण सरनाईक यांचा कलाविष्कार सदैव स्मरणात राहणारा : प्रकाश आबिटकर</t>
+          <t>अवयवदान इच्छा नोंदवणे ही एक जबाबदारी बनायला हवी - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री तथा पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-prakash-abitkar-remembers-arun-sarnaiak-for-his-timeless-art-ocd-94-5177138/</t>
+          <t>https://mahasamvad.in/175714/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant: 'माधुरी' लवकरच परतणार? नेमके काय म्हणाले पालकमंत्री प्रकाश आबिटकर? वाचाच...</t>
+          <t>Kolhapur Politics : 'खंडपीठ'साठी माणिक पाटलांचं आंदोलन; समजुतीसाठी भाजप अन् शिवसेनेचा पुढाकार, तर राष्ट्रवादी...</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/minister-prakash-abitkar-said-about-madhuri-mahadevi-elepahnt-nandni-math-vantara-947644.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-manik-patil-chuyekar-agitation-for-bench-court-was-stopped-in-the-presence-of-mp-dhananjay-mahadik-and-minister-prakashrao-abitkar-pp82-rg93</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>अनावश्यक गर्भाशय शस्त्रक्रिया करणाऱ्यांची गय करणार नाही, आरोग्य मंत्री प्रकाश आबिटकर यांचा इशारा</t>
+          <t>कोल्हापूर खंडपीठ: १५ दिवसांत मुख्यमंत्र्यांसोबत भेट, पालकमंत्री आबिटकर यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/strict-action-against-illegal-hysterectomy-warns-health-minister-mumbai-print-news-ocd-94-5149349/</t>
+          <t>https://www.lokmat.com/kolhapur/meeting-with-cm-in-15-days-for-kolhapur-bench-guardian-minister-prakash-abitkar-assurance-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>अवयवदान इच्छा नोंदवणे ही एक जबाबदारी बनायला हवी - सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री तथा पालकमंत्री प्रकाश आबिटकर</t>
+          <t>Rural Housing Scheme : घरकुलांच्या उद्दिष्टपूर्तीत दिरंगाई नको ः प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175714/</t>
+          <t>https://agrowon.esakal.com/agro-special/no-delays-tolerated-in-housing-schemes-strict-action-warns-guardian-minister-mj18</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>कोल्हापूर खंडपीठ: १५ दिवसांत मुख्यमंत्र्यांसोबत भेट, पालकमंत्री आबिटकर यांचे आश्वासन</t>
+          <t>अवयवदान पंधरवड्यास सुरुवात; आजपासून राज्यात जनजागृतीपर विविध उपक्रम</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/meeting-with-cm-in-15-days-for-kolhapur-bench-guardian-minister-prakash-abitkar-assurance-a-a746/</t>
+          <t>https://mahasamvad.in/174294/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : 'खंडपीठ'साठी माणिक पाटलांचं आंदोलन; समजुतीसाठी भाजप अन् शिवसेनेचा पुढाकार, तर राष्ट्रवादी...</t>
+          <t>बंधपत्रित वैद्यकीय अधिकाऱ्यांना ग्रामीण भागात सेवा देणे बंधनकारक - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-manik-patil-chuyekar-agitation-for-bench-court-was-stopped-in-the-presence-of-mp-dhananjay-mahadik-and-minister-prakashrao-abitkar-pp82-rg93</t>
+          <t>https://mahasamvad.in/154909/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>अवयवदान पंधरवड्यास सुरुवात; आजपासून राज्यात जनजागृतीपर विविध उपक्रम</t>
+          <t>कोल्हापूरसह पाच जिल्ह्यांत १८ रोजी ‘सर्किट बेंच’ प्रारंभाचा आनंदोत्सव</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174294/</t>
+          <t>https://www.loksatta.com/kolhapur/mumbai-high-court-circuit-bench-kolhapur-for-five-districts-prakash-abitkar-informed-css-98-5294507/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>बंधपत्रित वैद्यकीय अधिकाऱ्यांना ग्रामीण भागात सेवा देणे बंधनकारक - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Dr. Ashok Thorat : कोविड काळातील भ्रष्टाचार भोवला! बीड जिल्हा शल्य चिकित्सक अशोक थोरात यांचे निलंबन, प्रकाश आबिटकर यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154909/</t>
+          <t>https://www.esakal.com/maharashtra/beed-district-surgeon-dr-ashok-thorat-suspended-health-minister-prakash-abitkar-announcement-in-vidhansabha-ymk86</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
+          <t>कोल्हापूरच्या तीर्थक्षेत्रांना निधी कमी पडू देणार नाही</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/eknath-shinde-promises-funds-for-kolhapur-pilgrimage-sites</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>कोल्हापूरची ओळख ‘मेडिकल हब’ होईल : पालकमंत्री आबिटकर</t>
+          <t>Free cancer vaccine: राज्यातील 0-14 वयोगटातील मुलींना कॅन्सरविरोधी फ्री लस; कधी मिळणार लस, पाहा!</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-will-become-medical-hub-guardian-minister-abitkar</t>
+          <t>https://saamtv.esakal.com/lifestyle/free-cancer-vaccine-for-girls-aged-0-14-in-the-state-check-when-it-will-be-available-sjk95</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Dr. Ashok Thorat : कोविड काळातील भ्रष्टाचार भोवला! बीड जिल्हा शल्य चिकित्सक अशोक थोरात यांचे निलंबन, प्रकाश आबिटकर यांची विधानसभेत घोषणा</t>
+          <t>मेगा रक्तदान शिबिराचे आयोजन करू नये; राज्य रक्त संक्रमण परिषदेच्या रक्तपेढ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/beed-district-surgeon-dr-ashok-thorat-suspended-health-minister-prakash-abitkar-announcement-in-vidhansabha-ymk86</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-health-department-prakash-abitkar-limits-mega-blood-donation-camps-mumbai-print-news-rds-00-5227011/</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>कोल्हापूरसह पाच जिल्ह्यांत १८ रोजी ‘सर्किट बेंच’ प्रारंभाचा आनंदोत्सव</t>
+          <t>महात्मा ज्योतिराव फुले जन आरोग्य योजनेचा लाभ जास्तीत जास्त लाभार्थ्यांपर्यंत पोहोचवा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/mumbai-high-court-circuit-bench-kolhapur-for-five-districts-prakash-abitkar-informed-css-98-5294507/</t>
+          <t>https://mahasamvad.in/151398/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>मेगा रक्तदान शिबिराचे आयोजन करू नये; राज्य रक्त संक्रमण परिषदेच्या रक्तपेढ्यांना निर्देश</t>
+          <t>kolhapur Politics | पालकमंत्र्यांच्या तालुक्यातूनच महायुतीत बंडखोरीचे वारे</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-health-department-prakash-abitkar-limits-mega-blood-donation-camps-mumbai-print-news-rds-00-5227011/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/ftii-to-deliver-film-making-courses-in-kolhapur-film-city-ap84-2</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>कोल्हापूरच्या तीर्थक्षेत्रांना निधी कमी पडू देणार नाही</t>
+          <t>Kolhapur : ESI हॉस्पिटलमध्ये रुग्णांची हेळसांड,आरोग्यमंत्री ॲक्शन मोडवर</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/eknath-shinde-promises-funds-for-kolhapur-pilgrimage-sites</t>
+          <t>https://www.navarashtra.com/videos/kolhapur-patients-commotion-at-esi-hospital-health-minister-on-action-mode-906995.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>महात्मा ज्योतिराव फुले जन आरोग्य योजनेचा लाभ जास्तीत जास्त लाभार्थ्यांपर्यंत पोहोचवा - सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>महादेवी हत्ती परत येणार?, वनतारा सीईओंसोबतच्या बैठकीतून मठाचे महास्वामी बाहेर पडले, नेमकं काय घडलं.. वाचा</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151398/</t>
+          <t>https://www.lokmat.com/kolhapur/now-a-legal-battle-for-the-mahadevi-elephant-of-nandani-math-guardian-minister-prakash-abitkar-gave-information-after-a-discussion-between-the-ceo-of-vanatara-and-the-mathadhis-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kolhapur Politics | पालकमंत्र्यांच्या तालुक्यातूनच महायुतीत बंडखोरीचे वारे</t>
+          <t>Bandh: कोल्हापूर हद्दवाढीच्या विरोधात २० गावांत आज बंद; कृती समितीचा मंत्री आबिटकर, मुश्रीफांना इशारा</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/ftii-to-deliver-film-making-courses-in-kolhapur-film-city-ap84-2</t>
+          <t>https://www.lokmat.com/kolhapur/20-villages-to-observe-bandh-today-against-kolhapur-boundary-extension-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री-खंडपीठ कृती समिती यांच्यात लवकरच मुंबईत बैठक</t>
+          <t>Sharangdhar Deshmukh : कोल्हापुरात कॉंग्रेसला खिंडार, माजी नगरसेवक करणार शिंदे सेनेत प्रवेश</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/meeting-between-chief-minister-and-khandepeeth-action-committee-to-be-held-soon-in-mumbai-ap84</t>
+          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>१०० जेसीबीमधून उपमुख्यमंत्री एकनाथ शिंदे यांच्यावर होणार फुलांची उधळण !</t>
+          <t>शाहू महाराजांच्या विचारांनी कोल्हापूरचे नाव उज्ज्वल करूया : पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/100-jcbs-to-shower-flowers-on-deputy-cm-eknath-shinde</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/lets-glorify-kolhapur-with-shahu-maharajs-ideals-guardian-minister-abitkar-ap84</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Bandh: कोल्हापूर हद्दवाढीच्या विरोधात २० गावांत आज बंद; कृती समितीचा मंत्री आबिटकर, मुश्रीफांना इशारा</t>
+          <t>कोल्हापूर जिल्ह्याला प्रथमच 2 पालकमंत्री</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/20-villages-to-observe-bandh-today-against-kolhapur-boundary-extension-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-district-gets-2-guardian-ministers-for-the-first-time</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Sharangdhar Deshmukh : कोल्हापुरात कॉंग्रेसला खिंडार, माजी नगरसेवक करणार शिंदे सेनेत प्रवेश</t>
+          <t>Medical Recruitment 2025: मोठी बातमी! राज्यात डॉक्टरांची मेगाभरती, सरकारी नोकरीची सुवर्णसंधी; १,५०० जागा भरल्या जाणार</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/sharangdhar-deshmukh-enter-in-eknath-shinde-group-satej-patil-kolhapur-breaking/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Mahadevrao Mahadik : आप्पा महाडिकांनी दहीहंडी कार्यक्रमात आबिटकर, नरकेंशी केल्या कानगोष्टी; गोकुळ’ च्या राजकारणाला फुटणार उकळी, सतेज पाटलांचे काय?</t>
+          <t>शक्तिपीठ महामार्गावरून कोल्हापुरातील मंत्र्यांमधील मतभेद चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/during-kolhapur-dahi-handi-event-appa-mahadik-was-seen-whispering-with-prakash-abitkar-and-chandradeep-narke-political-temperature-around-gokul-dudh-sangh-may-rise-whats-satej-patils-move-srs92</t>
+          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>शाहू महाराजांच्या विचारांनी कोल्हापूरचे नाव उज्ज्वल करूया : पालकमंत्री आबिटकर</t>
+          <t>अलमट्टी उंचीला विरोध; बुधवारी जलसंपदामंत्र्यांबरोबर बैठक</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/lets-glorify-kolhapur-with-shahu-maharajs-ideals-guardian-minister-abitkar-ap84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/almatti-dam-height-opposition-ap84</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Free cancer vaccine: राज्यातील 0-14 वयोगटातील मुलींना कॅन्सरविरोधी फ्री लस; कधी मिळणार लस, पाहा!</t>
+          <t>राज्य कामगार विमा सोसायटीच्या रुग्णालयांमधून दर्जेदार आरोग्य सुविधा द्याव्यात- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/lifestyle/free-cancer-vaccine-for-girls-aged-0-14-in-the-state-check-when-it-will-be-available-sjk95</t>
+          <t>https://mahasamvad.in/151861/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>कोल्हापूर जिल्ह्याला प्रथमच 2 पालकमंत्री</t>
+          <t>kolhapur | पालकमंत्र्यांकडे जाणार्‍या फायली सहपालकमंत्र्यांमार्फत</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-district-gets-2-guardian-ministers-for-the-first-time</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shinde-shiv-sena-vs-bjp-kolhapur-political-clash-ap84</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Medical Recruitment 2025: मोठी बातमी! राज्यात डॉक्टरांची मेगाभरती, सरकारी नोकरीची सुवर्णसंधी; १,५०० जागा भरल्या जाणार</t>
+          <t>Maharashtra Government: अपघातग्रस्त रुग्णांना मिळणार १ लाख रुपयांपर्यंत कॅशलेस उपचार, फडणवीस सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-medical-recruitment-apply-online-doctors-bharti-2025-government-jobs-vacancy-1500-posts/articleshow/119328912.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/fadnavis-governments-big-move-maharashtra-govt-approves-rs-1-lakh-cashless-treatment-for-accident-victims-pvm91</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्गावरून कोल्हापुरातील मंत्र्यांमधील मतभेद चव्हाट्यावर</t>
+          <t>Gokul Election : विधानसभा, लोकसभेचे उट्टे 'गोकुळ'मध्ये निघणार; मुश्रीफ-सतेज यांची कोंडी, आबिटकर-मंडलिकांसह नरके ठरणार निर्णायक</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/in-kolhapur-disagreement-among-ministers-over-shaktipeeth-highway-project-print-politics-news-asj-82-4885640/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/gokul-dudh-sangh-president-election-hasan-mushrif-satej-patil-prakash-abitkar-sanjay-mandlik-role-important-bam92</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा सोसायटीच्या रुग्णालयांमधून दर्जेदार आरोग्य सुविधा द्याव्यात- सार्वजनिक आरोग्य मंत्री प्रकाश आबिटकर</t>
+          <t>Kolhapur politics : कारे दुरावा कारे अबोला! मंत्री आबिटकर-मुश्रीफ यांच्यातील नाराजी उघड, बँकेच्या अहवालात पालकमंत्र्यांचा फोटोच नाही</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/151861/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/tension-between-ministers-abitkar-and-mushrif-continues-guardian-minister-prakashrao-abitkars-photo-missing-from-kdcc-bank-report-book-srs92</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Maharashtra Government: अपघातग्रस्त रुग्णांना मिळणार १ लाख रुपयांपर्यंत कॅशलेस उपचार, फडणवीस सरकारचा मोठा निर्णय</t>
+          <t>Kolhapur : कोल्हापूरच्या हद्दवाढीसाठी शासनाची पुढची स्टेप, पालकमंत्री आबिटकरांनी कायदेशीर त्रुटी दूर करण्यावर दिला भर</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/fadnavis-governments-big-move-maharashtra-govt-approves-rs-1-lakh-cashless-treatment-for-accident-victims-pvm91</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/governments-next-step-for-kolhapur-boundary-expansion-guardian-minister-abitkar-emphasizes-on-removing-legal-loopholes-srs92</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>kolhapur | पालकमंत्र्यांकडे जाणार्‍या फायली सहपालकमंत्र्यांमार्फत</t>
+          <t>प्रकाश आबिटकर यांची माहिती, दोन हजार पदनिर्मितीसाठी शासनाची मान्यता</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shinde-shiv-sena-vs-bjp-kolhapur-political-clash-ap84</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Kolhapur politics : कारे दुरावा कारे अबोला! मंत्री आबिटकर-मुश्रीफ यांच्यातील नाराजी उघड, बँकेच्या अहवालात पालकमंत्र्यांचा फोटोच नाही</t>
+          <t>आरोग्य मंत्री प्रकाश आबिटकर यांनी घेतली अवयवादानाची शपथ</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/tension-between-ministers-abitkar-and-mushrif-continues-guardian-minister-prakashrao-abitkars-photo-missing-from-kdcc-bank-report-book-srs92</t>
+          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापूरच्या हद्दवाढीसाठी शासनाची पुढची स्टेप, पालकमंत्री आबिटकरांनी कायदेशीर त्रुटी दूर करण्यावर दिला भर</t>
+          <t>आदर्श गोठा अभियानाच्या धर्तीवर आता जिल्ह्यात स्वच्छ - सुंदर घर अभियान -पालकमंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/governments-next-step-for-kolhapur-boundary-expansion-guardian-minister-abitkar-emphasizes-on-removing-legal-loopholes-srs92</t>
+          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर यांची माहिती, दोन हजार पदनिर्मितीसाठी शासनाची मान्यता</t>
+          <t>मोठी बातमी! राज्यात 1500 डॉक्टरांची भरती होणार, 10 एप्रिल रोजी जाहिरात निघणार</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-said-2-thousand-vacant-post-will-filled/</t>
+          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>मंगेशकर रुग्णालय प्रकरणात कारवाई लवकरच; आरोग्यमंत्री आबिटकर यांची माहिती</t>
+          <t>राज्याच्या इतिहासात पहिल्यांदाच 'आरोग्य विषयक धोरण' : मंत्री प्रकाश आबिटकर -</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/health-minister-prakash-abitkar-on-dinanath-mangeshkar-hospital-probe/</t>
+          <t>https://livemarathi.in/health-policy-for-the-first-time-in-the-history-of-the-state-minister-prakash-abitkar/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>आरोग्य मंत्री प्रकाश आबिटकर यांनी घेतली अवयवादानाची शपथ</t>
+          <t>Prakash Abitkar : 4 कर्करोग रुग्णालयांची निर्मिती करणार; आरोग्यमंत्री प्रकाश आबिटकर यांनी केले जाहीर</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/health-minister-prakash-abitkar-took-the-pledge-of-organ-donation/</t>
+          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>आदर्श गोठा अभियानाच्या धर्तीवर आता जिल्ह्यात स्वच्छ - सुंदर घर अभियान -पालकमंत्री प्रकाश आबिटकर</t>
+          <t>दीनानाथ मंगेशकर रुग्णालयावर कारवाई कधी? आरोग्य मंत्री प्रकाश आबिटकर यांनी दिले उत्तर</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Based-on-the-Ideal-Shed-campaign--now-the-district-has-a-Clean---Beautiful-House-campaign-</t>
+          <t>https://www.tv9marathi.com/maharashtra/health-minister-prakash-abitkar-said-about-the-action-taken-by-dinanath-hospital-1387152.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>मोठी बातमी! राज्यात 1500 डॉक्टरांची भरती होणार, 10 एप्रिल रोजी जाहिरात निघणार</t>
+          <t>Maharashtra News Live Updates: कोरोनाचे लक्षण सौम्य असून काळजी घेणे गरजेचं - मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/news/maharashtra-government-to-recruit-1500-doctors-posts-advertisement-will-be-released-on-10-april-article-151293525</t>
+          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-live-news-updates-29-may-2025-heavy-rainfall-alert-across-maharashtra-mumbai-pune-red-alert-rains-weather-forecast-live-news-today-maharashtra-politics-corona-update-mumbai-pune-local-entertainment-sports-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : 4 कर्करोग रुग्णालयांची निर्मिती करणार; आरोग्यमंत्री प्रकाश आबिटकर यांनी केले जाहीर</t>
+          <t>Kolhapur City Extension : हद्दवाढ नाही तर निवडणूक नाही, कोल्हापूरची कृती समिती आक्रमक</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/prakash-abitkar-4-cancer-hospitals-to-be-built-health-minister-prakash-abitkar-announced/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-shahar-haddavad-samiti-warns-against-municipal-election-without-boundary-extension-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Maharashtra News Live Updates: कोरोनाचे लक्षण सौम्य असून काळजी घेणे गरजेचं - मंत्री प्रकाश आबिटकर</t>
+          <t>मोठी बातमी : सतेज पाटील आणि महाडिक यांच्यात पहिल्यांदाच एकमत, दोघेही एकाच फ्रेममध्ये!</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-live-news-updates-29-may-2025-heavy-rainfall-alert-across-maharashtra-mumbai-pune-red-alert-rains-weather-forecast-live-news-today-maharashtra-politics-corona-update-mumbai-pune-local-entertainment-sports-crime-top-headlines</t>
+          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>मोठी बातमी : सतेज पाटील आणि महाडिक यांच्यात पहिल्यांदाच एकमत, दोघेही एकाच फ्रेममध्ये!</t>
+          <t>Almatti Dam Height : अलमट्टी उंची बाबत 15 दिवसांनी सर्व पक्षीयांसह पुन्हा बैठक आंदोलक आणि</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/satej-patil-and-amal-mahadik-agree-both-in-the-same-frame-in-front-of-prakash-abitkar-kolhapur-politics-marathi-news-1358769</t>
+          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Kolhapur City Extension : हद्दवाढ नाही तर निवडणूक नाही, कोल्हापूरची कृती समिती आक्रमक</t>
+          <t>लाडक्या बहिणीनंतर मुलींसाठी सरकारची मोठी घोषणा, 14 वर्षांपर्यंत मुलींना मोफत मिळणार ही गोष्ट</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-shahar-haddavad-samiti-warns-against-municipal-election-without-boundary-extension-as11-rg93</t>
+          <t>https://www.tv9marathi.com/maharashtra/pune/maharashtra-government-to-provide-free-cancer-vaccine-for-girl-1358923.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>येरवडा रुग्णालयातून '11 लाखांची अंतर्वस्त्रे गायब,' चौकशी समितीच्या अहवालातून कोणता घोटाळा समोर आलाय?</t>
+          <t>Pune Deenanath Mangeshkar Hospital Highlights: भाजपा कार्यकर्त्यांकडून डॉ. सुश्रुत घैसास यांच्या भावाच्या घराची तोडफोड</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/articles/c93n25pxqe1o</t>
+          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Almatti Dam Height : अलमट्टी उंची बाबत 15 दिवसांनी सर्व पक्षीयांसह पुन्हा बैठक आंदोलक आणि</t>
+          <t>Shaktipeeth Expressway च्या भूसंपादनाला मंजुरी अन् 20 हजार कोटींची तरतूद, कोणत्या जिल्ह्यांमधून जाणार...</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/meeting-with-all-parties-again-after-15-days-regarding-almatti-height-kolhapur-sangli-maharashtra-marathi-news-update-1360314</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणीनंतर मुलींसाठी सरकारची मोठी घोषणा, 14 वर्षांपर्यंत मुलींना मोफत मिळणार ही गोष्ट</t>
+          <t>प्रकाश आबिटकर आणि जयकुमार गोरे यांचे आदेश, कंत्राटी कर्मचाऱ्यांना नियमित करा</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/pune/maharashtra-government-to-provide-free-cancer-vaccine-for-girl-1358923.html</t>
+          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>नांदणी मठाची 'माधुरी' परत येणार? वनताराचे CEO म्हणाले, कोल्हापूरकरांना सर्व सहकार्य</t>
+          <t>Prakash Abitkar : घाबरून न जाऊ नका, लोकांना पॅनिक करू नका – आरोग्यमंत्री अबिटकर</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
+          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Pune Deenanath Mangeshkar Hospital Highlights: भाजपा कार्यकर्त्यांकडून डॉ. सुश्रुत घैसास यांच्या भावाच्या घराची तोडफोड</t>
+          <t>Prakash Abitkar | Corona ला घाबरून न जाऊ नका, लोकांना पॅनिक करू नका : आरोग्यमंत्री</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-deenanath-mangeshkar-hospital-demands-20-lakhs-before-treatment-pregnant-woman-loses-life-live-updates-in-marathi-pmw-88-4997202/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway च्या भूसंपादनाला मंजुरी अन् 20 हजार कोटींची तरतूद, कोणत्या जिल्ह्यांमधून जाणार...</t>
+          <t>Shaktipeeth Highway : सांगली, हिंगोलीसह 10 जिल्ह्यात शक्तीपीठ महामार्गाला कडवा विरोध; कोल्हापुरबाबत पालकमंत्र्यांनी दिले संकेत</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-cabinet-approves-land-acquisition-for-shaktipeeth-mahamarg-despite-opposition-1430899.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-minister-prakash-abitkar-confirms-cancellation-of-shaktipeeth-highway-as11</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking LIVE: देश-विदेशातील महत्त्वाच्या घडामोडींचा आढावा फक्त एका क्लिकवर...</t>
+          <t>Mangeshkar Hospital: मंगेशकर रुग्णालय प्रकरणी कारवाई कधी होणार? आरोग्यमंत्री अबिटकर यांनी स्पष्ट सांगितलं</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
+          <t>https://www.esakal.com/maharashtra/mangeshkar-hospital-controversy-health-minister-prakash-abitkar-statement-about-action-aau85</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>प्रकाश आबिटकर आणि जयकुमार गोरे यांचे आदेश, कंत्राटी कर्मचाऱ्यांना नियमित करा</t>
+          <t>शक्तिपीठ महामार्गास 2 मंत्र्यांचा विरोध, मंत्रिमंडळ बैठकीत पडसाद राजू शेट्टी</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/prakash-abitkar-and-jayakumar-gore-regularize-contract-employees/</t>
+          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Prakash Abitkar : घाबरून न जाऊ नका, लोकांना पॅनिक करू नका – आरोग्यमंत्री अबिटकर</t>
+          <t>Maharashtra: Beed Surgeon Suspended For 'Embezzling Crores In Medicine Procurement During COVID-19'</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/corona-wave-update-maharashtra-health-minister-prakash-abitkar-statement-1414124.html</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Prakash Abitkar | Corona ला घाबरून न जाऊ नका, लोकांना पॅनिक करू नका : आरोग्यमंत्री</t>
+          <t>Maharashtra cancels Licenses of 258 Private Hospitals for Violations</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-prakash-abitkar-reaction-on-maharashtra-covid-cases-corona-update-29-may-2025-abp-majha-1361545</t>
+          <t>https://www.newsonair.gov.in/maharashtra-cancels-licenses-of-258-private-hospitals-for-violations/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Shaktipeeth Highway : सांगली, हिंगोलीसह 10 जिल्ह्यात शक्तीपीठ महामार्गाला कडवा विरोध; कोल्हापुरबाबत पालकमंत्र्यांनी दिले संकेत</t>
+          <t>Major Health Boost for Nagpur And Vidarbha: Govt plans facilities, incentives for doctors in remote areas</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-minister-prakash-abitkar-confirms-cancellation-of-shaktipeeth-highway-as11</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/major-health-boost-for-nagpur-and-vidarbha-govt-plans-facilities-incentives-for-doctors-in-remote-areas/articleshow/121276548.cms</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्गास 2 मंत्र्यांचा विरोध, मंत्रिमंडळ बैठकीत पडसाद राजू शेट्टी</t>
+          <t>Lack of voluntary blood donations help ‘red market’ thrive</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shaktipeeth-expresshighway-2-ministers-oppose-cabinet-meeting-hasan-mushrif-and-prakash-abitkar-raju-shetty-also-warns-kolhapur-1365930</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Maharashtra: Beed Surgeon Suspended For 'Embezzling Crores In Medicine Procurement During COVID-19'</t>
+          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की लड़कियों को फ्री में दी जाएगी कैंसर की वैक्सीन</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-beed-district-surgeon-suspended-over-irregularities-in-medicine-procurement-during-covid-19-enn25032502769</t>
+          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>GBS Outbreak: First fatality confirmed in Pune as cases surge</t>
+          <t>फडणवीस सरकार की 20,787 करोड़ रुपये की मंजूरी, तैयार होगा नागपुर-गोवा शक्तिपीठ एक्सप्रेसवे!</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
+          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Lack of voluntary blood donations help ‘red market’ thrive</t>
+          <t>Central team focuses on source, diagnosis amid GBS cases surge | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/lack-of-voluntary-blood-donations-help-red-market-thrive/articleshow/121834467.cms</t>
+          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की लड़कियों को फ्री में दी जाएगी कैंसर की वैक्सीन</t>
+          <t>CMO denies staying 3.2k cr contract of ex-health minister</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/fadnavis-government-of-maharashtra-gave-the-gift-of-giving-free-cancer-vaccine-to-girls-aged-0-to-14-years-201740835683271.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार का बड़ा फैसला, 14 साल तक की बेटियों के लिए किया ये ऐलान</t>
+          <t>Health dept to focus on doorstep services amid Covid cases, monsoon</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/devendra-fadnavis-government-announces-free-cancer-vaccine-for-girls-under-14-years-of-age-maharashtra-news/1088804/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार की 20,787 करोड़ रुपये की मंजूरी, तैयार होगा नागपुर-गोवा शक्तिपीठ एक्सप्रेसवे!</t>
+          <t>Charitable hospitals must comply with govt health scheme GR: Minister</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://hindi.newsdanka.com/politics/fadanvis-approves-20787-crore-shaktipith-expressway-nagpur-goa/104395/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Central team focuses on source, diagnosis amid GBS cases surge | Latest News India - Hindustan Times</t>
+          <t>State to set up Maharashtra Public Health Infrastructure Corporation</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/central-team-focuses-on-source-diagnosis-amid-gbs-cases-surge-101738175793660.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>CMO denies staying 3.2k cr contract of ex-health minister</t>
+          <t>GBS Outbreak: First fatality confirmed in Pune as cases surge</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cmo-denies-staying-3-2k-cr-contract-of-ex-health-minister/articleshow/118654151.cms</t>
+          <t>https://www.financialexpress.com/life/gbs-outbreak-first-fatality-confirmed-in-pune-as-cases-surge-3728389/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Charitable hospitals must comply with govt health scheme GR: Minister</t>
+          <t>खौफनाक: महाराष्ट्र में एक जिले में 14000 महिलाओं में मिले कैंसर के लक्षण, क्या बोले स्वास्थ्य मंत्री?</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/charitable-hospitals-must-comply-with-govt-health-scheme-gr-minister/articleshow/122866818.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>State to set up Maharashtra Public Health Infrastructure Corporation</t>
+          <t>No one has to worry, says Maharashtra Health Minister Abitkar on HMPV</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-set-up-maharashtra-public-health-infrastructure-corporation-101743108071583.html</t>
+          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>खौफनाक: महाराष्ट्र में एक जिले में 14000 महिलाओं में मिले कैंसर के लक्षण, क्या बोले स्वास्थ्य मंत्री?</t>
+          <t>Maharashtra cabinet approves Mahalaxmi &amp; Jotiba temple development plans</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-over-14-000-women-detected-with-cancer-like-symptoms-in-hingoli-health-minister-prakash-abitkar-tell-in-assembly-know-all/articleshow/122369652.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>No one has to worry, says Maharashtra Health Minister Abitkar on HMPV</t>
+          <t>One Day for Farmer initiative implemented in Kolhapur district</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/no-one-has-to-worry-says-maharashtra-health-minister-abitkar-on-hmpv-125010900068_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Statewide awareness campaign on organ donation from Aug 3 to 15</t>
+          <t>Maharashtra: Child Health Drive Faces Backlash Over Unpaid RBSK Medical Teams</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
+          <t>https://www.thebridgechronicle.com/news/maharashtra-child-health-drive-faces-backlash-over-unpaid-rbsk-medical-teams</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Maharashtra cabinet approves Mahalaxmi &amp; Jotiba temple development plans</t>
+          <t>Pune: Yerawada Mental Hospital Extends OPD Timing Till 5PM</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-cabinet-approves-mahalaxmi-jotiba-temple-development-plans/articleshow/120942684.cms</t>
+          <t>https://www.freepressjournal.in/pune/pune-yerawada-mental-hospital-extends-opd-timing-till-5pm</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>One Day for Farmer initiative implemented in Kolhapur district</t>
+          <t>Mushrif appeals to Gokul chairman Arun Dongale to resign</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/one-day-for-farmer-initiative-implemented-in-kolhapur-district/articleshow/122271778.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Maharashtra: Child Health Drive Faces Backlash Over Unpaid RBSK Medical Teams</t>
+          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/maharashtra-child-health-drive-faces-backlash-over-unpaid-rbsk-medical-teams</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Maharashtra To Launch Statewide Organ Donation Drive From August 3 To 15</t>
+          <t>Spell out measures taken to prevent children deaths in Maharashtra: NCP (SP) to govt | Latest News India</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-launch-statewide-organ-donation-drive-from-august-3-to-15</t>
+          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Pune: Yerawada Mental Hospital Extends OPD Timing Till 5PM</t>
+          <t>With 1.6L units till May, Pune dist ahead in blood donation so far this year</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-yerawada-mental-hospital-extends-opd-timing-till-5pm</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>JP Nadda Launches National Mass Drug Administration Round for Elimination of Lymphatic Filariasis</t>
+          <t>Maharashtra: Thousands Join Silent March In Kolhapur To Demand Return Of Elephant Mahadevi From Vantara</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://pragativadi.com/jp-nadda-launches-national-mass-drug-administration-round-for-elimination-of-lymphatic-filariasis/</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-thousands-join-silent-march-in-kolhapur-to-demand-return-of-elephant-mahadevi-from-vantara-video</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Mushrif appeals to Gokul chairman Arun Dongale to resign</t>
+          <t>One more decision of Shiv Sena ex-min Tanaji Sawant clouded by controversy</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mushrif-appeals-to-gokul-chairman-arun-dongale-to-resign/articleshow/121220071.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Maharashtra govt will take strict action against unnecessary Hysterectomies, says Health Minister Prakash Abitkar</t>
+          <t>Guillain-Barré Syndrome: An explainer as cases are on the rise in Maharashtra</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/-mumbai-customs-rescue-exotic-animals-including-iguanas-sugar-gliders-and-tortoise-at-airport-one-held-23565034</t>
+          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Spell out measures taken to prevent children deaths in Maharashtra: NCP (SP) to govt | Latest News India</t>
+          <t>How the transfer of an elephant in Kolhapur led to a boycott of Jio</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/spell-out-measures-taken-to-prevent-children-deaths-in-maharashtra-ncp-sp-to-govt-101751967947732.html</t>
+          <t>https://indianexpress.com/article/cities/pune/how-the-transfer-of-an-elephant-in-kolhapur-led-to-a-boycott-of-jio-10164145/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Health dept to focus on doorstep services amid Covid cases, monsoon</t>
+          <t>Deenanath Mangeshkar Hospital Controversy Deepens</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/health-dept-to-focus-on-doorstep-services-amid-covid-cases-monsoon-101749837464436.html</t>
+          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>With 1.6L units till May, Pune dist ahead in blood donation so far this year</t>
+          <t>Deenanath Mangeshkar Hospital Under Fire: BJP MLC’s PA’s Wife......</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/with-1-6l-units-till-may-pune-dist-ahead-in-blood-donation-so-far-this-year/articleshow/121837746.cms</t>
+          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy-pregnant-woman-death</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Maharashtra: Thousands Join Silent March In Kolhapur To Demand Return Of Elephant Mahadevi From Vantara</t>
+          <t>People staying within 100m periphery of Panhala fort fear displacement</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-thousands-join-silent-march-in-kolhapur-to-demand-return-of-elephant-mahadevi-from-vantara-video</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>One more decision of Shiv Sena ex-min Tanaji Sawant clouded by controversy</t>
+          <t>Vikhe Patil to irrigation dept: Study concerns on Almatti dam</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/one-more-decision-of-shiv-sena-ex-min-tanaji-sawant-clouded-by-controversy-101740857769024.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vikhe-patil-to-irrigation-dept-study-concerns-on-almatti-dam/articleshow/121323044.cms</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>How the transfer of an elephant in Kolhapur led to a boycott of Jio</t>
+          <t>Shaktipeeth Expressway: शक्तिपीठ एक्सप्रेसवे के खिलाफ सड़क पर उतरे किसान, फडणवीस ने विधानसभा में गिनाए महामार्ग के फायदे-नुकसान</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/how-the-transfer-of-an-elephant-in-kolhapur-led-to-a-boycott-of-jio-10164145/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Guillain-Barré Syndrome: An explainer as cases are on the rise in Maharashtra</t>
+          <t>शिंदे-दादा के क्षेत्र में सर्वाधिक फर्जी लाडली बहनें!</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/htcity/wellness/guillainbarr-syndrome-an-explainer-as-cases-are-on-the-rise-in-maharashtra-101738156519243.html</t>
+          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Deenanath Mangeshkar Hospital Controversy Deepens</t>
+          <t>महाराष्ट्र-कर्नाटक सीमा विवाद अब होगा हल! राज्य सरकार ने विपक्ष संग समिति का किया पुनर्गठन</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-government-reconstitutes-committee-resolve-border-dispute-karnataka-1260125.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Deenanath Mangeshkar Hospital Under Fire: BJP MLC’s PA’s Wife......</t>
+          <t>Assembly election losers from MVA first pick in Mahayuti poaching spree</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/deenanath-mangeshkar-hospital-controversy-pregnant-woman-death</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>People staying within 100m periphery of Panhala fort fear displacement</t>
+          <t>local body elections : मुख्यमंत्री, दोन उपमुख्यमंत्र्यांचे दौरे; नवी ‘जुळणी’</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/people-staying-within-100m-periphery-of-panhala-fort-fear-displacement/articleshow/122411210.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/local-self-government-election-preparations-ap84</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Vikhe Patil to irrigation dept: Study concerns on Almatti dam</t>
+          <t>Kolhapur politics : वडील उद्धव ठाकरेंसोबत तर मुलगा मात्र अजित पवारांच्या राष्ट्रवादीच्या स्टेजवर; कोल्हापूरचं हटके राजकारण!</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vikhe-patil-to-irrigation-dept-study-concerns-on-almatti-dam/articleshow/121323044.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-kp-patil-with-uddhav-thackeray-son-ranjit-patil-on-ajit-pawar-stage-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway: शक्तिपीठ एक्सप्रेसवे के खिलाफ सड़क पर उतरे किसान, फडणवीस ने विधानसभा में गिनाए महामार्ग के फायदे-नुकसान</t>
+          <t>‘पुढारी’कार डॉ. ग. गो. जाधव यांना अभिवादन</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/nagpur-goa-shaktipeeth-expressway-farmers-protest-devendra-fadnavis-listed-advantages-disadvantages-of-highway-in-assembly/articleshow/118941472.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/greetings-to-pudhari-dr-g-g-jadhav-ap84</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>शिंदे-दादा के क्षेत्र में सर्वाधिक फर्जी लाडली बहनें!</t>
+          <t>तुमच्यात काही मतभेद असतील तर सांगा, मी मिटवतो ! शाहू महाराजांची कोपरखळी, शिवसेना नेत्यांनाही हसू आवरेना</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/shinde-dadas-area-has-the-most-fake-ladli-sisters/</t>
+          <t>https://maharashtranews1.com/If-there-are-any-disagreements-among-you--tell-me--and-I-will-resolve-them--Shahu-Maharaj-s-jab-even-made-the-Shiv-Sena-leaders-unable-to-contain-their-laughter-</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>महाराष्ट्र-कर्नाटक सीमा विवाद अब होगा हल! राज्य सरकार ने विपक्ष संग समिति का किया पुनर्गठन</t>
+          <t>Maharashtra Government To Provide Free Cancer Vaccine For Girls Aged 0-14</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-government-reconstitutes-committee-resolve-border-dispute-karnataka-1260125.html</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-government-to-provide-free-cancer-vaccine-for-girls-aged-0-14-7825621</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Assembly election losers from MVA first pick in Mahayuti poaching spree</t>
+          <t>Maharashtra Expands Cashless Treatment For Accident Victims Up To ₹1 Lakh</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/assembly-election-losers-from-mva-first-pick-in-mahayuti-poaching-spree/articleshow/121785497.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-expands-cashless-treatment-for-accident-victims-up-to-1-lakh</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Kolhapur politics : वडील उद्धव ठाकरेंसोबत तर मुलगा मात्र अजित पवारांच्या राष्ट्रवादीच्या स्टेजवर; कोल्हापूरचं हटके राजकारण!</t>
+          <t>Kolhapur Politics : कोल्हापुरचं राजकारण फिरवणारे बंटी पाटील एकटे कसे पडले? 'घात' कुठे झाला?</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-kp-patil-with-uddhav-thackeray-son-ranjit-patil-on-ajit-pawar-stage-msr87-rg93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-satej-patil-political-isolation-hasan-mushrif-chandradeep-narke-defection-congress-maharashtra-hn97</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>‘पुढारी’कार डॉ. ग. गो. जाधव यांना अभिवादन</t>
+          <t>Kolhapur Politics : अखेर 80 वर्षांच्या के. पी. पाटलांना अजितदादांनी स्वीकारलंच: पक्षप्रवेशासाठी कोल्हापूरमध्ये जंगी मेळावा</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/greetings-to-pudhari-dr-g-g-jadhav-ap84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-mla-kp-patil-joins-ncp-ajit-pawar-kolhapur-visit-may-23-hn97</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>तुमच्यात काही मतभेद असतील तर सांगा, मी मिटवतो ! शाहू महाराजांची कोपरखळी, शिवसेना नेत्यांनाही हसू आवरेना</t>
+          <t>Maharashtra Guardian Ministers List : तीन नेत्यांकडे सहा जिल्हे, कोल्हापूर अन् मुंबईसाठी दोन -दोन कारभारी,</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/If-there-are-any-disagreements-among-you--tell-me--and-I-will-resolve-them--Shahu-Maharaj-s-jab-even-made-the-Shiv-Sena-leaders-unable-to-contain-their-laughter-</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Maharashtra Expands Cashless Treatment For Accident Victims Up To ₹1 Lakh</t>
+          <t>Gokul Politics : गोकुळमध्ये पुन्हा संघर्ष? वाढवलेल्या ठरावांचा नेता कोण? घमासान होण्याची चिन्हे</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-expands-cashless-treatment-for-accident-victims-up-to-1-lakh</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/the-impact-of-1800-new-members-in-gokul-dairy-union-depends-on-upcoming-alliance-between-mahayuti-or-mva-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : कोल्हापुरचं राजकारण फिरवणारे बंटी पाटील एकटे कसे पडले? 'घात' कुठे झाला?</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 24 जून 2025 | मंगळवार</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-satej-patil-political-isolation-hasan-mushrif-chandradeep-narke-defection-congress-maharashtra-hn97</t>
+          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers List : तीन नेत्यांकडे सहा जिल्हे, कोल्हापूर अन् मुंबईसाठी दोन -दोन कारभारी,</t>
+          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 1 जून 2025 | रविवार</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-three-leaders-have-six-districts-two-kolhapur-and-mumbai-have-to-ministers-of-guardian-ministry-devendra-fadnavis-masterstroke-to-avoid-conflict-marathi-news-1339325</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : अखेर 80 वर्षांच्या के. पी. पाटलांना अजितदादांनी स्वीकारलंच: पक्षप्रवेशासाठी कोल्हापूरमध्ये जंगी मेळावा</t>
+          <t>Hasan Mushrif : हसन मुश्रीफांना कोल्हापूर न देण्यामागचं कारण, दोस्ताना आला अंगलट?</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-mla-kp-patil-joins-ncp-ajit-pawar-kolhapur-visit-may-23-hn97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/why-hasan-mushrif-not-appointed-as-kolhapur-guardian-minister-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 24 जून 2025 | मंगळवार</t>
+          <t>Rahul Patil: काँग्रेस निष्ठावंतांचे पुत्र हाती घड्याळ बांधणार, करवीरचे राहुल पाटील राष्ट्रवादीत?</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/abp-majha-top-10-headlines-24-june-2025-tuesday-iran-israel-attack-and-shaktipeeth-expressway-mumbai-devendra-fadnavis-1365975</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-congress-leader-rahul-patil-to-join-ncp-mm76-rg93</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Gokul Politics : गोकुळमध्ये पुन्हा संघर्ष? वाढवलेल्या ठरावांचा नेता कोण? घमासान होण्याची चिन्हे</t>
+          <t>Agriculture University: कृषी विद्यापीठांचा फजितवाडा</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/the-impact-of-1800-new-members-in-gokul-dairy-union-depends-on-upcoming-alliance-between-mahayuti-or-mva-as11-rg93</t>
+          <t>https://agrowon.esakal.com/sampadkiya/the-dilemma-of-agricultural-universities-article-on-agrowon-rat16</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Hasan Mushrif : हसन मुश्रीफांना कोल्हापूर न देण्यामागचं कारण, दोस्ताना आला अंगलट?</t>
+          <t>Kolhapur Corona Update : महाराष्ट्राच्या आरोग्याची चावी हाती असलेल्या दोन मंत्र्यांच्या कोल्हापुरात</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/why-hasan-mushrif-not-appointed-as-kolhapur-guardian-minister-as11-rg93</t>
+          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ABP Majha Top 10 Headlines : ABP माझा टॉप 10 हेडलाईन्स | 1 जून 2025 | रविवार</t>
+          <t>Shivsena Politics: कोल्हापूरच्या राजकीय आखाड्यात शिंदेंच्या शिवसेनेला 'अच्छे दिन',इच्छुकांच्या रांगा; पण 'ही' असणार टांगती तलवार</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-1-june-2025-sunday-latest-marathi-news-update-maharashtra-politics-marathi-news-1362038</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-shiv-sena-gains-in-kolhapur-amid-rebellion-fears-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>kolhapur | मेहुणे-पाहुण्यांचा राजकीय संघर्ष मुश्रीफांमुळे संपणार</t>
+          <t>LMOTY 2025: हे चेहरे गाजवणार महाराष्ट्राचं पुढचं राजकारण; कोण ठरणार प्रॉमिसिंग राजकारणी?</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/political-conflict-between-k-p-patil-and-a-y-patil-will-end-due-to-mushrif-ap84</t>
+          <t>https://www.lokmat.com/maharashtra/lokmat-maharashtrian-of-the-year-awards-2025-here-are-the-nominations-for-promising-politician-category-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Rahul Patil: काँग्रेस निष्ठावंतांचे पुत्र हाती घड्याळ बांधणार, करवीरचे राहुल पाटील राष्ट्रवादीत?</t>
+          <t>Chandrahar Patil : चंद्रहार पाटील यांचे अखेर ठरले, ठाकरे सेनेला रामराम, सरकारसोबत जाणार; सांगलीच्या राजकारणात नवा ट्विस्ट</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-politics-congress-leader-rahul-patil-to-join-ncp-mm76-rg93</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Agriculture University: कृषी विद्यापीठांचा फजितवाडा</t>
+          <t>Kolhapur : कोल्हापुरात एकनाथ शिंदेंची 'जादू', एकाच वेळी काँग्रेस-भाजप आणि ताराराणी</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/sampadkiya/the-dilemma-of-agricultural-universities-article-on-agrowon-rat16</t>
+          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Kolhapur Corona Update : महाराष्ट्राच्या आरोग्याची चावी हाती असलेल्या दोन मंत्र्यांच्या कोल्हापुरात</t>
+          <t>Kolhapur APMC election | सभापती निवडीत पालकमंत्र्यांची एंट्री</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/corona-infected-woman-dies-in-kolhapur-staff-refuses-to-perform-last-rites-due-to-lack-of-ppe-kits-marathi-news-update-1361996</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-ministers-entry-in-kolhapur-agricultural-produce-market-committee-chairman-election-ap84</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Chandrahar Patil : चंद्रहार पाटील यांचे अखेर ठरले, ठाकरे सेनेला रामराम, सरकारसोबत जाणार; सांगलीच्या राजकारणात नवा ट्विस्ट</t>
+          <t>Gokul President Election : कोल्हापुरच्या राजकारणात मुश्रीफांची ताकद वाढली; जिल्हा बँक आणि गोकुळवर पितापुत्रांचं 'वर्चस्व', वाचा महिनाभरात काय काय घडलं?</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/chandrahar-patil-leaves-shivsena-ubt-and-decided-to-go-with-mahayuti-sarkar-brk/articleshow/121708979.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Shivsena Politics: कोल्हापूरच्या राजकीय आखाड्यात शिंदेंच्या शिवसेनेला 'अच्छे दिन',इच्छुकांच्या रांगा; पण 'ही' असणार टांगती तलवार</t>
+          <t>Kolhapur : महायुतीच्या ‘रडार’वर काँग्रेस; सत्तेसाठी लावणार कस</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-shiv-sena-gains-in-kolhapur-amid-rebellion-fears-dk88-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-political-move-to-keep-congress-out-of-kolhapur-municipal-corporation-dc95</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>LMOTY 2025: हे चेहरे गाजवणार महाराष्ट्राचं पुढचं राजकारण; कोण ठरणार प्रॉमिसिंग राजकारणी?</t>
+          <t>Chandrahar Patil : उद्धव ठाकरेंना मोठा धक्का! डबल महाराष्ट्र केसरी चंद्रहार पाटील आज शिंदेंच्या शिवसेनेत प्रवेश करणार</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/lokmat-maharashtrian-of-the-year-awards-2025-here-are-the-nominations-for-promising-politician-category-a-a301/</t>
+          <t>https://www.lokshahi.com/maharashtra/lokshahi-politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापुरात एकनाथ शिंदेंची 'जादू', एकाच वेळी काँग्रेस-भाजप आणि ताराराणी</t>
+          <t>Almatty Dam : कर्नाटक भाजपचे महाराष्ट्राविरोधात वाकडे पाऊल, अलमट्टी धरणाची उंची वाढवण्यासाठी केंद्रीय मंत्र्यांच्या गाठीभेटी, वाद चिघळणार?</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/kolhapur-20-corporaters-2-ex-mayor-joined-shiv-sena-eknath-shinde-mahapalika-elections-maharashtra-marathi-news-1365972</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/almatti-dam-height-increase-karnataka-bjp-mps-maharashtra-flood-risk-dispute-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Top Marathi News Today: अखेर कोकाटेंचं खातं बदललच;आता दिली 'या' खात्याची जबाबदारी</t>
+          <t>Almatti dam height : ‘आलमट्टी’वरून राजकीय वातावरण तापलं ; जलसंपदा मंत्री विखे पुन्हा घेणार सर्वपक्षीय बैठक!</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/radhakrishna-vikhe-patil-to-hold-all-party-meeting-on-almatti-dam-height-water-dispute-maharashtra-karnataka-msr87-rg93</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Kolhapur APMC election | सभापती निवडीत पालकमंत्र्यांची एंट्री</t>
+          <t>kolhapur | जिल्ह्यातील सहकारावर कागलचे वर्चस्व</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/guardian-ministers-entry-in-kolhapur-agricultural-produce-market-committee-chairman-election-ap84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mushrif-establishes-dominance-over-key-cooperative-institutions-in-district-ap84</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Gokul President Election : कोल्हापुरच्या राजकारणात मुश्रीफांची ताकद वाढली; जिल्हा बँक आणि गोकुळवर पितापुत्रांचं 'वर्चस्व', वाचा महिनाभरात काय काय घडलं?</t>
+          <t>नांदणी मठाची 'माधुरी' परत येणार? वनताराचे CEO म्हणाले, कोल्हापूरकरांना सर्व सहकार्य</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gokul-president-election-hasan-mushrif-son-elected-on-post-with-consent-of-satej-patil-kolhapur-politics/articleshow/121516780.cms</t>
+          <t>https://marathi.abplive.com/news/kolhapur/madhuri-mahadevi-elephant-vantara-ceo-meet-nandani-math-mathadipati-and-ready-to-provide-all-support-kolhapur-news-1374081</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Kolhapur : महायुतीच्या ‘रडार’वर काँग्रेस; सत्तेसाठी लावणार कस</t>
+          <t>Maharashtra Guardian Ministers List : पालकमंत्र्यांची यादी जाहीर, बीड आणि पुण्याबाबत सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-political-move-to-keep-congress-out-of-kolhapur-municipal-corporation-dc95</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Chandrahar Patil : उद्धव ठाकरेंना मोठा धक्का! डबल महाराष्ट्र केसरी चंद्रहार पाटील आज शिंदेंच्या शिवसेनेत प्रवेश करणार</t>
+          <t>Shiv Sena : कोल्हापुरात शिवसेनेचं वादळ, एकनाथ शिंदेंचा बंटी पाटील आणि महाडिक दोन्ही गटांना धक्का</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/maharashtra/lokshahi-politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Almatty Dam : कर्नाटक भाजपचे महाराष्ट्राविरोधात वाकडे पाऊल, अलमट्टी धरणाची उंची वाढवण्यासाठी केंद्रीय मंत्र्यांच्या गाठीभेटी, वाद चिघळणार?</t>
+          <t>Devendra Fadnavis : 'माधुरी'चा प्रश्न मार्गी लागणार? मंत्रिमंडळाच्या बैठकीत मुख्यमंत्री देवेंद्र फडणवीस यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/almatti-dam-height-increase-karnataka-bjp-mps-maharashtra-flood-risk-dispute-jap93-rg93</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Almatti dam height : ‘आलमट्टी’वरून राजकीय वातावरण तापलं ; जलसंपदा मंत्री विखे पुन्हा घेणार सर्वपक्षीय बैठक!</t>
+          <t>Maharashtra Karnataka Border Dispute: सीमाप्रश्नी उच्चाधिकार समितीची पुनर्रचना</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/radhakrishna-vikhe-patil-to-hold-all-party-meeting-on-almatti-dam-height-water-dispute-maharashtra-karnataka-msr87-rg93</t>
+          <t>https://agrowon.esakal.com/agro-special/reorganization-of-the-high-power-committee-on-border-issues-rat16</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : 'माधुरी'चा प्रश्न मार्गी लागणार? मंत्रिमंडळाच्या बैठकीत मुख्यमंत्री देवेंद्र फडणवीस यांची मोठी घोषणा</t>
+          <t>Maharashta Gurdian Ministers Full List : मुंबई ते गडचिरोली, बीड ते नागपूर, तुमच्या जिल्ह्याचा पालकमंत्री</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-on-mahadevi-elephant-of-nandani-math-to-file-petition-in-supreme-court/articleshow/123115303.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>kolhapur | जिल्ह्यातील सहकारावर कागलचे वर्चस्व</t>
+          <t>Mahayuti clash: महायुतीत पुन्हा धुसफूस, शिंदेंच्या मंत्र्यांच्या फाईल्स CMO मध्ये अडकल्या,</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mushrif-establishes-dominance-over-key-cooperative-institutions-in-district-ap84</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-shinde-shivsena-cabinet-ministers-get-angry-on-devendra-fadnavis-cmo-office-over-pa-and-osd-appointment-delay-1343532</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Maharashtra Guardian Ministers List : पालकमंत्र्यांची यादी जाहीर, बीड आणि पुण्याबाबत सरकारचा मोठा निर्णय</t>
+          <t>एकनाथ शिंदेंच्या वाढदिनी राज्यात उपमुख्यमंत्री वैद्यकीय मदत कक्षाची घोषणा</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-know-maharashtra-all-district-guardian-ministers-beed-ajit-pawar-dhananjay-munde-devendra-fadnavis-eknath-shinde-marathi-news-1339319</t>
+          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Shiv Sena : कोल्हापुरात शिवसेनेचं वादळ, एकनाथ शिंदेंचा बंटी पाटील आणि महाडिक दोन्ही गटांना धक्का</t>
+          <t>महादेवी हत्तीणीला परत आणण्यासाठी राज्य सरकार उचलणार मोठं पाऊल; मुख्यमंत्री देवेंद्र फडणवीसांनी सगळच सांगितलं</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/congress-leader-sharangdhar-deshmukh-and-many-bjp-formor-corporaters-joins-shiv-sena-in-kolhapur/articleshow/122053302.cms</t>
+          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Maharashtra Karnataka Border Dispute: सीमाप्रश्नी उच्चाधिकार समितीची पुनर्रचना</t>
+          <t>युवाशक्ती दहीहंडीला कोल्हापुरकरांनी मोठया संख्येने उपस्थित रहावे : खा. धनंजय महाडिक -</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/reorganization-of-the-high-power-committee-on-border-issues-rat16</t>
+          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Maharashta Gurdian Ministers Full List : मुंबई ते गडचिरोली, बीड ते नागपूर, तुमच्या जिल्ह्याचा पालकमंत्री</t>
+          <t>Nandani Math Mahadevi Elephant : नांदणी मठाची ‘माधुरी’ परत येणार? वनताराचे CEO काय म्हणाले?</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-guardian-ministers-list-declared-today-all-district-guardian-ministers-full-list-with-name-1339324</t>
+          <t>https://www.timemaharashtra.com/trending/nandani-math-mahadevi-elephant-will-nandani-maths-madhuri-return-what-did-vantaras-ceo-say/127830/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Mahayuti clash: महायुतीत पुन्हा धुसफूस, शिंदेंच्या मंत्र्यांच्या फाईल्स CMO मध्ये अडकल्या,</t>
+          <t>India reports 2 more deaths from Guillain-Barre Syndrome, raising total to 3</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-shinde-shivsena-cabinet-ministers-get-angry-on-devendra-fadnavis-cmo-office-over-pa-and-osd-appointment-delay-1343532</t>
+          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदेंच्या वाढदिनी राज्यात उपमुख्यमंत्री वैद्यकीय मदत कक्षाची घोषणा</t>
+          <t>More that 12k children died in Maharashtra between Apr last year and Feb 2025: Minister</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/on-eknath-shinde-birthday-deputy-chief-minister-announces-medical-aid-cell-in-the-state-mangesh-chivte-takes-responsibility-1343588</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>महादेवी हत्तीणीला परत आणण्यासाठी राज्य सरकार उचलणार मोठं पाऊल; मुख्यमंत्री देवेंद्र फडणवीसांनी सगळच सांगितलं</t>
+          <t>Statewide awareness campaign on organ donation from Aug 3 to 15</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/cm-devendra-fadnavis-first-reaction-about-mahadevi-hattini-case/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/statewide-awareness-campaign-on-organ-donation-from-aug-3-to-15/articleshow/123051558.cms</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>युवाशक्ती दहीहंडीला कोल्हापुरकरांनी मोठया संख्येने उपस्थित रहावे : खा. धनंजय महाडिक -</t>
+          <t>Maharashtra govt to set up vigilance cells to stop illegal uterus removals among cane cutters</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/kolhapurkars-should-attend-yuvashakti-dahi-handi-in-large-numbers-kha-dhananjay-mahadik/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Nandani Math Mahadevi Elephant : नांदणी मठाची ‘माधुरी’ परत येणार? वनताराचे CEO काय म्हणाले?</t>
+          <t>State govt proposes to amend Bombay Nursing Home Act; health dept to hire legal firm</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/trending/nandani-math-mahadevi-elephant-will-nandani-maths-madhuri-return-what-did-vantaras-ceo-say/127830/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>India reports 2 more deaths from Guillain-Barre Syndrome, raising total to 3</t>
+          <t>Kolhapur celebrates I-Day, Janmashtami &amp; Dahi Handi</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/asia-pacific/india-reports-2-more-deaths-from-guillain-barre-syndrome-raising-total-to-3/3465918</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>More that 12k children died in Maharashtra between Apr last year and Feb 2025: Minister</t>
+          <t>ZTCC, health minister honours families of deceased donors</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/more-that-12k-children-died-in-maharashtra-between-apr-last-year-and-feb-2025-minister/articleshow/122305074.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Maharashtra govt to set up vigilance cells to stop illegal uterus removals among cane cutters</t>
+          <t>Kolhapur IT Park &amp; employment initiatives announced at district investment summit</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/maharashtra-govt-to-set-up-vigilance-cells-to-stop-illegal-uterus-removals-among-cane-cutters/articleshow/121787362.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>State govt proposes to amend Bombay Nursing Home Act; health dept to hire legal firm</t>
+          <t>Kolhapur district planning body okays 67cr to revamp zilla parishad schools</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-govt-proposes-to-amend-bombay-nursing-home-act-health-dept-to-hire-legal-firm/articleshow/121275842.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Nurses’ strike leaves Sassoon wards deserted, administration struggles to find replacements</t>
+          <t>CA from Dhayari, 41, who died in Solapur, first GBS casualty; patient count in Pune touches 111</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-leaves-sassoon-wards-deserted-administration-struggles-to-find-replacements/articleshow/122844933.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ZTCC, health minister honours families of deceased donors</t>
+          <t>Patient records at 2,100 centres to be digitised</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ztcc-health-minister-honours-families-of-deceased-donors/articleshow/121456553.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Kolhapur IT Park &amp; employment initiatives announced at district investment summit</t>
+          <t>Tender scam hits Akola women’s hospital, dist civil surgeon, two other top officials suspended</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-it-park-employment-initiatives-announced-at-district-investment-summit/articleshow/120241529.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Kolhapur district planning body okays 67cr to revamp zilla parishad schools</t>
+          <t>Maharashtra health department cancels deputation of Nashik civic body’s medical superintendent</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-district-planning-body-okays-67cr-to-revamp-zilla-parishad-schools/articleshow/122031265.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CA from Dhayari, 41, who died in Solapur, first GBS casualty; patient count in Pune touches 111</t>
+          <t>Bike ambulances, ICUs along wari routes: State health min</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ca-from-dhayari-41-who-died-in-solapur-first-gbs-casualty-patient-count-in-pune-touches-111/articleshow/117612506.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Tender scam hits Akola women’s hospital, dist civil surgeon, two other top officials suspended</t>
+          <t>Will Elephant Mahadevi Return To Kolhapur From Jamnagars Vantara? Details Inside</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/tender-scam-hits-akola-womens-hospital-dist-civil-surgeon-two-other-top-officials-suspended/articleshow/123049068.cms</t>
+          <t>https://www.freepressjournal.in/pune/will-elephant-mahadevi-return-to-kolhapur-from-jamnagars-vantara-details-inside</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Patient records at 2,100 centres to be digitised</t>
+          <t>संपादकीय: सरकार कोई हल निकाले, किसानों की कर्ज माफी का मुद्दा ज्वलंत</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/patient-records-at-2100-centres-to-be-digitised/articleshow/120073226.cms</t>
+          <t>https://navbharatlive.com/special-coverage/high-level-committee-will-be-formed-within-15-days-to-take-a-decision-on-loan-waiver-1256403.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Maharashtra health department cancels deputation of Nashik civic body’s medical superintendent</t>
+          <t>महाराष्ट्र में मेडिकल व्यवस्था हुई 'बीमार', 200 से अधिक नए स्वास्थ्य केंद्रों पर लटका ताला</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/maharashtra-health-department-cancels-deputation-of-nashik-civic-bodys-medical-superintendent/articleshow/120136444.cms</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-more-than-200-newly-built-health-centres-locked-1224919.html</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Bike ambulances, ICUs along wari routes: State health min</t>
+          <t>NCP नेता हसन मुश्रीफ ने वाशिम के पालक मंत्री पद से दिया इस्तीफा, बोले- आने-जाने में होती हैं दिक्कत</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/bike-ambulances-icus-along-wari-routes-state-health-min/articleshow/121837480.cms</t>
+          <t>https://navbharatlive.com/maharashtra/washim/ncp-minister-hasan-mushrif-resigned-washim-guardian-minister-citing-travel-difficulties-1145083.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Will Elephant Mahadevi Return To Kolhapur From Jamnagars Vantara? Details Inside</t>
+          <t>Maharashtra’s roadmap discussed at NDTV Marathi Manch</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/will-elephant-mahadevi-return-to-kolhapur-from-jamnagars-vantara-details-inside</t>
+          <t>https://bestmediainfo.com/mediainfo/mediainfo-marketing/maharashtras-roadmap-discussed-at-ndtv-marathi-manch-9009029</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>संपादकीय: सरकार कोई हल निकाले, किसानों की कर्ज माफी का मुद्दा ज्वलंत</t>
+          <t>Maha govt launches organ donation fortnight, Minister Abitkar takes lead by filling form</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/special-coverage/high-level-committee-will-be-formed-within-15-days-to-take-a-decision-on-loan-waiver-1256403.html</t>
+          <t>https://ianslive.in/maharashtra-govt-launches-organ-donation-fortnight--20250804092958</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में मेडिकल व्यवस्था हुई 'बीमार', 200 से अधिक नए स्वास्थ्य केंद्रों पर लटका ताला</t>
+          <t>Cases rise amid 1st GBS death; Central team reaches Pune</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-more-than-200-newly-built-health-centres-locked-1224919.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>NCP नेता हसन मुश्रीफ ने वाशिम के पालक मंत्री पद से दिया इस्तीफा, बोले- आने-जाने में होती हैं दिक्कत</t>
+          <t>Maharashtra to implement ‘No shortage, no wastage’ policy for blood management</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/washim/ncp-minister-hasan-mushrif-resigned-washim-guardian-minister-citing-travel-difficulties-1145083.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Maharashtra’s roadmap discussed at NDTV Marathi Manch</t>
+          <t>Medical health complex &amp; upgraded facilities inaugurated at govt hospitals in Kolhapur</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://bestmediainfo.com/mediainfo/mediainfo-marketing/maharashtras-roadmap-discussed-at-ndtv-marathi-manch-9009029</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Maha govt launches organ donation fortnight, Minister Abitkar takes lead by filling form</t>
+          <t>Maharashtra health minister pushes reforms, seeks new policy and faster recruitment</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://ianslive.in/maharashtra-govt-launches-organ-donation-fortnight--20250804092958</t>
+          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Cases rise amid 1st GBS death; Central team reaches Pune</t>
+          <t>Maharashtra Gears Up for 68th National School Yoga Sports Championship Starting January 16</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cases-rise-amid-1st-gbs-death-central-team-reaches-pune-101738004588536.html</t>
+          <t>https://impressivetimes.com/latest/news-3192/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Maharashtra to implement ‘No shortage, no wastage’ policy for blood management</t>
+          <t>Sanjeevani: Transforming Cancer Care Through Unity and Awareness</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maharashtra-to-implement-no-shortage-no-wastage-policy-for-blood-management-101749837522129.html</t>
+          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Medical health complex &amp; upgraded facilities inaugurated at govt hospitals in Kolhapur</t>
+          <t>Pune Observes World Malaria Day With Awareness Rally At Tadiwala Road</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/medical-health-complex-upgraded-facilities-inaugurated-at-govt-hospitals-in-kolhapur/articleshow/122271776.cms</t>
+          <t>https://www.freepressjournal.in/pune/pune-observes-world-malaria-day-with-awareness-rally-at-tadiwala-road</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Maharashtra Gears Up for 68th National School Yoga Sports Championship Starting January 16</t>
+          <t>Deputy Chief Minister Ajit Pawar Inaugurates Special Health Screening Drive Under National Child Health Program In Pune</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/news-3192/</t>
+          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad News: PCMC Honoured with State Health Awards</t>
+          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pcmc/pimpri-chinchwad-news-pcmc-honoured-with-state-health-awards/</t>
+          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Sanjeevani: Transforming Cancer Care Through Unity and Awareness</t>
+          <t>Pune: Statewide Childrens Health Checkup Campaign Begins In Aundh Tomorrow</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3548680-sanjeevani-transforming-cancer-care-through-unity-and-awareness</t>
+          <t>https://www.freepressjournal.in/pune/pune-statewide-childrens-health-checkup-campaign-begins-in-aundh-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Pune Observes World Malaria Day With Awareness Rally At Tadiwala Road</t>
+          <t>Maharashtra School Education Minister Dadaji Bhuse Proposes Mobile App For Student Health Check-Ups Under RBSK</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-observes-world-malaria-day-with-awareness-rally-at-tadiwala-road</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-school-education-minister-dadaji-bhuse-proposes-mobile-app-for-student-health-check-ups-under-rbsk</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Deputy Chief Minister Ajit Pawar Inaugurates Special Health Screening Drive Under National Child Health Program In Pune</t>
+          <t>Maharashtra: Solapur man suspected to have died of Guillain-Barre syndrome; cases rise to 110 in Pune</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/deputy-chief-minister-ajit-pawar-inaugurates-special-health-screening-drive-under-national-child-health-program-in-pune/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
+          <t>Maharashtra Announces Free Cancer Vaccination for Girls Aged 0-14 Amid Rising Cases</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
+          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Pune: Statewide Childrens Health Checkup Campaign Begins In Aundh Tomorrow</t>
+          <t>Over 14,000 women detected with cancer-like symptoms in Maharashtra</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-statewide-childrens-health-checkup-campaign-begins-in-aundh-tomorrow</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-over-14000-women-detected-with-cancer-like-symptoms-in-hingoli-2753909-2025-07-10</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Maharashtra: Solapur man suspected to have died of Guillain-Barre syndrome; cases rise to 110 in Pune</t>
+          <t>Ashadhi Wari 2025: Maharashtra Plans Safer, Greener Pilgrimage to Pandharpur</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-solapur-man-suspected-to-have-died-of-guillain-barre-syndrome-cases-rise-to-110-in-pune-3375494</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Maharashtra Announces Free Cancer Vaccination for Girls Aged 0-14 Amid Rising Cases</t>
+          <t>Residents of 18 villages to observe bandh today to oppose merger into KMC limits</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://thelogicalindian.com/maharashtra-announces-free-cancer-vaccination-for-girls-aged-0-14-amid-rising-cases/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Over 14,000 women detected with cancer-like symptoms in Maharashtra</t>
+          <t>Another person dies in Maharashtra from Guillain-Barre syndrome: Death toll rises to 2, 16 new cases report...</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-over-14000-women-detected-with-cancer-like-symptoms-in-hingoli-2753909-2025-07-10</t>
+          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Maharashtra Faces Cancer Crisis: Over 14500 Women in Hingoli Show ‘Cancer-Like’ Symptoms During Govt Health Screening</t>
+          <t>शक्ति पीठ महामार्ग का प्रस्ताव … मलाई खाने के लिए भाजपा और शिंदे गुट में टकराव! … रु.२०,००० करोड़ के बजट पर है नजर</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.thehealthsite.com/news/maharashtra-faces-cancer-crisis-over-14500-women-in-hingoli-show-cancer-like-symptoms-during-govt-health-screening-1239129/</t>
+          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ashadhi Wari 2025: Maharashtra Plans Safer, Greener Pilgrimage to Pandharpur</t>
+          <t>MoS Civil Aviation Shri Murlidhar Mohol inaugurates new ATC Tower cum Technical Block cum Fire Station at Kolhapur Airport</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-plans-safer-greener-ashadhi-wari-pilgrimage-3562273</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2128928</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Residents of 18 villages to observe bandh today to oppose merger into KMC limits</t>
+          <t>Chief Justice Of India To Inaugurate Kolhapur Circuit Bench Of Bombay High Court</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/residents-of-18-villages-to-observe-bandh-today-to-oppose-merger-into-kmc-limits/articleshow/121893678.cms</t>
+          <t>https://www.livelaw.in/events/justice-bhushan-ramkrishna-gavai-kolhapur-circuit-bench-bombay-high-court-inaugration-events-300775</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Another person dies in Maharashtra from Guillain-Barre syndrome: Death toll rises to 2, 16 new cases report...</t>
+          <t>Shahu Maharaj’s 151st birth anniversary celebrated in Kolhapur</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/9-new-cases-of-guillain-barre-syndrome-in-solapur-maharashtra-total-case-rises-to-111-1-dead-134369537.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Maharashtra School Education Minister Dadaji Bhuse Proposes Mobile App For Student Health Check-Ups Under RBSK</t>
+          <t>Kolhapur : कोल्हापूर चित्रनगरीमधील चित्रीकरण स्थळांचं लोकार्पण व भूमिपूजन कार्यक्रम संपन्न</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-school-education-minister-dadaji-bhuse-proposes-mobile-app-for-student-health-check-ups-under-rbsk</t>
+          <t>https://www.navarashtra.com/videos/kolhapur-dedication-and-foundation-stone-laying-ceremony-of-filming-locations-in-kolhapur-chitranagari-concluded-914427.html</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Maharashtra health minister pushes reforms, seeks new policy and faster recruitment</t>
+          <t>मुख्यमंत्री रोजगार निर्मिती कार्यक्रम : कोल्हापूर जिल्हा राज्यात अग्रस्थानी</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/healthcare/maharashtra-health-minister-pushes-reforms-seeks-new-policy-and-faster-recruitment-19606814.htm</t>
+          <t>https://mahasamvad.in/170909/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>शक्ति पीठ महामार्ग का प्रस्ताव … मलाई खाने के लिए भाजपा और शिंदे गुट में टकराव! … रु.२०,००० करोड़ के बजट पर है नजर</t>
+          <t>Kolhapur Politics : शिंदेंचा बंटी पाटील अन् महाडिकांना धक्का; शारंगधर देशमुखांसह कोल्हापुरातील बड्या नेत्यांचा शिवसेनेत प्रवेश</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/proposal-for-shakti-peeth-highway-conflict-between-bjp-and-shinde-faction-for-getting-the-cream-eye-on-rs-20000-crore-budget/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-congress-leaders-join-shivsena-kolhapur-shock-satej-patil-and-dhananjay-mahadik-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>MoS Civil Aviation Shri Murlidhar Mohol inaugurates new ATC Tower cum Technical Block cum Fire Station at Kolhapur Airport</t>
+          <t>कोल्हापूर चित्रनगरीत मंत्री अॅड. आशिष शेलार यांच्या उपस्थितीत विविध विकासकामांचे उद्घाटन व लोकार्पण</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2128928</t>
+          <t>https://mahasamvad.in/170610/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Chief Justice Of India To Inaugurate Kolhapur Circuit Bench Of Bombay High Court</t>
+          <t>Kolhapur Circuit Bench Inauguration |कोल्हापूर सर्किट बेंचचा 17 ऑगस्टला शानदार शुभारंभ</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/events/justice-bhushan-ramkrishna-gavai-kolhapur-circuit-bench-bombay-high-court-inaugration-events-300775</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inauguration-17-august-chief-justice-gavai-arade-cm-grand-ceremony-5000-seating-sp96</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Kolhapur celebrates I-Day, Janmashtami &amp; Dahi Handi</t>
+          <t>ShivSena News : एकनाथ शिंदेंच्या 'मंगेशाची' आमदारकीसाठी मोर्चेबांधणी; चिवटेंना हवा 'गुरुजींचा' आशीर्वाद</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-celebrates-i-day-janmashtami-dahi-handi/articleshow/123339139.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mangesh-chivate-mlc-election-pune-teachers-constituency-eknath-shinde-shiv-sena-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Shahu Maharaj’s 151st birth anniversary celebrated in Kolhapur</t>
+          <t>हद्दवाढीसाठी आज मुंबईत बैठक</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/shahu-maharajs-151st-birth-anniversary-celebrated-in-kolhapur/articleshow/122098503.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/meeting-in-mumbai-today-for-boundary-extension</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Kolhapur : कोल्हापूर चित्रनगरीमधील चित्रीकरण स्थळांचं लोकार्पण व भूमिपूजन कार्यक्रम संपन्न</t>
+          <t>अंबाबाई, जोतिबा मंदिर विकासाच्या पहिल्या टप्प्याचे काम लवकरच सुरू</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/kolhapur-dedication-and-foundation-stone-laying-ceremony-of-filming-locations-in-kolhapur-chitranagari-concluded-914427.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/ambabai-jyotiba-temple-development-phase-one-to-begin-soon-dc95</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>मुख्यमंत्री रोजगार निर्मिती कार्यक्रम : कोल्हापूर जिल्हा राज्यात अग्रस्थानी</t>
+          <t>...तर शिंदे शिवसेनाही स्वबळावर स्थानिक स्वराज्यच्या मैदानात</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170909/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-municipal-corporation-election</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Kolhapur Political News : काँग्रेसला मोठं भगदाड, 35 जणांची यादी तयार, मुंबईत होणार पक्षप्रवेश</t>
+          <t>हद्दवाढीसंदर्भात सोमवारी मुंबईत उपमुख्यमंत्री शिंदे यांच्याकडे बैठक</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-elections-congress-35-leaders-will-join-shiv-sena-mumbai-entry-rm82-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-shinde-to-hold-meeting-in-mumbai-on-monday-regarding-boundary-extension</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>कोल्हापूर चित्रनगरीत मंत्री अॅड. आशिष शेलार यांच्या उपस्थितीत विविध विकासकामांचे उद्घाटन व लोकार्पण</t>
+          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170610/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/lokaraja-rajarshi-chhatrapati-shahu-jayanti-celebrations-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : शिंदेंचा बंटी पाटील अन् महाडिकांना धक्का; शारंगधर देशमुखांसह कोल्हापुरातील बड्या नेत्यांचा शिवसेनेत प्रवेश</t>
+          <t>हद्दवाढीचा प्रस्ताव महापालिकेकडून सरकारकडे सादर ! कोल्हापूरसाठी लवकरच तीन आनंदाच्या बातम्या !!</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-congress-leaders-join-shivsena-kolhapur-shock-satej-patil-and-dhananjay-mahadik-as11-rg93</t>
+          <t>https://maharashtranews1.com/The-proposal-for-the-extension-has-been-sent-from-the-municipality-to-the-government--Three-good-news-coming-soon-for-Kolhapur--</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench Inauguration |कोल्हापूर सर्किट बेंचचा 17 ऑगस्टला शानदार शुभारंभ</t>
+          <t>Maharashtra: 10,000 Farmers to Hold State-Wide March In Mumbai On March 12 Against 'Shaktipeeth Highway'</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inauguration-17-august-chief-justice-gavai-arade-cm-grand-ceremony-5000-seating-sp96</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>हद्दवाढीसाठी आज मुंबईत बैठक</t>
+          <t>Ajit Pawar’s Directive Clears Path for IT Hub in Kolhapur</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/meeting-in-mumbai-today-for-boundary-extension</t>
+          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ShivSena News : एकनाथ शिंदेंच्या 'मंगेशाची' आमदारकीसाठी मोर्चेबांधणी; चिवटेंना हवा 'गुरुजींचा' आशीर्वाद</t>
+          <t>बाजार समिती सभापतिपद अजित पवार गटाकडे</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mangesh-chivate-mlc-election-pune-teachers-constituency-eknath-shinde-shiv-sena-hn97-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/market-committee-chairmanship-to-ajit-pawar-group-ap84</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>अंबाबाई, जोतिबा मंदिर विकासाच्या पहिल्या टप्प्याचे काम लवकरच सुरू</t>
+          <t>Elephantiasis eradication drug campaign launched in 3 Vid districts</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/ambabai-jyotiba-temple-development-phase-one-to-begin-soon-dc95</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>...तर शिंदे शिवसेनाही स्वबळावर स्थानिक स्वराज्यच्या मैदानात</t>
+          <t>चौदा वर्षे वयापर्यंतच्या मुलींना कर्करोगप्रतिबंधक लस देण्याचा विचार; अजित पवार यांची माहिती</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-municipal-corporation-election</t>
+          <t>https://pudhari.news/maharashtra/pune/consideration-of-anti-cancer-vaccine-for-girls-up-to-fourteen-years-of-age-information-given-by-ajit-pawar</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>हद्दवाढीसंदर्भात सोमवारी मुंबईत उपमुख्यमंत्री शिंदे यांच्याकडे बैठक</t>
+          <t>सार्वजनिक आरोग्य पायाभूत सुविधा महामंडळ उभारणीसाठी कार्यवाही करावी- मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/deputy-chief-minister-shinde-to-hold-meeting-in-mumbai-on-monday-regarding-boundary-extension</t>
+          <t>https://mahasamvad.in/160560/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Shahu Maharaj Jayanti | लोकराजा राजर्षी छत्रपती शाहू जयंतीचा आज सोहळा</t>
+          <t>प्रत्येक बालकाला सशक्त आणि निरोगी जीवनाची हमी देण्याचे काम करुया – उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/lokaraja-rajarshi-chhatrapati-shahu-jayanti-celebrations-today-ap84</t>
+          <t>https://mahasamvad.in/157898/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>हद्दवाढीचा प्रस्ताव महापालिकेकडून सरकारकडे सादर ! कोल्हापूरसाठी लवकरच तीन आनंदाच्या बातम्या !!</t>
+          <t>ठाणे जिल्हा रुग्णालय एमएमआर मधील नागरिकांसाठी वरदान ठरणार – उपमुख्यमंत्री एकनाथ शिंदे</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-proposal-for-the-extension-has-been-sent-from-the-municipality-to-the-government--Three-good-news-coming-soon-for-Kolhapur--</t>
+          <t>https://mahasamvad.in/173688/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Maharashtra: 10,000 Farmers to Hold State-Wide March In Mumbai On March 12 Against 'Shaktipeeth Highway'</t>
+          <t>Government fully supports implementation of Jyotiba temple development plan: Fadnavis</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-farmers-to-hold-state-wide-march-in-mumbai-on-march-12-against-shaktipeeth-highway-enn25030105581</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Ajit Pawar’s Directive Clears Path for IT Hub in Kolhapur</t>
+          <t>Maharashtra approves Rs 20,787 crores for Nagpur-Goa Shaktipeeth Expressway</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/ajit-pawars-directive-clears-path-for-it-hub-in-kolhapur/</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-nagpur-goa-shaktipeeth-expressway-land-acquisition-pilgrimage-tourism-2745741-2025-06-25</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>बाजार समिती सभापतिपद अजित पवार गटाकडे</t>
+          <t>Rising GBS cases: Pune Municipal Corporation issues strict regulations for RO projects</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/market-committee-chairmanship-to-ajit-pawar-group-ap84</t>
+          <t>https://www.thehansindia.com/news/national/rising-gbs-cases-pune-municipal-corporation-issues-strict-regulations-for-ro-projects-946718</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Elephantiasis eradication drug campaign launched in 3 Vid districts</t>
+          <t>Shiv Sena names 17 district liaison mins, escalates power battle in Mahayuti</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/elephantiasis-eradication-drug-campaign-launched-in-3-vid-districts/articleshow/118126932.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>India Achieves Five Guinness World Records in Ayurveda</t>
+          <t>High-powered committee on Maharashtra-Karnataka boundary issue reconstituted</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://observervoice.com/india-achieves-five-guinness-world-records-in-ayurveda-97959/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>चौदा वर्षे वयापर्यंतच्या मुलींना कर्करोगप्रतिबंधक लस देण्याचा विचार; अजित पवार यांची माहिती</t>
+          <t>‘Jt guardian post introduced to include more ministers’</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/consideration-of-anti-cancer-vaccine-for-girls-up-to-fourteen-years-of-age-information-given-by-ajit-pawar</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>सार्वजनिक आरोग्य पायाभूत सुविधा महामंडळ उभारणीसाठी कार्यवाही करावी- मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>MP Shrikant Shinde refutes Sanjay Raut’s ambulance scam allegations</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160560/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>प्रत्येक बालकाला सशक्त आणि निरोगी जीवनाची हमी देण्याचे काम करुया – उपमुख्यमंत्री अजित पवार</t>
+          <t>Discord in Maharashtra govt over fund-shift to Ladki Bahin Yojana</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157898/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ठाणे जिल्हा रुग्णालय एमएमआर मधील नागरिकांसाठी वरदान ठरणार – उपमुख्यमंत्री एकनाथ शिंदे</t>
+          <t>Fadnavis first Maha CM to become guardian minister</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173688/</t>
+          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Government fully supports implementation of Jyotiba temple development plan: Fadnavis</t>
+          <t>MP राऊतांविषयी सवाल, MP Shrikant Shinde यांनी स्पष्टच केलं, कोण Sanjay Raut?</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/government-fully-supports-implementation-of-jyotiba-temple-development-plan-fadnavis/articleshow/121658981.cms</t>
+          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Maharashtra approves Rs 20,787 crores for Nagpur-Goa Shaktipeeth Expressway</t>
+          <t>Kolhapur Political News : काँग्रेसला मोठं भगदाड, 35 जणांची यादी तयार, मुंबईत होणार पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-nagpur-goa-shaktipeeth-expressway-land-acquisition-pilgrimage-tourism-2745741-2025-06-25</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-elections-congress-35-leaders-will-join-shiv-sena-mumbai-entry-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Shiv Sena names 17 district liaison mins, escalates power battle in Mahayuti</t>
+          <t>Kolhapur Ashokrao Mane : चर्चेचा विषय! आमदार अशोकराव माने नेमके कुणाचे? शिवसेना पक्ष कार्यालय उद्‌घाटनाला उपस्थित; राजकारण्यांना पडला प्रश्न</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/shiv-sena-names-17-district-liaison-mins-escalates-power-battle-in-mahayuti/articleshow/118768428.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/mla-ashokrao-mane-presence-at-a-shiv-sena-office-inauguration-has-stirred-political-debate-in-kolhapur-srs92</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>High-powered committee on Maharashtra-Karnataka boundary issue reconstituted</t>
+          <t>Maharashtra Health Department to set up committee for effective leprosy eradication</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/high-powered-committee-on-maharashtra-karnataka-boundary-issue-reconstituted-3594693</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-health-department-to-set-up-committee-for-effective-leprosy-eradication/article69815684.ece</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>‘Jt guardian post introduced to include more ministers’</t>
+          <t>111 Diagnosed With Guillain-Barre Syndrome In Maharashtra: Health Minister</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/jt-guardian-post-introduced-to-include-more-ministers/articleshow/117361674.cms</t>
+          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MP Shrikant Shinde refutes Sanjay Raut’s ambulance scam allegations</t>
+          <t>Health minister JP Nadda promises steady IVIG supply for Guillain-Barre Syndrome (GBS), say officials</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/mp-shrikant-shinde-refutes-sanjay-rauts-ambulance-scam-allegations/articleshow/122927746.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Discord in Maharashtra govt over fund-shift to Ladki Bahin Yojana</t>
+          <t>State to bring all diagnostic labs under health dept’s purview</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/discord-in-maha-govt-over-fund-shift-to-ladki-bahin-yojana/articleshow/120865279.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Fadnavis first Maha CM to become guardian minister</t>
+          <t>Pune: 76 Private Hospitals Issued Notices for Regulatory Violations</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/fadnavis-first-maha-cm-to-become-guardian-minister/articleshow/117364890.cms</t>
+          <t>https://www.thebridgechronicle.com/news/pune-76-private-hospitals-issued-notices-for-regulatory-violations</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MP राऊतांविषयी सवाल, MP Shrikant Shinde यांनी स्पष्टच केलं, कोण Sanjay Raut?</t>
+          <t>Guillain-Barré cases in Pune cross 100, health ministry sends expert team</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/shrikant-shinde-in-kolhapur-criticized-on-sanjay-raut-mahayuti-win-in-election-2025/</t>
+          <t>https://www.downtoearth.org.in/health/guillain-barr%C3%A9-cases-in-pune-cross-100-health-ministry-sends-expert-team-to-pune</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Shivsena Politics: महाडिक, मुश्रीफ अन् सतेज पाटलांच्या बालेकिल्ल्यात शिंदे मोठा धमाका करणार; एक दोन नव्हे,तर 30 मात्तबर नेते ...</t>
+          <t>State plans Maharashtra Institute of Virology, along the lines of NIV</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/eknath-shinde-big-move-in-kolhapur-stronghold-of-dhananjay-mahadik-hasan-mushrif-satej-patil-30-leaders-to-join-dk88-rg93</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Kolhapur Ashokrao Mane : चर्चेचा विषय! आमदार अशोकराव माने नेमके कुणाचे? शिवसेना पक्ष कार्यालय उद्‌घाटनाला उपस्थित; राजकारण्यांना पडला प्रश्न</t>
+          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/mla-ashokrao-mane-presence-at-a-shiv-sena-office-inauguration-has-stirred-political-debate-in-kolhapur-srs92</t>
+          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>मुश्रीफांनी सोडलं, अजित पवारांनी दत्ता मामांना घेरलं; कसा सुटला अखेर वाशिमच्या पालकमंत्रीपदाचा तिढा!</t>
+          <t>Tally of nerve disorder GBS rises to 180 in Pune; Mumbai records first case</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/datta-mama-bharne-appointed-as-guardian-minister-of-washim-district-ajit-pawar-hasan-mushrif-023877.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Maharashtra Health Department to set up committee for effective leprosy eradication</t>
+          <t>Nurses’ strike stalls health services at state-run hosps</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-health-department-to-set-up-committee-for-effective-leprosy-eradication/article69815684.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>111 Diagnosed With Guillain-Barre Syndrome In Maharashtra: Health Minister</t>
+          <t>Wildlife Protest Kolhapur: Thousands March to Demand Elephant Mahadevi's Return from Vantara</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/73-diagnosed-with-guillain-barre-syndrome-in-maharashtra-1-dead-health-minister-7571304</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Health minister JP Nadda promises steady IVIG supply for Guillain-Barre Syndrome (GBS), say officials</t>
+          <t>Accident victims to receive ₹1L cashless treatment, says health minister | Mumbai news</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/health-minister-jp-nadda-promises-steady-ivig-supply-for-guillain-barre-syndrome-gbs-say-officials/articleshow/117901162.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Pune: 76 Private Hospitals Issued Notices for Regulatory Violations</t>
+          <t>Maha govt signs two MoUs with PHFI, IMMAST for quality and capacity building in health sector</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/pune-76-private-hospitals-issued-notices-for-regulatory-violations</t>
+          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>State to bring all diagnostic labs under health dept’s purview</t>
+          <t>Nagpur Doctors Urge Govt to Simplify Hospital Renewal Process, Reduce Paperwork</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-to-bring-all-diagnostic-labs-under-health-dept-s-purview-101754853867506.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Guillain-Barré cases in Pune cross 100, health ministry sends expert team</t>
+          <t>After 13-yr delay, govt says will open Nagpur District Hospital in 3 months</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.downtoearth.org.in/health/guillain-barr%C3%A9-cases-in-pune-cross-100-health-ministry-sends-expert-team-to-pune</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>State plans Maharashtra Institute of Virology, along the lines of NIV</t>
+          <t>Sewage from hotels, poultry farms near Khadakwasla under scanner: Health minister</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-plans-maharashtra-institute-of-virology-along-the-lines-of-niv-101747166457054.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Pending ASHA honorariums released; Maharashtra govt announces major health reforms</t>
+          <t>Maharashtra govt eyeing to make HPV vaccine available for girls: Ajit Pawar</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/index.php/news/newsDisplay?newsID=1286583</t>
+          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Tally of nerve disorder GBS rises to 180 in Pune; Mumbai records first case</t>
+          <t>Maharashtra Faces Cancer Crisis: Over 14500 Women in Hingoli Show ‘Cancer-Like’ Symptoms During Govt Health Screening</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tally-of-nerve-disorder-gbs-rises-to-180-in-pune-mumbai-records-first-case-3396082</t>
+          <t>https://www.thehealthsite.com/news/maharashtra-faces-cancer-crisis-over-14500-women-in-hingoli-show-cancer-like-symptoms-during-govt-health-screening-1239129/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Nurses’ strike stalls health services at state-run hosps</t>
+          <t>Maha to amend Nursing Homes Registration rules</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nurses-strike-stalls-health-services-at-state-run-hosps/articleshow/122822145.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Committee to monitor leprosy elimination programmes to be set up: Health minister</t>
+          <t>Aarogya Mitras in Maharashtra call off indefinite strike</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/committee-to-monitor-leprosy-elimination-programmes-to-be-set-up-health-minister-101752693298474.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Accident victims to receive ₹1L cashless treatment, says health minister | Mumbai news</t>
+          <t>Maharashtra Government Plans To Introduce Extensive Health Policy For Medical Tourism</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/accident-victims-to-receive-1l-cashless-treatment-says-health-minister-101745004207376.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-plans-to-introduce-extensive-health-policy-for-medical-tourism</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Wildlife Protest Kolhapur: Thousands March to Demand Elephant Mahadevi's Return from Vantara</t>
+          <t>Crores Sanctioned, No Compound Walls Built: Corruption Cloud Over Pune’s Yerawada Mental Hospital</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thousands-participate-in-silent-march-to-seek-mahadevis-return-from-vantara-3663297</t>
+          <t>https://www.freepressjournal.in/pune/crores-sanctioned-no-compound-walls-built-corruption-cloud-over-punes-yerawada-mental-hospital</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Nagpur Doctors Urge Govt to Simplify Hospital Renewal Process, Reduce Paperwork</t>
+          <t>Over 14,500 Women Detected With Cancer-Like Symptoms Post Screening In Maharashtra's Hingoli</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nagpur-doctors-urge-govt-to-simplify-hospital-renewal-process-reduce-paperwork/articleshow/119412467.cms</t>
+          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Maha govt signs two MoUs with PHFI, IMMAST for quality and capacity building in health sector</t>
+          <t>Maharashtra govt framing policy to stop water contamination for prevention of illnesses: Minister</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-govt-signs-two-mous-with-phfi-immast-for-quality-and-capacity-building-in-health-sector-992487</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>After 13-yr delay, govt says will open Nagpur District Hospital in 3 months</t>
+          <t>Maharashtra Child Deaths: Over 12,000 Children Died Between April 2024 and Feb 2025</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/after-13-yr-delay-govt-says-will-open-nagpur-district-hospital-in-3-months/articleshow/118946488.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Sewage from hotels, poultry farms near Khadakwasla under scanner: Health minister</t>
+          <t>Maharashtra Live Updates : सरकारी दवाख्यान्यात बोगस औषधांचा पुरवठा? आरोग्य मंत्री प्रकाश आबिटकरांचीही कबुली</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/sewage-from-hotels-poultry-farms-near-khadakwasla-under-scanner-health-minister/articleshow/118035732.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-updates-17-july-2025-assembly-monsoon-session-mahayuti-vs-mahavikas-aghadi-raj-thackeray-uddhav-thackeray-alliance-sambhaji-brigade-pravin-gaikwad-ncp-jayant-patil-shashikant-shinde-rohit-pawar-sharad-pwar-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Maharashtra govt eyeing to make HPV vaccine available for girls: Ajit Pawar</t>
+          <t>Jyotiba Chaitra Yatra : जोतिबा डोंगरावर दुपारी बारालाच निघणार सासनकाठी मिरवणूक; मंदिर 79 तास राहणार खुले</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/maharashtra-govt-eyeing-to-make-hpv-vaccine-available-for-girls-ajit-pawar-12953935.html</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/jyotiba-chaitra-yatra-sasan-kathi-miravnuk-minister-prakash-abitkar-jyotiba-dongar-kolhapur-bam92</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Maha to amend Nursing Homes Registration rules</t>
+          <t>Maharashtra Breaking News LIVE 9 January 2025 : राज्यपाल नियुक्त 12 आमदारांबाबतची याचिका फेटाळली</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/maha-to-amend-nursing-homes-registration-rules-101738608962430.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Aarogya Mitras in Maharashtra call off indefinite strike</t>
+          <t>Top Marathi News Today: अखेर कोकाटेंचं खातं बदललच;आता दिली 'या' खात्याची जबाबदारी</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/aarogya-mitras-in-maharashtra-call-off-indefinite-strike-101740248468386.html</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-national-international-sports-crime-business-lifestyle-946881.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Maharashtra Government Plans To Introduce Extensive Health Policy For Medical Tourism</t>
+          <t>येरवडा रुग्णालयातून '11 लाखांची अंतर्वस्त्रे गायब,' चौकशी समितीच्या अहवालातून कोणता घोटाळा समोर आलाय?</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-plans-to-introduce-extensive-health-policy-for-medical-tourism</t>
+          <t>https://www.bbc.com/marathi/articles/c93n25pxqe1o</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Crores Sanctioned, No Compound Walls Built: Corruption Cloud Over Pune’s Yerawada Mental Hospital</t>
+          <t>देवस्थान जमिनी कसणाऱ्यांचे खंड शिबिराद्वारे भरून घ्या - पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/crores-sanctioned-no-compound-walls-built-corruption-cloud-over-punes-yerawada-mental-hospital</t>
+          <t>https://www.lokmat.com/kolhapur/fill-the-gaps-of-temple-land-cultivators-through-camps-says-guardian-minister-abitkar-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Over 14,500 Women Detected With Cancer-Like Symptoms Post Screening In Maharashtra's Hingoli</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/over-14-500-women-detected-with-cancer-like-symptoms-post-screening-in-maharashtra-hingoli-1787139</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Maharashtra govt framing policy to stop water contamination for prevention of illnesses: Minister</t>
+          <t>Nanded News : धक्कादायक! नांदेडच्या शासकीय ग्रामीण रुग्णालयात उंदरांचं साम्राज्य, चक्क</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-framing-policy-to-stop-water-contamination-for-prevention-of-illnesses-minister/118755456</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Maharashtra Child Deaths: Over 12,000 Children Died Between April 2024 and Feb 2025</t>
+          <t>शक्तिपीठ महामार्ग कोल्हापूर जिल्हा वगळून गोव्याला नेणार कसा? शेतकऱ्यांचा सवाल; जिल्हाधिकारी कार्यालयासमोर धरणे आंदोलन</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/more-that-12k-children-died-in-maharashtra-between-april-last-year-and-february-2025-minister-3619100</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-farmers-question-mahayuti-government-over-nagpur-goa-shaktipeeth-highway-bam92</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : सरकारी दवाख्यान्यात बोगस औषधांचा पुरवठा? आरोग्य मंत्री प्रकाश आबिटकरांचीही कबुली</t>
+          <t>Maharashtra Breaking LIVE: देश-विदेशातील महत्त्वाच्या घडामोडींचा आढावा फक्त एका क्लिकवर...</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-updates-17-july-2025-assembly-monsoon-session-mahayuti-vs-mahavikas-aghadi-raj-thackeray-uddhav-thackeray-alliance-sambhaji-brigade-pravin-gaikwad-ncp-jayant-patil-shashikant-shinde-rohit-pawar-sharad-pwar-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-breaking-live-updates-today-29th-may-2025-vishanavi-hagawane-case-pune-crime-monsoon-updates-mumbai-rains-1361408</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Jyotiba Chaitra Yatra : जोतिबा डोंगरावर दुपारी बारालाच निघणार सासनकाठी मिरवणूक; मंदिर 79 तास राहणार खुले</t>
+          <t>आता चिंता जलजन्य आजारांची; औषधांचा पुरेसा साठा राज्यात उपलब्ध करण्याचे आरोग्य मंत्री आबिटकर यांचे आदेश</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/jyotiba-chaitra-yatra-sasan-kathi-miravnuk-minister-prakash-abitkar-jyotiba-dongar-kolhapur-bam92</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/waterborne-diseases-health-minister-abitkar-orders-medicine-stock</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>आता चिंता जलजन्य आजारांची; औषधांचा पुरेसा साठा राज्यात उपलब्ध करण्याचे आरोग्य मंत्री आबिटकर यांचे आदेश</t>
+          <t>केंद्रीय आरोग्य सेवा योजनेच्या दरांमध्ये सुधारणा करणार – केंद्रीय मंत्री मनसुख मांडविया</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/waterborne-diseases-health-minister-abitkar-orders-medicine-stock</t>
+          <t>https://mahasamvad.in/172749/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>केंद्रीय आरोग्य सेवा योजनेच्या दरांमध्ये सुधारणा करणार – केंद्रीय मंत्री मनसुख मांडविया</t>
+          <t>३ ते १५ ऑगस्ट २०२५ या कालावधीत अवयवदान पंधरवडा साजरा होणार – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172749/</t>
+          <t>https://mahasamvad.in/173717/</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>३ ते १५ ऑगस्ट २०२५ या कालावधीत अवयवदान पंधरवडा साजरा होणार – सार्वजनिक आरोग्य व कुटुंब कल्याण मंत्री प्रकाश आबिटकर</t>
+          <t>विधानपरिषद प्रश्नोत्तरे</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173717/</t>
+          <t>https://mahasamvad.in/172235/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>विधानपरिषद प्रश्नोत्तरे</t>
+          <t>Mahadevi Elephant: कोल्हापुर की 'महादेवी' हथिनी को वनतारा से वापस लाने की मांग तेज, लोगों ने किया मौन मार्च</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172235/</t>
+          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant: कोल्हापुर की 'महादेवी' हथिनी को वनतारा से वापस लाने की मांग तेज, लोगों ने किया मौन मार्च</t>
+          <t>पुणे से देश की आर्थिक राजधानी पहुंचा गिलियन बैरे सिंड्रोम, मुंबई में जीबीएस का पहला केस</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mahadevi-elephant-demand-to-bring-back-from-vantara-intensifies-people-held-silent-march-mp-mla-meet-ministers-2025-08-03</t>
+          <t>https://zeenews.india.com/hindi/health/first-case-of-guillain-barre-syndrome-in-mumbai-total-gbs-patient-number-180-maharashtra/2637580</t>
         </is>
       </c>
     </row>
@@ -6023,120 +6023,120 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>आरोग्य क्षेत्रातील दर्जा व क्षमता वृद्धीसाठी पीएचएफआय, आयएमएमएएसटी यांच्यासोबत महाराष्ट्र शासनाचा सामंजस्य करार</t>
+          <t>पुणे में बरपा गुलियन-बैरे सिंड्रोम का कहर, दूषित पानी पीने से अस्पताल में लगा मरीजों का तांता</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173797/</t>
+          <t>https://www.totaltv.in/guillain-barre-syndrome-wreaks-havoc-in-pune-patients-throng-hospitals-due-to-drinking-contaminated-water/</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>सर्वांगीण निरोगी महाराष्ट्र घडविण्यासाठी राज्य शासन कटिबद्ध- उपमुख्यमंत्री अजित पवार</t>
+          <t>आरोग्य क्षेत्रातील दर्जा व क्षमता वृद्धीसाठी पीएचएफआय, आयएमएमएएसटी यांच्यासोबत महाराष्ट्र शासनाचा सामंजस्य करार</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163359/</t>
+          <t>https://mahasamvad.in/173797/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>‘रुग्ण सेवा हीच ईश्वर सेवा; जनसामान्यांची सेवा हाच धर्म’ – उपमुख्यमंत्री एकनाथ शिंदे</t>
+          <t>सर्वांगीण निरोगी महाराष्ट्र घडविण्यासाठी राज्य शासन कटिबद्ध- उपमुख्यमंत्री अजित पवार</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/155268/</t>
+          <t>https://mahasamvad.in/163359/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Rain causes road closures, travel delays in Satara and Kolhapur districts</t>
+          <t>‘रुग्ण सेवा हीच ईश्वर सेवा; जनसामान्यांची सेवा हाच धर्म’ – उपमुख्यमंत्री एकनाथ शिंदे</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
+          <t>https://mahasamvad.in/155268/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Kolhapur civic body yet to acquire Jayprabha Studio</t>
+          <t>Rain causes road closures, travel delays in Satara and Kolhapur districts</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/rain-causes-road-closures-travel-delays-in-satara-and-kolhapur-districts/articleshow/121996384.cms</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Double Maharashtra Kesari Chandrahar Patil Joins Shinde's Shiv Sena</t>
+          <t>Kolhapur civic body yet to acquire Jayprabha Studio</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/kolhapur-civic-body-yet-to-acquire-jayprabha-studio/articleshow/122146378.cms</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Maharashtra's Rs 123 crore mortuary van project stuck, 132 new vehicles unused</t>
+          <t>Double Maharashtra Kesari Chandrahar Patil Joins Shinde's Shiv Sena</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
+          <t>https://english.lokshahi.com/politics/chandrahar-patil-will-join-eknath-shinde-shivsena-today</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Senior NCP Minister Hasan Mushrif Steps Down As Washims Guardian Minister</t>
+          <t>Maharashtra's Rs 123 crore mortuary van project stuck, 132 new vehicles unused</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-senior-ncp-minister-hasan-mushrif-steps-down-as-washims-guardian-minister</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-government-rs-123-crore-mortuary-van-project-132-new-vehicles-unused-2693784-2025-03-15</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Gokul Dudh Sangh : ‘गोकुळ’मध्ये पुन्हा अरुणोदय की नव्या रक्ताला संधी; नव्या अध्यक्ष निवडीसाठी घडामोडींना वेग, पाटील-मुश्रीफांचा पुढील डाव काय?</t>
+          <t>Maharashtra Politics: Senior NCP Minister Hasan Mushrif Steps Down As Washims Guardian Minister</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-arun-dengle-get-president-of-gokul-dudh-sangh-or-will-give-a-chance-to-new-blood-vd83-rg-93</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-senior-ncp-minister-hasan-mushrif-steps-down-as-washims-guardian-minister</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : प्रकाश आबिटकरांना स्वकियांचेचं आव्हान, भाजप, अजित पवार गटाचा विरोध; जिल्हा नियोजन समितीवरून पडणार ठिणगी</t>
+          <t>Gokul Dudh Sangh : ‘गोकुळ’मध्ये पुन्हा अरुणोदय की नव्या रक्ताला संधी; नव्या अध्यक्ष निवडीसाठी घडामोडींना वेग, पाटील-मुश्रीफांचा पुढील डाव काय?</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/prakash-abitkar-kolhapur-guardian-minister-faced-dissent-from-bjp-especially-shinde-aligned-factions-during-a-district-planning-committee-meeting-srs92</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/will-arun-dengle-get-president-of-gokul-dudh-sangh-or-will-give-a-chance-to-new-blood-vd83-rg-93</t>
         </is>
       </c>
     </row>
@@ -6227,144 +6227,144 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>"No one has to worry": Maharashtra Health Minister Prakash Abitkar on HMPV virus</t>
+          <t>Sassoon Hospital awarded for organ transplant efforts - Hindustan Times</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/no-one-has-to-worry-maharashtra-health-minister-prakash-abitkar-on-hmpv-virus20250109063259</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Sassoon Hospital awarded for organ transplant efforts - Hindustan Times</t>
+          <t>AIIMS Nagpur Bags 3 More Awards For Excellence In Organ Donation</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/sassoon-hospital-awarded-for-organ-transplant-efforts-101754679587697-amp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>AIIMS Nagpur Bags 3 More Awards For Excellence In Organ Donation</t>
+          <t>Maharashtra Mumbai Rain Live Updates, 19 August 2025 : मुंबईला पावसाचा तडाखा, चेंबूरमध्ये मोनोरेल थांबली; बचावकार्याचा थरार जारी</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/aiims-nagpur-bags-3-more-awards-for-excellence-in-organ-donation/articleshow/123124288.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Kolhapur residents hold silent march, seek return of elephant Mahadevi from Gujarat’s Vantara</t>
+          <t>राज्यात अवयवदान पंधरवड्याला प्रारंभ</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
+          <t>https://www.newsonair.gov.in/mr/organ-donation-fortnight-begins-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Maharashtra Live News 8th August 2025 : गोपीचंद पडळकर शरणू हांडेंच्या भेटीला रुग्णालयात</t>
+          <t>Maharashtra Live Updates : पंकजा मुंडेंकडे दाद मागणाऱ्या आंदोलकाच्या कमरेत पोलिस अधिकाऱ्यानेच घातली लाथ</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-15-august-2025-latest-marathi-political-news-eknath-shinde-aaditya-thackeray-bdd-chawl-redevelopment-best-election-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-ajit-pawar-devendra-fadnavis-uddhav-thackeray-india-alliance-mns-shivsena-kabutarkhana-dhananjay-munde-pm-modi-speech-live-79th-independence-day</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>राज्यात अवयवदान पंधरवड्याला प्रारंभ</t>
+          <t>Maharashtra News: स्वातंत्र्य दिनाचा मुख्य शासकीय समारोह मुंबईत; पाहा कोण कुठे करणार ध्वजारोहण, संपूर्ण यादी Independence Day main government ceremony will be held in Mumbai; See who will hoist the flag where?</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/organ-donation-fortnight-begins-in-the-state/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : पंकजा मुंडेंकडे दाद मागणाऱ्या आंदोलकाच्या कमरेत पोलिस अधिकाऱ्यानेच घातली लाथ</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा झटपट आढावा</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-15-august-2025-latest-marathi-political-news-eknath-shinde-aaditya-thackeray-bdd-chawl-redevelopment-best-election-mumbai-mahayuti-rahul-gandhi-congress-india-aghadi-election-commission-ajit-pawar-devendra-fadnavis-uddhav-thackeray-india-alliance-mns-shivsena-kabutarkhana-dhananjay-munde-pm-modi-speech-live-79th-independence-day</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Maharashtra News: स्वातंत्र्य दिनाचा मुख्य शासकीय समारोह मुंबईत; पाहा कोण कुठे करणार ध्वजारोहण, संपूर्ण यादी Independence Day main government ceremony will be held in Mumbai; See who will hoist the flag where?</t>
+          <t>नांदणी मठाची ‘माधुरी’ परत येणार? वनताराच्या CEO ने कोल्हापूरकरांना दिली ग्वाही</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/independence-day-main-government-ceremony-will-be-held-in-mumbai-see-who-will-hoist-the-flag-where-88154</t>
+          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा झटपट आढावा</t>
+          <t>Independence Day 2025 : स्वातंत्र्यदिनानिमित्त तुमच्या जिल्ह्यात कोण करणार ध्वजारोहण?; वाचा यादी</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-august-02-breaking-news-in-marathi-929005</t>
+          <t>https://puneprimenews.com/pune/independence-day-2025-who-will-hoist-the-flag-in-your-district-on-independence-day-read-the-list/</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Independence Day 2025 : स्वातंत्र्यदिनानिमित्त तुमच्या जिल्ह्यात कोण करणार ध्वजारोहण?; वाचा यादी</t>
+          <t>Kolhapur Circuit Bench | कोल्हापूर सर्किट बेंचचे सरन्यायाधीशांच्या हस्ते दिमाखात उद्घाटन; कोल्हापुरात मोठा उत्साह</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/independence-day-2025-who-will-hoist-the-flag-in-your-district-on-independence-day-read-the-list/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inaugurated-by-the-chief-justice-great-excitement-in-kolhapur-an01</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench | कोल्हापूर सर्किट बेंचचे सरन्यायाधीशांच्या हस्ते दिमाखात उद्घाटन; कोल्हापुरात मोठा उत्साह</t>
+          <t>Devendra Fadnavis : ‘आपले सरकार’ सेवांतील विलंबावर आळा घालण्यासाठी अधिकाऱ्यांवर दररोज दंड लावण्याचे निर्देश</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-circuit-bench-inaugurated-by-the-chief-justice-great-excitement-in-kolhapur-an01</t>
+          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Maharashtra Mumbai Rain Live Updates, 19 August 2025 : मुंबईला पावसाचा तडाखा, चेंबूरमध्ये मोनोरेल थांबली; बचावकार्याचा थरार जारी</t>
+          <t>Maharashtra Live News 8th August 2025 : गोपीचंद पडळकर शरणू हांडेंच्या भेटीला रुग्णालयात</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-19th-august-2025-marathi-live-updates-heavy-rain-in-mumbai-maharashtra-weather-update/liveblog/123376395.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-august-2025-live-updates-mumbai-maharashtra-weather-uddhav-thackeray-in-delhi-ban-on-feeding-pigeons-at-kabutar-khana-uttarkashi-cloudburst/liveblog/123178672.cms</t>
         </is>
       </c>
     </row>
@@ -6383,216 +6383,216 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Nanded News : धक्कादायक! नांदेडच्या शासकीय ग्रामीण रुग्णालयात उंदरांचं साम्राज्य, चक्क</t>
+          <t>Madhuri Elephant | 'माधुरी हत्तीणी'साठी राज्य सरकार आणि मठ सुप्रीम कोर्टात याचिका दाखल करणार</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-government-rural-hospital-rats-playing-on-female-patient-body-maharashtra-marathi-news-1373983</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-government-and-nandani-math-will-file-petition-in-supreme-court-for-madhuri-elephant-db79</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : ‘आपले सरकार’ सेवांतील विलंबावर आळा घालण्यासाठी अधिकाऱ्यांवर दररोज दंड लावण्याचे निर्देश</t>
+          <t>बेमुदत कामबंद आंदोलनास सुरुवात; NHM अंतर्गत १० हजारांहून अधिक अधिकारी-कर्मचारी रस्त्यावर</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/aaple-sarkar-directs-to-impose-daily-fines-on-officials-to-curb-delays-in-services-268424/amp/</t>
+          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Madhuri Elephant | 'माधुरी हत्तीणी'साठी राज्य सरकार आणि मठ सुप्रीम कोर्टात याचिका दाखल करणार</t>
+          <t>Madhuri Elephant | माधुरी हत्तीण परत येणार? कोल्हापुरकरांना मुख्यमंत्र्यांचा मोठा शब्द</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-government-and-nandani-math-will-file-petition-in-supreme-court-for-madhuri-elephant-db79</t>
+          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>नांदणी मठाची ‘माधुरी’ परत येणार? वनताराच्या CEO ने कोल्हापूरकरांना दिली ग्वाही</t>
+          <t>Hindustani Bhau : 'तुम्ही जेवता ना @# तर नाही खात ना?'; माधुरी हत्तीण वादात हिंदुस्थानी भाऊची उडी, Video व्हायरल</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/madhuri-the-elephant-may-return-to-nandani-math-if-supreme-court-allows-says-vantara-ceo/</t>
+          <t>https://www.dainikprabhat.com/maharashtra-news-hindustani-bhau-madhuri-elephant-kolhapur-vantara/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>बेमुदत कामबंद आंदोलनास सुरुवात; NHM अंतर्गत १० हजारांहून अधिक अधिकारी-कर्मचारी रस्त्यावर</t>
+          <t>न्यायाच्या कोल्हापूर पर्वाला उद्यापासून सुरुवात</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://vsrsnews.com/health/indefinite-work-stoppage-begins-more-than-10000-officers-and-employees-on-the-streets-under-nhm/</t>
+          <t>https://ratnagirikhabardar.com/news/74101/</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Madhuri Elephant | माधुरी हत्तीण परत येणार? कोल्हापुरकरांना मुख्यमंत्र्यांचा मोठा शब्द</t>
+          <t>रत्नागिरी : राष्ट्रीय आरोग्य अभियान (एनआरएचएम) कर्मचाऱ्यांचा उद्यापासून बेमुदत संप</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/will-madhuri-the-elephant-return-chief-ministers-big-word-to-kolhapur-residents/</t>
+          <t>https://ratnagirikhabardar.com/news/74350/</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>युवाशक्ती दहीहंडीचा थरार २४ ऑगस्टला रंगणार, प्रथम क्रमांकाला ३ लाख रूपयांचे बक्षीस</t>
+          <t>कोल्हापूर सर्किट बेंच इमारतीचे दिमाखदार उद्घाटन</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-excitement-of-Youth-Power-Dahi-Handi-will-take-place-on-August-24--with-a-prize-of-3-lakh-rupees-for-the-first-place-</t>
+          <t>https://ratnagirikhabardar.com/news/74156/</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench : न्यायाच्या कोल्हापूर पर्वाला सुरुवात; सरन्यायाधीशांच्‍या उपस्थितीत सर्किट बेंचचे होणार उद्घाटन</t>
+          <t>Guillain Barre Syndrome Cases: Health Ministry Deploys 7-member team to Pune</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/kolhapur-circuit-bench-kolhapur-festival-of-justice-begins-circuit-bench-to-be-inaugurated-in-the-presence-of-chief-justice/</t>
+          <t>https://medicaldialogues.in/news/health/guillain-barre-syndrome-cases-health-ministry-deploys-7-member-team-to-pune-142306</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>न्यायाच्या कोल्हापूर पर्वाला उद्यापासून सुरुवात</t>
+          <t>NHM employees begin indefinite strike, healthcare services impacted</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74101/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>रत्नागिरी : राष्ट्रीय आरोग्य अभियान (एनआरएचएम) कर्मचाऱ्यांचा उद्यापासून बेमुदत संप</t>
+          <t>Of 1.4L+ docs in Maha, only 10k opt in for ‘KYD’ QR code scheme</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74350/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Indian city faces rising cases of GBS disease</t>
+          <t>Thousands participate in silent march to seek Mahadevi's return from Vantara</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://www.dw.com/en/indian-city-faces-rising-cases-of-gbs-disease/a-71430960</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>NHM employees begin indefinite strike, healthcare services impacted</t>
+          <t>Kolhapur residents hold silent march, seek return of elephant Mahadevi from Gujarat’s Vantara</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-begin-indefinite-strike-healthcare-services-impacted/articleshow/123394385.cms</t>
+          <t>https://nenow.in/national/kolhapur-residents-hold-silent-march-seek-return-of-elephant-mahadevi-from-gujarats-vantara.html</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Of 1.4L+ docs in Maha, only 10k opt in for ‘KYD’ QR code scheme</t>
+          <t>Maharashtra To Launch Statewide Organ Donation Drive From August 3 To 15</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/of-1-4l-docs-in-maha-only-10k-opt-in-for-kyd-qr-code-scheme/articleshow/123103167.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-launch-statewide-organ-donation-drive-from-august-3-to-15</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Thousands participate in silent march to seek Mahadevi's return from Vantara</t>
+          <t>Exclusive: राज्यात राष्ट्रीय बाल स्वास्थ्य कार्यक्रमाची ऐसीतैसी!</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/03/bom5-mh-elephant-morcha.html</t>
+          <t>https://www.tendernama.com/scam-scanner/maharashtra-health-department-tender-scam</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Exclusive: राज्यात राष्ट्रीय बाल स्वास्थ्य कार्यक्रमाची ऐसीतैसी!</t>
+          <t>गतवर्षी प्रमाणे यंदाही वारकरी दिंड्यांना सरकार अनुदान देणार : आचार्य तुषार भोसले</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/scam-scanner/maharashtra-health-department-tender-scam</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>गतवर्षी प्रमाणे यंदाही वारकरी दिंड्यांना सरकार अनुदान देणार : आचार्य तुषार भोसले</t>
+          <t>माधुरी हत्तीण परत आणण्याबाबत राज्य शासनाने घेतला ‘हा’ मोठा निर्णय; वाचा सविस्तर…</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/14/government-will-provide-subsidy-to-Warkari-Dindya-Acharya-Tushar-Bhosale.html</t>
+          <t>https://puneprimenews.com/mumbai/the-state-government-took-this-big-decision-to-bring-back-madhuri-the-elephant-read-in-detail/</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>माधुरी हत्तीण परत आणण्याबाबत राज्य शासनाने घेतला ‘हा’ मोठा निर्णय; वाचा सविस्तर…</t>
+          <t>न्यायाच्या कोल्हापूर पर्वाला १७ ऑगस्टपासून सुरुवात</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/the-state-government-took-this-big-decision-to-bring-back-madhuri-the-elephant-read-in-detail/</t>
+          <t>https://mahasamvad.in/175429/</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>न्यायाच्या कोल्हापूर पर्वाला १७ ऑगस्टपासून सुरुवात</t>
+          <t>Mahadevi Elephant : महादेवी मठात परतणार? वनतारा अन् राज्य सरकारच मोठं पाऊल, नांदणीत पुनर्वसन केंद्र उभारणार?</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175429/</t>
+          <t>https://www.dainikprabhat.com/vantara-and-the-state-government-will-jointly-file-a-petition-in-the-supreme-court-for-mahadevi/</t>
         </is>
       </c>
     </row>
@@ -6683,12 +6683,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE 9 January 2025 : राज्यपाल नियुक्त 12 आमदारांबाबतची याचिका फेटाळली</t>
+          <t>Latest Marathi News Updates : देश-विदेशासह राज्यात दिवसभरात काय घडलं? वाचा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-updates-on-maharashtra-politics-santosh-deshmukh-murder-case-walmik-karad-cm-devendra-fadnavis-hmpv-virus-news-in-marathi-aajchya-thalak-batmya-thursday-8th-january-20-1331560.html</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
@@ -6700,355 +6700,355 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-january-28-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-881014</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Latest Marathi News Updates : देश-विदेशासह राज्यात दिवसभरात काय घडलं? वाचा एका क्लिकवर</t>
+          <t>ABP माझा टॉप 10 हेडलाईन्स | 12 मे 2025 | सोमवार</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-live-marathi-news-12-july-2025-shivaji-maharaj-forts-unesco-world-heritage-sites-language-issue-raj-thackeray-uddhav-thackeray-monsoon-kokan-pune-mumbai-vidarbha-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-stock-market-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>Breaking News Today : महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-february-14-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-885459</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>ABP माझा टॉप 10 हेडलाईन्स | 12 मे 2025 | सोमवार</t>
+          <t>Mumbai: देवेंद्र फडणवीसांचा मोठा निर्णय, आता घरबसल्या करता येणार दस्त नोंदणी वन</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/abp-majha-top-10-headlines-12-may-2025-narendra-modi-india-pak-devendra-fadnavis-sharad-pawar-maharashtra-politics-marathi-news-1358801</t>
+          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Breaking News Today : महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
+          <t>अधिवेशनात गाजला बीड आरोग्य विभागातील घोटाळा; जिल्हा शल्य चिकित्सकांचं निलंबन</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-july-2025-marathi-live-updates-maharashtra-rain-raj-thackeray-uddhav-thackeray-legislative-assembly-monsoon-session-2025/liveblog/122260508.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Mumbai: देवेंद्र फडणवीसांचा मोठा निर्णय, आता घरबसल्या करता येणार दस्त नोंदणी वन</t>
+          <t>गुलाल खोबऱ्याची उधळण; जोतिबाच्या नावानं चांगभलंच्या गजरात चैत्र यात्रेला सुरुवात</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/mumbai-maharashtra-marathi-news-devendra-fadnavis-big-decision-now-document-registration-can-be-done-from-home-one-state-one-registration-will-be-implemented-soon-1337614</t>
+          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>अधिवेशनात गाजला बीड आरोग्य विभागातील घोटाळा; जिल्हा शल्य चिकित्सकांचं निलंबन</t>
+          <t>पाच लाख भाविकांच्या उपस्थितीत दख्खनचा राजा जोतिबाची चैत्र यात्रा, डोंगरावर 'चांगभलं'चा गजर - JOTIBA CHAITRA YATRA 2025</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/beed-district-surgeon-suspended-by-health-minister-for-fraud-in-covid-period-namita-mundada-asked-questions-in-assembly-budget-session-2025-maharashtra-news-mhs25032501768</t>
+          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>गुलाल खोबऱ्याची उधळण; जोतिबाच्या नावानं चांगभलंच्या गजरात चैत्र यात्रेला सुरुवात</t>
+          <t>राजर्षी छत्रपती शाहू महाराजांची जयंती उत्साहात साजरी; शरद पवारांसह विविध मान्यवरांनी केलं अभिवादन</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jotiba-yatra-2025-shree-jyotiba-devsthan-kolhapur-temple-management-committee-and-administration-ready-for-jyotiba-chaitra-yatra-maharashtra-news-mhs25041104772</t>
+          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Kolhapur News: उद्योजकाच्या लेकाचा जीव गेला, १२ लाखांच्या बाईकचा चेंदामेंदा, ७० हजारांच्या हेल्मेटचा चुराडा</t>
+          <t>तिजोरीतील खडखडाटामुळे ५० वर्षानंतर सरकारनं घेतला महत्त्वाचा निर्णय, तळीरामांसह व्यावसायिकांसाठी नवीन संधी</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/kolhapur-businessman-son-died-in-horrifying-accident-with-car-expensive-bike-and-helmet-broken-into-pieces/articleshow/120491249.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/new-wine-shop-license-in-maharashtra-ajit-pawar-lead-committee-to-issue-new-liquor-licenses-to-328-wine-shops-to-increase-revenue-in-state-treasury-maharashtra-news-mhs25071302746</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>पाच लाख भाविकांच्या उपस्थितीत दख्खनचा राजा जोतिबाची चैत्र यात्रा, डोंगरावर 'चांगभलं'चा गजर - JOTIBA CHAITRA YATRA 2025</t>
+          <t>Maharashtra cancels registration of 258 Private Hospitals</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/jyotiba-chaitra-yatra-in-the-presence-of-lakhs-of-devotees-at-jyotiba-temple-kolhapur-maharashtra-news-mhs25041203162</t>
+          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/maharashtra-cancels-registration-of-258-private-hospitals-152138</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>राजर्षी छत्रपती शाहू महाराजांची जयंती उत्साहात साजरी; शरद पवारांसह विविध मान्यवरांनी केलं अभिवादन</t>
+          <t>Maharashtra govt to provide free cancer vaccine for girls, takes precautions against bird flu</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shahu-maharaj-jayanti-celebrated-with-great-enthusiasm-in-kolhapur-mp-shahu-maharaj-chhatrapati-and-sharad-pawar-pay-tribute-to-shahu-maharaj-maharashtra-news-mhs25062605058</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>शक्तिपीठ महामार्ग कोल्हापूर जिल्हा वगळून गोव्याला नेणार कसा? शेतकऱ्यांचा सवाल; जिल्हाधिकारी कार्यालयासमोर धरणे आंदोलन</t>
+          <t>India Achieves Five Guinness World Records in Ayurveda</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-farmers-question-mahayuti-government-over-nagpur-goa-shaktipeeth-highway-bam92</t>
+          <t>https://observervoice.com/india-achieves-five-guinness-world-records-in-ayurveda-97959/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Maharashtra cancels registration of 258 Private Hospitals</t>
+          <t>kolhapur News : अधिकार्‍यांनी नावीन्यतेसह गुणवत्तापूर्ण कामे करावीत</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/hospital-diagnostics/maharashtra-cancels-registration-of-258-private-hospitals-152138</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/guardian-minister-abitkar-reviews-all-departments-in-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Maharashtra govt to provide free cancer vaccine for girls, takes precautions against bird flu</t>
+          <t>Dairy Farming: आदर्श गोठा पुरस्काराचा राज्यभरात आदर्श घ्यावा; पालकमंत्री आबिटकर</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-govt-to-provide-free-cancer-vaccine-for-girls-takes-precautions-against-bird-flu/118649890</t>
+          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Dairy Farming: आदर्श गोठा पुरस्काराचा राज्यभरात आदर्श घ्यावा; पालकमंत्री आबिटकर</t>
+          <t>कोल्हापूर : गावठाणाबाहेरील मिळकतींनाही मिळणार प्रॉपर्टी कार्ड</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/model-cattle-shed-award-ceremony-in-kolhapur-2025-sai29</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-property-cards-for-non-gaothan-properties-dc95</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>कोल्हापूर : गावठाणाबाहेरील मिळकतींनाही मिळणार प्रॉपर्टी कार्ड</t>
+          <t>Cashless Treatment of Up to Rs 1 Lakh Announced for Accident Victims in Maharashtra</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-property-cards-for-non-gaothan-properties-dc95</t>
+          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>PMC felicitated for ABDM Excellence</t>
+          <t>मोठी बातमी ! अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार, आरोग्य खात्याचा महत्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-launches-cashless-accident-treatment-up-to-1-lakh-1387143.html</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Cashless Treatment of Up to Rs 1 Lakh Announced for Accident Victims in Maharashtra</t>
+          <t>महात्मा फुले जनआरोग्य योजनेबाबत आरोग्यमंत्र्यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cashless-treatment-of-up-to-rs-1-lakh-announced-for-accident-victims-in-maharashtra/</t>
+          <t>https://www.loksatta.com/pune/health-minister-big-announcement-regarding-mahatma-phule-jan-arogya-yojana-pune-print-news-amy-95-5251004/</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>मोठी बातमी ! अपघातग्रस्त रुग्णांसाठी 1 लाखांपर्यंत कॅशलेस उपचार, आरोग्य खात्याचा महत्वपूर्ण निर्णय</t>
+          <t>महात्मा जोतिराव फुले जनआरोग्य योजना ठप्प</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-launches-cashless-accident-treatment-up-to-1-lakh-1387143.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mahatma-jyotirao-phule-janarogya-yojana-halted</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>महात्मा फुले जनआरोग्य योजनेबाबत आरोग्यमंत्र्यांची मोठी घोषणा</t>
+          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/health-minister-big-announcement-regarding-mahatma-phule-jan-arogya-yojana-pune-print-news-amy-95-5251004/</t>
+          <t>https://www.mahasamvad.in/154371/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>महात्मा जोतिराव फुले जनआरोग्य योजना ठप्प</t>
+          <t>‘लाडकी बहीण’मुळे आरोग्याचा खेळखंडोबा</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mahatma-jyotirao-phule-janarogya-yojana-halted</t>
+          <t>https://dainikekmat.com/%E0%A4%B2%E0%A4%BE%E0%A4%A1%E0%A4%95%E0%A5%80-%E0%A4%AC%E0%A4%B9%E0%A5%80%E0%A4%A3%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8B%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%BE/96992/</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>प्रधानमंत्री आवास योजनेतील घरकुलांच्या कामांना गती द्या – मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Maharashtra CM Fadnavis orders special arrangements for treating GBS patients</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/154371/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>‘लाडकी बहीण’मुळे आरोग्याचा खेळखंडोबा</t>
+          <t>Maharashtra Plans Bigger Organ Transplant Budget Under MJPJAY; Wadia Hospital Gets Pediatric Heart Transplant</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B2%E0%A4%BE%E0%A4%A1%E0%A4%95%E0%A5%80-%E0%A4%AC%E0%A4%B9%E0%A5%80%E0%A4%A3%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%86%E0%A4%B0%E0%A5%8B%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%BE/96992/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-plans-bigger-organ-transplant-budget-under-mjpjay-wadia-hospital-gets-pediatric-heart-transplant-license</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis orders special arrangements for treating GBS patients</t>
+          <t>जागतिक आरोग्य दिनी विविध आरोग्य योजनांचा शुभारंभ</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cm-fadnavis-orders-special-arrangements-for-treating-gbs-patients-3376753</t>
+          <t>https://mahasamvad.in/161521/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Maharashtra Plans Bigger Organ Transplant Budget Under MJPJAY; Wadia Hospital Gets Pediatric Heart Transplant</t>
+          <t>GBS Outbreak in Pune: Citizens Confront Central Health Team Over Alleged Inspection Failure</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-plans-bigger-organ-transplant-budget-under-mjpjay-wadia-hospital-gets-pediatric-heart-transplant-license</t>
+          <t>https://www.thebridgechronicle.com/news/gbs-outbreak-in-pune-citizens-confront-central-health-team-over-alleged-inspection-failure</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>जागतिक आरोग्य दिनी विविध आरोग्य योजनांचा शुभारंभ</t>
+          <t>Pune Pregnant Woman's Death: Preliminary Report Highlights Negligence by Deenanath Mangeshkar Hospital</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161521/</t>
+          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>GBS Outbreak in Pune: Citizens Confront Central Health Team Over Alleged Inspection Failure</t>
+          <t>Pune: शहरात 76 खासगी रुग्णालयांना नोटीस</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/gbs-outbreak-in-pune-citizens-confront-central-health-team-over-alleged-inspection-failure</t>
+          <t>https://pudhari.news/maharashtra/pune/notice-to-76-private-hospitals-in-the-city</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Pune Pregnant Woman's Death: Preliminary Report Highlights Negligence by Deenanath Mangeshkar Hospital</t>
+          <t>MLA Bhimrao Tapkir : सर्व पाणीपुरवठा स्त्रोतांचे नियमित क्लोरीनेशन करून त्यावर देखरेख ठेवा; जीबीएसबाबत उपाययोजनेचे दिले आदेश</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-pregnant-womans-death-preliminary-report-highlights-negligence-by-deenanath-mangeshkar-hospital/</t>
+          <t>https://www.esakal.com/pune/regular-chlorination-of-all-water-supply-sources-ordered-by-gbs-for-safety-mla-bhimrao-tapkir-khadakwasla-pjp78</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Pune: शहरात 76 खासगी रुग्णालयांना नोटीस</t>
+          <t>Four organ transplant coordination centres to be set up in Maharashtra</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/notice-to-76-private-hospitals-in-the-city</t>
+          <t>https://theprint.in/india/four-organ-transplant-coordination-centres-to-be-set-up-in-maharashtra/2602255/</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MLA Bhimrao Tapkir : सर्व पाणीपुरवठा स्त्रोतांचे नियमित क्लोरीनेशन करून त्यावर देखरेख ठेवा; जीबीएसबाबत उपाययोजनेचे दिले आदेश</t>
+          <t>Pune hospital conferred 'Best BSD Award' and 'Best Organ Transplant Coordinator Award'</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/regular-chlorination-of-all-water-supply-sources-ordered-by-gbs-for-safety-mla-bhimrao-tapkir-khadakwasla-pjp78</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
         </is>
       </c>
     </row>
@@ -7115,336 +7115,336 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Mahadevi Elephant Case: State Government Takes Proactive Role, Matter to Be Reconsidered in Supreme Court</t>
+          <t>Maharashtra to launch accreditation system for private hospitals</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/top-stories/mahadevi-elephant-state-governments-proactive-role-for-mahadevi-madhuri-elephant-will-be-reconsidered-in-the-supreme-court</t>
+          <t>https://medicalbuyer.co.in/maharashtra-to-launch-accreditation-system-for-private-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>More than 14.5k women detected with cancer-like symptoms post screening in Hingoli</t>
+          <t>Mahadevi Elephant Case: State Government Takes Proactive Role, Matter to Be Reconsidered in Supreme Court</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
+          <t>https://english.lokshahi.com/top-stories/mahadevi-elephant-state-governments-proactive-role-for-mahadevi-madhuri-elephant-will-be-reconsidered-in-the-supreme-court</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक; प्रस्ताव सादर करण्याचे मंत्री आबिटकर यांचे निर्देश</t>
+          <t>More than 14.5k women detected with cancer-like symptoms post screening in Hingoli</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/workers-insurance-scheme-healthcare-infrastructure-prakash-abhitkar</t>
+          <t>https://health.economictimes.indiatimes.com/news/industry/mass-screening-in-hingoli-reveals-cancer-like-symptoms-in-over-14500-women/122380886</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>वारी मार्गावर ९ लाखांहून अधिक वारकऱ्यांना आरोग्य सेवा</t>
+          <t>राज्य कामगार विमा योजनेतील रुग्णालये होणार अत्याधुनिक; प्रस्ताव सादर करण्याचे मंत्री आबिटकर यांचे निर्देश</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171744/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/workers-insurance-scheme-healthcare-infrastructure-prakash-abhitkar</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>इंडियन इन्स्टिट्युट ऑफ पब्लिक हेल्थ आयआयटी, आयआयएमच्या धर्तीवर - Indian Institute of Public Health (IIPH) on the basis of IIT and IIM</t>
+          <t>वारी मार्गावर ९ लाखांहून अधिक वारकऱ्यांना आरोग्य सेवा</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
+          <t>https://mahasamvad.in/171744/</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Maharashtra to file review petition to bring back elephant Madhuri to Kolhapur</t>
+          <t>इंडियन इन्स्टिट्युट ऑफ पब्लिक हेल्थ आयआयटी, आयआयएमच्या धर्तीवर - Indian Institute of Public Health (IIPH) on the basis of IIT and IIM</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-to-file-review-petition-to-bring-back-elephant-madhuri-to-kolhapur-2766892-2025-08-06</t>
+          <t>https://www.jantaparishad.com/2025/05/indian-institute-of-public-health-iiph.html</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Kolhapur residents hold 45-km silent march for elephant’s return | Mumbai news</t>
+          <t>March for Mahadevi: Why thousands are walking 40 km for an elephant in Kolhapur and how is Vantara involved</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
+          <t>https://www.msn.com/en-in/news/India/march-for-mahadevi-why-thousands-are-walking-40-km-for-an-elephant-in-kolhapur-and-how-is-vantara-involved/ar-AA1JVic0</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Thousands Participate in a Silent March to Seek Mahadevi's Return from Vantara</t>
+          <t>Kolhapur residents hold 45-km silent march for elephant’s return</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/kolhapur-residents-hold-45-km-silent-march-for-elephant-s-return-101754247583784.html</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Kolhapur Rises for Mahadevi: Thousands Join Silent March Demanding Elephant's Return From Vantara</t>
+          <t>Maharashtra to file review petition to bring back elephant Madhuri to Kolhapur</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-to-file-review-petition-to-bring-back-elephant-madhuri-to-kolhapur-2766892-2025-08-06</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Silent march in Kolhapur demands return of elephant Mahadevi from Vantara</t>
+          <t>Thousands Participate in a Silent March to Seek Mahadevi's Return from Vantara</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://www.dynamitenews.com/national/silent-march-in-kolhapur-demands-return-of-elephant-mahadevi-from-vantara</t>
+          <t>https://www.pgurus.com/thousands-participate-in-a-silent-march-to-seek-mahadevis-return-from-vantara/</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>“Madhuri Should Come Back To The Math”: Maharashtra To File Review Petition For Elephant’s Return, Says CM Devendra Fadnavis</t>
+          <t>Kolhapur Rises for Mahadevi: Thousands Join Silent March Demanding Elephant's Return From Vantara</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
+          <t>https://www.oneindia.com/mumbai/kolhapur-rises-for-mahadevi-thousands-join-silent-march-demanding-elephants-return-from-vantara-011-7820557.html</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>‘स्मार्ट’ अंतर्गत नोंदणीकृत प्रकल्प कालबद्धरितीने पूर्ण करा – कृषी मंत्री ॲड. माणिकराव कोकाटे</t>
+          <t>Silent march in Kolhapur demands return of elephant Mahadevi from Vantara</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/167140/</t>
+          <t>https://www.dynamitenews.com/national/silent-march-in-kolhapur-demands-return-of-elephant-mahadevi-from-vantara</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Blood Donation : 'ई-रक्तकोष पोर्टल' गरजूंना मिळवून देणार रक्त; अफवांवर विश्वास न ठेवता बिनधास्त करा रक्तदान, वाचा रक्तदानाचे फायदे !</t>
+          <t>“Madhuri Should Come Back To The Math”: Maharashtra To File Review Petition For Elephant’s Return, Says CM Devendra Fadnavis</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
+          <t>https://lawchakra.in/legal-updates/madhuri-elephant-cm-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Maharashtra rains: School wall collapses in Bhilar village</t>
+          <t>Mahadevi Elephant : ‘महादेवी हत्तीण’ प्रकरणी मुंबईतील बैठकीत तीन मुद्यांवर होणार चर्चा, प्रशासन कायदेतज्ज्ञांच्या संपर्कात</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-rains-school-wall-collapses-in-bhilar-village/articleshow/123403288.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/three-major-issues-in-the-mahadevi-elephant-case-to-be-discussed-in-mumbai-administration-consults-legal-experts-for-further-course-of-action-srs92</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Preparations on in full swing after high court approved circuit bench in Kolhapur</t>
+          <t>‘स्मार्ट’ अंतर्गत नोंदणीकृत प्रकल्प कालबद्धरितीने पूर्ण करा – कृषी मंत्री ॲड. माणिकराव कोकाटे</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
+          <t>https://mahasamvad.in/167140/</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: सर्किट बेंचच्या उद्घाटनासाठी करवीरनगरी सज्ज</t>
+          <t>Blood Donation : 'ई-रक्तकोष पोर्टल' गरजूंना मिळवून देणार रक्त; अफवांवर विश्वास न ठेवता बिनधास्त करा रक्तदान, वाचा रक्तदानाचे फायदे !</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
+          <t>https://www.dainikprabhat.com/blood-donation-e-blood-bank-portal-will-provide-blood-to-the-needy-donate-blood-without-hesitation-without-believing-in-rumors-read-the-benefits-of-blood-donation/</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench | सर्किट बेंचचे आज उद्घाटन</t>
+          <t>Maharashtra rains: School wall collapses in Bhilar village</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-inauguration-today-ap84</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-rains-school-wall-collapses-in-bhilar-village/articleshow/123403288.cms</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Bhushan Gavai: कोल्हापूर खंडपीठ देशातील सामाजिक आणि आर्थिक न्यायासाठी मैलाचा दगड, लवकरच</t>
+          <t>Preparations on in full swing after high court approved circuit bench in Kolhapur</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/preparations-on-in-full-swing-after-high-court-approved-circuit-bench-in-kolhapur/articleshow/123068318.cms</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Kolhapur Circuit Bench: रस्त्यांपासून पॅचवर्कपर्यंत ते वाहतूक व्यवस्थेपर्यंत सर्किंट बेंचच्या</t>
+          <t>Kolhapur Circuit Bench: सर्किट बेंचच्या उद्घाटनासाठी करवीरनगरी सज्ज</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
+          <t>https://www.tarunbharat.com/kolhapur-karveernagari-ready-for-inauguration-kolhapur-circuit-bench-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>रत्नागिरी : शिरगाव येथे उभारणार अत्याधुनिक ग्रामीण रुग्णालय</t>
+          <t>Kolhapur Circuit Bench | सर्किट बेंचचे आज उद्घाटन</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/modern-rural-hospital-to-be-built-shirgaon-ratnagiri-dc95</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/circuit-bench-inauguration-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>महायुतीत पुन्हा वाद पेटणार! १५ ऑगस्टला रायगडमध्ये अदिती तटकरेंच्या हस्ते होणार ध्वजारोहण, गोगावलेंना संधी नाहीच</t>
+          <t>Bhushan Gavai: कोल्हापूर खंडपीठ देशातील सामाजिक आणि आर्थिक न्यायासाठी मैलाचा दगड, लवकरच</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/chief-justice-of-india-bhushan-gavai-says-kolhapur-bench-is-a-milestone-for-social-and-economic-justice-in-the-country-will-soon-be-converted-into-a-bench-1377738</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>लोकांच्या चाळीस वर्षाच्या लढयाला यश ! कोल्हापुरात सर्किट बेंच !!</t>
+          <t>रत्नागिरी : शिरगाव येथे उभारणार अत्याधुनिक ग्रामीण रुग्णालय</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Success-to-the-people-s-forty-year-struggle--Circuit-bench-in-Kolhapur--</t>
+          <t>https://pudhari.news/maharashtra/kokan/ratnagiri/modern-rural-hospital-to-be-built-shirgaon-ratnagiri-dc95</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>कोल्हापूर सर्किट बेंच इमारतीचे दिमाखदार उद्घाटन</t>
+          <t>Kolhapur Circuit Bench: रस्त्यांपासून पॅचवर्कपर्यंत ते वाहतूक व्यवस्थेपर्यंत सर्किंट बेंचच्या</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/74156/</t>
+          <t>https://marathi.abplive.com/news/kolhapur/from-roads-to-patchwork-to-transportation-system-kolhapur-goes-all-out-for-the-inauguration-of-the-circuit-bench-1377058</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Transfer 34 hectares of Shendapark Land for IT Hub in Kolhapur: Ajit Pawar</t>
+          <t>महायुतीत पुन्हा वाद पेटणार! १५ ऑगस्टला रायगडमध्ये अदिती तटकरेंच्या हस्ते होणार ध्वजारोहण, गोगावलेंना संधी नाहीच</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/transfer-34-hectares-of-shendapark-land-for-it-hub-in-kolhapur-ajit-pawar/articleshow/119875458.cms</t>
+          <t>https://deshdoot.com/maharashtra-government-announces-list-of-ministers-who-will-hoist-the-flag-on-august-15/</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>25 ऑगस्टला कोल्हापूरात मोठा निर्णय! भावकीचा वाद मिटणार? मेहुणे-पाहुणे एक दिलाने लढणार</t>
+          <t>लोकांच्या चाळीस वर्षाच्या लढयाला यश ! कोल्हापुरात सर्किट बेंच !!</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ajit-pawars-kolhapur-visit-on-august-25-hasan-mushrif-likely-to-resolve-kp-patil-ay-patil-dispute-as11-rg93</t>
+          <t>https://maharashtranews1.com/Success-to-the-people-s-forty-year-struggle--Circuit-bench-in-Kolhapur--</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>स्वातंत्र्यदिनाचा मुख्य शासकीय समारोह मुंबईत; मुख्यमंत्र्यांच्या हस्ते ध्वजारोहण</t>
+          <t>25 ऑगस्टला कोल्हापूरात मोठा निर्णय! भावकीचा वाद मिटणार? मेहुणे-पाहुणे एक दिलाने लढणार</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174988/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ajit-pawars-kolhapur-visit-on-august-25-hasan-mushrif-likely-to-resolve-kp-patil-ay-patil-dispute-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Maharashtra: Kolhapur Residents Appeal to President To Bring Back Beloved Elephant Mahadevi</t>
+          <t>महिलांच्या सक्षमीकरणासाठी वर्षभरात दहा हजार ई-रिक्षांचे वितरण-मंत्री आदिती तटकरे</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
+          <t>https://maharashtranews1.com/Distribution-of-ten-thousand-e-rickshaws-within-a-year-for-the-empowerment-of-women---Minister-Aditi-Tatkare</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>I am driven to bring prosperity to people:, says Maharashtra deputy chief minister Eknath Shinde</t>
+          <t>Maharashtra: Kolhapur Residents Appeal to President To Bring Back Beloved Elephant Mahadevi</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/i-am-driven-to-bring-prosperity-to-people-says-maharashtra-deputy-chief-minister-eknath-shinde/articleshow/120023921.cms</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-kolhapur-residents-appeal-to-president-to-bring-back-beloved-elephant-mahadevi-enn25080300643</t>
         </is>
       </c>
     </row>
@@ -7475,216 +7475,216 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+          <t>PMC felicitated for ABDM Excellence</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://businessnewsthisweek.com/business/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/</t>
+          <t>https://www.newsband.in/article_detail/pmc-felicitated-for-abdm-excellence</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Pune hospital conferred 'Best BSD Award' and 'Best Organ Transplant Coordinator Award'</t>
+          <t>First Phase of ‘Desh Ka Prakriti Parikshan Abhiyaan’ concludes with Historic 5 Guinness World Records</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-hospital-conferred-with-best-bsd-award-and-best-organ-transplant-coordinator-award/articleshow/123162129.cms</t>
+          <t>https://pragativadi.com/first-phase-of-desh-ka-prakriti-parikshan-abhiyaan-concludes-with-historic-5-guinness-world-records/</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Maharashtra To Convert All Govt Hospitals Into Organ Retrieval Centres To Boost Donations</t>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-convert-all-govt-hospitals-into-organ-retrieval-centres-to-boost-donations</t>
+          <t>https://businessnewsthisweek.com/business/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>लाडक्या बहिणीच्या नादात राज्यात आरोग्य व्यवस्थेच्या चिंधड्या राज्य सरकारकडून</t>
+          <t>Maharashtra To Convert All Govt Hospitals Into Organ Retrieval Centres To Boost Donations</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-convert-all-govt-hospitals-into-organ-retrieval-centres-to-boost-donations</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Maharashtra launches Inspection drive for blood banks</t>
+          <t>लाडक्या बहिणीच्या नादात राज्यात आरोग्य व्यवस्थेच्या चिंधड्या राज्य सरकारकडून</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/health/maharashtra-launches-inspection-drive-for-blood-banks-146154</t>
+          <t>https://marathi.abplive.com/news/maharashtra/more-than-270-crores-due-from-mahatma-phule-and-ayushman-yojana-affiliated-hospitals-from-the-maharashtra-mahayuti-government-1352831</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Maharashtra: Over 5,000 Hospitals Found Violating Nursing Act, Face Action</t>
+          <t>Maharashtra launches Inspection drive for blood banks</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-over-5000-hospitals-found-violating-nursing-act-face-action</t>
+          <t>https://medicaldialogues.in/news/health/maharashtra-launches-inspection-drive-for-blood-banks-146154</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+          <t>Maharashtra: Over 5,000 Hospitals Found Violating Nursing Act, Face Action</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-over-5000-hospitals-found-violating-nursing-act-face-action</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Satej Patil Vs Shivsena : सतेज पाटलांचे शिलेदार शिंदेंनी स्वत:कडे वळवले, निवडणुकीच्या तोंडावर कोल्हापुरात सेनेचं पारडं जड?</t>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
+          <t>https://m.thewire.in/article/ptiprnews/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-across-india/amp?utm=relatedarticles</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Maharashtra govt announces names of 36 guardian ministers: Dhananjay Munde not in list, CM Fadnavis gets Gadchiroli</t>
+          <t>Satej Patil Vs Shivsena : सतेज पाटलांचे शिलेदार शिंदेंनी स्वत:कडे वळवले, निवडणुकीच्या तोंडावर कोल्हापुरात सेनेचं पारडं जड?</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-announces-names-of-36-guardian-ministers-munde-not-in-list-9786173/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/satej-patil-closed-leader-sharangdhar-deshmukh-prepering-to-join-shivsena-eknath-shinde-ahead-local-election/articleshow/121674598.cms</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>SDMA structure to be changed to accommodate Maharashtra deputy CMs</t>
+          <t>Maharashtra govt announces names of 36 guardian ministers: Dhananjay Munde not in list, CM Fadnavis gets Gadchiroli</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sdma-structure-to-be-changed-to-accommodate-maharashtra-deputy-cms-3400638</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-announces-names-of-36-guardian-ministers-munde-not-in-list-9786173/</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Announces Guardian Ministers List; NCP's Dhananjay Munde Dropped | Full List</t>
+          <t>SDMA structure to be changed to accommodate Maharashtra deputy CMs</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://www.outlookindia.com/national/maharashtra-govt-announces-guardian-ministers-list-ncps-dhananjay-munde-dropped-full-list</t>
+          <t>https://www.deccanherald.com/india/maharashtra/sdma-structure-to-be-changed-to-accommodate-maharashtra-deputy-cms-3400638</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>With new move, Eknath Shinde signals fresh tussle in Mahayuti govt</t>
+          <t>Maharashtra Govt Announces Guardian Ministers List; NCP's Dhananjay Munde Dropped | Full List</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
+          <t>https://www.outlookindia.com/national/maharashtra-govt-announces-guardian-ministers-list-ncps-dhananjay-munde-dropped-full-list</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>kolhapur | महायुतीची सत्ता आणण्यासाठी सज्ज राहा : खा. श्रीकांत शिंदे</t>
+          <t>With new move, Eknath Shinde signals fresh tussle in Mahayuti govt</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mp-shrikant-shinde-says-be-ready-to-bring-mahayuti-to-power-ap84</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/with-new-move-eknath-shinde-signals-fresh-tussle-in-mahayuti-govt/articleshow/118319103.cms</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Govt shielding Deenanath Mangeshkar Hospital management in the Bhise death case: Danve</t>
+          <t>kolhapur | महायुतीची सत्ता आणण्यासाठी सज्ज राहा : खा. श्रीकांत शिंदे</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mp-shrikant-shinde-says-be-ready-to-bring-mahayuti-to-power-ap84</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Wadia hospital to offer more affordable heart transplants to children</t>
+          <t>Govt shielding Deenanath Mangeshkar Hospital management in the Bhise death case: Danve</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-shielding-deenanath-mangeshkar-hospital-management-in-the-bhise-death-case-danve/articleshow/122394938.cms</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>DMER to start full-time nurse recruitment in August; MSNA calls off strike after state assurances</t>
+          <t>March for Mahadevi: Why thousands are walking 40 km for an elephant in Kolhapur and how is Vantara involve</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
+          <t>https://m.economictimes.com/news/new-updates/march-for-mahadevi-why-thousands-are-walking-40-km-for-an-elephant-in-kolhapur-and-how-is-vantara-involved/articleshow/123111263.cms</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Over 14,500 Women Show Cancer-Like Symptoms After Screening Drive In Hingoli</t>
+          <t>Wadia hospital to offer more affordable heart transplants to children</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/over-14-500-women-show-cancer-like-symptoms-after-screening-drive-in-hingoli-7797015.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/wadia-hospital-to-offer-more-affordable-heart-transplants-to-children-101755198510805.html</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Pune: University Road Flyover Partially Opens on May 1; Full Completion by August</t>
+          <t>DMER to start full-time nurse recruitment in August; MSNA calls off strike after state assurances</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/dmer-to-start-full-time-nurse-recruitment-in-august-msna-calls-off-strike-after-state-assurances-101753469782825.html</t>
         </is>
       </c>
     </row>
@@ -7703,106 +7703,154 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Update : राज्य सरकार एसटी महामंडळासह कामगारांच्या पाठिशी : अजित पवार</t>
+          <t>Pune: University Road Flyover Partially Opens on May 1; Full Completion by August</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-01-august-2025-mahayuti-vs-mahavikas-aghadi-ncp-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi-ajit-pawar-sharad-pawar-devendra-fadnavis-shivsena-ubt-sharad-pawar-mahayuti-cabinet-reshuffle-datta-bharane-new-agriculture-minister-manikrao-kokate-donald-trump-tarrif</t>
+          <t>https://www.punekarnews.in/pune-university-road-flyover-partially-opens-on-may-1-full-completion-by-august/</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>या जिल्ह्यात हे पालकमंत्री स्वातंत्र्य दिनी ध्वजारोहण करणार</t>
+          <t>Maharashtra Politics Update : राज्य सरकार एसटी महामंडळासह कामगारांच्या पाठिशी : अजित पवार</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-live-01-august-2025-mahayuti-vs-mahavikas-aghadi-ncp-latest-rajkaran-batmya-government-news-breaking-headlines-in-marathi-ajit-pawar-sharad-pawar-devendra-fadnavis-shivsena-ubt-sharad-pawar-mahayuti-cabinet-reshuffle-datta-bharane-new-agriculture-minister-manikrao-kokate-donald-trump-tarrif</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Eknath Shinde : कोल्हापूर सर्किट बेंचमुळे शेकडो मैल दूर असलेला न्याय घरापर्यंत आला; शिंदेंचे प्रतिपादन</t>
+          <t>Akola : अकोल्यात स्त्री रूग्णालयातील भ्रष्टाचार उघड, जिल्हा शल्यचिकित्सकासह तीन</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
+          <t>https://marathi.abplive.com/news/akola/akola-woman-hospital-nicu-tender-contract-corruption-district-surgeon-suspended-health-marathi-news-1374092</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Arogya Mitras to go on indefinite statewide strike from Feb 12</t>
+          <t>या जिल्ह्यात हे पालकमंत्री स्वातंत्र्य दिनी ध्वजारोहण करणार</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
+          <t>https://www.marathiebatmya.com/political/this-guardian-minister-will-hoist-the-flag-on-independence-day-in-this-district/</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Maharashtra: CM Devendra Fadnavis instructs to make special arrangement for treatment of GBS patients</t>
+          <t>CM tells health officials to expand digital services</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-instructs-to-make-special-arrangement-for-treatment-of-gbs-patients20250128191358/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/cm-tells-health-officials-expand-digital-services-10117190/</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Singapore tourism board partners with IndiGo to boost travel</t>
+          <t>Maharashtra Government Appoints New Guardian Ministers; Dhananjay Munde Excluded from List</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+          <t>https://www.oneindia.com/india/maharashtra-guardian-ministers-dhananjay-munde-excluded-011-4046325.html</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+          <t>Eknath Shinde : कोल्हापूर सर्किट बेंचमुळे शेकडो मैल दूर असलेला न्याय घरापर्यंत आला; शिंदेंचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278523385/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-acrob-india</t>
+          <t>https://www.mymahanagar.com/maharashtra/eknath-shinde-asserted-that-justice-which-was-hundreds-of-miles-away-has-reached-home-thanks-to-the-kolhapur-circuit-bench/913002/</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>‘अवयवदान पंधरवड्या’ला राज्यभरात सुरुवात</t>
+          <t>Arogya Mitras to go on indefinite statewide strike from Feb 12</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b26885-txt-mumbai-20250803041544</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/arogya-mitras-to-go-on-indefinite-statewide-strike-from-feb-12-101737405442305.html</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
+          <t>Maharashtra: CM Devendra Fadnavis instructs to make special arrangement for treatment of GBS patients</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://aninews.in/news/national/general-news/maharashtra-cm-devendra-fadnavis-instructs-to-make-special-arrangement-for-treatment-of-gbs-patients20250128191358/</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Singapore tourism board partners with IndiGo to boost travel</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/singapore-tourism-board-partners-with-indigo-to-boost-travel-23587111</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Sanjeevani 2025 Mobilizes Communities, Creates Momentum for Early Cancer Screening Across India</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://www.bignewsnetwork.com/news/278523385/sanjeevani-2025-mobilizes-communities-creates-momentum-for-early-cancer-screening-acrob-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>‘अवयवदान पंधरवड्या’ला राज्यभरात सुरुवात</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b26885-txt-mumbai-20250803041544</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
           <t>सार्वजनिक आरोग्य विभागाच्या जास्तीत जास्त सेवा ऑनलाईन करा – मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>https://mahasamvad.in/171817/</t>
         </is>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,28 +494,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/is-fighting-for-justice-and-rights-a-crime-angry-health-workers-question-the-administration-977234.html</t>
+          <t>https://www.msn.com/mr-in/news/other/gokul-%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%B3-%E0%A4%AE%E0%A4%A7-%E0%A4%B2-%E0%A4%9C-%E0%A4%9C%E0%A4%AE-%E0%A4%98%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%B3-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%AB-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%A8%E0%A4%B0%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%AA%E0%A5%8D%E0%A4%AA-%E0%A4%95/ar-AA1M9nH2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/gokul-gift-scam-why-are-abhitkar-mushrif-patil-narke-kore-silent-ap84</t>
+          <t>https://www.navarashtra.com/maharashtra/is-fighting-for-justice-and-rights-a-crime-angry-health-workers-question-the-administration-977234.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/changes-will-be-in-the-gr-regarding-healthcare-workers-drawn-by-tanaji-sawant-vd83</t>
+          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-mahadwar-road-ganpati-mandal-update</t>
+          <t>https://sarkarnama.esakal.com/mumbai/changes-will-be-in-the-gr-regarding-healthcare-workers-drawn-by-tanaji-sawant-vd83</t>
         </is>
       </c>
     </row>
@@ -557,49 +557,63 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://newsmarathi24.com/68178/</t>
+          <t>https://www.etvbharat.com/mr/!state/historic-golden-ceremony-of-the-mandal-in-kolhapur-whopping-1-kg-gold-necklace-was-offered-to-bappa-maharashtra-news-mhs25090600860</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maratha-reservation-news-suspend-all-the-doctors-who-came-to-conduct-the-examination-manoj-jarange-demands-health-minister-prakash-abitkar-1381217</t>
+          <t>https://newsmarathi24.com/68178/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/theweek/specials/2025/09/06/organ-donation-awareness-mumbai.amp.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maratha-reservation-news-suspend-all-the-doctors-who-came-to-conduct-the-examination-manoj-jarange-demands-health-minister-prakash-abitkar-1381217</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/historic-golden-ceremony-of-the-mandal-in-kolhapur-whopping-1-kg-gold-necklace-was-offered-to-bappa-maharashtra-news-mhs25090600860</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-mahadwar-road-ganpati-mandal-update</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/rural-women-to-receive-direct-support-for-homes-and-grocery-shops-under-makan-kirana-scheme-local18-1474089.html</t>
+          <t>https://www.theweek.in/theweek/specials/2025/09/06/organ-donation-awareness-mumbai.amp.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-emotional-child-video-bappa-immersion-anant-chaturdashi-spb94</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/gokul-gift-scam-why-are-abhitkar-mushrif-patil-narke-kore-silent-ap84</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%AC-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A5%87-80-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%8F%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B8%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%85%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0/ar-AA1xXkGu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.dainikprabhat.com/the-first-ever-ganpati-visarjan-procession-in-kolhapur-begins-chants-of-ganpati-bappa-morya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/rural-women-to-receive-direct-support-for-homes-and-grocery-shops-under-makan-kirana-scheme-local18-1474089.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-emotional-child-video-bappa-immersion-anant-chaturdashi-spb94</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,182 +438,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/Health-dept-to-probe-into-claim-about-Pune-hospital-s-refusal-to-admit-pregnant-woman/2433535</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-health-proposals-in-nagpur-amravati-melghat-bawankule/articleshow/123816301.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/theweek/specials/2025/09/06/organ-donation-awareness-mumbai.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-call-off-strike-after-health-ministers-assurances/articleshow/123816244.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.expresshealthcare.in/news/cii-hospital-tech-2025-to-convene-healthcare-leaders-in-mumbai-for-dialogue-on-innovation-and-health-systems/450583/</t>
+          <t>https://www.freepressjournal.in/pune/pune-ncp-sp-mp-supriya-sule-flags-medicine-shortage-at-bhor-sub-district-hospital-seeks-urgent-intervention-from-health-minister</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-25-year-old-woman-delivers-baby-girl-in-ambulance-en-route-to-hospital-in-palghar</t>
+          <t>https://www.freepressjournal.in/pune/pune-nhm-strike-ends-after-govt-accepts-salary-insurance-regularisation-demands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/palghar-woman-delivers-baby-girl-inside-108-ambulance-amid-emergency-transfer-a525/</t>
+          <t>https://goemkarponn.com/rane-showcases-goa-model-at-cii-hospital-tech-2025/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/historic-golden-ceremony-of-the-mandal-in-kolhapur-whopping-one-kg-gold-necklace-was-offered-to-bappa-hindi-news-hin25090602323</t>
+          <t>https://mandalnews.com/vidarbha/improvement-in-health-services-in-nagpur-amravati-melghat-areas/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-on-strike-ordered-to-resume-work-or-face-action-committee-decries-pressure-tactics/articleshow/123642982.cms</t>
+          <t>https://deshbandhump.com/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95%E0%A5%8B-%E0%A4%98%E0%A4%AC%E0%A4%B0%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%B0%E0%A5%82/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-district-bank-report-prakash-abitkar-hasan-mushrif-mahayuti-jap93-rg93</t>
+          <t>https://www.esakal.com/uttar-maharashtra/dhule-cardiac-cath-lab-inauguration-public-health-services-minister-prakash-abitkar-nmk01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/gokul-%E0%A4%97-%E0%A4%95%E0%A5%81%E0%A4%B3-%E0%A4%AE%E0%A4%A7-%E0%A4%B2-%E0%A4%9C-%E0%A4%9C%E0%A4%AE-%E0%A4%98%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%B3-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%B5%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%86%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%B6%E0%A5%8D%E0%A4%B0-%E0%A4%AB-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%A8%E0%A4%B0%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%AA%E0%A5%8D%E0%A4%AA-%E0%A4%95/ar-AA1M9nH2</t>
+          <t>https://www.etvbharat.com/mr/!state/sickle-cell-disease-needs-serious-attention-air-ambulances-will-be-considered-in-very-remote-areas-health-minister-prakash-abitkar-maharashtra-news-mhs25091204509</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/is-fighting-for-justice-and-rights-a-crime-angry-health-workers-question-the-administration-977234.html</t>
+          <t>https://mahasamvad.in/178324/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
+          <t>https://www.loksatta.com/pune/strike-by-nhm-employees-ended-on-wednesday-after-meeting-with-health-minister-prakash-abitkar-sud-02-5363343/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/changes-will-be-in-the-gr-regarding-healthcare-workers-drawn-by-tanaji-sawant-vd83</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/nhm-strike-ends-health-minister-promises-demands-135887825.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-prakash-abitkar-promises-immediate-relief-to-affected-farmers-sdj87</t>
+          <t>https://pudhari.news/maharashtra/satara/nhm-staff-strike-ends-on-23rd-day-sk95</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-guardian-minister-prakashrao-abitkar-has-finally-been-mentioned-in-the-kdcc-bank-report-find-out-what-the-report-reveals-and-its-possible-political-impact-srs92</t>
+          <t>https://www.tv9marathi.com/maharashtra/shiv-sena-shinde-faction-is-upset-on-bjp-office-bearers-in-dhule-expressed-their-displeasure-in-minister-abitkar-meeting-1491451.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Soon-there-will-be-a-conference-for-entrepreneurs-in-the-IT-sector-in-Kolhapur---Industry-Minister-Uday-Samant</t>
+          <t>https://mahasamvad.in/178441/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-wedding-ceremony-of-Prithvi-More-and-Rituja-Mohite-was-grand--with-the-presence-of-dignitaries-</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/aurangabad/jalna/news/health-workers-strike-called-off-10-demands-approved-in-principle-135907407.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/18-hour-festive-procession-of-Ganesh-immersion-in-Kolhapur-</t>
+          <t>https://pudhari.news/maharashtra/solapur/nrhm-employees-strike-finally-called-off-employees-celebrate-np88</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/historic-golden-ceremony-of-the-mandal-in-kolhapur-whopping-1-kg-gold-necklace-was-offered-to-bappa-maharashtra-news-mhs25090600860</t>
+          <t>https://www.mahasamvad.in/178397/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://newsmarathi24.com/68178/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-prakash-abitkar-promises-immediate-relief-to-affected-farmers-sdj87</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maratha-reservation-news-suspend-all-the-doctors-who-came-to-conduct-the-examination-manoj-jarange-demands-health-minister-prakash-abitkar-1381217</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/gokul-gift-scam-why-are-abhitkar-mushrif-patil-narke-kore-silent-ap84</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-mahadwar-road-ganpati-mandal-update</t>
+          <t>https://www.mahasamvad.in/page/4/?m=0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/theweek/specials/2025/09/06/organ-donation-awareness-mumbai.amp.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/akola-district-hospital-dirt-health-minister-prakash-abitkar-visit-cancelled-mla-criticism-government-slammed-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/gokul-gift-scam-why-are-abhitkar-mushrif-patil-narke-kore-silent-ap84</t>
+          <t>https://www.esakal.com/amp/pimpri-chinchwad/todays-latest-marathi-news-pne25l38633-txt-pc-today-20250914110635</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/the-first-ever-ganpati-visarjan-procession-in-kolhapur-begins-chants-of-ganpati-bappa-morya/</t>
+          <t>https://www.esakal.com/amp/health/body-gives-you-these-two-warning-signs-before-paralysis-attack-never-ignore-stroke-symptoms-ssg2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/rural-women-to-receive-direct-support-for-homes-and-grocery-shops-under-makan-kirana-scheme-local18-1474089.html</t>
+          <t>https://www.esakal.com/amp/uttar-maharashtra/jalgaon-viral-infections-post-rainfall-respiratory-illness-hospitals-patient-surge-nmk01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-ganesh-visarjan-2025-emotional-child-video-bappa-immersion-anant-chaturdashi-spb94</t>
+          <t>https://www.esakal.com/amp/marathwada/aurangabad/custodial-death-case-high-court-orders-clear-affidavit-submission-by-october-3-vsb99</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://maharashtranews1.com/English-medium-schools-should-strive-for-quality-education---Guardian-Minister-Prakash-Abitkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/shiv-sena-shinde-faction-is-upset-on-bjp-office-bearers-in-dhule-expressed-their-displeasure-in-minister-abitkar-meeting-1491451.html/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/akola-district-hospital-dirt-health-minister-prakash-abitkar-visit-cancelled-mla-criticism-government-slammed-latest-marathi-news-yps99</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/ahmednagar/container-with-brake-failure-crushes-9-vehicles-in-ahilyanagar-truck-accident-vru98</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/ratnagiri/the-strike-called-by-the-employees-of-the-national-health-mission-was-finally-called-off-after-a-meeting-with-health-minister-prakash-abitkar-a-a746/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/kolhapur-haddwadh-process-stopped-question-to-guardian-minister-marathi-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/prakash-abitkar-assures-maratha-reservation-justice-without-harming-obc-rights-5000-new-health-sector-jobs-vsd-99-5366250/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/uttar-maharashtra/dhule-cardiac-cath-lab-inauguration-public-health-services-minister-prakash-abitkar-nmk01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-call-off-strike-after-health-ministers-assurances/amp_articleshow/123816244.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/minister-bharat-gogavale-and-former-mla-aniket-tatkare-criticized-each-other-over-controversy-over-chintaman-deshmukh-hall-maharashtra-news-mhs25091402646</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/mla-amashya-padvi-warning-to-government-over-reservation-for-banjara-and-dhangar-communities-maharashtra-news-mhs25091308686</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/kolhapur/city-boundary-expansion-before-december-31-ap84</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-health-proposals-in-nagpur-amravati-melghat-bawankule/articleshow/123816321.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/paschim-maharashtra/solapur/victory-for-health-workers-nhm-employees-end-strike-following-agreement-sdj87</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/nhm-employees-strike-finally-called-off/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ncp-former-mla-aniket-tatkare-slams-shivsena-mla-bharat-gogawale-over-rights-breach-warning-to-on-roha-nagar-palika-invitation-controversy-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/dhule/news/review-of-health-facilities-in-remote-areas-minister-abitkar-understood-the-problems-visits-to-akkalkuwa-molagi-daab-bilgaon-bhusha-135907565.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/politics/shiv-sena-shinde-faction-is-upset-on-bjp-office-bearers-in-dhule-expressed-their-displeasure-in-minister-abitkar-meeting-1491451.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-live-news-13th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-local-train-block-uddhav-thackeray-cm-devendra-fadnavis/liveblog/123862426.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nashik/nandurbar-health-action-team-formed-fight-malnutrition-sickle-cell-new-ambulances-better-tribal-healthcare-vsd-99-5372053/lite/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%AC-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A5%87-80-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%8F%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B8%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%85%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0/ar-AA1xXkGu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/kolhapur/winners-and-losers-in-zilla-parishad-and-panchayat-samiti-to-contest-gokul-elections-ap84</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,357 +438,343 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-health-proposals-in-nagpur-amravati-melghat-bawankule/articleshow/123816301.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/articleshow/124003944.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-call-off-strike-after-health-ministers-assurances/articleshow/123816244.cms</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-ncp-sp-mp-supriya-sule-flags-medicine-shortage-at-bhor-sub-district-hospital-seeks-urgent-intervention-from-health-minister</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-nhm-strike-ends-after-govt-accepts-salary-insurance-regularisation-demands</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://goemkarponn.com/rane-showcases-goa-model-at-cii-hospital-tech-2025/</t>
+          <t>https://www.newsdrum.in/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday-10474617</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/vidarbha/improvement-in-health-services-in-nagpur-amravati-melghat-areas/</t>
+          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A4%A4%E0%A5%80%E0%A4%AF%E0%A5%8B%E0%A4%82-%E0%A4%95%E0%A5%8B-%E0%A4%98%E0%A4%AC%E0%A4%B0%E0%A4%BE%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%80-%E0%A4%9C%E0%A4%B0%E0%A5%82/</t>
+          <t>https://hindi.oneindia.com/news/india/shiv-sena-celebrates-pm-narendra-modi-birthday-initiatives-011-1388481.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/uttar-maharashtra/dhule-cardiac-cath-lab-inauguration-public-health-services-minister-prakash-abitkar-nmk01</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/super-hospital-doctors-strike-over-government-releases-fund-1362443.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sickle-cell-disease-needs-serious-attention-air-ambulances-will-be-considered-in-very-remote-areas-health-minister-prakash-abitkar-maharashtra-news-mhs25091204509</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/on-pm-modis-75th-birthday-the-shrikant-shinde-foundation-inaugurated-75-new-ambulances-1359823.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178324/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/strike-by-nhm-employees-ended-on-wednesday-after-meeting-with-health-minister-prakash-abitkar-sud-02-5363343/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%9A-%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%B2%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%9D-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B8-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9C%E0%A4%A8%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0-%E0%A4%95%E0%A4%B0/ar-AA1DlKs7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/nhm-strike-ends-health-minister-promises-demands-135887825.html</t>
+          <t>https://mahasamvad.in/178819/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/nhm-staff-strike-ends-on-23rd-day-sk95</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/shiv-sena-shinde-faction-is-upset-on-bjp-office-bearers-in-dhule-expressed-their-displeasure-in-minister-abitkar-meeting-1491451.html</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28078-txt-mumbai-20250918045706</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178441/</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/aurangabad/jalna/news/health-workers-strike-called-off-10-demands-approved-in-principle-135907407.html</t>
+          <t>https://www.lokmat.com/kolhapur/bhudargarh-police-station-will-change-form/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/nrhm-employees-strike-finally-called-off-employees-celebrate-np88</t>
+          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178397/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/guardian-minister-prakash-abitkar-promises-immediate-relief-to-affected-farmers-sdj87</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/super-hospital-doctors-strike-over-government-releases-fund-1362443.html/amp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/gokul-gift-scam-why-are-abhitkar-mushrif-patil-narke-kore-silent-ap84</t>
+          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/4/?m=0</t>
+          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mbi25b28093-txt-mumbai-20250919015621</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/akola-district-hospital-dirt-health-minister-prakash-abitkar-visit-cancelled-mla-criticism-government-slammed-latest-marathi-news-yps99</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/pimpri-chinchwad/todays-latest-marathi-news-pne25l38633-txt-pc-today-20250914110635</t>
+          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/health/body-gives-you-these-two-warning-signs-before-paralysis-attack-never-ignore-stroke-symptoms-ssg2</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/uttar-maharashtra/jalgaon-viral-infections-post-rainfall-respiratory-illness-hospitals-patient-surge-nmk01</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/on-pm-modis-75th-birthday-the-shrikant-shinde-foundation-inaugurated-75-new-ambulances-1359823.html/amp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/marathwada/aurangabad/custodial-death-case-high-court-orders-clear-affidavit-submission-by-october-3-vsb99</t>
+          <t>https://mandalnews.com/amravati/sulabha-khodkes-initiative-resolved-the-issue-of-strike-by-super-specialty-doctors/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/English-medium-schools-should-strive-for-quality-education---Guardian-Minister-Prakash-Abitkar</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/amp_articleshow/124003944.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/shiv-sena-shinde-faction-is-upset-on-bjp-office-bearers-in-dhule-expressed-their-displeasure-in-minister-abitkar-meeting-1491451.html/amp</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/akola-district-hospital-dirt-health-minister-prakash-abitkar-visit-cancelled-mla-criticism-government-slammed-latest-marathi-news-yps99</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/ahmednagar/container-with-brake-failure-crushes-9-vehicles-in-ahilyanagar-truck-accident-vru98</t>
+          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/?amp=1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/ratnagiri/the-strike-called-by-the-employees-of-the-national-health-mission-was-finally-called-off-after-a-meeting-with-health-minister-prakash-abitkar-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/kolhapur-haddwadh-process-stopped-question-to-guardian-minister-marathi-news/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/prakash-abitkar-assures-maratha-reservation-justice-without-harming-obc-rights-5000-new-health-sector-jobs-vsd-99-5366250/</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/uttar-maharashtra/dhule-cardiac-cath-lab-inauguration-public-health-services-minister-prakash-abitkar-nmk01</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/nhm-employees-call-off-strike-after-health-ministers-assurances/amp_articleshow/123816244.cms</t>
+          <t>https://menafn.com/1110064474/Maha-CM-To-Develop-A-Comprehensive-Policy-For-Cancer-Treatment</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/minister-bharat-gogavale-and-former-mla-aniket-tatkare-criticized-each-other-over-controversy-over-chintaman-deshmukh-hall-maharashtra-news-mhs25091402646</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mla-amashya-padvi-warning-to-government-over-reservation-for-banjara-and-dhangar-communities-maharashtra-news-mhs25091308686</t>
+          <t>https://www.msn.com/mr-in/news/other/guillain-barre-syndrome-%E0%A4%97-%E0%A4%AF-%E0%A4%AC-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%A1%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%B8%E0%A4%82%E0%A4%96%E0%A5%8D%E0%A4%AF-130-%E0%A4%B5%E0%A4%B0/ar-AA1y9GYn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/city-boundary-expansion-before-december-31-ap84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-health-proposals-in-nagpur-amravati-melghat-bawankule/articleshow/123816321.cms</t>
+          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/solapur/victory-for-health-workers-nhm-employees-end-strike-following-agreement-sdj87</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/nhm-employees-strike-finally-called-off/</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ncp-former-mla-aniket-tatkare-slams-shivsena-mla-bharat-gogawale-over-rights-breach-warning-to-on-roha-nagar-palika-invitation-controversy-as11</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/dhule/news/review-of-health-facilities-in-remote-areas-minister-abitkar-understood-the-problems-visits-to-akkalkuwa-molagi-daab-bilgaon-bhusha-135907565.html</t>
+          <t>https://www.etvbharat.com/amp/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/shiv-sena-shinde-faction-is-upset-on-bjp-office-bearers-in-dhule-expressed-their-displeasure-in-minister-abitkar-meeting-1491451.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-live-news-13th-september-2025-marathi-batmya-maharashtra-weather-update-mumbai-local-train-block-uddhav-thackeray-cm-devendra-fadnavis/liveblog/123862426.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ganeshotsav-2025-kolhapur-ganpati-bappa-say-goodbye-marathi-news/</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom59-mh-pm-bday-ld-shinde.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/nandurbar-health-action-team-formed-fight-malnutrition-sickle-cell-new-ambulances-better-tribal-healthcare-vsd-99-5372053/lite/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%9C-%E0%A4%AC-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A5%87-80-%E0%A4%AB-%E0%A4%B8%E0%A4%A6-%E0%A4%AE-%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%8F%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%86%E0%A4%B8%E0%A4%AA-%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%B6-%E0%A4%85%E0%A4%AC-%E0%A4%9F%E0%A4%95%E0%A4%B0/ar-AA1xXkGu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/winners-and-losers-in-zilla-parishad-and-panchayat-samiti-to-contest-gokul-elections-ap84</t>
+          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom59-mh-pm-bday-ld-shinde.html</t>
         </is>
       </c>
     </row>
@@ -459,14 +459,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/full-page-newspaper-ads-and-slew-of-initiatives-shiv-sena-goes-all-out-to-celebrate-pms-birthday-10474617</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
@@ -487,292 +487,236 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/super-hospital-doctors-strike-over-government-releases-fund-1362443.html</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/on-pm-modis-75th-birthday-the-shrikant-shinde-foundation-inaugurated-75-new-ambulances-1359823.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/on-pm-modis-75th-birthday-the-shrikant-shinde-foundation-inaugurated-75-new-ambulances-1359823.html</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://mahasamvad.in/178819/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%9A-%E0%A4%B0-%E0%A4%A4-%E0%A4%B9%E0%A4%B2%E0%A4%97%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%9D-%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B8-%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A5%8D%E0%A4%9C%E0%A4%A8%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%A4%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B0-%E0%A4%95%E0%A4%B0/ar-AA1DlKs7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28078-txt-mumbai-20250918045706</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178819/</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28078-txt-mumbai-20250918045706</t>
+          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/bhudargarh-police-station-will-change-form/</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28213-txt-mumbai-20250923060756</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
+          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/super-hospital-doctors-strike-over-government-releases-fund-1362443.html/amp</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mbi25b28093-txt-mumbai-20250919015621</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/on-pm-modis-75th-birthday-the-shrikant-shinde-foundation-inaugurated-75-new-ambulances-1359823.html/amp</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/sulabha-khodkes-initiative-resolved-the-issue-of-strike-by-super-specialty-doctors/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/amp_articleshow/124003944.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/?amp=1</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/amp/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%9A%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%95%E0%A4%AA-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%9A%E0%A4%B9-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%95%E0%A4%AA%E0%A4%B9-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%AA-%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A5%87%E0%A4%A4/ar-BB1r7UnW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://menafn.com/1110064474/Maha-CM-To-Develop-A-Comprehensive-Policy-For-Cancer-Treatment</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/guillain-barre-syndrome-%E0%A4%97-%E0%A4%AF-%E0%A4%AC-%E0%A4%B0%E0%A5%8D%E0%A4%B0%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%A1%E0%A5%8D%E0%A4%B0-%E0%A4%AE%E0%A4%9A-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%95%E0%A4%B9%E0%A4%B0-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%B8%E0%A4%82%E0%A4%96%E0%A5%8D%E0%A4%AF-130-%E0%A4%B5%E0%A4%B0/ar-AA1y9GYn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
+          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178863/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/amp/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom59-mh-pm-bday-ld-shinde.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
         <is>
           <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/18/bom59-mh-pm-bday-ld-shinde.html</t>
+          <t>https://tripuratimes.com/ttimes/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment-31447.html</t>
         </is>
       </c>
     </row>
@@ -459,14 +459,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
@@ -487,14 +487,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/on-pm-modis-75th-birthday-the-shrikant-shinde-foundation-inaugurated-75-new-ambulances-1359823.html</t>
+          <t>https://navbharatlive.com/maharashtra/amravati/super-hospital-doctors-strike-over-government-releases-fund-1362443.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
@@ -529,28 +529,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/jay-kumar-gore-says-true-strength-lies-in-the-coordination-village-marathi-news/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28213-txt-mumbai-20250923060756</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28213-txt-mumbai-20250923060756</t>
+          <t>https://www.mahasamvad.in/page/45/?m=0</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178863/</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
@@ -620,105 +620,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/amp/</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
+          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%9A%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%95%E0%A4%AA-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%9A%E0%A4%B9-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%95%E0%A4%AA%E0%A4%B9-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%A6%E0%A5%8D%E0%A4%A6%E0%A4%AA-%E0%A4%B0-%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%95%E0%A5%87%E0%A4%A4/ar-BB1r7UnW?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/government-fund-for-treatments-above-5-lakh-number-of-beneficiaries-to-increase-cm-devendra-fadnavis-pjp78</t>
+          <t>https://mahasamvad.in/178534/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
+          <t>https://mahasamvad.in/178863/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
           <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://tripuratimes.com/ttimes/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment-31447.html</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
@@ -459,14 +459,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://orissadiary.com/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
         </is>
       </c>
     </row>
@@ -487,168 +487,168 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/super-hospital-doctors-strike-over-government-releases-fund-1362443.html</t>
+          <t>https://mahasamvad.in/178819/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178819/</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28078-txt-mumbai-20250918045706</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ayushman-bharat-phule-arogya-treatment-expansion-ab96</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
+          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28213-txt-mumbai-20250923060756</t>
+          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/45/?m=0</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
+          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28208/</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
+          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://mahasamvad.in/179319/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
+          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>
@@ -656,41 +656,6 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178863/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://tripuratimes.com/ttimes/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment-31447.html</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
@@ -487,175 +487,210 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178819/</t>
+          <t>https://www.thehawk.in/news/health/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ayushman-bharat-phule-arogya-treatment-expansion-ab96</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ayushman-bharat-phule-arogya-treatment-expansion-ab96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
+          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28208/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/eknath-shinde-said-healthy-women-strong-families-campaign-continue-the-year/</t>
+          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
+          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
+          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-advocate-general-birendra-saraf-resigns-will-continue-his-work-till-january/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179319/</t>
+          <t>https://sarkarnama.esakal.com/kolhapur/kolhapur-world-record-preamble-of-the-indian-constitution-sung-in-19-languages-how-was-the-ceremony-need-to-know-aau85</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
+          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-marathi-live-news-19-september-2025-rahul-gandhi-election-commission-meenatai-thackeray-statue-case-maratha-obc-reservation-manoj-jarange-pm-narendra-modi-us-president-donald-trump-weather-update-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://civicmirror.in/maharashtra/paint-thrown-on-meenatai-thackerays-statue-in-mumbai-shiv-sena-aggressive/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
+          <t>https://civicmirror.in/maharashtra/maharashtra-cabinet-meeting-cabinet-approves-states-new-gaming-policy-know-8-major-decisions-from-the-cabinet-meeting/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
+          <t>https://civicmirror.in/maharashtra/now-the-licenses-of-vehicles-transporting-sand-illegally-will-be-suspended-a-strict-decision-by-the-transport-department/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/public-health-scheme-%E0%A4%AE%E0%A4%B9-%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%AB%E0%A5%81%E0%A4%B2%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A4%86%E0%A4%B0-%E0%A4%97%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%9C%E0%A4%A8%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF-%E0%A4%9C-%E0%A4%B9-%E0%A4%B0/ar-AA1MEbnE</t>
+          <t>https://civicmirror.in/maharashtra/will-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-in-august-and-september-agriculture-minister-dattatreya-bharane/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/health/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,14 +452,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
+          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
+          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
         </is>
       </c>
     </row>
@@ -487,210 +487,133 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/health/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment</t>
+          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
+          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
+          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ayushman-bharat-phule-arogya-treatment-expansion-ab96</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ayushman-bharat-phule-arogya-treatment-expansion-ab96</t>
+          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
+          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
+          <t>https://lokashanews.com/28208/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://lokashanews.com/28208/</t>
+          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
+          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
+          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/zp-election-2025-kolhapur-women-election-mahayuti-obc-ready-marathi-news/</t>
+          <t>https://sarkarnama.esakal.com/kolhapur/kolhapur-world-record-preamble-of-the-indian-constitution-sung-in-19-languages-how-was-the-ceremony-need-to-know-aau85</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-advocate-general-birendra-saraf-resigns-will-continue-his-work-till-january/</t>
+          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
+          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/kolhapur/kolhapur-world-record-preamble-of-the-indian-constitution-sung-in-19-languages-how-was-the-ceremony-need-to-know-aau85</t>
+          <t>https://www.thehawk.in/news/health/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167842</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://lokmanthan.com/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/paint-thrown-on-meenatai-thackerays-statue-in-mumbai-shiv-sena-aggressive/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/maharashtra-cabinet-meeting-cabinet-approves-states-new-gaming-policy-know-8-major-decisions-from-the-cabinet-meeting/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/now-the-licenses-of-vehicles-transporting-sand-illegally-will-be-suspended-a-strict-decision-by-the-transport-department/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/will-conduct-a-panchnama-of-the-damage-caused-by-heavy-rains-in-august-and-september-agriculture-minister-dattatreya-bharane/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapur-witnesses-historic-multilingual-mass-recitation-of-indian-constitution-preamble-ramdas-athawale-maharashtra-news-mhs25091501055</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/health/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment-1/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
+          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
         </is>
       </c>
     </row>

--- a/Output/Prakash Abitkar/extracted_links.xlsx
+++ b/Output/Prakash Abitkar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,188 +435,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/abitkar-bats-for-state-level-wild-egetable-festival/articleshow/124003944.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://tripuratimes.com/ttimes/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment-31447.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://kashmirobserver.net/2025/09/18/full-page-newspaper-ads-shiv-sena-pulls-out-all-stops-for-pms-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://medicalbuyer.co.in/maharashtra-launches-floating-hospitals/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://indiaeducationdiary.in/deputy-cm-eknath-shinde-launches-state-level-swasth-nari-sashakt-parivar-abhiyaan-in-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://mandalnews.com/amravati/beds-are-lying-vacant-in-super-specialty-hospital/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/india/shiv-sena-celebrates-pm-narendra-modi-birthday-initiatives-011-1388481.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/kolhapurs-wild-vegetable-festival-promotes-local-cuisine-and-women-culinary-talent-maharashtra-news-mhs25092003298</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/cities/big-news-regarding-mahatma-jyotirao-phule-jan-arogya-yojana-government-makes-big-change-9281814</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/major-update-government-announces-significant-reforms-in-the-mahatma-jyotirao-phule-jan-arogya-yojana-health-scheme-article-152828817</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ayushman-bharat-phule-arogya-treatment-expansion-ab96</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/pradhan-mantri-jan-arogya-284260/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/cm-samruddha-panchayatraj-campaign-should-become-mass-movement-says-rural-development-minister-gore-ap84</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shahi-dasara-festival-begins-today-ap84</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://maharashtranews1.com/The-Panchayati-Raj-campaign-with-a-prize-of-five-crore-rupees-is-the-only-one-in-the-country---Jaykumar-Gore</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://lokashanews.com/28208/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/health/cm-fadnavis-directive-corpus-fund-for-treatment-of-more-than-five-lakh-rupees/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/nashik/sickle-cell-crisis-in-nandurbar-exposes-poor-health-governance-health-minister-prakash-abitkar-expresses-anger-rds-00-5373636/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://www.socialnews.xyz/2025/09/15/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2167743</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/kolhapur/kolhapur-world-record-preamble-of-the-indian-constitution-sung-in-19-languages-how-was-the-ceremony-need-to-know-aau85</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-politics-eknath-shinde-uddhav-thackeray-faction-defections-kolhapur-leaders-rm82-rg93</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://dainikekmat.com/2399-types-of-treatment-will-be-available-under-the-prime-minister-and-mahatma-jyotirao-phule-jan-arogya-yojana/117278/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/provision-of-corpus-fund-for-treatment-worth-more-than-five-lakhs-chief-minister-devendra-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.thehawk.in/news/health/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://www.mangalorean.com/maha-cm-to-develop-a-comprehensive-policy-for-cancer-treatment/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
